--- a/FOA SETS/Outdoor-Set.xlsx
+++ b/FOA SETS/Outdoor-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,78 @@
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFE2F3"/>
+        <bgColor rgb="FFCFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE5CD"/>
+        <bgColor rgb="FFFCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAD1DC"/>
+        <bgColor rgb="FFEAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E0E3"/>
+        <bgColor rgb="FFD0E0E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor rgb="FFF9CB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
+        <bgColor rgb="FFD9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4C2F4"/>
+        <bgColor rgb="FFA4C2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
+        <bgColor rgb="FFFFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6B26B"/>
+        <bgColor rgb="FFF6B26B"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -102,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,6 +193,30 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -652,7 +748,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Dining Set</t>
         </is>
@@ -665,21 +761,20 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-Gather around ALYCIA 7 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White  or  Beige  or  Gray tones, the Aluminum, Polyester Canvas, Glass, Others build keeps the look polished and practical.
+Gather around ALYCIA 7 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White or Beige or Gray tones, the Aluminum, Polyester Canvas, Glass, build keeps the look polished and practical.
 Features
 - White or Beige or Gray
 - Aluminum Construction
-- 5mm Tempered Glass Table
-Included items and dimensions:
-- Arm Chair w/ Cushion (6 or CTN): color: White  or  Beige  or  Gray; dimensions: 22 3 or 8" W x 27"D x 33 1 or 2-35 1 or 2" H; feature: Transitional
-Materials: Aluminum, Polyester Canvas, Glass, Others
-Color: White  or  Beige  or  Gray
+- 5mm Tempered Glass Table Included items and dimensions:
+- Arm Chair w/ Cushion (6 or CTN): color: White or Beige or Gray; dimensions: 22 3 or 8" W x 27"D x 33 1 or 2-35 1 or 2" H; feature: Transitional
+Materials: Aluminum, Polyester Canvas, Glass.
+Color: White or Beige or Gray
 Weight: 217.82 lbs</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ALYCIA 7 Pc. Patio Dining Set in White  or  Beige  or  Gray | GOODDEGG</t>
+          <t>ALYCIA 7 Pc. Patio Dining Set in White or Beige or Gray | GOODDEGG</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -764,7 +859,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -777,8 +872,8 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-ANTIGUA 4 Pc. Patio Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Aluminum, Polyethylene Wicker, Polyspun and finished in Gun Metal  or  Brown  or  Gray tones for a clean, cohesive look.
-Product Dimensions: 63" L x 35 1 or 2" W x 17 3 or 4 - 27" H
+ANTIGUA 4 Pc. Patio Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Aluminum, Polyethylene Wicker, Polyspun and finished in Gun Metal or Brown or Gray tones for a clean, cohesive look.
+Product Dimensions: 63"L X 35 1/2"W X 17 3/4 - 27"H
 Features
 - Gun Metal or Brown or Gray
 - Adjustable backrest with gas springs
@@ -786,19 +881,18 @@
 - Adjustable table height
 - Padded headrest cushion
 - Washable cushion covers
-- Table includes umbrella hole and cap
-Included items and dimensions:
-- Adjustable Table Height: color: Gun Metal  or  Brown  or  Gray; dimensions: 63" L x 35 1 or 2" W x 17 3 or 4 - 27" H; feature: Contemporary
-- Sofa: color: Gun Metal  or  Brown  or  Gray; dimensions: 76 3 or 4" L x 34" W x 43" H; feature: Contemporary
-- Arm Chair: color: Gun Metal  or  Brown  or  Gray; dimensions: 25 1 or 2" W x 29 1 or 2"D x 40 1 or 4" H; feature: Contemporary
-Materials: Aluminum, Polyethylene Wicker, Polyspun
-Color: Gun Metal  or  Brown  or  Gray
+- Table includes umbrella hole and cap Included items and dimensions:
+- Adjustable Table Height: color: Gun Metal or Brown or Gray; dimensions: 63" L x 35 1 or 2" W x 17 3 or 4 - 27" H; feature: Contemporary
+- Sofa: color: Gun Metal or Brown or Gray; dimensions: 76 3 or 4" L x 34" W x 43" H; feature: Contemporary
+- Arm Chair: color: Gun Metal or Brown or Gray; dimensions: 25 1 or 2" W x 29 1 or 2"D x 40 1 or 4" H; feature: Contemporary
+Materials: Aluminum, Polyethylene Wicker, Polyspun.
+Color: Gun Metal or Brown or Gray
 Weight: 174 lbs</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ANTIGUA 4 Pc. Patio Set in Gun Metal  or  Brown  or  Gray | GOODDEGG</t>
+          <t>ANTIGUA 4 Pc. Patio Set in Gun Metal or Brown or Gray | GOODDEGG</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -888,7 +982,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -901,8 +995,8 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Polyethylene Wicker, Polyspun, then finished in Gun Metal  or  Brown  or  Gray tones to suit a range of interiors.
-Product Dimensions: 63" L x 35 1 or 2" W x 17 3 or 4 - 27" H
+ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Polyethylene Wicker, Polyspun, then finished in Gun Metal or Brown or Gray tones to suit a range of interiors.
+Product Dimensions: 63"L X 35 1/2"W X 17 3/4 - 27"H
 Features
 - Gun Metal or Brown or Gray
 - Adjustable backrest with gas springs
@@ -910,14 +1004,13 @@
 - Adjustable table height
 - Padded headrest cushion
 - Washable cushion covers
-- Table includes umbrella hole and cap
-Included items and dimensions:
-- Adjustable Table Height: color: Gun Metal  or  Brown  or  Gray; dimensions: 63" L x 35 1 or 2" W x 17 3 or 4 - 27" H; feature: Contemporary
-- Sofa: color: Gun Metal  or  Brown  or  Gray; dimensions: 76 3 or 4" L x 34" W x 43" H; feature: Contemporary
-- Arm Chair: color: Gun Metal  or  Brown  or  Gray; dimensions: 25 1 or 2" W x 29 1 or 2"D x 40 1 or 4" H; feature: Contemporary
-- Ottoman (2 or CTN): color: Gun Metal  or  Brown  or  Gray; dimensions: 17 3 or 4" L x 17 3 or 4" W x 16 1 or 4" H; feature: Contemporary
-Materials: Aluminum, Polyethylene Wicker, Polyspun
-Color: Gun Metal  or  Brown  or  Gray
+- Table includes umbrella hole and cap Included items and dimensions:
+- Adjustable Table Height: color: Gun Metal or Brown or Gray; dimensions: 63" L x 35 1 or 2" W x 17 3 or 4 - 27" H; feature: Contemporary
+- Sofa: color: Gun Metal or Brown or Gray; dimensions: 76 3 or 4" L x 34" W x 43" H; feature: Contemporary
+- Arm Chair: color: Gun Metal or Brown or Gray; dimensions: 25 1 or 2" W x 29 1 or 2"D x 40 1 or 4" H; feature: Contemporary
+- Ottoman (2 / CTN): color: Gun Metal or Brown or Gray; dimensions: 17 3 or 4" L x 17 3 or 4" W x 16 1 or 4" H; feature: Contemporary
+Materials: Aluminum, Polyethylene Wicker, Polyspun.
+Color: Gun Metal or Brown or Gray
 Weight: 191.9 lbs</t>
         </is>
       </c>
@@ -1013,7 +1106,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -1026,26 +1119,25 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-AROSA 3 Pc. Fire Pit Counter Height Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Ceramic Tile, Polyrattan, Polyspun Fabric construction and Black  or  Gray tones, it blends durability with visual warmth.
-Product Dimensions: Table: 36.4" L x 36.4" W x 36.6" H, Chair: 25.1" W x 26.3"D x 44.8" H
+AROSA 3 Pc. Fire Pit Counter Height Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Ceramic Tile, Polyrattan, Polyspun Fabric construction and Black or Gray tones, it blends durability with visual warmth.
+Product Dimensions: Table: 36.4"L X 36.4"W X 36.6"H, Chair: 25.1"W X 26.3"D X 44.8"H
 Features
 - Black or Gray
 - 360-Degree Swivel Seats
 - Tile Top Firepit Tabletop
 - Mixed Material Construction
 - Powder Coated Steel Frame
-- Easy To Assemble
-Included items and dimensions:
-- Fire Pit Counter Height Table: color: Black  or  Gray; dimensions: 36.5" W x 36.5"D x 36.5" H; feature: Contemporary
-- Swivel Counter Height Arm Chair (2 or CTN): color: Black  or  Gray; dimensions: 25" W x 26"D x 45" H; feature: Contemporary
-Materials: Steel, Ceramic Tile, Polyrattan, Polyspun Fabric
-Color: Black  or  Gray
+- Easy To Assemble Included items and dimensions:
+- Fire Pit Counter Height Table: color: Black or Gray; dimensions: 36.5" W x 36.5"D x 36.5" H; feature: Contemporary
+- Swivel Counter Height Arm Chair (2 / CTN): color: Black or Gray; dimensions: 25" W x 26"D x 45" H; feature: Contemporary
+Materials: Steel, Ceramic Tile, Polyrattan, Polyspun Fabric.
+Color: Black or Gray
 Weight: 154 lbs</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AROSA 3 Pc. Fire Pit Counter Height Set in Black  or  Gray | GOODDEGG</t>
+          <t>AROSA 3 Pc. Fire Pit Counter Height Set in Black or Gray | GOODDEGG</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1227,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -1149,18 +1241,17 @@
         <is>
           <t>FREE SHIPPING
 BARBUDA 6 Pc. Conversation Set w/ Fire Pit is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyrattan, Polyspun Fabric and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: Fire Pit Table: 39"DIA x 27" H, Semi-circle Sectional: 64" W x 29"D x 33.5" H, End Table: 21" W x 28.5"D x 24" H
+Product Dimensions: Fire Pit Table: 39"DIA X 27"H, Semi-circle Sectional: 64"W X 29"D X 33.5"H, End Table: 21"W X 28.5"D X 24"H
 Features
 - Modular Design
 - Tile Top Firepit Tabletop
 - FSC Certified Teak Wood
 - Mixed Material Construction
 - Powder Coated Steel Frame
-- Washable Cushion Covers
-Included items and dimensions:
+- Washable Cushion Covers Included items and dimensions:
 - Fire Pit Table: color: Gray; dimensions: 39" DIA x 27.2" H; feature: Contemporary
-- 5 Pc. Sectional Sofa w/ 2 End Tables: color: Gray  or  Natural; dimensions: Sofa: 64.25" W x 29"D x 33.5" H, End Table: 21.25" L x 28.7" W x 24" H; feature: Contemporary
-Materials: Steel, Polyrattan, Polyspun Fabric
+- 5 Pc. Sectional Sofa w/ 2 End Tables: color: Gray or Natural; dimensions: Sofa: 64.25" W x 29"D x 33.5" H, End Table: 21.25" L x 28.7" W x 24" H; feature: Contemporary
+Materials: Steel, Polyrattan, Polyspun Fabric.
 Color: Gray
 Weight: 322.87 lbs</t>
         </is>
@@ -1257,7 +1348,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -1270,8 +1361,8 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-BORDEAUX 6 Pc. Dining Set w/ Bench brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural  or  Light Gray  or  Beige tones, the Aluminum, Stainless Steel, Polyspun Fabric build keeps the look polished and practical.
-Product Dimensions: Table: 70.5" W x 38.5"D x 29" H, Chair: 20" W x 26.5"D x 32" H, Armless Chair: 20" W x 26.5"D x 32" H, Bench: 57" W x 16"D x 18.5" H
+BORDEAUX 6 Pc. Dining Set w/ Bench brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural or Light Gray or Beige tones, the Aluminum, Stainless Steel, Polyspun Fabric build keeps the look polished and practical.
+Product Dimensions: Table: 70.5"W X 38.5"D X 29"H, Chair: 20"W X 26.5"D X 32"H, Armless Chair: 20"W X 26.5"D X 32"H, Bench: 57"W X 16"D X 18.5"H
 Features
 - Natural or Light Gray or Beige
 - Tabletop Fire Pit with Storage Cabinet
@@ -1280,13 +1371,12 @@
 - Stainless Steel Ice Chest with Cover
 - Hand-brushed Wood Texture
 - Washable Cushion Cover
-- UV &amp; Water-Resistant
-Included items and dimensions:
-- Side Chair (2 or CTN): color: Natural  or  Beige; dimensions: 20" W x 26.5"D x 33" H; feature: Contemporary
-- Bench: color: Natural  or  Beige; dimensions: 57" W x 16.5"D x 18.5" H; feature: Contemporary
-- Arm Chair (2 or CTN): color: Natural  or  Beige; dimensions: 24" W x 26.5"D x 33" H; feature: Contemporary
-Materials: Aluminum, Stainless Steel, Polyspun Fabric
-Color: Natural  or  Light Gray  or  Beige
+- UV &amp; Water-Resistant Included items and dimensions:
+- Side Chair (2 / CTN): color: Natural or Beige; dimensions: 20" W x 26.5"D x 33" H; feature: Contemporary
+- Bench: color: Natural or Beige; dimensions: 57" W x 16.5"D x 18.5" H; feature: Contemporary
+- Arm Chair (2 / CTN): color: Natural or Beige; dimensions: 24" W x 26.5"D x 33" H; feature: Contemporary
+Materials: Aluminum, Stainless Steel, Polyspun Fabric.
+Color: Natural or Light Gray or Beige
 Weight: 307.89 lbs</t>
         </is>
       </c>
@@ -1382,7 +1472,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -1395,26 +1485,25 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-JOHARI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural  or  Beige tones, the Steel, Fabric, Foam, PE Rattan build keeps the look polished and practical.
-Product Dimensions: COFFEE TABLE: 30" W x 30"D x 16.5" H, CHAIR: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
+JOHARI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural or Beige tones, the Steel, Fabric, Foam, PE Rattan build keeps the look polished and practical.
+Product Dimensions: COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5")
 Features
 - Natural or Beige
 - Powder Coated Steel Frame
 - 10mm Round Wicker
 - Seat Cushion
 - Pillow Back w/ 100% Fiber Fill
-- Weather Resistant
-Included items and dimensions:
-- Patio Chair (2 or CTN): dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
+- Weather Resistant Included items and dimensions:
+- Patio Chair (2 / CTN): dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
 - Patio Coffee Table: dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
-Materials: Steel, Fabric, Foam, PE Rattan
-Color: Natural  or  Beige
+Materials: Steel, Fabric, Foam, PE Rattan.
+Color: Natural or Beige
 Weight: 91.3 lbs</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JOHARI 3 Pc. Conversation Set in Natural  or  Beige | GOODDEGG</t>
+          <t>JOHARI 3 Pc. Conversation Set in Natural or Beige | GOODDEGG</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1504,7 +1593,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -1517,27 +1606,26 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-JOHARI 4 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel, Fabric, Foam, PE Rattan and finished in Natural  or  Beige tones for a clean, cohesive look.
-Product Dimensions: COFFEE TABLE: 30" W x 30"D x 16.5" H, CHAIR: 30" W x 29"D x 25.5" H (SEAT HT: 16.5"), BENCH: 58" W x 29"D x 25.5" H (SEAT HT: 16.5")
+JOHARI 4 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel, Fabric, Foam, PE Rattan and finished in Natural or Beige tones for a clean, cohesive look.
+Product Dimensions: COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5"), BENCH: 58"W X 29"D X 25.5"H (SEAT HT: 16.5")
 Features
 - Natural or Beige
 - Powder Coated Steel Frame
 - 10mm Round Wicker
 - Seat Cushion
 - Pillow Back w/ 100% Fiber Fill
-- Weather Resistant
-Included items and dimensions:
-- Patio Chair (2 or CTN): dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
+- Weather Resistant Included items and dimensions:
+- Patio Chair (2 / CTN): dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
 - Patio Bench: dimensions: 58" W x 29"D x 25.5" H (SEAT HT: 16.5")
 - Patio Coffee Table: dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
-Materials: Steel, Fabric, Foam, PE Rattan
-Color: Natural  or  Beige
+Materials: Steel, Fabric, Foam, PE Rattan.
+Color: Natural or Beige
 Weight: 144.1 lbs</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JOHARI 4 Pc. Conversation Set in Natural  or  Beige | GOODDEGG</t>
+          <t>JOHARI 4 Pc. Conversation Set in Natural or Beige | GOODDEGG</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1612,716 +1700,746 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="18" t="n"/>
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>FM80001BB-SET</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>KIMARA 3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KIMARA 3 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and finished in Black tones for a clean, cohesive look.
-Product Dimensions: Table: 56.5" W x 29"D x 26.5" H, Sectional: 97" W x 70.5"D x 28.5" H
+Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H
 Features
 - Sturdy &amp; Durable Design
-- Weather Resistance
-Included items and dimensions:
-- Dining Table: color: Black  or  Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam
+- Weather Resistance Included items and dimensions:
+- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
+Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
 Color: Black
 Weight: 149.1 lbs</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>KIMARA 3 Pc. Patio Dining Set in Black | GOODDEGG</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>KIMARA</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="18" t="inlineStr">
         <is>
           <t>3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" s="18" t="n"/>
+      <c r="N10" s="18" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="18" t="inlineStr">
         <is>
           <t>FM80001BB-1, FM80001BB-2, FM80001BB-T</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="18" t="inlineStr">
         <is>
           <t>FM80001BB-SET-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="18" t="n">
         <v>419</v>
       </c>
-      <c r="R10" s="1" t="n">
+      <c r="R10" s="19" t="n">
         <v>419</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="18" t="n">
         <v>957</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" s="18" t="n">
         <v>149.1</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" s="18" t="inlineStr">
         <is>
           <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V10" s="18" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W10" s="18" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X10" s="18" t="inlineStr">
         <is>
           <t>Contemporary,Black,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y10" s="18" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC10" t="n">
+      <c r="Z10" s="18" t="n"/>
+      <c r="AA10" s="18" t="n"/>
+      <c r="AB10" s="18" t="n"/>
+      <c r="AC10" s="18" t="n">
         <v>26.9</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="18" t="n"/>
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>FM80001GG-SET</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>KIMARA 3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KIMARA 3 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, then finished in Gray tones to suit a range of interiors.
-Product Dimensions: Table: 56.5" W x 29"D x 26.5" H, Sectional: 97" W x 70.5"D x 28.5" H
+Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H
 Features
 - Sturdy &amp; Durable Design
-- Weather Resistance
-Included items and dimensions:
-- Dining Table: color: Black  or  Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam
+- Weather Resistance Included items and dimensions:
+- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
+Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
 Color: Gray
 Weight: 150.7 lbs</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>KIMARA 3 Pc. Patio Dining Set in Gray | GOODDEGG</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="18" t="inlineStr">
         <is>
           <t>KIMARA</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="18" t="inlineStr">
         <is>
           <t>3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="M11" s="18" t="n"/>
+      <c r="N11" s="18" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="18" t="inlineStr">
         <is>
           <t>FM80001GG-T, FM80001GG-1, FM80001GG-2</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="18" t="inlineStr">
         <is>
           <t>FM80001GG-SET-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="18" t="n">
         <v>399</v>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="R11" s="19" t="n">
         <v>399</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="18" t="n">
         <v>957</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" s="18" t="n">
         <v>150.7</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" s="18" t="inlineStr">
         <is>
           <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V11" s="18" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W11" s="18" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X11" s="18" t="inlineStr">
         <is>
           <t>Contemporary,Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y11" s="18" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC11" t="n">
+      <c r="Z11" s="18" t="n"/>
+      <c r="AA11" s="18" t="n"/>
+      <c r="AB11" s="18" t="n"/>
+      <c r="AC11" s="18" t="n">
         <v>28.1</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="20" t="n"/>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>FM80001BB-SET+2CH</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>KIMARA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KIMARA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam construction and Black tones, it blends durability with visual warmth.
-Product Dimensions: Table: 56.5" W x 29"D x 26.5" H, Sectional: 97" W x 70.5"D x 28.5" H, Chair: 25" W x 23"D x 30.5" H
+Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 25"W X 23"D X 30.5"H
 Features
 - Sturdy &amp; Durable Design
-- Weather Resistance
-Included items and dimensions:
-- Dining Table: color: Black  or  Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
-- Patio Chair (2 or CTN): color: Black; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam
+- Weather Resistance Included items and dimensions:
+- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
+- Patio Chair (2 / CTN): color: Black; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary
+Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
 Color: Black
 Weight: 175 lbs</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>KIMARA 5 Pc. Patio Dining Set in Black | GOODDEGG</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>KIMARA</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>FM80001BB-T, FM80001BB-1, FM80001BB-2, FM80002BB-CH-2PK</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="20" t="inlineStr">
         <is>
           <t>FM80001BB-SET+2CH-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="20" t="n">
         <v>559</v>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="R12" s="21" t="n">
         <v>559</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12" s="20" t="n">
         <v>1287</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" s="20" t="n">
         <v>175</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" s="20" t="inlineStr">
         <is>
           <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 25"W X 23"D X 30.5"H</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V12" s="20" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W12" s="20" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X12" s="20" t="inlineStr">
         <is>
           <t>Contemporary,Black,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y12" s="20" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC12" t="n">
+      <c r="Z12" s="20" t="n"/>
+      <c r="AA12" s="20" t="n"/>
+      <c r="AB12" s="20" t="n"/>
+      <c r="AC12" s="20" t="n">
         <v>34.1</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>FM80001GG-SET+2CH</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>KIMARA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KIMARA 5 Pc. Patio Dining Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Gray tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam build keeps the look polished and practical.
-Product Dimensions: Table: 56.5" W x 29"D x 26.5" H, Sectional: 97" W x 70.5"D x 28.5" H, Chair: 22.5" W x 23.5"D x 35" H
+Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 22.5"W X 23.5"D X 35"H
 Features
 - Sturdy &amp; Durable Design
-- Weather Resistance
-Included items and dimensions:
-- Dining Table: color: Black  or  Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
+- Weather Resistance Included items and dimensions:
+- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
 - Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam
+Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
 Color: Gray
 Weight: 174.9 lbs</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>KIMARA 5 Pc. Patio Dining Set in Gray | GOODDEGG</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>KIMARA</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="M13" s="20" t="n"/>
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>FM80001GG-T, FM80001GG-1, FM80001GG-2, FM80006GY-CH-2PK</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="20" t="inlineStr">
         <is>
           <t>FM80001GG-SET+2CH-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13" s="20" t="n">
         <v>529</v>
       </c>
-      <c r="R13" s="1" t="n">
+      <c r="R13" s="21" t="n">
         <v>529</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" s="20" t="n">
         <v>1257</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T13" s="20" t="n">
         <v>174.9</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" s="20" t="inlineStr">
         <is>
           <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 22.5"W X 23.5"D X 35"H</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V13" s="20" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W13" s="20" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X13" s="20" t="inlineStr">
         <is>
           <t>Contemporary,Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y13" s="20" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC13" t="n">
+      <c r="Z13" s="20" t="n"/>
+      <c r="AA13" s="20" t="n"/>
+      <c r="AB13" s="20" t="n"/>
+      <c r="AC13" s="20" t="n">
         <v>45.6</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="22" t="n"/>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Beige/Natural</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>GM-1022BG-4PC</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>KYUSHU 4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-KYUSHU 4 Pc. Patio Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Acacia Wood, Polyester construction and Beige  or  Natural tones, it blends durability with visual warmth.
-Product Dimensions: LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H, TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H
+KYUSHU 4 Pc. Patio Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Acacia Wood, Polyester construction and Beige or Natural tones, it blends durability with visual warmth.
+Product Dimensions: LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H
 Features
 - Rustic
 - Beige or Natural
 - Weather-resistant
 - Natural acacia wood
 - Includes tie-back cushions
-- Easy to assemble with included hardware kit
-Included items and dimensions:
-- Table  and  Loveseat: color: Beige  or  Natural; dimensions: TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H; feature: Rustic
-- Chair (2 or CTN): color: Beige  or  Natural; dimensions: CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H; feature: Rustic
-Materials: Acacia Wood, Polyester
-Color: Beige  or  Natural
+- Easy to assemble with included hardware kit Included items and dimensions:
+- Table and Loveseat: color: Beige or Natural; dimensions: TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H; feature: Rustic
+- Chair (2 / CTN): color: Beige or Natural; dimensions: CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H; feature: Rustic
+Materials: Acacia Wood, Polyester.
+Color: Beige or Natural
 Weight: 125.04 lbs</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>KYUSHU 4 Pc. Patio Set in Beige  or  Natural | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>KYUSHU 4 Pc. Patio Set in Beige or Natural | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>The KYUSHU Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>KYUSHU</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="22" t="inlineStr">
         <is>
           <t>4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="22" t="inlineStr">
         <is>
           <t>GM-1022BG-2PK, GM-1023BG-2PK</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="22" t="inlineStr">
         <is>
           <t>GM-1022BG-1.jpg,GM-1022BG-2.jpg</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14" s="22" t="n">
         <v>319</v>
       </c>
-      <c r="R14" s="1" t="n">
+      <c r="R14" s="23" t="n">
         <v>319</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14" s="22" t="n">
         <v>807</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14" s="22" t="n">
         <v>125.04</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U14" s="22" t="inlineStr">
         <is>
           <t>LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V14" s="22" t="inlineStr">
         <is>
           <t>Rustic</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W14" s="22" t="inlineStr">
         <is>
           <t>Acacia Wood, Polyester</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X14" s="22" t="inlineStr">
         <is>
           <t>Rustic,Beige/Natural,Acacia Wood, Polyester,Weather-resistant,Natural acacia wood,Includes tie-back cushions,Easy to assemble with included hardware kit</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y14" s="22" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC14" t="n">
+      <c r="Z14" s="22" t="n"/>
+      <c r="AA14" s="22" t="n"/>
+      <c r="AB14" s="22" t="n"/>
+      <c r="AC14" s="22" t="n">
         <v>15.1</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Black/Natural</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>GM-1022BK-4PC</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>KYUSHU 4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-KYUSHU 4 Pc. Patio Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Black  or  Natural tones, the Acacia Wood, Polyester build keeps the look polished and practical.
-Product Dimensions: LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H, TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H
+KYUSHU 4 Pc. Patio Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Black or Natural tones, the Acacia Wood, Polyester build keeps the look polished and practical.
+Product Dimensions: LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H
 Features
 - Rustic
 - Black or Natural
 - Weather-resistant
 - Natural acacia wood
 - Includes tie-back cushions
-- Easy to assemble with included hardware kit
-Included items and dimensions:
-- Table  and  Loveseat: color: Black  or  Natural; dimensions: TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H; feature: Rustic
-- Chair (2 or CTN): color: Black  or  Natural; dimensions: CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H; feature: Rustic
-Materials: Acacia Wood, Polyester
-Color: Black  or  Natural
+- Easy to assemble with included hardware kit Included items and dimensions:
+- Table and Loveseat: color: Black or Natural; dimensions: TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H; feature: Rustic
+- Chair (2 / CTN): color: Black or Natural; dimensions: CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H; feature: Rustic
+Materials: Acacia Wood, Polyester.
+Color: Black or Natural
 Weight: 125.04 lbs</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>KYUSHU 4 Pc. Patio Set in Black  or  Natural | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>KYUSHU 4 Pc. Patio Set in Black or Natural | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>The KYUSHU Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>KYUSHU</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="22" t="inlineStr">
         <is>
           <t>GM-1022BK-2PK, GM-1023BK-2PK</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="22" t="inlineStr">
         <is>
           <t>GM-1022BK-1.jpg,GM-1022BK-2.jpg</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="22" t="n">
         <v>319</v>
       </c>
-      <c r="R15" s="1" t="n">
+      <c r="R15" s="23" t="n">
         <v>319</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="22" t="n">
         <v>807</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" s="22" t="n">
         <v>125.04</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U15" s="22" t="inlineStr">
         <is>
           <t>LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V15" s="22" t="inlineStr">
         <is>
           <t>Rustic</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W15" s="22" t="inlineStr">
         <is>
           <t>Acacia Wood, Polyester</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X15" s="22" t="inlineStr">
         <is>
           <t>Rustic,Black/Natural,Acacia Wood, Polyester,Weather-resistant,Natural acacia wood,Includes tie-back cushions,Easy to assemble with included hardware kit</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y15" s="22" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC15" t="n">
+      <c r="Z15" s="22" t="n"/>
+      <c r="AA15" s="22" t="n"/>
+      <c r="AB15" s="22" t="n"/>
+      <c r="AC15" s="22" t="n">
         <v>15.1</v>
       </c>
     </row>
@@ -2341,7 +2459,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -2354,26 +2472,25 @@
       <c r="H16" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-LOTUS 5 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black  or  Light Brown tones, the Aluminum, Fabric, Ceramic build keeps the look polished and practical.
-Product Dimensions: Sofa: 74 1 or 4" W x 29 1 or 2"D x 34" H, Coffee Table: 47 1 or 4" L x 25 1 or 2" W x 15 1 or 2" H, Chair: 28 1 or 4" W x 26 1 or 2"D x 37" H
+LOTUS 5 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black or Light Brown tones, the Aluminum, Fabric, Ceramic build keeps the look polished and practical.
+Product Dimensions: Sofa: 74 1/4"W X 29 1/2"D X 34"H, Coffee Table: 47 1/4"L X 25 1/2"W X 15 1/2"H, Chair: 28 1/4"W X 26 1/2"D X 37"H
 Features
 - Black or Light Brown
 - Washable Cushion Covers
 - Open Storage Shelf
 - Slatted Tabletop Design
 - Durable Aluminum Frame
-- Ceramic Tabletop on End Table
-Included items and dimensions:
-- Sofa &amp; Coffee Table Set: color: Black  or  Light Brown; dimensions: Sofa: 74" W x 29.5"D x 34" H, Table: 47" W x 25.5"D x 15.5" H; feature: Contemporary
-- 3 Pc. Patio Set: color: Black  or  Light Brown; dimensions: Chair: 74" W x 29.5"D x 34" H, Table: 28" W x 26.5"D x 37" H; feature: Contemporary
-Materials: Aluminum, Fabric, Ceramic
-Color: Black  or  Light Brown
+- Ceramic Tabletop on End Table Included items and dimensions:
+- Sofa &amp; Coffee Table Set: color: Black or Light Brown; dimensions: Sofa: 74" W x 29.5"D x 34" H, Table: 47" W x 25.5"D x 15.5" H; feature: Contemporary
+- 3 Pc. Patio Set: color: Black or Light Brown; dimensions: Chair: 74" W x 29.5"D x 34" H, Table: 28" W x 26.5"D x 37" H; feature: Contemporary
+Materials: Aluminum, Fabric, Ceramic.
+Color: Black or Light Brown
 Weight: 96.8 lbs</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LOTUS 5 Pc. Conversation Set in Black  or  Light Brown | GOODDEGG</t>
+          <t>LOTUS 5 Pc. Conversation Set in Black or Light Brown | GOODDEGG</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2463,7 +2580,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -2476,19 +2593,18 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-LYON 5 Pc. Game Table Set w/ 4 Arm Chairs brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black  or  Natural  or  Brown tones, the Aluminum, Outdoor Fabric build keeps the look polished and practical.
-Product Dimensions: Table: 50.5" DIA x 29.5" H, Arm Chair: 20" W x 26.5"D x 32.25" H
+LYON 5 Pc. Game Table Set w/ 4 Arm Chairs brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black or Natural or Brown tones, the Aluminum, Outdoor Fabric build keeps the look polished and practical.
+Product Dimensions: Table: 50.5" DIA X 29.5"H, Arm Chair: 20"W X 26.5"D X 32.25"H
 Features
 - Black or Natural or Brown
 - Inlaid Chess Board
 - Teak Poker Race Track Table
 - UV &amp; Rain-Resistant
-- FSC Certified Teak Wood
-Included items and dimensions:
-- Game Table: color: Black  or  Natural  or  Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary
-- Arm Chair (2 or CTN): color: Natural  or  Beige; dimensions: 24" W x 26.5"D x 33" H; feature: Contemporary
-Materials: Aluminum, Outdoor Fabric
-Color: Black  or  Natural  or  Brown
+- FSC Certified Teak Wood Included items and dimensions:
+- Game Table: color: Black or Natural or Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary
+- Arm Chair (2 / CTN): color: Natural or Beige; dimensions: 24" W x 26.5"D x 33" H; feature: Contemporary
+Materials: Aluminum, Outdoor Fabric.
+Color: Black or Natural or Brown
 Weight: 184.85 lbs</t>
         </is>
       </c>
@@ -2584,7 +2700,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -2597,19 +2713,18 @@
       <c r="H18" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-LYON 5 Pc. Game Table Set w/ 4 Armless Chairs is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, Outdoor Fabric and finished in Black  or  Natural  or  Brown tones for a clean, cohesive look.
-Product Dimensions: Table: 50.5" DIA x 29.5" H
+LYON 5 Pc. Game Table Set w/ 4 Armless Chairs is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, Outdoor Fabric and finished in Black or Natural or Brown tones for a clean, cohesive look.
+Product Dimensions: Table: 50.5" DIA X 29.5"H
 Features
 - Black or Natural or Brown
 - Inlaid Chess Board
 - Teak Poker Race Track Table
 - UV &amp; Rain-Resistant
-- FSC Certified Teak Wood
-Included items and dimensions:
-- Game Table: color: Black  or  Natural  or  Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary
-- Side Chair (2 or CTN): color: Natural  or  Beige; dimensions: 20" W x 26.5"D x 33" H; feature: Contemporary
-Materials: Aluminum, Outdoor Fabric
-Color: Black  or  Natural  or  Brown
+- FSC Certified Teak Wood Included items and dimensions:
+- Game Table: color: Black or Natural or Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary
+- Side Chair (2 / CTN): color: Natural or Beige; dimensions: 20" W x 26.5"D x 33" H; feature: Contemporary
+Materials: Aluminum, Outdoor Fabric.
+Color: Black or Natural or Brown
 Weight: 175.17 lbs</t>
         </is>
       </c>
@@ -2705,7 +2820,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -2718,19 +2833,18 @@
       <c r="H19" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Aluminum, Outdoor Fabric, then finished in Black  or  Natural  or  Brown tones to suit a range of interiors.
-Product Dimensions: Table: 50.5" DIA x 29.5" H
+LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Aluminum, Outdoor Fabric, then finished in Black or Natural or Brown tones to suit a range of interiors.
+Product Dimensions: Table: 50.5" DIA X 29.5"H
 Features
 - Black or Natural or Brown
 - Inlaid Chess Board
 - Teak Poker Race Track Table
 - UV &amp; Rain-Resistant
-- FSC Certified Teak Wood
-Included items and dimensions:
-- Game Table: color: Black  or  Natural  or  Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary
-- Stacking Chair: color: Gun Metal  or  Natural Teak; dimensions: 22.5" W x 25"D x 34" H; feature: Contemporary
-Materials: Aluminum, Outdoor Fabric
-Color: Black  or  Natural  or  Brown
+- FSC Certified Teak Wood Included items and dimensions:
+- Game Table: color: Black or Natural or Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary
+- Stacking Chair: color: Gun Metal or Natural Teak; dimensions: 22.5" W x 25"D x 34" H; feature: Contemporary
+Materials: Aluminum, Outdoor Fabric.
+Color: Black or Natural or Brown
 Weight: 105.33 lbs</t>
         </is>
       </c>
@@ -2826,7 +2940,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -2839,22 +2953,21 @@
       <c r="H20" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-MONZA 7 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Tempered Glass, Textilene, then finished in Gun Metal  or  Gray tones to suit a range of interiors.
-Product Dimensions: Table: 63" (EXTENDED: 94 1 or 2") L x 35 1 or 2" W x 29 1 or 2" H
+MONZA 7 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Tempered Glass, Textilene, then finished in Gun Metal or Gray tones to suit a range of interiors.
+Product Dimensions: Table: 63" (EXTENDED: 94 1/2") L X 35 1/2"W X 29 1/2"H
 Features
 - Gun Metal or Gray
 - Extendable Top
-- 5-way Adjustable Seat Back
-Included items and dimensions:
-- Extendable Dining Table: color: Gun Metal  or  Gray; dimensions: 63" (EXTENDED 94.5")W x 35.5"D x 29.5" H; feature: Contemporary
-- Adjustable Chairs (2 or CTN): color: Gun Metal  or  Gray; dimensions: 27.5"D x 23"D x 43" H; feature: Contemporary
-Materials: Aluminum, Tempered Glass, Textilene
-Color: Gun Metal  or  Gray</t>
+- 5-way Adjustable Seat Back Included items and dimensions:
+- Extendable Dining Table: color: Gun Metal or Gray; dimensions: 63" (EXTENDED 94.5")W x 35.5"D x 29.5" H; feature: Contemporary
+- Adjustable Chairs (2 / CTN): color: Gun Metal or Gray; dimensions: 27.5"D x 23"D x 43" H; feature: Contemporary
+Materials: Aluminum, Tempered Glass, Textilene.
+Color: Gun Metal or Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MONZA 7 Pc. Dining Table Set in Gun Metal  or  Gray | GOODDEGG</t>
+          <t>MONZA 7 Pc. Dining Table Set in Gun Metal or Gray | GOODDEGG</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2941,7 +3054,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -2955,14 +3068,13 @@
         <is>
           <t>FREE SHIPPING
 NIAMBI 3 Pc. Patio Bistro Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber construction and Natural tones, it blends durability with visual warmth.
-Product Dimensions: Table: 26.6" x 23.6" x 29.1" H, Chair: 21.3" x 25.2" x 34.3" H
+Product Dimensions: Table: 26.6" x 23.6" x 29.1"H, Chair: 21.3" x 25.2" x 34.3"H
 Features
 - Marble Base
 - Sturdy &amp; Durable Design
-- Easy to store
-Included items and dimensions:
+- Easy to store Included items and dimensions:
 - Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary
-Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber
+Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.
 Color: Natural
 Weight: 50.2 lbs</t>
         </is>
@@ -3059,7 +3171,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -3073,14 +3185,13 @@
         <is>
           <t>FREE SHIPPING
 NIAMBI 3 Pc. Patio Dining Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber build keeps the look polished and practical.
-Product Dimensions: Table: 26.5" W x 23.5"D x 29" H, Chair : 22.5" W x 23.5"D x 35" H
+Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 22.5"W X 23.5"D X 35"H
 Features
 - Marble Base
 - Sturdy &amp; Durable Design
-- Easy to store
-Included items and dimensions:
+- Easy to store Included items and dimensions:
 - Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary
-Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber
+Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.
 Color: Gray
 Weight: 58 lbs</t>
         </is>
@@ -3162,238 +3273,248 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>FM80004GY-5PC-06GY</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>NIAMBI 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 NIAMBI 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: Table: 26.5" W x 23.5"D x 29" H, Chair : 22.5" W x 23.5"D x 35" H
+Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 22.5"W X 23.5"D X 35"H
 Features
 - Marble Base
 - Sturdy &amp; Durable Design
-- Easy to store
-Included items and dimensions:
+- Easy to store Included items and dimensions:
 - Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary
-Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber
+Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.
 Color: Gray
 Weight: 82.2 lbs</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="24" t="inlineStr">
         <is>
           <t>NIAMBI 5 Pc. Patio Dining Set in Gray | GOODDEGG</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="24" t="inlineStr">
         <is>
           <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="24" t="inlineStr">
         <is>
           <t>NIAMBI</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="24" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="M23" s="24" t="n"/>
+      <c r="N23" s="24" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="24" t="inlineStr">
         <is>
           <t>FM80004GY-T-1, FM80004GY-T-2, FM80006GY-CH-2PK</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="24" t="inlineStr">
         <is>
           <t>FM80004GY-5PC-06GY-1-Z.jpg,FM80006GY-CH-1.jpg</t>
         </is>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23" s="24" t="n">
         <v>379</v>
       </c>
-      <c r="R23" s="1" t="n">
+      <c r="R23" s="25" t="n">
         <v>379</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" s="24" t="n">
         <v>837</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T23" s="24" t="n">
         <v>82.2</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U23" s="24" t="inlineStr">
         <is>
           <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 22.5"W X 23.5"D X 35"H</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V23" s="24" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W23" s="24" t="inlineStr">
         <is>
           <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X23" s="24" t="inlineStr">
         <is>
           <t>Contemporary,Gray,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y23" s="24" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC23" t="n">
+      <c r="Z23" s="24" t="n"/>
+      <c r="AA23" s="24" t="n"/>
+      <c r="AB23" s="24" t="n"/>
+      <c r="AC23" s="24" t="n">
         <v>37.1</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>FM80004NT-5PC-05NT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>NIAMBI 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 NIAMBI 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber, then finished in Natural tones to suit a range of interiors.
-Product Dimensions: Table: 26.5" W x 23.5"D x 29" H, Chair : 21" W x 25"D x 34" H
+Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 21"W X 25"D X 34"H
 Features
 - Marble Base
 - Sturdy &amp; Durable Design
-- Easy to store
-Included items and dimensions:
+- Easy to store Included items and dimensions:
 - Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary
-Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber
+Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.
 Color: Natural
 Weight: 66.6 lbs</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>NIAMBI 5 Pc. Patio Dining Set in Natural | GOODDEGG</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="24" t="inlineStr">
         <is>
           <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="24" t="inlineStr">
         <is>
           <t>NIAMBI</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="24" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="M24" s="24" t="n"/>
+      <c r="N24" s="24" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="24" t="inlineStr">
         <is>
           <t>FM80004NT-T-1, FM80004NT-T-2, FM80005NT-CH-2PK</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="24" t="inlineStr">
         <is>
           <t>FM80004NT-5PC-05NT-1-Z.jpg,FM80005NT-CH-1.jpg</t>
         </is>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24" s="24" t="n">
         <v>249</v>
       </c>
-      <c r="R24" s="1" t="n">
+      <c r="R24" s="25" t="n">
         <v>249</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S24" s="24" t="n">
         <v>477</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T24" s="24" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U24" s="24" t="inlineStr">
         <is>
           <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 21"W X 25"D X 34"H</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V24" s="24" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W24" s="24" t="inlineStr">
         <is>
           <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X24" s="24" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y24" s="24" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC24" t="n">
+      <c r="Z24" s="24" t="n"/>
+      <c r="AA24" s="24" t="n"/>
+      <c r="AB24" s="24" t="n"/>
+      <c r="AC24" s="24" t="n">
         <v>40.8</v>
       </c>
     </row>
@@ -3413,7 +3534,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -3427,15 +3548,14 @@
         <is>
           <t>FREE SHIPPING
 NUSA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Teak Wood construction and Natural tones, it blends durability with visual warmth.
-Product Dimensions: Table: 78 3 or 4" L x 47 1 or 4" W x 29 1 or 2" H
+Product Dimensions: Table: 78 3/4"L X 47 1/4"W X 29 1/2"H
 Features
 - Slat Design
 - Pedestal Base
 - 5-way Adjustable Chair
-- Sand Finish
-Included items and dimensions:
+- Sand Finish Included items and dimensions:
 - Folding Arm Chair: color: Natural; dimensions: 22" W x 24.5"D x 37.5" H; feature: Transitional
-Materials: Teak Wood
+Materials: Teak Wood.
 Color: Natural
 Weight: 307.2 lbs</t>
         </is>
@@ -3532,7 +3652,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -3545,8 +3665,8 @@
       <c r="H26" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-PALMA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Glass, Polyspun Fabric construction and Black  or  Gray tones, it blends durability with visual warmth.
-Product Dimensions: Table: 70.8" L x 35.4" W x 27.9" H, Chair: 24" W x 33"D x 38.3" H
+PALMA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Glass, Polyspun Fabric construction and Black or Gray tones, it blends durability with visual warmth.
+Product Dimensions: Table: 70.8"L X 35.4"W X 27.9"H, Chair: 24"W X 33"D X 38.3"H
 Features
 - Black or Gray
 - 5mm Tempered Water Wave Glass Tabletop
@@ -3555,18 +3675,17 @@
 - Washable Cushion Cover
 - Built-In Umbrella Hole
 - Tie-Back Cushions
-- Lumbar Pillows Included
-Included items and dimensions:
-- Dining Table: color: Black  or  Gray; dimensions: 71" W x 35.5"D x 28" H; feature: Contemporary
-- Adjustable Chairs (6 or CTN): color: Black  or  Gray; dimensions: 24" W x 33"D x 38" H; feature: Contemporary
-Materials: Steel, Glass, Polyspun Fabric
-Color: Black  or  Gray
+- Lumbar Pillows Included Included items and dimensions:
+- Dining Table: color: Black or Gray; dimensions: 71" W x 35.5"D x 28" H; feature: Contemporary
+- Adjustable Chairs (6 or CTN): color: Black or Gray; dimensions: 24" W x 33"D x 38" H; feature: Contemporary
+Materials: Steel, Glass, Polyspun Fabric.
+Color: Black or Gray
 Weight: 190.6 lbs</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PALMA 7 Pc. Dining Table Set in Black  or  Gray | GOODDEGG</t>
+          <t>PALMA 7 Pc. Dining Table Set in Black or Gray | GOODDEGG</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3656,7 +3775,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -3669,24 +3788,23 @@
       <c r="H27" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-SARABI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Black  or  Natural tones, the Steel, Wicker, Fabric build keeps the look polished and practical.
-Product Dimensions: TABLE: 21.5" W x 21.5"D x 15.5" H, CHAIR: 25.5" W x 28.5"D x 26.5" H (SEAT HT: 14", SEAT DP: 20")
+SARABI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Black or Natural tones, the Steel, Wicker, Fabric build keeps the look polished and practical.
+Product Dimensions: TABLE: 21.5"W X 21.5"D X 15.5"H, CHAIR: 25.5"W X 28.5"D X 26.5"H (SEAT HT: 14", SEAT DP: 20")
 Features
 - Black or Natural
 - Powder-coated Steel Frame
 - 3.5mm Round Wicker
-- Sloped Back &amp; Curbed Seat Lounge Chair
-Included items and dimensions:
+- Sloped Back &amp; Curbed Seat Lounge Chair Included items and dimensions:
 - Patio Side Table: dimensions: 21.5" W x 21.5"D x 15.5" H
-- Patio Chair (2 or CTN): dimensions: CHAIR: 25.5" W x 28.5"D x 26.5" H (SEAT HT: 14", SEAT DP: 20")
-Materials: Steel, Wicker, Fabric
-Color: Black  or  Natural
+- Patio Chair (2 / CTN): dimensions: CHAIR: 25.5" W x 28.5"D x 26.5" H (SEAT HT: 14", SEAT DP: 20")
+Materials: Steel, Wicker, Fabric.
+Color: Black or Natural
 Weight: 11.7 lbs</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SARABI 3 Pc. Conversation Set in Black  or  Natural | GOODDEGG</t>
+          <t>SARABI 3 Pc. Conversation Set in Black or Natural | GOODDEGG</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3776,7 +3894,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -3789,25 +3907,24 @@
       <c r="H28" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-SEGOVIA 5 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Steel, Polyethylene Wicker, Ceremic, Polyspun, then finished in Navy  or  Black  or  Gray tones to suit a range of interiors.
-Product Dimensions: Firepit Table: 40" L x 40" W x 26 1 or 2" H Chair: 30 3 or 4" W x 25 1 or 2"D x 30 3 or 4" H"
+SEGOVIA 5 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Steel, Polyethylene Wicker, Ceremic, Polyspun, then finished in Navy or Black or Gray tones to suit a range of interiors.
+Product Dimensions: Firepit Table: 40"L X 40"W X 26 1/2"H Chair: 30 3/4"W X 25 1/2"D X 30 3/4"H"
 Features
 - Navy or Black or Gray
 - 360-degree Swivel Glider
 - Gray Ceramic Tile Table Top
 - Fire Pit Table with Tile Table Top
-- Includes Cushions and Pillows
-Included items and dimensions:
-- Fire Pit Table: color: Black  or  Gray; dimensions: 40" W x 40"D x 26.5" H; feature: Contemporary
-- Swivel Glider Arm Chair (2 or CTN): color: Navy  or  Black  or  Gray; dimensions: 30.5" W x 25.5"D x 30.5" H; feature: Transitional
-Materials: Steel, Polyethylene Wicker, Ceremic, Polyspun
-Color: Navy  or  Black  or  Gray
+- Includes Cushions and Pillows Included items and dimensions:
+- Fire Pit Table: color: Black or Gray; dimensions: 40" W x 40"D x 26.5" H; feature: Contemporary
+- Swivel Glider Arm Chair (2 / CTN): color: Navy or Black or Gray; dimensions: 30.5" W x 25.5"D x 30.5" H; feature: Transitional
+Materials: Steel, Polyethylene Wicker, Ceremic, Polyspun.
+Color: Navy or Black or Gray
 Weight: 263.1 lbs</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SEGOVIA 5 Pc. Dining Table Set in Navy  or  Black  or  Gray | GOODDEGG</t>
+          <t>SEGOVIA 5 Pc. Dining Table Set in Navy or Black or Gray | GOODDEGG</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3897,7 +4014,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -3910,25 +4027,24 @@
       <c r="H29" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-SEGOVIA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Steel, Polyethylene Wicker, Polyspun construction and Black  or  Gray tones, it blends durability with visual warmth.
-Product Dimensions: 40" L x 40" W x 26 1 or 2" H
+SEGOVIA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Steel, Polyethylene Wicker, Polyspun construction and Black or Gray tones, it blends durability with visual warmth.
+Product Dimensions: 40"L X 40"W X 26 1/2"H
 Features
 - Black or Gray
 - 360-degree swivel rockers
 - Gray ceramic tile table top
 - Fire pit table with tile-top and wicker base
-- Includes cushions and pillows
-Included items and dimensions:
-- Fire Pit Table: color: Black  or  Gray; dimensions: 40" W x 40"D x 26.5" H; feature: Contemporary
-- Swivel Chair: color: Black  or  Gray; dimensions: 29 3 or 4" W x 27 1 or 4"D x 33 1 or 4" H; feature: Contemporary
-Materials: Steel, Polyethylene Wicker, Polyspun
-Color: Black  or  Gray
+- Includes cushions and pillows Included items and dimensions:
+- Fire Pit Table: color: Black or Gray; dimensions: 40" W x 40"D x 26.5" H; feature: Contemporary
+- Swivel Chair: color: Black or Gray; dimensions: 29 3 or 4" W x 27 1 or 4"D x 33 1 or 4" H; feature: Contemporary
+Materials: Steel, Polyethylene Wicker, Polyspun.
+Color: Black or Gray
 Weight: 248.1 lbs</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SEGOVIA 5 Pc. Patio Dining Set in Black  or  Gray | GOODDEGG</t>
+          <t>SEGOVIA 5 Pc. Patio Dining Set in Black or Gray | GOODDEGG</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4003,244 +4119,254 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="26" t="n"/>
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Black/Gray</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>GM-2012-5PC-10</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="26" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="26" t="inlineStr">
         <is>
           <t>SINTRA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="26" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-SINTRA 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyethylene Wicker, Polyspun and finished in Black  or  Gray tones for a clean, cohesive look.
-Product Dimensions: 40" L x 40" W x 28" H
+SINTRA 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyethylene Wicker, Polyspun and finished in Black or Gray tones for a clean, cohesive look.
+Product Dimensions: 40"L X 40"W X 28"H
 Features
 - Black or Gray
 - Ceramic tile table top
 - Rust-resistant
 - powder-coated steel frame
-- Includes umbrella hole and cap
-Included items and dimensions:
-- Patio Dining Table: color: Black  or  Gray; dimensions: 40" L x 40" W x 28" H; feature: Contemporary
-- Swivel Chair: color: Black  or  Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
-Materials: Steel, Polyethylene Wicker, Polyspun
-Color: Black  or  Gray
+- Includes umbrella hole and cap Included items and dimensions:
+- Patio Dining Table: color: Black or Gray; dimensions: 40" L x 40" W x 28" H; feature: Contemporary
+- Swivel Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
+Materials: Steel, Polyethylene Wicker, Polyspun.
+Color: Black or Gray
 Weight: 180.7 lbs</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>SINTRA 5 Pc. Patio Dining Set in Black  or  Gray | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="I30" s="26" t="inlineStr">
+        <is>
+          <t>SINTRA 5 Pc. Patio Dining Set in Black or Gray | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J30" s="26" t="inlineStr">
         <is>
           <t>The SINTRA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="26" t="inlineStr">
         <is>
           <t>SINTRA</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="26" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="M30" s="26" t="n"/>
+      <c r="N30" s="26" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="26" t="inlineStr">
         <is>
           <t>GM-2012, GM-2010-2PK</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" s="26" t="inlineStr">
         <is>
           <t>GM-2012-5PC-10.jpg,GM-2012-1.jpg,GM-2012-WB-1.jpg,GM-2012-2.jpg,GM-2012-3.jpg,GM-2012-4.jpg,GM-2010-2PK-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" s="26" t="n">
         <v>539</v>
       </c>
-      <c r="R30" s="2" t="n">
+      <c r="R30" s="27" t="n">
         <v>539</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S30" s="26" t="n">
         <v>1377</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T30" s="26" t="n">
         <v>180.7</v>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U30" s="26" t="inlineStr">
         <is>
           <t>40"L X 40"W X 28"H</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V30" s="26" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W30" s="26" t="inlineStr">
         <is>
           <t>Steel, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X30" s="26" t="inlineStr">
         <is>
           <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,Ceramic tile table top,Rust-resistant, powder-coated steel frame,Includes umbrella hole and cap</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y30" s="26" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC30" t="n">
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="26" t="n"/>
+      <c r="AB30" s="26" t="n"/>
+      <c r="AC30" s="26" t="n">
         <v>22.4</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="26" t="n"/>
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Black/Gray</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>GM-2012-5PC-11</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="26" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="26" t="inlineStr">
         <is>
           <t>SINTRA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="26" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-SINTRA 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel, Polyethylene Wicker, Polyspun, then finished in Black  or  Gray tones to suit a range of interiors.
-Product Dimensions: 40" L x 40" W x 28" H
+SINTRA 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel, Polyethylene Wicker, Polyspun, then finished in Black or Gray tones to suit a range of interiors.
+Product Dimensions: 40"L X 40"W X 28"H
 Features
 - Black or Gray
 - Ceramic tile table top
 - Rust-resistant
 - powder-coated steel frame
-- Includes umbrella hole and cap
-Included items and dimensions:
-- Patio Dining Table: color: Black  or  Gray; dimensions: 40" L x 40" W x 28" H; feature: Contemporary
-- Arm Chair: color: Black  or  Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
-Materials: Steel, Polyethylene Wicker, Polyspun
-Color: Black  or  Gray
+- Includes umbrella hole and cap Included items and dimensions:
+- Patio Dining Table: color: Black or Gray; dimensions: 40" L x 40" W x 28" H; feature: Contemporary
+- Arm Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
+Materials: Steel, Polyethylene Wicker, Polyspun.
+Color: Black or Gray
 Weight: 156.5 lbs</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>SINTRA 5 Pc. Patio Dining Set in Black  or  Gray | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="I31" s="26" t="inlineStr">
+        <is>
+          <t>SINTRA 5 Pc. Patio Dining Set in Black or Gray | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J31" s="26" t="inlineStr">
         <is>
           <t>The SINTRA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="26" t="inlineStr">
         <is>
           <t>SINTRA</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="26" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="M31" s="26" t="n"/>
+      <c r="N31" s="26" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="26" t="inlineStr">
         <is>
           <t>GM-2012, GM-2011-2PK</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" s="26" t="inlineStr">
         <is>
           <t>GM-2012-5PC-11.jpg,GM-2012-1.jpg,GM-2012-WB-1.jpg,GM-2012-2.jpg,GM-2012-3.jpg,GM-2012-4.jpg,GM-2011-2PK-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31" s="26" t="n">
         <v>419</v>
       </c>
-      <c r="R31" s="2" t="n">
+      <c r="R31" s="27" t="n">
         <v>419</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S31" s="26" t="n">
         <v>1017</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T31" s="26" t="n">
         <v>156.5</v>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U31" s="26" t="inlineStr">
         <is>
           <t>40"L X 40"W X 28"H</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V31" s="26" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W31" s="26" t="inlineStr">
         <is>
           <t>Steel, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X31" s="26" t="inlineStr">
         <is>
           <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,Ceramic tile table top,Rust-resistant, powder-coated steel frame,Includes umbrella hole and cap</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y31" s="26" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC31" t="n">
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="26" t="n"/>
+      <c r="AB31" s="26" t="n"/>
+      <c r="AC31" s="26" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4260,7 +4386,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
@@ -4273,8 +4399,8 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-SINTRA 6 Pc. Patio Dining Set w/ Bench creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel, Polyspun construction and Black  or  Gray tones, it blends durability with visual warmth.
-Product Dimensions: 76" L x 40" W x 28" H
+SINTRA 6 Pc. Patio Dining Set w/ Bench creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel, Polyspun construction and Black or Gray tones, it blends durability with visual warmth.
+Product Dimensions: 76"L X 40"W X 28"H
 Features
 - Black or Gray
 - Ceramic tile table top
@@ -4282,20 +4408,19 @@
 - Rust-resistant
 - powder-coated steel frame
 - Table includes umbrella hole and cap
-- Chair includes cushion and pillow
-Included items and dimensions:
-- Patio Dining Table: color: Black  or  Gray; dimensions: 76" L x 40" W x 28" H; feature: Contemporary
-- Arm Chair: color: Black  or  Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
-- Swivel Chair: color: Black  or  Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
-- Bench: color: Black  or  Gray; dimensions: 59" W x 15 3 or 4"D x 17 1 or 4" H; feature: Contemporary
-Materials: Steel, Polyspun
-Color: Black  or  Gray
+- Chair includes cushion and pillow Included items and dimensions:
+- Patio Dining Table: color: Black or Gray; dimensions: 76" L x 40" W x 28" H; feature: Contemporary
+- Arm Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
+- Swivel Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
+- Bench: color: Black or Gray; dimensions: 59" W x 15 3 or 4"D x 17 1 or 4" H; feature: Contemporary
+Materials: Steel, Polyspun.
+Color: Black or Gray
 Weight: 234.5 lbs</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SINTRA 6 Pc. Patio Dining Set w/ Bench in Black  or  Gray | GOODDEG</t>
+          <t>SINTRA 6 Pc. Patio Dining Set w/ Bench in Black or Gray | GOODDEG</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4370,986 +4495,1030 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>FM80010BK-T-3PC</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="28" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="28" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="28" t="inlineStr">
         <is>
           <t>ZALIKA 3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="28" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZALIKA 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Fabric, Steel, PE Rattan, Foam build keeps the look polished and practical.
-Product Dimensions: TABLE: 19.5" W x 19.5"D x 21" HCHAIR: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
+Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")
 Features
 - Powder-Coated Steel Frame
 - 3.5mm Round Wicker
-- Tempered Glass Table Top
-Included items and dimensions:
+- Tempered Glass Table Top Included items and dimensions:
 - Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H
-- Patio Chair (2 or CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
-Materials: Fabric, Steel, PE Rattan, Foam
+- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
+Materials: Fabric, Steel, PE Rattan, Foam.
 Color: Black</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="28" t="inlineStr">
         <is>
           <t>ZALIKA 3 Pc. Conversation Set in Black | GOODDEGG</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="28" t="inlineStr">
         <is>
           <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="28" t="inlineStr">
         <is>
           <t>ZALIKA</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="28" t="inlineStr">
         <is>
           <t>3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="M33" s="28" t="n"/>
+      <c r="N33" s="28" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="28" t="inlineStr">
         <is>
           <t>FM80010BK-T, FM80010BK-CH-2PK</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P33" s="28" t="inlineStr">
         <is>
           <t>FM80010BK-T-3PC-1.jpg</t>
         </is>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q33" s="28" t="n">
         <v>199</v>
       </c>
-      <c r="R33" s="1" t="n">
+      <c r="R33" s="29" t="n">
         <v>199</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S33" s="28" t="n">
         <v>507</v>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="T33" s="28" t="n"/>
+      <c r="U33" s="28" t="inlineStr">
         <is>
           <t>TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V33" s="28" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W33" s="28" t="inlineStr">
         <is>
           <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X33" s="28" t="inlineStr">
         <is>
           <t>Contemporary,Black,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Y33" s="28" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC33" t="n">
+      <c r="Z33" s="28" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="28" t="n">
         <v>10.9</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="28" t="n"/>
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>FM80010NT-T-3PC</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="28" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="28" t="inlineStr">
         <is>
           <t>ZALIKA 3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="28" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZALIKA 3 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Steel, PE Rattan, Foam and finished in Natural tones for a clean, cohesive look.
-Product Dimensions: TABLE: 19.5" W x 19.5"D x 21" HCHAIR: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
+Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")
 Features
 - Powder-Coated Steel Frame
 - 3.5mm Round Wicker
-- Tempered Glass Table Top
-Included items and dimensions:
+- Tempered Glass Table Top Included items and dimensions:
 - Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H
-- Patio Chair (2 or CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
-Materials: Fabric, Steel, PE Rattan, Foam
+- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
+Materials: Fabric, Steel, PE Rattan, Foam.
 Color: Natural</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="28" t="inlineStr">
         <is>
           <t>ZALIKA 3 Pc. Conversation Set in Natural | GOODDEGG</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="28" t="inlineStr">
         <is>
           <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="28" t="inlineStr">
         <is>
           <t>ZALIKA</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="28" t="inlineStr">
         <is>
           <t>3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="M34" s="28" t="n"/>
+      <c r="N34" s="28" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="28" t="inlineStr">
         <is>
           <t>FM80010NT-T, FM80010NT-CH-2PK</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P34" s="28" t="inlineStr">
         <is>
           <t>FM80010NT-T-3PC-1.jpg</t>
         </is>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q34" s="28" t="n">
         <v>199</v>
       </c>
-      <c r="R34" s="1" t="n">
+      <c r="R34" s="29" t="n">
         <v>199</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S34" s="28" t="n">
         <v>507</v>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="T34" s="28" t="n"/>
+      <c r="U34" s="28" t="inlineStr">
         <is>
           <t>TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V34" s="28" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W34" s="28" t="inlineStr">
         <is>
           <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X34" s="28" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" s="28" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC34" t="n">
+      <c r="Z34" s="28" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="28" t="n">
         <v>10.9</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="30" t="n"/>
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>FM80010BK-T-4PC-BN</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="30" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="30" t="inlineStr">
         <is>
           <t>ZALIKA 4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="30" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZALIKA 4 Pc. Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Steel, PE Rattan, Foam, then finished in Black tones to suit a range of interiors.
-Product Dimensions: TABLE: 19.5" W x 19.5"D x 21" H, CHAIR: 22" W x 26.5"D x 35" H, BENCH: 51.5" W x 26.5"D x 35" H
+Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H
 Features
 - Powder-Coated Steel Frame
 - 3.5mm Round Wicker
-- Tempered Glass Table Top
-Included items and dimensions:
+- Tempered Glass Table Top Included items and dimensions:
 - Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H
-- Patio Chair (2 or CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
+- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
 - Patio Bench: dimensions: 51.5" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
-Materials: Fabric, Steel, PE Rattan, Foam
+Materials: Fabric, Steel, PE Rattan, Foam.
 Color: Black</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="30" t="inlineStr">
         <is>
           <t>ZALIKA 4 Pc. Conversation Set in Black | GOODDEGG</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="30" t="inlineStr">
         <is>
           <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="30" t="inlineStr">
         <is>
           <t>ZALIKA</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="30" t="inlineStr">
         <is>
           <t>4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="M35" s="30" t="n"/>
+      <c r="N35" s="30" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" s="30" t="inlineStr">
         <is>
           <t>FM80010BK-T, FM80010BK-CH-2PK, FM80010BK-BN</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P35" s="30" t="inlineStr">
         <is>
           <t>FM80010BK-T-4PC-BN-1.jpg</t>
         </is>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q35" s="30" t="n">
         <v>418</v>
       </c>
-      <c r="R35" s="1" t="n">
+      <c r="R35" s="31" t="n">
         <v>418</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S35" s="30" t="n">
         <v>984</v>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="T35" s="30" t="n"/>
+      <c r="U35" s="30" t="inlineStr">
         <is>
           <t>TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V35" s="30" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W35" s="30" t="inlineStr">
         <is>
           <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X35" s="30" t="inlineStr">
         <is>
           <t>Contemporary,Black,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" s="30" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC35" t="n">
+      <c r="Z35" s="30" t="n"/>
+      <c r="AA35" s="30" t="n"/>
+      <c r="AB35" s="30" t="n"/>
+      <c r="AC35" s="30" t="n">
         <v>28.6</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="30" t="n"/>
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="C36" s="30" t="n"/>
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>FM80010NT-T-4PC-BN</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="30" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="30" t="inlineStr">
         <is>
           <t>ZALIKA 4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZALIKA 4 Pc. Conversation Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Fabric, Steel, PE Rattan, Foam construction and Natural tones, it blends durability with visual warmth.
-Product Dimensions: TABLE: 19.5" W x 19.5"D x 21" H, CHAIR: 22" W x 26.5"D x 35" H, BENCH: 51.5" W x 26.5"D x 35" H
+Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H
 Features
 - Powder-Coated Steel Frame
 - 3.5mm Round Wicker
-- Tempered Glass Table Top
-Included items and dimensions:
+- Tempered Glass Table Top Included items and dimensions:
 - Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H
-- Patio Chair (2 or CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
+- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
 - Patio Bench: dimensions: 51.5" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
-Materials: Fabric, Steel, PE Rattan, Foam
+Materials: Fabric, Steel, PE Rattan, Foam.
 Color: Natural</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="30" t="inlineStr">
         <is>
           <t>ZALIKA 4 Pc. Conversation Set in Natural | GOODDEGG</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="30" t="inlineStr">
         <is>
           <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="30" t="inlineStr">
         <is>
           <t>ZALIKA</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="30" t="inlineStr">
         <is>
           <t>4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="M36" s="30" t="n"/>
+      <c r="N36" s="30" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" s="30" t="inlineStr">
         <is>
           <t>FM80010NT-T, FM80010NT-CH-2PK, FM80010NT-BN</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P36" s="30" t="inlineStr">
         <is>
           <t>FM80010NT-T-4PC-BN-1.jpg</t>
         </is>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q36" s="30" t="n">
         <v>418</v>
       </c>
-      <c r="R36" s="1" t="n">
+      <c r="R36" s="31" t="n">
         <v>418</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S36" s="30" t="n">
         <v>984</v>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="T36" s="30" t="n"/>
+      <c r="U36" s="30" t="inlineStr">
         <is>
           <t>TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V36" s="30" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W36" s="30" t="inlineStr">
         <is>
           <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X36" s="30" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" s="30" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC36" t="n">
+      <c r="Z36" s="30" t="n"/>
+      <c r="AA36" s="30" t="n"/>
+      <c r="AB36" s="30" t="n"/>
+      <c r="AC36" s="30" t="n">
         <v>28.6</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="32" t="n"/>
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>Natural/Black</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-02BB</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="32" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="32" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="32" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural  or  Black tones to suit a range of interiors.
-Product Dimensions: Table: 21.5" W x 21.5"D x 15.5" H, Chair: 25" W x 23.5"D x 31" H
+ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H
 Features
 - Natural or Black
 - Sturdy &amp; Durable Design
 - Easy to store
-- Handcrafted BOHO Chic
-Included items and dimensions:
+- Handcrafted BOHO Chic Included items and dimensions:
 - Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary
-- Patio Chair (2 or CTN): color: Black; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric
-Color: Natural  or  Black
+- Patio Chair (2 / CTN): color: Black; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary
+Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.
+Color: Natural or Black
 Weight: 37.6 lbs</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural  or  Black | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="I37" s="32" t="inlineStr">
+        <is>
+          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural or Black | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J37" s="32" t="inlineStr">
         <is>
           <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="32" t="inlineStr">
         <is>
           <t>ZUBERI</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="32" t="inlineStr">
         <is>
           <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="32" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" s="32" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-T, FM80002BB-CH-2PK</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P37" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-02BB-1-Z.jpg,FM80002BB-CH-1.jpg,FM80003NT-T-1.jpg</t>
         </is>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q37" s="32" t="n">
         <v>179</v>
       </c>
-      <c r="R37" s="1" t="n">
+      <c r="R37" s="33" t="n">
         <v>179</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S37" s="32" t="n">
         <v>417</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T37" s="32" t="n">
         <v>37.6</v>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U37" s="32" t="inlineStr">
         <is>
           <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V37" s="32" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W37" s="32" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X37" s="32" t="inlineStr">
         <is>
           <t>Contemporary,Natural/Black,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Y37" s="32" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC37" t="n">
+      <c r="Z37" s="32" t="n"/>
+      <c r="AA37" s="32" t="n"/>
+      <c r="AB37" s="32" t="n"/>
+      <c r="AC37" s="32" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="32" t="n"/>
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="C38" s="32" t="n"/>
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-02NT</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="32" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="32" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="32" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZUBERI 3 Pc. Patio Conversation Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric construction and Natural tones, it blends durability with visual warmth.
-Product Dimensions: Table: 21.5" W x 21.5"D x 15.5" H, Chair: 25" W x 23.5"D x 31" H
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H
 Features
 - Sturdy &amp; Durable Design
 - Easy to store
-- Handcrafted BOHO Chic
-Included items and dimensions:
+- Handcrafted BOHO Chic Included items and dimensions:
 - Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary
-- Patio Chair (2 or CTN): color: Natural; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric
+- Patio Chair (2 / CTN): color: Natural; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary
+Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.
 Color: Natural
 Weight: 21.3 lbs</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set in Natural | GOODDEGG</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="32" t="inlineStr">
         <is>
           <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="32" t="inlineStr">
         <is>
           <t>ZUBERI</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" s="32" t="inlineStr">
         <is>
           <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="M38" s="32" t="n"/>
+      <c r="N38" s="32" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O38" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-T, FM80002NT-CH-2PK</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P38" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-02NT-1-Z.jpg,FM80002NT-CH-1.jpg,FM80003NT-T-1.jpg</t>
         </is>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q38" s="32" t="n">
         <v>179</v>
       </c>
-      <c r="R38" s="1" t="n">
+      <c r="R38" s="33" t="n">
         <v>179</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S38" s="32" t="n">
         <v>417</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T38" s="32" t="n">
         <v>21.3</v>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U38" s="32" t="inlineStr">
         <is>
           <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V38" s="32" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W38" s="32" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X38" s="32" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Y38" s="32" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC38" t="n">
+      <c r="Z38" s="32" t="n"/>
+      <c r="AA38" s="32" t="n"/>
+      <c r="AB38" s="32" t="n"/>
+      <c r="AC38" s="32" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="32" t="n"/>
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="C39" s="32" t="n"/>
+      <c r="D39" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-05NT</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="32" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="32" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZUBERI 3 Pc. Patio Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric build keeps the look polished and practical.
-Product Dimensions: Table: 21.5" W x 21.5"D x 15.5" H, Chair: 23" W x 23.5"D x 35" H
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H
 Features
 - Sturdy &amp; Durable Design
 - Easy to store
-- Handcrafted BOHO Chic
-Included items and dimensions:
+- Handcrafted BOHO Chic Included items and dimensions:
 - Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary
 - Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric
+Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.
 Color: Natural
 Weight: 28.1 lbs</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set in Natural | GOODDEGG</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="32" t="inlineStr">
         <is>
           <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="32" t="inlineStr">
         <is>
           <t>ZUBERI</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="32" t="inlineStr">
         <is>
           <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="M39" s="32" t="n"/>
+      <c r="N39" s="32" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O39" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-T, FM80005NT-CH-2PK</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P39" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-05NT-1-Z.jpg,FM80003NT-T-1.jpg,FM80005NT-CH-1.jpg</t>
         </is>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q39" s="32" t="n">
         <v>169</v>
       </c>
-      <c r="R39" s="1" t="n">
+      <c r="R39" s="33" t="n">
         <v>169</v>
       </c>
-      <c r="S39" t="n">
+      <c r="S39" s="32" t="n">
         <v>327</v>
       </c>
-      <c r="T39" t="n">
+      <c r="T39" s="32" t="n">
         <v>28.1</v>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U39" s="32" t="inlineStr">
         <is>
           <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V39" s="32" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W39" s="32" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X39" s="32" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Y39" s="32" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC39" t="n">
+      <c r="Z39" s="32" t="n"/>
+      <c r="AA39" s="32" t="n"/>
+      <c r="AB39" s="32" t="n"/>
+      <c r="AC39" s="32" t="n">
         <v>24.1</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="32" t="n"/>
+      <c r="B40" s="32" t="inlineStr">
         <is>
           <t>Natural/Gray</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="C40" s="32" t="n"/>
+      <c r="D40" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-06GY</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="32" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="32" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="32" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-ZUBERI 3 Pc. Patio Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric and finished in Natural  or  Gray tones for a clean, cohesive look.
-Product Dimensions: Table: 21.5" W x 21.5"D x 15.5" H, Chair: 23" W x 23.5"D x 35" H
+ZUBERI 3 Pc. Patio Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric and finished in Natural or Gray tones for a clean, cohesive look.
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H
 Features
 - Natural or Gray
 - Sturdy &amp; Durable Design
 - Easy to store
-- Handcrafted BOHO Chic
-Included items and dimensions:
+- Handcrafted BOHO Chic Included items and dimensions:
 - Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary
 - Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric
-Color: Natural  or  Gray
+Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.
+Color: Natural or Gray
 Weight: 35.9 lbs</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural  or  Gray | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="I40" s="32" t="inlineStr">
+        <is>
+          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural or Gray | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J40" s="32" t="inlineStr">
         <is>
           <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="32" t="inlineStr">
         <is>
           <t>ZUBERI</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="32" t="inlineStr">
         <is>
           <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M40" s="32" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" s="32" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O40" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-T, FM80006GY-CH-2PK</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P40" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-06GY-1-Z.jpg,FM80003NT-T-1.jpg,FM80006GY-CH-1.jpg</t>
         </is>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q40" s="32" t="n">
         <v>249</v>
       </c>
-      <c r="R40" s="1" t="n">
+      <c r="R40" s="33" t="n">
         <v>249</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S40" s="32" t="n">
         <v>477</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T40" s="32" t="n">
         <v>35.9</v>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U40" s="32" t="inlineStr">
         <is>
           <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V40" s="32" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W40" s="32" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X40" s="32" t="inlineStr">
         <is>
           <t>Contemporary,Natural/Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Y40" s="32" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC40" t="n">
+      <c r="Z40" s="32" t="n"/>
+      <c r="AA40" s="32" t="n"/>
+      <c r="AB40" s="32" t="n"/>
+      <c r="AC40" s="32" t="n">
         <v>22.3</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="34" t="n"/>
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="C41" s="34" t="n"/>
+      <c r="D41" s="34" t="inlineStr">
         <is>
           <t>GM-1010BK-SET</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="34" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="34" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="34" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 BREEZE Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Crafted with Steel, Mesh, Fabric, then finished in Black tones to suit a range of interiors.
-Product Dimensions: 28"" W x 34 1 or 4""D x 46"" H"
+Product Dimensions: 28""W X 34 1/4""D X 46""H"
 Features
 - Modern
 - For indoor or outdoor use
@@ -5357,122 +5526,127 @@
 - Breathable and UV-resistant mesh
 - Includes back and seat cushions
 - Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs
-Included items and dimensions:
+- Max weight capacity: 220 lbs Included items and dimensions:
 - Swing Chair: color: Black; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern
 - Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric
+Materials: Steel, Mesh, Fabric.
 Color: Black
 Weight: 71.42 lbs</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand in Black | GOODDEGG</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="34" t="inlineStr">
         <is>
           <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="34" t="inlineStr">
         <is>
           <t>BREEZE</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" s="34" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="M41" s="34" t="n"/>
+      <c r="N41" s="34" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O41" s="34" t="inlineStr">
         <is>
           <t>GM-1010BK, GM-1012</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P41" s="34" t="inlineStr">
         <is>
           <t>GM-1010BK-1-Z.jpg,GM-1010BK-1.jpg</t>
         </is>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41" s="34" t="n">
         <v>219</v>
       </c>
-      <c r="R41" s="1" t="n">
+      <c r="R41" s="35" t="n">
         <v>219</v>
       </c>
-      <c r="S41" t="n">
+      <c r="S41" s="34" t="n">
         <v>567</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T41" s="34" t="n">
         <v>71.42</v>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U41" s="34" t="inlineStr">
         <is>
           <t>28""W X 34 1/4""D X 46""H"</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V41" s="34" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W41" s="34" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X41" s="34" t="inlineStr">
         <is>
           <t>Modern,Black,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Y41" s="34" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC41" t="n">
+      <c r="Z41" s="34" t="n"/>
+      <c r="AA41" s="34" t="n"/>
+      <c r="AB41" s="34" t="n"/>
+      <c r="AC41" s="34" t="n">
         <v>6.6</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
+      <c r="A42" s="34" t="n"/>
+      <c r="B42" s="34" t="inlineStr">
         <is>
           <t>Dark Gray</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="C42" s="34" t="n"/>
+      <c r="D42" s="34" t="inlineStr">
         <is>
           <t>GM-1010DG-SET</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="34" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="34" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="34" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 BREEZE Swing Chair w/ Stand creates a cohesive setup that feels inviting the moment you walk in. As a outdoor chair, it is designed to coordinate with matching pieces. The Modern character adds definition without feeling heavy. With Steel, Mesh, Fabric construction and Dark Gray tones, it blends durability with visual warmth.
-Product Dimensions: 28"" W x 34 1 or 4""D x 46"" H"
+Product Dimensions: 28""W X 34 1/4""D X 46""H"
 Features
 - Modern
 - For indoor or outdoor use
@@ -5480,122 +5654,127 @@
 - Breathable and UV-resistant mesh
 - Includes back and seat cushions
 - Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs
-Included items and dimensions:
+- Max weight capacity: 220 lbs Included items and dimensions:
 - Swing Chair: color: Dark Gray; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern
 - Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric
+Materials: Steel, Mesh, Fabric.
 Color: Dark Gray
 Weight: 71.42 lbs</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand in Dark Gray | GOODDEGG</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="34" t="inlineStr">
         <is>
           <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="34" t="inlineStr">
         <is>
           <t>BREEZE</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="34" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="M42" s="34" t="n"/>
+      <c r="N42" s="34" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O42" s="34" t="inlineStr">
         <is>
           <t>GM-1010DG, GM-1012</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P42" s="34" t="inlineStr">
         <is>
           <t>GM-1010DG-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q42" s="34" t="n">
         <v>219</v>
       </c>
-      <c r="R42" s="1" t="n">
+      <c r="R42" s="35" t="n">
         <v>219</v>
       </c>
-      <c r="S42" t="n">
+      <c r="S42" s="34" t="n">
         <v>567</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T42" s="34" t="n">
         <v>71.42</v>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U42" s="34" t="inlineStr">
         <is>
           <t>28""W X 34 1/4""D X 46""H"</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V42" s="34" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W42" s="34" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X42" s="34" t="inlineStr">
         <is>
           <t>Modern,Dark Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Y42" s="34" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC42" t="n">
+      <c r="Z42" s="34" t="n"/>
+      <c r="AA42" s="34" t="n"/>
+      <c r="AB42" s="34" t="n"/>
+      <c r="AC42" s="34" t="n">
         <v>6.6</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="34" t="n"/>
+      <c r="B43" s="34" t="inlineStr">
         <is>
           <t>Light Gray</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="C43" s="34" t="n"/>
+      <c r="D43" s="34" t="inlineStr">
         <is>
           <t>GM-1010LG-SET</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="34" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="34" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="34" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 BREEZE Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. This outdoor chair is made to fit naturally into the room. A Modern profile gives the space a refined, approachable look. Finished in Light Gray tones, the Steel, Mesh, Fabric build keeps the look polished and practical.
-Product Dimensions: 28"" W x 34 1 or 4""D x 46"" H"
+Product Dimensions: 28""W X 34 1/4""D X 46""H"
 Features
 - Modern
 - For indoor or outdoor use
@@ -5603,122 +5782,127 @@
 - Breathable and UV-resistant mesh
 - Includes back and seat cushions
 - Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs
-Included items and dimensions:
+- Max weight capacity: 220 lbs Included items and dimensions:
 - Swing Chair: color: Light Gray; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern
 - Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric
+Materials: Steel, Mesh, Fabric.
 Color: Light Gray
 Weight: 71.42 lbs</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand in Light Gray | GOODDEGG</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="34" t="inlineStr">
         <is>
           <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="34" t="inlineStr">
         <is>
           <t>BREEZE</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" s="34" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="M43" s="34" t="n"/>
+      <c r="N43" s="34" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O43" s="34" t="inlineStr">
         <is>
           <t>GM-1010LG, GM-1012</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P43" s="34" t="inlineStr">
         <is>
           <t>GM-1010LG-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q43" s="34" t="n">
         <v>219</v>
       </c>
-      <c r="R43" s="1" t="n">
+      <c r="R43" s="35" t="n">
         <v>219</v>
       </c>
-      <c r="S43" t="n">
+      <c r="S43" s="34" t="n">
         <v>567</v>
       </c>
-      <c r="T43" t="n">
+      <c r="T43" s="34" t="n">
         <v>71.42</v>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U43" s="34" t="inlineStr">
         <is>
           <t>28""W X 34 1/4""D X 46""H"</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V43" s="34" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W43" s="34" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X43" s="34" t="inlineStr">
         <is>
           <t>Modern,Light Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Y43" s="34" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC43" t="n">
+      <c r="Z43" s="34" t="n"/>
+      <c r="AA43" s="34" t="n"/>
+      <c r="AB43" s="34" t="n"/>
+      <c r="AC43" s="34" t="n">
         <v>6.6</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="36" t="n"/>
+      <c r="B44" s="36" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="C44" s="36" t="n"/>
+      <c r="D44" s="36" t="inlineStr">
         <is>
           <t>GM-1011BK-SET</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F44" s="36" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="36" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 CRUSH Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Steel, Mesh, Fabric build keeps the look polished and practical.
-Product Dimensions: 28 1 or 4"" W x 29 1 or 2""D x 43 1 or 4"" H"
+Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"
 Features
 - Modern
 - For indoor or outdoor use
@@ -5726,122 +5910,127 @@
 - Breathable and UV-resistant mesh
 - Includes back and seat cushions
 - Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs
-Included items and dimensions:
+- Max weight capacity: 220 lbs Included items and dimensions:
 - Swing Chair: color: Black; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern
 - Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric
+Materials: Steel, Mesh, Fabric.
 Color: Black
 Weight: 68.12 lbs</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand in Black | GOODDEGG</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="36" t="inlineStr">
         <is>
           <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="36" t="inlineStr">
         <is>
           <t>CRUSH</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" s="36" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="M44" s="36" t="n"/>
+      <c r="N44" s="36" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O44" s="36" t="inlineStr">
         <is>
           <t>GM-1011BK, GM-1012</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P44" s="36" t="inlineStr">
         <is>
           <t>GM-1011BK-WB-1.jpg,GM-1011BK-1.jpg</t>
         </is>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q44" s="36" t="n">
         <v>219</v>
       </c>
-      <c r="R44" s="1" t="n">
+      <c r="R44" s="37" t="n">
         <v>219</v>
       </c>
-      <c r="S44" t="n">
+      <c r="S44" s="36" t="n">
         <v>567</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T44" s="36" t="n">
         <v>68.12</v>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U44" s="36" t="inlineStr">
         <is>
           <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V44" s="36" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W44" s="36" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X44" s="36" t="inlineStr">
         <is>
           <t>Modern,Black,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Y44" s="36" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC44" t="n">
+      <c r="Z44" s="36" t="n"/>
+      <c r="AA44" s="36" t="n"/>
+      <c r="AB44" s="36" t="n"/>
+      <c r="AC44" s="36" t="n">
         <v>6.8</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="36" t="n"/>
+      <c r="B45" s="36" t="inlineStr">
         <is>
           <t>Dark Gray</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="C45" s="36" t="n"/>
+      <c r="D45" s="36" t="inlineStr">
         <is>
           <t>GM-1011DG-SET</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F45" s="36" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="36" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 CRUSH Swing Chair w/ Stand is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Modern character adds definition without feeling heavy. Built from Steel, Mesh, Fabric and finished in Dark Gray tones for a clean, cohesive look.
-Product Dimensions: 28 1 or 4"" W x 29 1 or 2""D x 43 1 or 4"" H"
+Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"
 Features
 - Modern
 - For indoor or outdoor use
@@ -5849,122 +6038,127 @@
 - Breathable and UV-resistant mesh
 - Includes back and seat cushions
 - Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs
-Included items and dimensions:
+- Max weight capacity: 220 lbs Included items and dimensions:
 - Swing Chair: color: Dark Gray; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern
 - Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric
+Materials: Steel, Mesh, Fabric.
 Color: Dark Gray
 Weight: 68.12 lbs</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand in Dark Gray | GOODDEGG</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="36" t="inlineStr">
         <is>
           <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="36" t="inlineStr">
         <is>
           <t>CRUSH</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="36" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="M45" s="36" t="n"/>
+      <c r="N45" s="36" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O45" s="36" t="inlineStr">
         <is>
           <t>GM-1011DG, GM-1012</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P45" s="36" t="inlineStr">
         <is>
           <t>GM-1011DG-WB-1.jpg,GM-1011DG-1.jpg</t>
         </is>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q45" s="36" t="n">
         <v>219</v>
       </c>
-      <c r="R45" s="1" t="n">
+      <c r="R45" s="37" t="n">
         <v>219</v>
       </c>
-      <c r="S45" t="n">
+      <c r="S45" s="36" t="n">
         <v>567</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T45" s="36" t="n">
         <v>68.12</v>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U45" s="36" t="inlineStr">
         <is>
           <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V45" s="36" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W45" s="36" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X45" s="36" t="inlineStr">
         <is>
           <t>Modern,Dark Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Y45" s="36" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC45" t="n">
+      <c r="Z45" s="36" t="n"/>
+      <c r="AA45" s="36" t="n"/>
+      <c r="AB45" s="36" t="n"/>
+      <c r="AC45" s="36" t="n">
         <v>6.8</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="36" t="n"/>
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t>Light Gray</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="C46" s="36" t="n"/>
+      <c r="D46" s="36" t="inlineStr">
         <is>
           <t>GM-1011LG-SET</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="36" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="36" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 CRUSH Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor chair is made to fit naturally into the room. A Modern profile gives the space a refined, approachable look. Crafted with Steel, Mesh, Fabric, then finished in Light Gray tones to suit a range of interiors.
-Product Dimensions: 28 1 or 4"" W x 29 1 or 2""D x 43 1 or 4"" H"
+Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"
 Features
 - Modern
 - For indoor or outdoor use
@@ -5972,88 +6166,91 @@
 - Breathable and UV-resistant mesh
 - Includes back and seat cushions
 - Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs
-Included items and dimensions:
+- Max weight capacity: 220 lbs Included items and dimensions:
 - Swing Chair: color: Light Gray; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern
 - Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric
+Materials: Steel, Mesh, Fabric.
 Color: Light Gray
 Weight: 68.12 lbs</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand in Light Gray | GOODDEGG</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="36" t="inlineStr">
         <is>
           <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="36" t="inlineStr">
         <is>
           <t>CRUSH</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L46" s="36" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="M46" s="36" t="n"/>
+      <c r="N46" s="36" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O46" s="36" t="inlineStr">
         <is>
           <t>GM-1011LG, GM-1012</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P46" s="36" t="inlineStr">
         <is>
           <t>GM-1011LG-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q46" s="36" t="n">
         <v>219</v>
       </c>
-      <c r="R46" s="1" t="n">
+      <c r="R46" s="37" t="n">
         <v>219</v>
       </c>
-      <c r="S46" t="n">
+      <c r="S46" s="36" t="n">
         <v>567</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T46" s="36" t="n">
         <v>68.12</v>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U46" s="36" t="inlineStr">
         <is>
           <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V46" s="36" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W46" s="36" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X46" s="36" t="inlineStr">
         <is>
           <t>Modern,Light Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Y46" s="36" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC46" t="n">
+      <c r="Z46" s="36" t="n"/>
+      <c r="AA46" s="36" t="n"/>
+      <c r="AB46" s="36" t="n"/>
+      <c r="AC46" s="36" t="n">
         <v>6.8</v>
       </c>
     </row>
@@ -6073,35 +6270,34 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MACKAY 2 Reclining Chairs  and  2 Ottomans</t>
+          <t>MACKAY 2 Reclining Chairs and 2 Ottomans</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-MACKAY 2 Reclining Chairs  and  2 Ottomans is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Beige  or  Natural Teak tones for a clean, cohesive look.
-Product Dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H
+MACKAY 2 Reclining Chairs and 2 Ottomans is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Beige or Natural Teak tones for a clean, cohesive look.
+Product Dimensions: 24 1/2"W X 27 1/2"D X 42 1/2"H
 Features
 - Beige or Natural Teak
-- Button-tufted cushion
-Included items and dimensions:
-- Reclining Chair (2 or CTN): color: Beige  or  Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
-- Ottoman (2 or CTN): color: Beige  or  Natural Teak; dimensions: 21 1 or 4" L x 21 1 or 4" W x 16 1 or 2" H; feature: Contemporary
-Materials: Aluminum, FSC Certified 100% Teak Wood
-Color: Beige  or  Natural Teak
+- Button-tufted cushion Included items and dimensions:
+- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
+- Ottoman (2 / CTN): color: Beige or Natural Teak; dimensions: 21 1 or 4" L x 21 1 or 4" W x 16 1 or 2" H; feature: Contemporary
+Materials: Aluminum, FSC Certified 100% Teak Wood.
+Color: Beige or Natural Teak
 Weight: 90.37 lbs</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MACKAY 2 Reclining Chairs  and  2 Ottomans | GOODDEGG</t>
+          <t>MACKAY 2 Reclining Chairs and 2 Ottomans | GOODDEGG</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6191,7 +6387,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Bar Table Set</t>
         </is>
@@ -6205,16 +6401,15 @@
         <is>
           <t>FREE SHIPPING
 CYPRUS 7 Pc. Bar Table Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor bar table set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, Polyethylene Wicker, Polyspun construction and Gray tones, it blends durability with visual warmth.
-Product Dimensions: 46"DIA x 39 1 or 2" H
+Product Dimensions: 46"DIA X 39 1/2"H
 Features
 - Includes stainless steel ice bucket
 - Removable bucket with center cover
 - Stackable wicker chairs
 - Stainless steel footrest around base
-- Includes umbrella hole and space for umbrella base
-Included items and dimensions:
+- Includes umbrella hole and space for umbrella base Included items and dimensions:
 - Bar Chair: color: Gray; dimensions: 20 1 or 4" W x 18"D x 41 3 or 4" H; feature: Contemporary
-Materials: Aluminum, Polyethylene Wicker, Polyspun
+Materials: Aluminum, Polyethylene Wicker, Polyspun.
 Color: Gray
 Weight: 144.5 lbs</t>
         </is>
@@ -6296,496 +6491,516 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="38" t="n"/>
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>Brown/Beige</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="C49" s="38" t="n"/>
+      <c r="D49" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-SET5</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="38" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F49" s="38" t="inlineStr">
         <is>
           <t>Sofa Set</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>ILONA L-Sectional  and  Coffee Table  and  End Table</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="G49" s="38" t="inlineStr">
+        <is>
+          <t>ILONA L-Sectional and Coffee Table and End Table</t>
+        </is>
+      </c>
+      <c r="H49" s="38" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-ILONA L-Sectional  and  Coffee Table  and  End Table is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor sofa set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, Polyester Canvas, Faux Rattan and finished in Brown  or  Beige tones for a clean, cohesive look.
-Product Dimensions: L-SECTIONAL: 103 1 or 4" W x 79 1 or 4"D x 25 1 or 2-31" H
+ILONA L-Sectional and Coffee Table and End Table is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor sofa set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, Polyester Canvas, Faux Rattan and finished in Brown or Beige tones for a clean, cohesive look.
+Product Dimensions: L-SECTIONAL: 103 1/4"W X 79 1/4"D X 25 1/2-31"H
 Features
 - Brown or Beige
 - Aluminum Frame
 - Modular Design
 - 5mm Tempered Glass Table Tops
 - UV &amp; Water Resistant
-- Beige Fabric Cushions
-Included items and dimensions:
-- Left Arm Chair: color: Brown  or  Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
-- Corner: color: Brown  or  Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
-- Ottoman: color: Brown  or  Beige; dimensions: 27 3 or 4" W x 27 1 or 4"D x 18" H; feature: Contemporary
-- Coffee Table: color: Brown  or  Beige; dimensions: 34 5 or 8" L x 19 1 or 4" W x 13 3 or 4" H; feature: Contemporary
-- End Table: color: Brown  or  Beige; dimensions: 17 3 or 4" L x 17 3 or 4" W x 19 5 or 8" H; feature: Contemporary
-- Armless Chair: color: Brown  or  Beige; dimensions: 24 1 or 4" W x 27 1 or 2"D x 25 1 or 2 - 31" H; feature: Contemporary
-Materials: Aluminum, Polyester Canvas, Faux Rattan
-Color: Brown  or  Beige
+- Beige Fabric Cushions Included items and dimensions:
+- Left Arm Chair: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
+- Corner: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
+- Ottoman: color: Brown or Beige; dimensions: 27 3 or 4" W x 27 1 or 4"D x 18" H; feature: Contemporary
+- Coffee Table: color: Brown or Beige; dimensions: 34 5 or 8" L x 19 1 or 4" W x 13 3 or 4" H; feature: Contemporary
+- End Table: color: Brown or Beige; dimensions: 17 3 or 4" L x 17 3 or 4" W x 19 5 or 8" H; feature: Contemporary
+- Armless Chair: color: Brown or Beige; dimensions: 24 1 or 4" W x 27 1 or 2"D x 25 1 or 2 - 31" H; feature: Contemporary
+Materials: Aluminum, Polyester Canvas, Faux Rattan.
+Color: Brown or Beige
 Weight: 204 lbs</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>ILONA L-Sectional  and  Coffee Table  and  End Table | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="I49" s="38" t="inlineStr">
+        <is>
+          <t>ILONA L-Sectional and Coffee Table and End Table | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J49" s="38" t="inlineStr">
         <is>
           <t>ILONA L-Sectional and Coffee Table and End Table offers relaxed seating for everyday. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="38" t="inlineStr">
         <is>
           <t>ILONA</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" s="38" t="inlineStr">
         <is>
           <t>L-Sectional + Coffee Table + End Table</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="M49" s="38" t="n"/>
+      <c r="N49" s="38" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O49" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-A, CM-OS2136-C, CM-OS2136-E, CM-OS2136-F, CM-OS2136-G, CM-OS2136-H</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P49" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-5.jpg,CM-OS2136-1.jpg,CM-OS2136-2.jpg</t>
         </is>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q49" s="38" t="n">
         <v>1082</v>
       </c>
-      <c r="R49" s="2" t="n">
+      <c r="R49" s="39" t="n">
         <v>1082</v>
       </c>
-      <c r="S49" t="n">
+      <c r="S49" s="38" t="n">
         <v>2817</v>
       </c>
-      <c r="T49" t="n">
+      <c r="T49" s="38" t="n">
         <v>204</v>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U49" s="38" t="inlineStr">
         <is>
           <t>L-SECTIONAL: 103 1/4"W X 79 1/4"D X 25 1/2-31"H</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V49" s="38" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W49" s="38" t="inlineStr">
         <is>
           <t>Aluminum, Polyester Canvas, Faux Rattan</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="X49" s="38" t="inlineStr">
         <is>
           <t>Contemporary,Brown/Beige,Aluminum, Polyester Canvas, Faux Rattan,Aluminum Frame,Modular Design,5mm Tempered Glass Table Tops,UV &amp; Water Resistant,Beige Fabric Cushions</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Y49" s="38" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC49" t="n">
+      <c r="Z49" s="38" t="n"/>
+      <c r="AA49" s="38" t="n"/>
+      <c r="AB49" s="38" t="n"/>
+      <c r="AC49" s="38" t="n">
         <v>45.7</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="38" t="n"/>
+      <c r="B50" s="38" t="inlineStr">
         <is>
           <t>Brown/Beige</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-SET7</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="38" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F50" s="38" t="inlineStr">
         <is>
           <t>Sofa Set</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>ILONA L-Sectional  and  Coffee Table  and  End Table</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="G50" s="38" t="inlineStr">
+        <is>
+          <t>ILONA L-Sectional and Coffee Table and End Table</t>
+        </is>
+      </c>
+      <c r="H50" s="38" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-ILONA L-Sectional  and  Coffee Table  and  End Table offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor sofa set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, Polyester Canvas, Faux Rattan, then finished in Brown  or  Beige tones to suit a range of interiors.
-Product Dimensions: L-SECTIONAL: 79 1 or 2" W x 79"D x 25 1 or 2-31" H
+ILONA L-Sectional and Coffee Table and End Table offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor sofa set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, Polyester Canvas, Faux Rattan, then finished in Brown or Beige tones to suit a range of interiors.
+Product Dimensions: L-SECTIONAL: 79 1/2"W X 79"D X 25 1/2-31"H
 Features
 - Brown or Beige
 - Aluminum Frame
 - Modular Design
 - 5mm Tempered Glass Table Tops
 - UV &amp; Water Resistant
-- Beige Fabric Cushions
-Included items and dimensions:
-- Left Arm Chair: color: Brown  or  Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
-- Corner: color: Brown  or  Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
-- Ottoman: color: Brown  or  Beige; dimensions: 27 3 or 4" W x 27 1 or 4"D x 18" H; feature: Contemporary
-- Coffee Table: color: Brown  or  Beige; dimensions: 34 5 or 8" L x 19 1 or 4" W x 13 3 or 4" H; feature: Contemporary
-- End Table: color: Brown  or  Beige; dimensions: 17 3 or 4" L x 17 3 or 4" W x 19 5 or 8" H; feature: Contemporary
-- Armless Chair: color: Brown  or  Beige; dimensions: 24 1 or 4" W x 27 1 or 2"D x 25 1 or 2 - 31" H; feature: Contemporary
-Materials: Aluminum, Polyester Canvas, Faux Rattan
-Color: Brown  or  Beige
+- Beige Fabric Cushions Included items and dimensions:
+- Left Arm Chair: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
+- Corner: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
+- Ottoman: color: Brown or Beige; dimensions: 27 3 or 4" W x 27 1 or 4"D x 18" H; feature: Contemporary
+- Coffee Table: color: Brown or Beige; dimensions: 34 5 or 8" L x 19 1 or 4" W x 13 3 or 4" H; feature: Contemporary
+- End Table: color: Brown or Beige; dimensions: 17 3 or 4" L x 17 3 or 4" W x 19 5 or 8" H; feature: Contemporary
+- Armless Chair: color: Brown or Beige; dimensions: 24 1 or 4" W x 27 1 or 2"D x 25 1 or 2 - 31" H; feature: Contemporary
+Materials: Aluminum, Polyester Canvas, Faux Rattan.
+Color: Brown or Beige
 Weight: 179 lbs</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>ILONA L-Sectional  and  Coffee Table  and  End Table | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I50" s="38" t="inlineStr">
+        <is>
+          <t>ILONA L-Sectional and Coffee Table and End Table | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J50" s="38" t="inlineStr">
         <is>
           <t>ILONA L-Sectional and Coffee Table and End Table offers relaxed seating for everyday. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" s="38" t="inlineStr">
         <is>
           <t>ILONA</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L50" s="38" t="inlineStr">
         <is>
           <t>L-Sectional + Coffee Table + End Table</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="M50" s="38" t="n"/>
+      <c r="N50" s="38" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O50" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-A, CM-OS2136-C, CM-OS2136-E, CM-OS2136-F, CM-OS2136-G, CM-OS2136-H</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P50" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-7.jpg,CM-OS2136-1.jpg,CM-OS2136-2.jpg</t>
         </is>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q50" s="38" t="n">
         <v>933</v>
       </c>
-      <c r="R50" s="2" t="n">
+      <c r="R50" s="39" t="n">
         <v>933</v>
       </c>
-      <c r="S50" t="n">
+      <c r="S50" s="38" t="n">
         <v>2427</v>
       </c>
-      <c r="T50" t="n">
+      <c r="T50" s="38" t="n">
         <v>179</v>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U50" s="38" t="inlineStr">
         <is>
           <t>L-SECTIONAL: 79 1/2"W X 79"D X 25 1/2-31"H</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V50" s="38" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W50" s="38" t="inlineStr">
         <is>
           <t>Aluminum, Polyester Canvas, Faux Rattan</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X50" s="38" t="inlineStr">
         <is>
           <t>Contemporary,Brown/Beige,Aluminum, Polyester Canvas, Faux Rattan,Aluminum Frame,Modular Design,5mm Tempered Glass Table Tops,UV &amp; Water Resistant,Beige Fabric Cushions</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Y50" s="38" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC50" t="n">
+      <c r="Z50" s="38" t="n"/>
+      <c r="AA50" s="38" t="n"/>
+      <c r="AB50" s="38" t="n"/>
+      <c r="AC50" s="38" t="n">
         <v>40.2</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="40" t="n"/>
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>Beige/Natural Teak</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="C51" s="40" t="n"/>
+      <c r="D51" s="40" t="inlineStr">
         <is>
           <t>GM-2001-5PC</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="40" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F51" s="14" t="inlineStr">
+      <c r="F51" s="40" t="inlineStr">
         <is>
           <t>Patio Dining Set</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="40" t="inlineStr">
         <is>
           <t>MACKAY 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="40" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-MACKAY 5 Pc. Patio Dining Set sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, FSC Certified 100% Teak Wood, then finished in Beige  or  Natural Teak tones to suit a range of interiors.
-Product Dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H
+MACKAY 5 Pc. Patio Dining Set sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, FSC Certified 100% Teak Wood, then finished in Beige or Natural Teak tones to suit a range of interiors.
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H
 Features
 - Beige or Natural Teak
 - Mixed material of teak wood and metal frame
 - Extends from 61" to 84" w/ butterfly leaf
 - Seats up to 8 people
-- Level control table legs
-Included items and dimensions:
-- Patio Dining Table: color: Gun Metal  or  Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary
-- Reclining Chair (2 or CTN): color: Beige  or  Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
-Materials: Aluminum, FSC Certified 100% Teak Wood
-Color: Beige  or  Natural Teak
+- Level control table legs Included items and dimensions:
+- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary
+- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
+Materials: Aluminum, FSC Certified 100% Teak Wood.
+Color: Beige or Natural Teak
 Weight: 174.14 lbs</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>MACKAY 5 Pc. Patio Dining Set in Beige  or  Natural Teak | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I51" s="40" t="inlineStr">
+        <is>
+          <t>MACKAY 5 Pc. Patio Dining Set in Beige or Natural Teak | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J51" s="40" t="inlineStr">
         <is>
           <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="40" t="inlineStr">
         <is>
           <t>MACKAY</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L51" s="40" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="M51" s="40" t="n"/>
+      <c r="N51" s="40" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="40" t="inlineStr">
         <is>
           <t>GM-2001, GM-2002-2PK</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P51" s="40" t="inlineStr">
         <is>
           <t>GM-2001-1-Z.jpg,GM-2001-2.jpg,GM-2001-3.jpg,GM-2001-4.jpg,GM-2001-5.jpg,GM-2001-6.jpg,GM-2001-7.jpg,GM-2001-8.jpg,GM-2001-9.jpg,GM-2001-9.jpg</t>
         </is>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q51" s="40" t="n">
         <v>789</v>
       </c>
-      <c r="R51" s="1" t="n">
+      <c r="R51" s="41" t="n">
         <v>789</v>
       </c>
-      <c r="S51" t="n">
+      <c r="S51" s="40" t="n">
         <v>2127</v>
       </c>
-      <c r="T51" t="n">
+      <c r="T51" s="40" t="n">
         <v>174.14</v>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U51" s="40" t="inlineStr">
         <is>
           <t>61 1/2 - 84"L X 35 1/2"W X 30"H</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V51" s="40" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="W51" s="40" t="inlineStr">
         <is>
           <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X51" s="40" t="inlineStr">
         <is>
           <t>Contemporary,Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Extends from 61" to 84" w/ butterfly leaf,Seats up to 8 people,Level control table legs</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Y51" s="40" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC51" t="n">
+      <c r="Z51" s="40" t="n"/>
+      <c r="AA51" s="40" t="n"/>
+      <c r="AB51" s="40" t="n"/>
+      <c r="AC51" s="40" t="n">
         <v>28.3</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
+      <c r="A52" s="40" t="n"/>
+      <c r="B52" s="40" t="inlineStr">
         <is>
           <t>Gun Metal/Natural Teak</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="C52" s="40" t="n"/>
+      <c r="D52" s="40" t="inlineStr">
         <is>
           <t>GM-2004-5PC</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="40" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F52" s="40" t="inlineStr">
         <is>
           <t>Patio Dining Set</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="40" t="inlineStr">
         <is>
           <t>MACKAY 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="40" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-Gather around MACKAY 5 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, FSC Certified 100% Teak Wood construction and Gun Metal  or  Natural Teak tones, it blends durability with visual warmth.
-Product Dimensions: 59" L x 35 1 or 2" W x 29" H
+Gather around MACKAY 5 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, FSC Certified 100% Teak Wood construction and Gun Metal or Natural Teak tones, it blends durability with visual warmth.
+Product Dimensions: 59"L X 35 1/2"W X 29"H
 Features
 - Gun Metal or Natural Teak
 - Mixed material of teak wood and metal frame
 - Seats up to 6 people
 - Level control table legs
-- Includes umbrella hole and cap
-Included items and dimensions:
-- Patio Dining Table: color: Gun Metal  or  Natural Teak; dimensions: 59" L x 35 1 or 2" W x 29" H; feature: Contemporary
-- Stacking Chair: color: Gun Metal  or  Natural Teak; dimensions: 22.5" W x 25"D x 34" H; feature: Contemporary
-Materials: Aluminum, FSC Certified 100% Teak Wood
-Color: Gun Metal  or  Natural Teak
+- Includes umbrella hole and cap Included items and dimensions:
+- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 59" L x 35 1 or 2" W x 29" H; feature: Contemporary
+- Stacking Chair: color: Gun Metal or Natural Teak; dimensions: 22.5" W x 25"D x 34" H; feature: Contemporary
+Materials: Aluminum, FSC Certified 100% Teak Wood.
+Color: Gun Metal or Natural Teak
 Weight: 55.1 lbs</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>MACKAY 5 Pc. Patio Dining Set in Gun Metal  or  Natural Teak | GOODDEG</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="I52" s="40" t="inlineStr">
+        <is>
+          <t>MACKAY 5 Pc. Patio Dining Set in Gun Metal or Natural Teak | GOODDEG</t>
+        </is>
+      </c>
+      <c r="J52" s="40" t="inlineStr">
         <is>
           <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="40" t="inlineStr">
         <is>
           <t>MACKAY</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L52" s="40" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="M52" s="40" t="n"/>
+      <c r="N52" s="40" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" s="40" t="inlineStr">
         <is>
           <t>GM-2004, GM-2005</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P52" s="40" t="inlineStr">
         <is>
           <t>GM-2004-5PC.jpg,GM-2004-WB-4.jpg,GM-2004-WB-5.jpg</t>
         </is>
       </c>
-      <c r="Q52" t="n">
+      <c r="Q52" s="40" t="n">
         <v>499</v>
       </c>
-      <c r="R52" s="1" t="n">
+      <c r="R52" s="41" t="n">
         <v>499</v>
       </c>
-      <c r="S52" t="n">
+      <c r="S52" s="40" t="n">
         <v>1047</v>
       </c>
-      <c r="T52" t="n">
+      <c r="T52" s="40" t="n">
         <v>55.1</v>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="U52" s="40" t="inlineStr">
         <is>
           <t>59"L X 35 1/2"W X 29"H</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V52" s="40" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="W52" s="40" t="inlineStr">
         <is>
           <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X52" s="40" t="inlineStr">
         <is>
           <t>Contemporary,Gun Metal/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Seats up to 6 people,Level control table legs,Includes umbrella hole and cap</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Y52" s="40" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC52" t="n">
+      <c r="Z52" s="40" t="n"/>
+      <c r="AA52" s="40" t="n"/>
+      <c r="AB52" s="40" t="n"/>
+      <c r="AC52" s="40" t="n">
         <v>50</v>
       </c>
     </row>
@@ -6805,7 +7020,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Patio Dining Set</t>
         </is>
@@ -6818,19 +7033,18 @@
       <c r="H53" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-MACKAY 7 Pc. Patio Dining Set anchors the dining area with a cohesive look that feels easy and welcoming. As a outdoor patio dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Gun Metal  or  Beige  or  Natural Teak tones, the Aluminum, FSC Certified 100% Teak Wood build keeps the look polished and practical.
-Product Dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H
+MACKAY 7 Pc. Patio Dining Set anchors the dining area with a cohesive look that feels easy and welcoming. As a outdoor patio dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Gun Metal or Beige or Natural Teak tones, the Aluminum, FSC Certified 100% Teak Wood build keeps the look polished and practical.
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H
 Features
 - Gun Metal or Beige or Natural Teak
 - Mixed material of teak wood and metal frame
 - Extends from 61" to 84" w/ butterfly leaf
 - Seats up to 8 people
-- Level control table legs
-Included items and dimensions:
-- Patio Dining Table: color: Gun Metal  or  Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary
-- Reclining Chair (2 or CTN): color: Beige  or  Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
-Materials: Aluminum, FSC Certified 100% Teak Wood
-Color: Gun Metal  or  Beige  or  Natural Teak
+- Level control table legs Included items and dimensions:
+- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary
+- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
+Materials: Aluminum, FSC Certified 100% Teak Wood.
+Color: Gun Metal or Beige or Natural Teak
 Weight: 234.76 lbs</t>
         </is>
       </c>
@@ -6926,7 +7140,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Patio Dining Set</t>
         </is>
@@ -6939,20 +7153,19 @@
       <c r="H54" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Gun Metal  or  Beige  or  Natural Teak tones for a clean, cohesive look.
-Product Dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H
+MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Gun Metal or Beige or Natural Teak tones for a clean, cohesive look.
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H
 Features
 - Gun Metal or Beige or Natural Teak
 - Mixed material of teak wood and metal frame
 - Extends from 61" to 84" w/ butterfly leaf
 - Seats up to 8 people
-- Level control table legs
-Included items and dimensions:
-- Patio Dining Table: color: Gun Metal  or  Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary
-- Reclining Chair (2 or CTN): color: Beige  or  Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
-- Ottoman (2 or CTN): color: Beige  or  Natural Teak; dimensions: 21 1 or 4" L x 21 1 or 4" W x 16 1 or 2" H; feature: Contemporary
-Materials: Aluminum, FSC Certified 100% Teak Wood
-Color: Gun Metal  or  Beige  or  Natural Teak
+- Level control table legs Included items and dimensions:
+- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary
+- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
+- Ottoman (2 / CTN): color: Beige or Natural Teak; dimensions: 21 1 or 4" L x 21 1 or 4" W x 16 1 or 2" H; feature: Contemporary
+Materials: Aluminum, FSC Certified 100% Teak Wood.
+Color: Gun Metal or Beige or Natural Teak
 Weight: 203.89 lbs</t>
         </is>
       </c>
@@ -7048,7 +7261,7 @@
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="F55" s="16" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Patio Dining Table</t>
         </is>
@@ -7062,7 +7275,7 @@
         <is>
           <t>FREE SHIPPING
 Gather around MALIA 6 Pc. Patio Dining Set w/ Bench, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining table, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build keeps the look polished and practical.
-Product Dimensions: 59" L x 31 1 or 4" W x 26 3 or 4" H
+Product Dimensions: 59"L X 31 1/4"W X 26 3/4"H
 Features
 - Modular Design
 - Sectional and two sofas settings
@@ -7072,11 +7285,10 @@
 - Flap-open side storage
 - Includes cushions
 - pillows
-- and protective covers
-Included items and dimensions:
+- and protective covers Included items and dimensions:
 - Patio Dining Table: color: Gray; dimensions: 59" L x 31 1 or 4" W x 26 3 or 4" H; feature: Contemporary
 - 5 Pc. Sectional Set w/ Bench: color: Gray; dimensions: LEFT SOFA: 86 1 or 4" L x 31" W x 33" H, RIGHT SOFA: 78" L x 31" W x 33" H, OTTOMAN: 15" L x 15" W x 16" H, BENCH: 55" W x 15"D x 19 3 or 4" H; feature: Contemporary
-Materials: Aluminum, Polyethylene Wicker, Polyspun
+Materials: Aluminum, Polyethylene Wicker, Polyspun.
 Color: Gray
 Weight: 199.5 lbs</t>
         </is>

--- a/FOA SETS/Outdoor-Set.xlsx
+++ b/FOA SETS/Outdoor-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,183 +582,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AD55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Subcategory</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>seo title(70char)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>seo title(70char)</t>
+          <t>seo description(160char)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>seo description(160char)</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Short Description</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Short Description</t>
+          <t>Short Description - Red Text</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Short Description - Red Text</t>
+          <t>Item Type</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Parts for Group Items</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Parts for Group Items</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>East(cost)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>East(cost)</t>
+          <t>EAST COST (Updated)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>EAST COST (Updated)</t>
+          <t>MSRP</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>MSRP</t>
+          <t>Weight (LB)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Weight (LB)</t>
+          <t>Product Dimension (Inch)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Product Dimension (Inch)</t>
+          <t>Style</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Style</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Shipping Length (IN)</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Shipping Length (IN)</t>
+          <t>Shipping Width (IN)</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Shipping Width (IN)</t>
+          <t>Shipping Height (IN)</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Shipping Height (IN)</t>
+          <t>Volume (CUFT)</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Volume (CUFT)</t>
+          <t>Fixed tags</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Variable tags</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>White/Beige/Gray</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CM-OT2141T-7PC</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CM-OT2141T-7PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Dining Set</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dining Set</t>
+          <t>ALYCIA 7 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>ALYCIA 7 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Gather around ALYCIA 7 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White or Beige or Gray tones, the Aluminum, Polyester Canvas, Glass, build keeps the look polished and practical.
@@ -772,104 +777,114 @@
 Weight: 217.82 lbs</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ALYCIA 7 Pc. Patio Dining Set in White Beige Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ALYCIA 7 Pc. Patio Dining Set in White or Beige or Gray | GOODDEGG</t>
+          <t>The ALYCIA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>The ALYCIA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALYCIA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ALYCIA</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>7 Pc. Patio Dining Set</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>CM-OT2141T-1, CM-OT2141T-2, CM-OT2141AC-6PK</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>CM-OT2141T-1, CM-OT2141T-2, CM-OT2141AC-6PK</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
           <t>CM-OT2141-1.jpg,CM-OT2141T-WB-1.jpg,CM-OT2141SC-WB-1.jpg,CM-OT2141-3.jpg,CM-OT2141-4.jpg,CM-OT2141-5.jpg</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="P2" t="n">
         <v>849</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>849</v>
       </c>
+      <c r="R2" t="n">
+        <v>2247</v>
+      </c>
       <c r="S2" t="n">
-        <v>2247</v>
-      </c>
-      <c r="T2" t="n">
         <v>217.82</v>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Transitional</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Aluminum, Polyester Canvas, Glass, Others</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Aluminum, Polyester Canvas, Glass, Others</t>
+          <t>Transitional,White/Beige/Gray,Aluminum, Polyester Canvas, Glass, Others,Aluminum Construction,5mm Tempered Glass Table</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Transitional,White/Beige/Gray,Aluminum, Polyester Canvas, Glass, Others,Aluminum Construction,5mm Tempered Glass Table</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC2" t="n">
+      <c r="AB2" t="n">
         <v>34.9</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Outdoor, Dining Set, ALYCIA</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Gun Metal/Brown/Gray</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GM-1003-4PC</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GM-1003-4PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>ANTIGUA 4 Pc. Patio Set</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>ANTIGUA 4 Pc. Patio Set</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ANTIGUA 4 Pc. Patio Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Aluminum, Polyethylene Wicker, Polyspun and finished in Gun Metal or Brown or Gray tones for a clean, cohesive look.
@@ -890,109 +905,119 @@
 Weight: 174 lbs</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ANTIGUA 4 Pc. Patio Set in Gun Metal Brown Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ANTIGUA 4 Pc. Patio Set in Gun Metal or Brown or Gray | GOODDEGG</t>
+          <t>The ANTIGUA Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The ANTIGUA Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTIGUA</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ANTIGUA</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
           <t>4 Pc. Patio Set</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1003, GM-1004, GM-1005</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GM-1003, GM-1004, GM-1005</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
           <t>GM-1003-1-Z.jpg,GM-1003-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="P3" t="n">
         <v>1129</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="Q3" s="1" t="n">
         <v>1129</v>
       </c>
+      <c r="R3" t="n">
+        <v>2877</v>
+      </c>
       <c r="S3" t="n">
-        <v>2877</v>
-      </c>
-      <c r="T3" t="n">
         <v>174</v>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>63"L X 35 1/2"W X 17 3/4 - 27"H</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63"L X 35 1/2"W X 17 3/4 - 27"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Aluminum, Polyethylene Wicker, Polyspun</t>
+          <t>Contemporary,Gun Metal/Brown/Gray,Aluminum, Polyethylene Wicker, Polyspun,Adjustable backrest with gas springs,Ottoman as footrest or extra seats,Adjustable table height,Padded headrest cushion,Washable cushion covers,Table includes umbrella hole and cap</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Contemporary,Gun Metal/Brown/Gray,Aluminum, Polyethylene Wicker, Polyspun,Adjustable backrest with gas springs,Ottoman as footrest or extra seats,Adjustable table height,Padded headrest cushion,Washable cushion covers,Table includes umbrella hole and cap</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC3" t="n">
+      <c r="AB3" t="n">
         <v>60.7</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, ANTIGUA</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Gun Metal/Brown/Gray</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GM-1003-6PC</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GM-1003-6PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Polyethylene Wicker, Polyspun, then finished in Gun Metal or Brown or Gray tones to suit a range of interiors.
@@ -1014,109 +1039,119 @@
 Weight: 191.9 lbs</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans | GOODDEGG</t>
+          <t>The ANTIGUA Patio w/ Ottomans makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>The ANTIGUA Patio w/ Ottomans makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTIGUA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ANTIGUA</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
           <t>6 Pc. Patio Set w/ 2 Ottomans</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1003, GM-1004, GM-1005, GM-1006-2PK</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GM-1003, GM-1004, GM-1005, GM-1006-2PK</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
           <t>GM-1003-6PC.jpg,GM-1003-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="P4" t="n">
         <v>1299</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="Q4" s="1" t="n">
         <v>1299</v>
       </c>
+      <c r="R4" t="n">
+        <v>3297</v>
+      </c>
       <c r="S4" t="n">
-        <v>3297</v>
-      </c>
-      <c r="T4" t="n">
         <v>191.9</v>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>63"L X 35 1/2"W X 17 3/4 - 27"H</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>63"L X 35 1/2"W X 17 3/4 - 27"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Aluminum, Polyethylene Wicker, Polyspun</t>
+          <t>Contemporary,Gun Metal/Brown/Gray,Aluminum, Polyethylene Wicker, Polyspun,Adjustable backrest with gas springs,Ottoman as footrest or extra seats,Adjustable table height,Padded headrest cushion,Washable cushion covers,Table includes umbrella hole and cap</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Contemporary,Gun Metal/Brown/Gray,Aluminum, Polyethylene Wicker, Polyspun,Adjustable backrest with gas springs,Ottoman as footrest or extra seats,Adjustable table height,Padded headrest cushion,Washable cushion covers,Table includes umbrella hole and cap</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC4" t="n">
+      <c r="AB4" t="n">
         <v>71</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, ANTIGUA</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Black/Gray</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GM-2024-3PC</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GM-2024-3PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>AROSA 3 Pc. Fire Pit Counter Height Set</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>AROSA 3 Pc. Fire Pit Counter Height Set</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 AROSA 3 Pc. Fire Pit Counter Height Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Ceramic Tile, Polyrattan, Polyspun Fabric construction and Black or Gray tones, it blends durability with visual warmth.
@@ -1135,109 +1170,119 @@
 Weight: 154 lbs</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AROSA 3 Pc. Fire Pit Counter Height Set in Black Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AROSA 3 Pc. Fire Pit Counter Height Set in Black or Gray | GOODDEGG</t>
+          <t>AROSA Fire Pit Counter Height makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AROSA Fire Pit Counter Height makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AROSA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AROSA</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
           <t>3 Pc. Fire Pit Counter Height Set</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2024, GM-2025-2PK</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GM-2024, GM-2025-2PK</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
           <t>GM-2024-3PC.jpg,GM-2024-3PC-WB-1.jpg,GM-2024-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="P5" t="n">
         <v>649</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="Q5" s="1" t="n">
         <v>649</v>
       </c>
+      <c r="R5" t="n">
+        <v>1707</v>
+      </c>
       <c r="S5" t="n">
-        <v>1707</v>
-      </c>
-      <c r="T5" t="n">
         <v>154</v>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Table: 36.4"L X 36.4"W X 36.6"H, Chair: 25.1"W X 26.3"D X 44.8"H</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Table: 36.4"L X 36.4"W X 36.6"H, Chair: 25.1"W X 26.3"D X 44.8"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel, Ceramic Tile, Polyrattan, Polyspun Fabric</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Steel, Ceramic Tile, Polyrattan, Polyspun Fabric</t>
+          <t>Contemporary,Black/Gray,Steel, Ceramic Tile, Polyrattan, Polyspun Fabric,360-Degree Swivel Seats,Tile Top Firepit Tabletop,Mixed Material Construction,Powder Coated Steel Frame,Easy To Assemble</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Gray,Steel, Ceramic Tile, Polyrattan, Polyspun Fabric,360-Degree Swivel Seats,Tile Top Firepit Tabletop,Mixed Material Construction,Powder Coated Steel Frame,Easy To Assemble</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC5" t="n">
+      <c r="AB5" t="n">
         <v>20.3</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, AROSA</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GM-1045-6PC</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GM-1045-6PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>BARBUDA 6 Pc. Conversation Set w/ Fire Pit</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>BARBUDA 6 Pc. Conversation Set w/ Fire Pit</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 BARBUDA 6 Pc. Conversation Set w/ Fire Pit is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyrattan, Polyspun Fabric and finished in Gray tones for a clean, cohesive look.
@@ -1256,109 +1301,119 @@
 Weight: 322.87 lbs</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>BARBUDA 6 Pc. Conversation Set w/ Fire Pit in Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BARBUDA 6 Pc. Conversation Set w/ Fire Pit in Gray | GOODDEGG</t>
+          <t>BARBUDA Conversation w/ Fire Pit makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>BARBUDA Conversation w/ Fire Pit makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BARBUDA</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>BARBUDA</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
           <t>6 Pc. Conversation Set w/ Fire Pit</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1045, GM-1046-5PK</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GM-1045, GM-1046-5PK</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
           <t>GM-1045-6PC-1.jpg,GM-1045-6PC-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="P6" t="n">
         <v>1749</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>1749</v>
       </c>
+      <c r="R6" t="n">
+        <v>4497</v>
+      </c>
       <c r="S6" t="n">
-        <v>4497</v>
-      </c>
-      <c r="T6" t="n">
         <v>322.87</v>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Fire Pit Table: 39"DIA X 27"H, Semi-circle Sectional: 64"W X 29"D X 33.5"H, End Table: 21"W X 28.5"D X 24"H</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Fire Pit Table: 39"DIA X 27"H, Semi-circle Sectional: 64"W X 29"D X 33.5"H, End Table: 21"W X 28.5"D X 24"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel, Polyrattan, Polyspun Fabric</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Steel, Polyrattan, Polyspun Fabric</t>
+          <t>Contemporary,Gray,Steel, Polyrattan, Polyspun Fabric,Modular Design,Tile Top Firepit Tabletop,FSC Certified Teak Wood,Mixed Material Construction,Powder Coated Steel Frame,Washable Cushion Covers</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Contemporary,Gray,Steel, Polyrattan, Polyspun Fabric,Modular Design,Tile Top Firepit Tabletop,FSC Certified Teak Wood,Mixed Material Construction,Powder Coated Steel Frame,Washable Cushion Covers</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC6" t="n">
+      <c r="AB6" t="n">
         <v>64.5</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, BARBUDA</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Natural/Light Gray/Beige</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GM-2017-6PC</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GM-2017-6PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>BORDEAUX 6 Pc. Dining Set w/ Bench</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>BORDEAUX 6 Pc. Dining Set w/ Bench</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 BORDEAUX 6 Pc. Dining Set w/ Bench brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural or Light Gray or Beige tones, the Aluminum, Stainless Steel, Polyspun Fabric build keeps the look polished and practical.
@@ -1380,109 +1435,119 @@
 Weight: 307.89 lbs</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>BORDEAUX 6 Pc. Dining Set w/ Bench | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BORDEAUX 6 Pc. Dining Set w/ Bench | GOODDEGG</t>
+          <t>The BORDEAUX Dining w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>The BORDEAUX Dining w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORDEAUX</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BORDEAUX</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
           <t>6 Pc. Dining Set w/ Bench</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2017-1, GM-2017-2, GM-2020-2PK, GM-2021, GM-2019-2PK</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GM-2017-1, GM-2017-2, GM-2020-2PK, GM-2021, GM-2019-2PK</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
           <t>GM-2017-6PC.jpg,GM-2017-WB-1.jpg,GM-2017-2.jpg,GM-2017-3.jpg,GM-2017-2.jpg,GM-2017-3.jpg,GM-2017-4.jpg,GM-2017-5.jpg,GM-2017-6.jpg,GM-2017-7.jpg</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="P7" t="n">
         <v>2099</v>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="Q7" s="1" t="n">
         <v>2099</v>
       </c>
+      <c r="R7" t="n">
+        <v>5697</v>
+      </c>
       <c r="S7" t="n">
-        <v>5697</v>
-      </c>
-      <c r="T7" t="n">
         <v>307.89</v>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Table: 70.5"W X 38.5"D X 29"H, Chair: 20"W X 26.5"D X 32"H, Armless Chair: 20"W X 26.5"D X 32"H, Bench: 57"W X 16"D X 18.5"H</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Table: 70.5"W X 38.5"D X 29"H, Chair: 20"W X 26.5"D X 32"H, Armless Chair: 20"W X 26.5"D X 32"H, Bench: 57"W X 16"D X 18.5"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Stainless Steel, Polyspun Fabric</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Aluminum, Stainless Steel, Polyspun Fabric</t>
+          <t>Contemporary,Natural/Light Gray/Beige,Aluminum, Stainless Steel, Polyspun Fabric,Tabletop Fire Pit with Storage Cabinet,Heat Output: 55000BTU,Propane Tank Capacity: 20 Pound,Stainless Steel Ice Chest with Cover,Hand-brushed Wood Texture,Washable Cushion Cover,UV &amp; Water-Resistant</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Contemporary,Natural/Light Gray/Beige,Aluminum, Stainless Steel, Polyspun Fabric,Tabletop Fire Pit with Storage Cabinet,Heat Output: 55000BTU,Propane Tank Capacity: 20 Pound,Stainless Steel Ice Chest with Cover,Hand-brushed Wood Texture,Washable Cushion Cover,UV &amp; Water-Resistant</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC7" t="n">
+      <c r="AB7" t="n">
         <v>49.1</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, BORDEAUX</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Natural/Beige</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FM80016NT-3PC</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FM80016NT-3PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>JOHARI 3 Pc. Conversation Set</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>JOHARI 3 Pc. Conversation Set</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 JOHARI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural or Beige tones, the Steel, Fabric, Foam, PE Rattan build keeps the look polished and practical.
@@ -1501,109 +1566,119 @@
 Weight: 91.3 lbs</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>JOHARI 3 Pc. Conversation Set in Natural Beige | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JOHARI 3 Pc. Conversation Set in Natural or Beige | GOODDEGG</t>
+          <t>The JOHARI Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>The JOHARI Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOHARI</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>JOHARI</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
           <t>3 Pc. Conversation Set</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80016NT-CH, FM80016NT-T</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>FM80016NT-CH, FM80016NT-T</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
           <t>FM80016NT-3PC-1.jpg</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="P8" t="n">
         <v>389</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="Q8" s="1" t="n">
         <v>389</v>
       </c>
+      <c r="R8" t="n">
+        <v>897</v>
+      </c>
       <c r="S8" t="n">
-        <v>897</v>
-      </c>
-      <c r="T8" t="n">
         <v>91.3</v>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5")</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5")</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel, Fabric, Foam, PE Rattan</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Steel, Fabric, Foam, PE Rattan</t>
+          <t>Contemporary,Natural/Beige,Steel, Fabric, Foam, PE Rattan,Powder Coated Steel Frame,10mm Round Wicker,Seat Cushion,Pillow Back w/ 100% Fiber Fill,Weather Resistant</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Contemporary,Natural/Beige,Steel, Fabric, Foam, PE Rattan,Powder Coated Steel Frame,10mm Round Wicker,Seat Cushion,Pillow Back w/ 100% Fiber Fill,Weather Resistant</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC8" t="n">
+      <c r="AB8" t="n">
         <v>19.4</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, JOHARI</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Natural/Beige</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FM80016NT-4PC-BN</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FM80016NT-4PC-BN</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>JOHARI 4 Pc. Conversation Set</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
-        <is>
-          <t>JOHARI 4 Pc. Conversation Set</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 JOHARI 4 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel, Fabric, Foam, PE Rattan and finished in Natural or Beige tones for a clean, cohesive look.
@@ -1623,111 +1698,120 @@
 Weight: 144.1 lbs</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>JOHARI 4 Pc. Conversation Set in Natural Beige | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JOHARI 4 Pc. Conversation Set in Natural or Beige | GOODDEGG</t>
+          <t>The JOHARI Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>The JOHARI Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOHARI</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>JOHARI</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
           <t>4 Pc. Conversation Set</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80016NT-CH, FM80016NT-BN, FM80016NT-T</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>FM80016NT-CH, FM80016NT-BN, FM80016NT-T</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
           <t>FM80016NT-4PC-BN-1.jpg</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="P9" t="n">
         <v>669</v>
       </c>
-      <c r="R9" s="1" t="n">
+      <c r="Q9" s="1" t="n">
         <v>669</v>
       </c>
+      <c r="R9" t="n">
+        <v>1587</v>
+      </c>
       <c r="S9" t="n">
-        <v>1587</v>
-      </c>
-      <c r="T9" t="n">
         <v>144.1</v>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5"), BENCH: 58"W X 29"D X 25.5"H (SEAT HT: 16.5")</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5"), BENCH: 58"W X 29"D X 25.5"H (SEAT HT: 16.5")</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel, Fabric, Foam, PE Rattan</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Steel, Fabric, Foam, PE Rattan</t>
+          <t>Contemporary,Natural/Beige,Steel, Fabric, Foam, PE Rattan,Powder Coated Steel Frame,10mm Round Wicker,Seat Cushion,Pillow Back w/ 100% Fiber Fill,Weather Resistant</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Contemporary,Natural/Beige,Steel, Fabric, Foam, PE Rattan,Powder Coated Steel Frame,10mm Round Wicker,Seat Cushion,Pillow Back w/ 100% Fiber Fill,Weather Resistant</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC9" t="n">
+      <c r="AB9" t="n">
         <v>38.1</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, JOHARI</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>FM80001BB-SET</t>
+        </is>
+      </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>FM80001BB-SET</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>KIMARA 3 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>KIMARA 3 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KIMARA 3 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and finished in Black tones for a clean, cohesive look.
@@ -1741,115 +1825,124 @@
 Weight: 149.1 lbs</t>
         </is>
       </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>KIMARA 3 Pc. Patio Dining Set in Black | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>KIMARA 3 Pc. Patio Dining Set in Black | GOODDEGG</t>
+          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J10" s="18" t="inlineStr">
         <is>
-          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMARA</t>
         </is>
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
-          <t>KIMARA</t>
-        </is>
-      </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
           <t>3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M10" s="18" t="n"/>
+      <c r="L10" s="18" t="n"/>
+      <c r="M10" s="18" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N10" s="18" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80001BB-1, FM80001BB-2, FM80001BB-T</t>
         </is>
       </c>
       <c r="O10" s="18" t="inlineStr">
         <is>
-          <t>FM80001BB-1, FM80001BB-2, FM80001BB-T</t>
-        </is>
-      </c>
-      <c r="P10" s="18" t="inlineStr">
-        <is>
           <t>FM80001BB-SET-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q10" s="18" t="n">
+      <c r="P10" s="18" t="n">
         <v>419</v>
       </c>
-      <c r="R10" s="19" t="n">
+      <c r="Q10" s="19" t="n">
         <v>419</v>
       </c>
+      <c r="R10" s="18" t="n">
+        <v>957</v>
+      </c>
       <c r="S10" s="18" t="n">
-        <v>957</v>
-      </c>
-      <c r="T10" s="18" t="n">
         <v>149.1</v>
       </c>
+      <c r="T10" s="18" t="inlineStr">
+        <is>
+          <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H</t>
+        </is>
+      </c>
       <c r="U10" s="18" t="inlineStr">
         <is>
-          <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V10" s="18" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
       <c r="W10" s="18" t="inlineStr">
         <is>
-          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
+          <t>Contemporary,Black,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
       <c r="X10" s="18" t="inlineStr">
         <is>
-          <t>Contemporary,Black,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
-        </is>
-      </c>
-      <c r="Y10" s="18" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y10" s="18" t="n"/>
       <c r="Z10" s="18" t="n"/>
       <c r="AA10" s="18" t="n"/>
-      <c r="AB10" s="18" t="n"/>
-      <c r="AC10" s="18" t="n">
+      <c r="AB10" s="18" t="n">
         <v>26.9</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, KIMARA</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>FM80001GG-SET</t>
+        </is>
+      </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>FM80001GG-SET</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>KIMARA 3 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>KIMARA 3 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KIMARA 3 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, then finished in Gray tones to suit a range of interiors.
@@ -1863,115 +1956,124 @@
 Weight: 150.7 lbs</t>
         </is>
       </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>KIMARA 3 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>KIMARA 3 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
-          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMARA</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
         <is>
-          <t>KIMARA</t>
-        </is>
-      </c>
-      <c r="L11" s="18" t="inlineStr">
-        <is>
           <t>3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M11" s="18" t="n"/>
+      <c r="L11" s="18" t="n"/>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N11" s="18" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80001GG-T, FM80001GG-1, FM80001GG-2</t>
         </is>
       </c>
       <c r="O11" s="18" t="inlineStr">
         <is>
-          <t>FM80001GG-T, FM80001GG-1, FM80001GG-2</t>
-        </is>
-      </c>
-      <c r="P11" s="18" t="inlineStr">
-        <is>
           <t>FM80001GG-SET-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q11" s="18" t="n">
+      <c r="P11" s="18" t="n">
         <v>399</v>
       </c>
-      <c r="R11" s="19" t="n">
+      <c r="Q11" s="19" t="n">
         <v>399</v>
       </c>
+      <c r="R11" s="18" t="n">
+        <v>957</v>
+      </c>
       <c r="S11" s="18" t="n">
-        <v>957</v>
-      </c>
-      <c r="T11" s="18" t="n">
         <v>150.7</v>
       </c>
+      <c r="T11" s="18" t="inlineStr">
+        <is>
+          <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H</t>
+        </is>
+      </c>
       <c r="U11" s="18" t="inlineStr">
         <is>
-          <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V11" s="18" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
       <c r="W11" s="18" t="inlineStr">
         <is>
-          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
+          <t>Contemporary,Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
       <c r="X11" s="18" t="inlineStr">
         <is>
-          <t>Contemporary,Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
-        </is>
-      </c>
-      <c r="Y11" s="18" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y11" s="18" t="n"/>
       <c r="Z11" s="18" t="n"/>
       <c r="AA11" s="18" t="n"/>
-      <c r="AB11" s="18" t="n"/>
-      <c r="AC11" s="18" t="n">
+      <c r="AB11" s="18" t="n">
         <v>28.1</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, KIMARA</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n"/>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>FM80001BB-SET+2CH</t>
+        </is>
+      </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>FM80001BB-SET+2CH</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>KIMARA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>KIMARA 5 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KIMARA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam construction and Black tones, it blends durability with visual warmth.
@@ -1986,115 +2088,124 @@
 Weight: 175 lbs</t>
         </is>
       </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>KIMARA 5 Pc. Patio Dining Set in Black | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>KIMARA 5 Pc. Patio Dining Set in Black | GOODDEGG</t>
+          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMARA</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
         <is>
-          <t>KIMARA</t>
-        </is>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M12" s="20" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80001BB-T, FM80001BB-1, FM80001BB-2, FM80002BB-CH-2PK</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr">
         <is>
-          <t>FM80001BB-T, FM80001BB-1, FM80001BB-2, FM80002BB-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P12" s="20" t="inlineStr">
-        <is>
           <t>FM80001BB-SET+2CH-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q12" s="20" t="n">
+      <c r="P12" s="20" t="n">
         <v>559</v>
       </c>
-      <c r="R12" s="21" t="n">
+      <c r="Q12" s="21" t="n">
         <v>559</v>
       </c>
+      <c r="R12" s="20" t="n">
+        <v>1287</v>
+      </c>
       <c r="S12" s="20" t="n">
-        <v>1287</v>
-      </c>
-      <c r="T12" s="20" t="n">
         <v>175</v>
       </c>
+      <c r="T12" s="20" t="inlineStr">
+        <is>
+          <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 25"W X 23"D X 30.5"H</t>
+        </is>
+      </c>
       <c r="U12" s="20" t="inlineStr">
         <is>
-          <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 25"W X 23"D X 30.5"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V12" s="20" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
       <c r="W12" s="20" t="inlineStr">
         <is>
-          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
+          <t>Contemporary,Black,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
       <c r="X12" s="20" t="inlineStr">
         <is>
-          <t>Contemporary,Black,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
-        </is>
-      </c>
-      <c r="Y12" s="20" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y12" s="20" t="n"/>
       <c r="Z12" s="20" t="n"/>
       <c r="AA12" s="20" t="n"/>
-      <c r="AB12" s="20" t="n"/>
-      <c r="AC12" s="20" t="n">
+      <c r="AB12" s="20" t="n">
         <v>34.1</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, KIMARA</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n"/>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n"/>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>FM80001GG-SET+2CH</t>
+        </is>
+      </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>FM80001GG-SET+2CH</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>KIMARA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
-        <is>
-          <t>KIMARA 5 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KIMARA 5 Pc. Patio Dining Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Gray tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam build keeps the look polished and practical.
@@ -2109,115 +2220,124 @@
 Weight: 174.9 lbs</t>
         </is>
       </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>KIMARA 5 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>KIMARA 5 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMARA</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
         <is>
-          <t>KIMARA</t>
-        </is>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
-        <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M13" s="20" t="n"/>
+      <c r="L13" s="20" t="n"/>
+      <c r="M13" s="20" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80001GG-T, FM80001GG-1, FM80001GG-2, FM80006GY-CH-2PK</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
         <is>
-          <t>FM80001GG-T, FM80001GG-1, FM80001GG-2, FM80006GY-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P13" s="20" t="inlineStr">
-        <is>
           <t>FM80001GG-SET+2CH-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q13" s="20" t="n">
+      <c r="P13" s="20" t="n">
         <v>529</v>
       </c>
-      <c r="R13" s="21" t="n">
+      <c r="Q13" s="21" t="n">
         <v>529</v>
       </c>
+      <c r="R13" s="20" t="n">
+        <v>1257</v>
+      </c>
       <c r="S13" s="20" t="n">
-        <v>1257</v>
-      </c>
-      <c r="T13" s="20" t="n">
         <v>174.9</v>
       </c>
+      <c r="T13" s="20" t="inlineStr">
+        <is>
+          <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 22.5"W X 23.5"D X 35"H</t>
+        </is>
+      </c>
       <c r="U13" s="20" t="inlineStr">
         <is>
-          <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 22.5"W X 23.5"D X 35"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V13" s="20" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
       <c r="W13" s="20" t="inlineStr">
         <is>
-          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
+          <t>Contemporary,Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
       <c r="X13" s="20" t="inlineStr">
         <is>
-          <t>Contemporary,Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
-        </is>
-      </c>
-      <c r="Y13" s="20" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y13" s="20" t="n"/>
       <c r="Z13" s="20" t="n"/>
       <c r="AA13" s="20" t="n"/>
-      <c r="AB13" s="20" t="n"/>
-      <c r="AC13" s="20" t="n">
+      <c r="AB13" s="20" t="n">
         <v>45.6</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, KIMARA</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Beige/Natural</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n"/>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>GM-1022BG-4PC</t>
+        </is>
+      </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>GM-1022BG-4PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>KYUSHU 4 Pc. Patio Set</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
-        <is>
-          <t>KYUSHU 4 Pc. Patio Set</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KYUSHU 4 Pc. Patio Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Acacia Wood, Polyester construction and Beige or Natural tones, it blends durability with visual warmth.
@@ -2236,115 +2356,124 @@
 Weight: 125.04 lbs</t>
         </is>
       </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>KYUSHU 4 Pc. Patio Set in Beige Natural | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>KYUSHU 4 Pc. Patio Set in Beige or Natural | GOODDEGG</t>
+          <t>The KYUSHU Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
         <is>
-          <t>The KYUSHU Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KYUSHU</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
         <is>
-          <t>KYUSHU</t>
-        </is>
-      </c>
-      <c r="L14" s="22" t="inlineStr">
-        <is>
           <t>4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="M14" s="22" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N14" s="22" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1022BG-2PK, GM-1023BG-2PK</t>
         </is>
       </c>
       <c r="O14" s="22" t="inlineStr">
         <is>
-          <t>GM-1022BG-2PK, GM-1023BG-2PK</t>
-        </is>
-      </c>
-      <c r="P14" s="22" t="inlineStr">
-        <is>
           <t>GM-1022BG-1.jpg,GM-1022BG-2.jpg</t>
         </is>
       </c>
-      <c r="Q14" s="22" t="n">
+      <c r="P14" s="22" t="n">
         <v>319</v>
       </c>
-      <c r="R14" s="23" t="n">
+      <c r="Q14" s="23" t="n">
         <v>319</v>
       </c>
+      <c r="R14" s="22" t="n">
+        <v>807</v>
+      </c>
       <c r="S14" s="22" t="n">
-        <v>807</v>
-      </c>
-      <c r="T14" s="22" t="n">
         <v>125.04</v>
       </c>
+      <c r="T14" s="22" t="inlineStr">
+        <is>
+          <t>LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H</t>
+        </is>
+      </c>
       <c r="U14" s="22" t="inlineStr">
         <is>
-          <t>LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H</t>
+          <t>Rustic</t>
         </is>
       </c>
       <c r="V14" s="22" t="inlineStr">
         <is>
-          <t>Rustic</t>
+          <t>Acacia Wood, Polyester</t>
         </is>
       </c>
       <c r="W14" s="22" t="inlineStr">
         <is>
-          <t>Acacia Wood, Polyester</t>
+          <t>Rustic,Beige/Natural,Acacia Wood, Polyester,Weather-resistant,Natural acacia wood,Includes tie-back cushions,Easy to assemble with included hardware kit</t>
         </is>
       </c>
       <c r="X14" s="22" t="inlineStr">
         <is>
-          <t>Rustic,Beige/Natural,Acacia Wood, Polyester,Weather-resistant,Natural acacia wood,Includes tie-back cushions,Easy to assemble with included hardware kit</t>
-        </is>
-      </c>
-      <c r="Y14" s="22" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y14" s="22" t="n"/>
       <c r="Z14" s="22" t="n"/>
       <c r="AA14" s="22" t="n"/>
-      <c r="AB14" s="22" t="n"/>
-      <c r="AC14" s="22" t="n">
+      <c r="AB14" s="22" t="n">
         <v>15.1</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, KYUSHU</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Black/Natural</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n"/>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>GM-1022BK-4PC</t>
+        </is>
+      </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>GM-1022BK-4PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>KYUSHU 4 Pc. Patio Set</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
-        <is>
-          <t>KYUSHU 4 Pc. Patio Set</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 KYUSHU 4 Pc. Patio Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Black or Natural tones, the Acacia Wood, Polyester build keeps the look polished and practical.
@@ -2363,113 +2492,123 @@
 Weight: 125.04 lbs</t>
         </is>
       </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>KYUSHU 4 Pc. Patio Set in Black Natural | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t>KYUSHU 4 Pc. Patio Set in Black or Natural | GOODDEGG</t>
+          <t>The KYUSHU Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
         <is>
-          <t>The KYUSHU Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KYUSHU</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
         <is>
-          <t>KYUSHU</t>
-        </is>
-      </c>
-      <c r="L15" s="22" t="inlineStr">
-        <is>
           <t>4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="M15" s="22" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N15" s="22" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1022BK-2PK, GM-1023BK-2PK</t>
         </is>
       </c>
       <c r="O15" s="22" t="inlineStr">
         <is>
-          <t>GM-1022BK-2PK, GM-1023BK-2PK</t>
-        </is>
-      </c>
-      <c r="P15" s="22" t="inlineStr">
-        <is>
           <t>GM-1022BK-1.jpg,GM-1022BK-2.jpg</t>
         </is>
       </c>
-      <c r="Q15" s="22" t="n">
+      <c r="P15" s="22" t="n">
         <v>319</v>
       </c>
-      <c r="R15" s="23" t="n">
+      <c r="Q15" s="23" t="n">
         <v>319</v>
       </c>
+      <c r="R15" s="22" t="n">
+        <v>807</v>
+      </c>
       <c r="S15" s="22" t="n">
-        <v>807</v>
-      </c>
-      <c r="T15" s="22" t="n">
         <v>125.04</v>
       </c>
+      <c r="T15" s="22" t="inlineStr">
+        <is>
+          <t>LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H</t>
+        </is>
+      </c>
       <c r="U15" s="22" t="inlineStr">
         <is>
-          <t>LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H</t>
+          <t>Rustic</t>
         </is>
       </c>
       <c r="V15" s="22" t="inlineStr">
         <is>
-          <t>Rustic</t>
+          <t>Acacia Wood, Polyester</t>
         </is>
       </c>
       <c r="W15" s="22" t="inlineStr">
         <is>
-          <t>Acacia Wood, Polyester</t>
+          <t>Rustic,Black/Natural,Acacia Wood, Polyester,Weather-resistant,Natural acacia wood,Includes tie-back cushions,Easy to assemble with included hardware kit</t>
         </is>
       </c>
       <c r="X15" s="22" t="inlineStr">
         <is>
-          <t>Rustic,Black/Natural,Acacia Wood, Polyester,Weather-resistant,Natural acacia wood,Includes tie-back cushions,Easy to assemble with included hardware kit</t>
-        </is>
-      </c>
-      <c r="Y15" s="22" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y15" s="22" t="n"/>
       <c r="Z15" s="22" t="n"/>
       <c r="AA15" s="22" t="n"/>
-      <c r="AB15" s="22" t="n"/>
-      <c r="AC15" s="22" t="n">
+      <c r="AB15" s="22" t="n">
         <v>15.1</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, KYUSHU</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Black/Light Brown</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GM-1049BK-5PC</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GM-1049BK-5PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>LOTUS 5 Pc. Conversation Set</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
-        <is>
-          <t>LOTUS 5 Pc. Conversation Set</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 LOTUS 5 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black or Light Brown tones, the Aluminum, Fabric, Ceramic build keeps the look polished and practical.
@@ -2488,109 +2627,119 @@
 Weight: 96.8 lbs</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>LOTUS 5 Pc. Conversation Set in Black Light Brown | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LOTUS 5 Pc. Conversation Set in Black or Light Brown | GOODDEGG</t>
+          <t>The LOTUS Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>The LOTUS Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOTUS</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LOTUS</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
           <t>5 Pc. Conversation Set</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1049BK-2PK, GM-1024BK-3PK</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>GM-1049BK-2PK, GM-1024BK-3PK</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
           <t>GM-1049-5PC-1.jpg,GM-1049-5PC-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="P16" t="n">
         <v>1099</v>
       </c>
-      <c r="R16" s="1" t="n">
+      <c r="Q16" s="1" t="n">
         <v>1099</v>
       </c>
+      <c r="R16" t="n">
+        <v>2817</v>
+      </c>
       <c r="S16" t="n">
-        <v>2817</v>
-      </c>
-      <c r="T16" t="n">
         <v>96.8</v>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Sofa: 74 1/4"W X 29 1/2"D X 34"H, Coffee Table: 47 1/4"L X 25 1/2"W X 15 1/2"H, Chair: 28 1/4"W X 26 1/2"D X 37"H</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Sofa: 74 1/4"W X 29 1/2"D X 34"H, Coffee Table: 47 1/4"L X 25 1/2"W X 15 1/2"H, Chair: 28 1/4"W X 26 1/2"D X 37"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Fabric, Ceramic</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Aluminum, Fabric, Ceramic</t>
+          <t>Contemporary,Black/Light Brown,Aluminum, Fabric, Ceramic,Washable Cushion Covers,Open Storage Shelf,Slatted Tabletop Design,Durable Aluminum Frame,Ceramic Tabletop on End Table</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Light Brown,Aluminum, Fabric, Ceramic,Washable Cushion Covers,Open Storage Shelf,Slatted Tabletop Design,Durable Aluminum Frame,Ceramic Tabletop on End Table</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC16" t="n">
+      <c r="AB16" t="n">
         <v>54.3</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, LOTUS</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Black/Natural/Brown</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GM-2018-5PC-19</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GM-2018-5PC-19</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>LYON 5 Pc. Game Table Set w/ 4 Arm Chairs</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
-        <is>
-          <t>LYON 5 Pc. Game Table Set w/ 4 Arm Chairs</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 LYON 5 Pc. Game Table Set w/ 4 Arm Chairs brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black or Natural or Brown tones, the Aluminum, Outdoor Fabric build keeps the look polished and practical.
@@ -2608,109 +2757,119 @@
 Weight: 184.85 lbs</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>LYON 5 Pc. Game Table Set w/ 4 Arm Chairs | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LYON 5 Pc. Game Table Set w/ 4 Arm Chairs | GOODDEGG</t>
+          <t>LYON Game Table w/ Arm Chairs makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>LYON Game Table w/ Arm Chairs makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYON</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LYON</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
           <t>5 Pc. Game Table Set w/ 4 Arm Chairs</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2018, GM-2019-2PK</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GM-2018, GM-2019-2PK</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
           <t>GM-2018-5PC-19-1.jpg,GM-2018-WB-3.jpg,GM-2018-WB-2.jpg,GM-2018-WB-1.jpg,GM-2018-WB-4.jpg</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="P17" t="n">
         <v>1209</v>
       </c>
-      <c r="R17" s="1" t="n">
+      <c r="Q17" s="1" t="n">
         <v>1209</v>
       </c>
+      <c r="R17" t="n">
+        <v>3357</v>
+      </c>
       <c r="S17" t="n">
-        <v>3357</v>
-      </c>
-      <c r="T17" t="n">
         <v>184.85</v>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Table: 50.5" DIA X 29.5"H, Arm Chair: 20"W X 26.5"D X 32.25"H</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Table: 50.5" DIA X 29.5"H, Arm Chair: 20"W X 26.5"D X 32.25"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Outdoor Fabric</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Aluminum, Outdoor Fabric</t>
+          <t>Contemporary,Black/Natural/Brown,Aluminum, Outdoor Fabric,Inlaid Chess Board,Teak Poker Race Track Table,UV &amp; Rain-Resistant,FSC Certified Teak Wood</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Natural/Brown,Aluminum, Outdoor Fabric,Inlaid Chess Board,Teak Poker Race Track Table,UV &amp; Rain-Resistant,FSC Certified Teak Wood</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC17" t="n">
+      <c r="AB17" t="n">
         <v>24.9</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, LYON</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Black/Natural/Brown</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GM-2018-5PC-20</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GM-2018-5PC-20</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>LYON 5 Pc. Game Table Set w/ 4 Armless Chairs</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
-        <is>
-          <t>LYON 5 Pc. Game Table Set w/ 4 Armless Chairs</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 LYON 5 Pc. Game Table Set w/ 4 Armless Chairs is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, Outdoor Fabric and finished in Black or Natural or Brown tones for a clean, cohesive look.
@@ -2728,109 +2887,119 @@
 Weight: 175.17 lbs</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LYON 5 Pc. Game Table Set w/ 4 Armless Chairs | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LYON 5 Pc. Game Table Set w/ 4 Armless Chairs | GOODDEGG</t>
+          <t>LYON Game Table w/ Armless Chairs makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>LYON Game Table w/ Armless Chairs makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYON</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LYON</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
           <t>5 Pc. Game Table Set w/ 4 Armless Chairs</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2018, GM-2020-2PK</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GM-2018, GM-2020-2PK</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
           <t>GM-2018-5PC-20-WB-1.jpg,GM-2018-WB-3.jpg,GM-2018-WB-2.jpg,GM-2018-WB-1.jpg,GM-2018-WB-4.jpg</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="P18" t="n">
         <v>1149</v>
       </c>
-      <c r="R18" s="1" t="n">
+      <c r="Q18" s="1" t="n">
         <v>1149</v>
       </c>
+      <c r="R18" t="n">
+        <v>3177</v>
+      </c>
       <c r="S18" t="n">
-        <v>3177</v>
-      </c>
-      <c r="T18" t="n">
         <v>175.17</v>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Table: 50.5" DIA X 29.5"H</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Table: 50.5" DIA X 29.5"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Outdoor Fabric</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Aluminum, Outdoor Fabric</t>
+          <t>Contemporary,Black/Natural/Brown,Aluminum, Outdoor Fabric,Inlaid Chess Board,Teak Poker Race Track Table,UV &amp; Rain-Resistant,FSC Certified Teak Wood</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Natural/Brown,Aluminum, Outdoor Fabric,Inlaid Chess Board,Teak Poker Race Track Table,UV &amp; Rain-Resistant,FSC Certified Teak Wood</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC18" t="n">
+      <c r="AB18" t="n">
         <v>23.1</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, LYON</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Black/Natural/Brown</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GM-2018-5PC-05</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GM-2018-5PC-05</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
-        <is>
-          <t>LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Aluminum, Outdoor Fabric, then finished in Black or Natural or Brown tones to suit a range of interiors.
@@ -2848,109 +3017,119 @@
 Weight: 105.33 lbs</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs | GOODDEGG</t>
+          <t>LYON Game Table w/ Stacking Chairs makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>LYON Game Table w/ Stacking Chairs makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYON</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LYON</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
           <t>5 Pc. Game Table Set w/ 4 Stacking Chairs</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2018, GM-2005</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GM-2018, GM-2005</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
           <t>GM-2018-5PC-05-1.jpg,GM-2018-WB-3.jpg,GM-2018-WB-2.jpg,GM-2018-WB-1.jpg,GM-2018-WB-4.jpg</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="P19" t="n">
         <v>949</v>
       </c>
-      <c r="R19" s="1" t="n">
+      <c r="Q19" s="1" t="n">
         <v>949</v>
       </c>
+      <c r="R19" t="n">
+        <v>2397</v>
+      </c>
       <c r="S19" t="n">
-        <v>2397</v>
-      </c>
-      <c r="T19" t="n">
         <v>105.33</v>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Table: 50.5" DIA X 29.5"H</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Table: 50.5" DIA X 29.5"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Outdoor Fabric</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Aluminum, Outdoor Fabric</t>
+          <t>Contemporary,Black/Natural/Brown,Aluminum, Outdoor Fabric,Inlaid Chess Board,Teak Poker Race Track Table,UV &amp; Rain-Resistant,FSC Certified Teak Wood</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Natural/Brown,Aluminum, Outdoor Fabric,Inlaid Chess Board,Teak Poker Race Track Table,UV &amp; Rain-Resistant,FSC Certified Teak Wood</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC19" t="n">
+      <c r="AB19" t="n">
         <v>54.9</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, LYON</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Gun Metal/Gray</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GM-2027-7PC</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GM-2027-7PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>MONZA 7 Pc. Dining Table Set</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
-        <is>
-          <t>MONZA 7 Pc. Dining Table Set</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MONZA 7 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Tempered Glass, Textilene, then finished in Gun Metal or Gray tones to suit a range of interiors.
@@ -2965,106 +3144,116 @@
 Color: Gun Metal or Gray</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>MONZA 7 Pc. Dining Table Set in Gun Metal Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MONZA 7 Pc. Dining Table Set in Gun Metal or Gray | GOODDEGG</t>
+          <t>The MONZA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>The MONZA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONZA</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>MONZA</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
           <t>7 Pc. Dining Table Set</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2027, GM-2028-2PK</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GM-2027, GM-2028-2PK</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
           <t>GM-2027-7PC-1.jpg,GM-2027-2.jpg,GM-2028-2PK-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="P20" t="n">
         <v>759</v>
       </c>
-      <c r="R20" s="1" t="n">
+      <c r="Q20" s="1" t="n">
         <v>759</v>
       </c>
-      <c r="S20" t="n">
+      <c r="R20" t="n">
         <v>1977</v>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Table: 63" (EXTENDED: 94 1/2") L X 35 1/2"W X 29 1/2"H</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Table: 63" (EXTENDED: 94 1/2") L X 35 1/2"W X 29 1/2"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Tempered Glass, Textilene</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Aluminum, Tempered Glass, Textilene</t>
+          <t>Contemporary,Gun Metal/Gray,Aluminum, Tempered Glass, Textilene,Extendable Top,5-way Adjustable Seat Back</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Contemporary,Gun Metal/Gray,Aluminum, Tempered Glass, Textilene,Extendable Top,5-way Adjustable Seat Back</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC20" t="n">
+      <c r="AB20" t="n">
         <v>20.7</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, MONZA</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FM80004NT-3PC-05NT</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FM80004NT-3PC-05NT</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>NIAMBI 3 Pc. Patio Bistro Set</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
-        <is>
-          <t>NIAMBI 3 Pc. Patio Bistro Set</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 NIAMBI 3 Pc. Patio Bistro Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber construction and Natural tones, it blends durability with visual warmth.
@@ -3079,109 +3268,119 @@
 Weight: 50.2 lbs</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NIAMBI 3 Pc. Patio Bistro Set in Natural | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NIAMBI 3 Pc. Patio Bistro Set in Natural | GOODDEGG</t>
+          <t>The NIAMBI Patio Bistro makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>The NIAMBI Patio Bistro makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIAMBI</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>NIAMBI</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
           <t>3 Pc. Patio Bistro Set</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80004NT-T-1, FM80004NT-T-2, FM80005NT-CH-2PK</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>FM80004NT-T-1, FM80004NT-T-2, FM80005NT-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
           <t>FM80004NT-3PC-05NT-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="P21" t="n">
         <v>169</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>169</v>
       </c>
+      <c r="R21" t="n">
+        <v>357</v>
+      </c>
       <c r="S21" t="n">
-        <v>357</v>
-      </c>
-      <c r="T21" t="n">
         <v>50.2</v>
       </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Table: 26.6" x 23.6" x 29.1"H, Chair: 21.3" x 25.2" x 34.3"H</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Table: 26.6" x 23.6" x 29.1"H, Chair: 21.3" x 25.2" x 34.3"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
+          <t>Contemporary,Natural,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Contemporary,Natural,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC21" t="n">
+      <c r="AB21" t="n">
         <v>21.5</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, NIAMBI</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FM80004GY-3PC-06GY</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FM80004GY-3PC-06GY</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>NIAMBI 3 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
-        <is>
-          <t>NIAMBI 3 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 NIAMBI 3 Pc. Patio Dining Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber build keeps the look polished and practical.
@@ -3196,111 +3395,120 @@
 Weight: 58 lbs</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NIAMBI 3 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NIAMBI 3 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+          <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIAMBI</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>NIAMBI</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
           <t>3 Pc. Patio Dining Set</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80004GY-T-1, FM80004GY-T-2, FM80006GY-CH-2PK</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>FM80004GY-T-1, FM80004GY-T-2, FM80006GY-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
           <t>FM80004GY-3PC-06GY-1-Z.jpg,FM80006GY-CH-1.jpg</t>
         </is>
       </c>
-      <c r="Q22" t="n">
+      <c r="P22" t="n">
         <v>249</v>
       </c>
-      <c r="R22" s="1" t="n">
+      <c r="Q22" s="1" t="n">
         <v>249</v>
       </c>
+      <c r="R22" t="n">
+        <v>507</v>
+      </c>
       <c r="S22" t="n">
-        <v>507</v>
-      </c>
-      <c r="T22" t="n">
         <v>58</v>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 22.5"W X 23.5"D X 35"H</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 22.5"W X 23.5"D X 35"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
+          <t>Contemporary,Gray,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Contemporary,Gray,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC22" t="n">
+      <c r="AB22" t="n">
         <v>19.6</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, NIAMBI</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="n"/>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="C23" s="24" t="n"/>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>FM80004GY-5PC-06GY</t>
+        </is>
+      </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>FM80004GY-5PC-06GY</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>NIAMBI 5 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
-        <is>
-          <t>NIAMBI 5 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 NIAMBI 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber and finished in Gray tones for a clean, cohesive look.
@@ -3315,115 +3523,124 @@
 Weight: 82.2 lbs</t>
         </is>
       </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>NIAMBI 5 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>NIAMBI 5 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+          <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
-          <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIAMBI</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr">
         <is>
-          <t>NIAMBI</t>
-        </is>
-      </c>
-      <c r="L23" s="24" t="inlineStr">
-        <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M23" s="24" t="n"/>
+      <c r="L23" s="24" t="n"/>
+      <c r="M23" s="24" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N23" s="24" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80004GY-T-1, FM80004GY-T-2, FM80006GY-CH-2PK</t>
         </is>
       </c>
       <c r="O23" s="24" t="inlineStr">
         <is>
-          <t>FM80004GY-T-1, FM80004GY-T-2, FM80006GY-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P23" s="24" t="inlineStr">
-        <is>
           <t>FM80004GY-5PC-06GY-1-Z.jpg,FM80006GY-CH-1.jpg</t>
         </is>
       </c>
-      <c r="Q23" s="24" t="n">
+      <c r="P23" s="24" t="n">
         <v>379</v>
       </c>
-      <c r="R23" s="25" t="n">
+      <c r="Q23" s="25" t="n">
         <v>379</v>
       </c>
+      <c r="R23" s="24" t="n">
+        <v>837</v>
+      </c>
       <c r="S23" s="24" t="n">
-        <v>837</v>
-      </c>
-      <c r="T23" s="24" t="n">
         <v>82.2</v>
       </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 22.5"W X 23.5"D X 35"H</t>
+        </is>
+      </c>
       <c r="U23" s="24" t="inlineStr">
         <is>
-          <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 22.5"W X 23.5"D X 35"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V23" s="24" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
         </is>
       </c>
       <c r="W23" s="24" t="inlineStr">
         <is>
-          <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
+          <t>Contemporary,Gray,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
         </is>
       </c>
       <c r="X23" s="24" t="inlineStr">
         <is>
-          <t>Contemporary,Gray,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
-        </is>
-      </c>
-      <c r="Y23" s="24" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y23" s="24" t="n"/>
       <c r="Z23" s="24" t="n"/>
       <c r="AA23" s="24" t="n"/>
-      <c r="AB23" s="24" t="n"/>
-      <c r="AC23" s="24" t="n">
+      <c r="AB23" s="24" t="n">
         <v>37.1</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, NIAMBI</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="n"/>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="C24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>FM80004NT-5PC-05NT</t>
+        </is>
+      </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>FM80004NT-5PC-05NT</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>NIAMBI 5 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
-        <is>
-          <t>NIAMBI 5 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 NIAMBI 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber, then finished in Natural tones to suit a range of interiors.
@@ -3438,113 +3655,123 @@
 Weight: 66.6 lbs</t>
         </is>
       </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>NIAMBI 5 Pc. Patio Dining Set in Natural | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I24" s="24" t="inlineStr">
         <is>
-          <t>NIAMBI 5 Pc. Patio Dining Set in Natural | GOODDEGG</t>
+          <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J24" s="24" t="inlineStr">
         <is>
-          <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIAMBI</t>
         </is>
       </c>
       <c r="K24" s="24" t="inlineStr">
         <is>
-          <t>NIAMBI</t>
-        </is>
-      </c>
-      <c r="L24" s="24" t="inlineStr">
-        <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M24" s="24" t="n"/>
+      <c r="L24" s="24" t="n"/>
+      <c r="M24" s="24" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N24" s="24" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80004NT-T-1, FM80004NT-T-2, FM80005NT-CH-2PK</t>
         </is>
       </c>
       <c r="O24" s="24" t="inlineStr">
         <is>
-          <t>FM80004NT-T-1, FM80004NT-T-2, FM80005NT-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P24" s="24" t="inlineStr">
-        <is>
           <t>FM80004NT-5PC-05NT-1-Z.jpg,FM80005NT-CH-1.jpg</t>
         </is>
       </c>
-      <c r="Q24" s="24" t="n">
+      <c r="P24" s="24" t="n">
         <v>249</v>
       </c>
-      <c r="R24" s="25" t="n">
+      <c r="Q24" s="25" t="n">
         <v>249</v>
       </c>
+      <c r="R24" s="24" t="n">
+        <v>477</v>
+      </c>
       <c r="S24" s="24" t="n">
-        <v>477</v>
-      </c>
-      <c r="T24" s="24" t="n">
         <v>66.59999999999999</v>
       </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 21"W X 25"D X 34"H</t>
+        </is>
+      </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 21"W X 25"D X 34"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V24" s="24" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
         </is>
       </c>
       <c r="W24" s="24" t="inlineStr">
         <is>
-          <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
+          <t>Contemporary,Natural,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
         </is>
       </c>
       <c r="X24" s="24" t="inlineStr">
         <is>
-          <t>Contemporary,Natural,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
-        </is>
-      </c>
-      <c r="Y24" s="24" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y24" s="24" t="n"/>
       <c r="Z24" s="24" t="n"/>
       <c r="AA24" s="24" t="n"/>
-      <c r="AB24" s="24" t="n"/>
-      <c r="AC24" s="24" t="n">
+      <c r="AB24" s="24" t="n">
         <v>40.8</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, NIAMBI</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GM-2031-7PC-2037</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GM-2031-7PC-2037</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>NUSA 7 Pc. Dining Table Set</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
-        <is>
-          <t>NUSA 7 Pc. Dining Table Set</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 NUSA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Teak Wood construction and Natural tones, it blends durability with visual warmth.
@@ -3560,109 +3787,119 @@
 Weight: 307.2 lbs</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NUSA 7 Pc. Dining Table Set in Natural | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NUSA 7 Pc. Dining Table Set in Natural | GOODDEGG</t>
+          <t>The NUSA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>The NUSA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUSA</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>NUSA</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
           <t>7 Pc. Dining Table Set</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2031-1, GM-2031-2, GM-2037</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>GM-2031-1, GM-2031-2, GM-2037</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
           <t>GM-2031-7PC-2037.jpg</t>
         </is>
       </c>
-      <c r="Q25" t="n">
+      <c r="P25" t="n">
         <v>1399</v>
       </c>
-      <c r="R25" s="1" t="n">
+      <c r="Q25" s="1" t="n">
         <v>1399</v>
       </c>
+      <c r="R25" t="n">
+        <v>3597</v>
+      </c>
       <c r="S25" t="n">
-        <v>3597</v>
-      </c>
-      <c r="T25" t="n">
         <v>307.2</v>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Table: 78 3/4"L X 47 1/4"W X 29 1/2"H</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Table: 78 3/4"L X 47 1/4"W X 29 1/2"H</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Teak Wood</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Teak Wood</t>
+          <t>Transitional,Natural,Teak Wood,Slat Design,Pedestal Base,5-way Adjustable Chair,Sand Finish</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Transitional,Natural,Teak Wood,Slat Design,Pedestal Base,5-way Adjustable Chair,Sand Finish</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="AC25" t="n">
+      <c r="AB25" t="n">
         <v>52.8</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, NUSA</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Black/Gray</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GM-2022-7PC</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GM-2022-7PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>PALMA 7 Pc. Dining Table Set</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
-        <is>
-          <t>PALMA 7 Pc. Dining Table Set</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 PALMA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Glass, Polyspun Fabric construction and Black or Gray tones, it blends durability with visual warmth.
@@ -3683,109 +3920,119 @@
 Weight: 190.6 lbs</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PALMA 7 Pc. Dining Table Set in Black Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PALMA 7 Pc. Dining Table Set in Black or Gray | GOODDEGG</t>
+          <t>The PALMA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The PALMA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALMA</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>PALMA</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
           <t>7 Pc. Dining Table Set</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2022, GM-2023-6PK</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>GM-2022, GM-2023-6PK</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
           <t>GM-2022-7PC-1-Z.jpg,GM-2022-WB-1.jpg,GM-2023-6PK-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q26" t="n">
+      <c r="P26" t="n">
         <v>649</v>
       </c>
-      <c r="R26" s="2" t="n">
+      <c r="Q26" s="2" t="n">
         <v>649</v>
       </c>
+      <c r="R26" t="n">
+        <v>1647</v>
+      </c>
       <c r="S26" t="n">
-        <v>1647</v>
-      </c>
-      <c r="T26" t="n">
         <v>190.6</v>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Table: 70.8"L X 35.4"W X 27.9"H, Chair: 24"W X 33"D X 38.3"H</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Table: 70.8"L X 35.4"W X 27.9"H, Chair: 24"W X 33"D X 38.3"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel, Glass, Polyspun Fabric</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Steel, Glass, Polyspun Fabric</t>
+          <t>Contemporary,Black/Gray,Steel, Glass, Polyspun Fabric,5mm Tempered Water Wave Glass Tabletop,Powder Coated Steel Frame,Reclining Backrest,Washable Cushion Cover,Built-In Umbrella Hole,Tie-Back Cushions,Lumbar Pillows Included</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Gray,Steel, Glass, Polyspun Fabric,5mm Tempered Water Wave Glass Tabletop,Powder Coated Steel Frame,Reclining Backrest,Washable Cushion Cover,Built-In Umbrella Hole,Tie-Back Cushions,Lumbar Pillows Included</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC26" t="n">
+      <c r="AB26" t="n">
         <v>27.2</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, PALMA</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Black/Natural</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FM80003BK-T-3PC</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FM80003BK-T-3PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>SARABI 3 Pc. Conversation Set</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
-        <is>
-          <t>SARABI 3 Pc. Conversation Set</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 SARABI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Black or Natural tones, the Steel, Wicker, Fabric build keeps the look polished and practical.
@@ -3802,109 +4049,119 @@
 Weight: 11.7 lbs</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SARABI 3 Pc. Conversation Set in Black Natural | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SARABI 3 Pc. Conversation Set in Black or Natural | GOODDEGG</t>
+          <t>The SARABI Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>The SARABI Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SARABI</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SARABI</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
           <t>3 Pc. Conversation Set</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80003BK-T, FM80020NT-CH-2PK</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>FM80003BK-T, FM80020NT-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
           <t>FM80003BK-T-3PC-1.jpg</t>
         </is>
       </c>
-      <c r="Q27" t="n">
+      <c r="P27" t="n">
         <v>219</v>
       </c>
-      <c r="R27" s="1" t="n">
+      <c r="Q27" s="1" t="n">
         <v>219</v>
       </c>
+      <c r="R27" t="n">
+        <v>507</v>
+      </c>
       <c r="S27" t="n">
-        <v>507</v>
-      </c>
-      <c r="T27" t="n">
         <v>11.7</v>
       </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>TABLE: 21.5"W X 21.5"D X 15.5"H, CHAIR: 25.5"W X 28.5"D X 26.5"H (SEAT HT: 14", SEAT DP: 20")</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>TABLE: 21.5"W X 21.5"D X 15.5"H, CHAIR: 25.5"W X 28.5"D X 26.5"H (SEAT HT: 14", SEAT DP: 20")</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel, Wicker, Fabric</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Steel, Wicker, Fabric</t>
+          <t>Contemporary,Black/Natural,Steel, Wicker, Fabric,Powder-coated Steel Frame,3.5mm Round Wicker,Sloped Back &amp; Curbed Seat Lounge Chair</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Natural,Steel, Wicker, Fabric,Powder-coated Steel Frame,3.5mm Round Wicker,Sloped Back &amp; Curbed Seat Lounge Chair</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC27" t="n">
+      <c r="AB27" t="n">
         <v>14.3</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, SARABI</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Navy/Black/Gray</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GM-2013-5PC-2039</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GM-2013-5PC-2039</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>SEGOVIA 5 Pc. Dining Table Set</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
-        <is>
-          <t>SEGOVIA 5 Pc. Dining Table Set</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 SEGOVIA 5 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Steel, Polyethylene Wicker, Ceremic, Polyspun, then finished in Navy or Black or Gray tones to suit a range of interiors.
@@ -3922,109 +4179,119 @@
 Weight: 263.1 lbs</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SEGOVIA 5 Pc. Dining Table Set in Navy Black Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SEGOVIA 5 Pc. Dining Table Set in Navy or Black or Gray | GOODDEGG</t>
+          <t>The SEGOVIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>The SEGOVIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
           <t>5 Pc. Dining Table Set</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2013, GM-2039-2PK</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>GM-2013, GM-2039-2PK</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
           <t>GM-2013-5PC-2039-1.jpg,GM-2013-2.jpg,GM-2013-WB-2.jpg,GM-2013-WB-3.jpg</t>
         </is>
       </c>
-      <c r="Q28" t="n">
+      <c r="P28" t="n">
         <v>859</v>
       </c>
-      <c r="R28" s="2" t="n">
+      <c r="Q28" s="2" t="n">
         <v>859</v>
       </c>
+      <c r="R28" t="n">
+        <v>2307</v>
+      </c>
       <c r="S28" t="n">
-        <v>2307</v>
-      </c>
-      <c r="T28" t="n">
         <v>263.1</v>
       </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Firepit Table: 40"L X 40"W X 26 1/2"H Chair: 30 3/4"W X 25 1/2"D X 30 3/4"H"</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Firepit Table: 40"L X 40"W X 26 1/2"H Chair: 30 3/4"W X 25 1/2"D X 30 3/4"H"</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Steel, Polyethylene Wicker, Ceremic, Polyspun</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Steel, Polyethylene Wicker, Ceremic, Polyspun</t>
+          <t>Transitional,Navy/Black/Gray,Steel, Polyethylene Wicker, Ceremic, Polyspun,360-degree Swivel Glider,Gray Ceramic Tile Table Top,Fire Pit Table with Tile Table Top,Includes Cushions and Pillows</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Transitional,Navy/Black/Gray,Steel, Polyethylene Wicker, Ceremic, Polyspun,360-degree Swivel Glider,Gray Ceramic Tile Table Top,Fire Pit Table with Tile Table Top,Includes Cushions and Pillows</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC28" t="n">
+      <c r="AB28" t="n">
         <v>23.4</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, SEGOVIA</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Black/Gray</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GM-2013-5PC</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GM-2013-5PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>SEGOVIA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
-        <is>
-          <t>SEGOVIA 5 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 SEGOVIA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Steel, Polyethylene Wicker, Polyspun construction and Black or Gray tones, it blends durability with visual warmth.
@@ -4042,111 +4309,120 @@
 Weight: 248.1 lbs</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SEGOVIA 5 Pc. Patio Dining Set in Black Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SEGOVIA 5 Pc. Patio Dining Set in Black or Gray | GOODDEGG</t>
+          <t>The SEGOVIA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>The SEGOVIA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SEGOVIA</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SEGOVIA</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2013, GM-2014-4PK</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>GM-2013, GM-2014-4PK</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
           <t>GM-2013-1.jpg,GM-2013-2.jpg,GM-2013-WB-2.jpg,GM-2013-WB-3.jpg</t>
         </is>
       </c>
-      <c r="Q29" t="n">
+      <c r="P29" t="n">
         <v>799</v>
       </c>
-      <c r="R29" s="2" t="n">
+      <c r="Q29" s="2" t="n">
         <v>799</v>
       </c>
+      <c r="R29" t="n">
+        <v>2097</v>
+      </c>
       <c r="S29" t="n">
-        <v>2097</v>
-      </c>
-      <c r="T29" t="n">
         <v>248.1</v>
       </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>40"L X 40"W X 26 1/2"H</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>40"L X 40"W X 26 1/2"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Steel, Polyethylene Wicker, Polyspun</t>
+          <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,360-degree swivel rockers,Gray ceramic tile table top,Fire pit table with tile-top and wicker base,Includes cushions and pillows</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,360-degree swivel rockers,Gray ceramic tile table top,Fire pit table with tile-top and wicker base,Includes cushions and pillows</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC29" t="n">
+      <c r="AB29" t="n">
         <v>33.7</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, SEGOVIA</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="n"/>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>Black/Gray</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n"/>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>GM-2012-5PC-10</t>
+        </is>
+      </c>
       <c r="D30" s="26" t="inlineStr">
         <is>
-          <t>GM-2012-5PC-10</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E30" s="26" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F30" s="26" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>SINTRA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G30" s="26" t="inlineStr">
-        <is>
-          <t>SINTRA 5 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H30" s="26" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 SINTRA 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyethylene Wicker, Polyspun and finished in Black or Gray tones for a clean, cohesive look.
@@ -4164,115 +4440,124 @@
 Weight: 180.7 lbs</t>
         </is>
       </c>
+      <c r="H30" s="26" t="inlineStr">
+        <is>
+          <t>SINTRA 5 Pc. Patio Dining Set in Black Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I30" s="26" t="inlineStr">
         <is>
-          <t>SINTRA 5 Pc. Patio Dining Set in Black or Gray | GOODDEGG</t>
+          <t>The SINTRA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J30" s="26" t="inlineStr">
         <is>
-          <t>The SINTRA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA</t>
         </is>
       </c>
       <c r="K30" s="26" t="inlineStr">
         <is>
-          <t>SINTRA</t>
-        </is>
-      </c>
-      <c r="L30" s="26" t="inlineStr">
-        <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M30" s="26" t="n"/>
+      <c r="L30" s="26" t="n"/>
+      <c r="M30" s="26" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N30" s="26" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2012, GM-2010-2PK</t>
         </is>
       </c>
       <c r="O30" s="26" t="inlineStr">
         <is>
-          <t>GM-2012, GM-2010-2PK</t>
-        </is>
-      </c>
-      <c r="P30" s="26" t="inlineStr">
-        <is>
           <t>GM-2012-5PC-10.jpg,GM-2012-1.jpg,GM-2012-WB-1.jpg,GM-2012-2.jpg,GM-2012-3.jpg,GM-2012-4.jpg,GM-2010-2PK-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q30" s="26" t="n">
+      <c r="P30" s="26" t="n">
         <v>539</v>
       </c>
-      <c r="R30" s="27" t="n">
+      <c r="Q30" s="27" t="n">
         <v>539</v>
       </c>
+      <c r="R30" s="26" t="n">
+        <v>1377</v>
+      </c>
       <c r="S30" s="26" t="n">
-        <v>1377</v>
-      </c>
-      <c r="T30" s="26" t="n">
         <v>180.7</v>
       </c>
+      <c r="T30" s="26" t="inlineStr">
+        <is>
+          <t>40"L X 40"W X 28"H</t>
+        </is>
+      </c>
       <c r="U30" s="26" t="inlineStr">
         <is>
-          <t>40"L X 40"W X 28"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V30" s="26" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
       <c r="W30" s="26" t="inlineStr">
         <is>
-          <t>Steel, Polyethylene Wicker, Polyspun</t>
+          <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,Ceramic tile table top,Rust-resistant, powder-coated steel frame,Includes umbrella hole and cap</t>
         </is>
       </c>
       <c r="X30" s="26" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,Ceramic tile table top,Rust-resistant, powder-coated steel frame,Includes umbrella hole and cap</t>
-        </is>
-      </c>
-      <c r="Y30" s="26" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y30" s="26" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="26" t="n"/>
-      <c r="AB30" s="26" t="n"/>
-      <c r="AC30" s="26" t="n">
+      <c r="AB30" s="26" t="n">
         <v>22.4</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, SINTRA</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="n"/>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>Black/Gray</t>
         </is>
       </c>
-      <c r="C31" s="26" t="n"/>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>GM-2012-5PC-11</t>
+        </is>
+      </c>
       <c r="D31" s="26" t="inlineStr">
         <is>
-          <t>GM-2012-5PC-11</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E31" s="26" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F31" s="26" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>SINTRA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G31" s="26" t="inlineStr">
-        <is>
-          <t>SINTRA 5 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H31" s="26" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 SINTRA 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel, Polyethylene Wicker, Polyspun, then finished in Black or Gray tones to suit a range of interiors.
@@ -4290,113 +4575,123 @@
 Weight: 156.5 lbs</t>
         </is>
       </c>
+      <c r="H31" s="26" t="inlineStr">
+        <is>
+          <t>SINTRA 5 Pc. Patio Dining Set in Black Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I31" s="26" t="inlineStr">
         <is>
-          <t>SINTRA 5 Pc. Patio Dining Set in Black or Gray | GOODDEGG</t>
+          <t>The SINTRA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J31" s="26" t="inlineStr">
         <is>
-          <t>The SINTRA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA</t>
         </is>
       </c>
       <c r="K31" s="26" t="inlineStr">
         <is>
-          <t>SINTRA</t>
-        </is>
-      </c>
-      <c r="L31" s="26" t="inlineStr">
-        <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M31" s="26" t="n"/>
+      <c r="L31" s="26" t="n"/>
+      <c r="M31" s="26" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N31" s="26" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2012, GM-2011-2PK</t>
         </is>
       </c>
       <c r="O31" s="26" t="inlineStr">
         <is>
-          <t>GM-2012, GM-2011-2PK</t>
-        </is>
-      </c>
-      <c r="P31" s="26" t="inlineStr">
-        <is>
           <t>GM-2012-5PC-11.jpg,GM-2012-1.jpg,GM-2012-WB-1.jpg,GM-2012-2.jpg,GM-2012-3.jpg,GM-2012-4.jpg,GM-2011-2PK-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q31" s="26" t="n">
+      <c r="P31" s="26" t="n">
         <v>419</v>
       </c>
-      <c r="R31" s="27" t="n">
+      <c r="Q31" s="27" t="n">
         <v>419</v>
       </c>
+      <c r="R31" s="26" t="n">
+        <v>1017</v>
+      </c>
       <c r="S31" s="26" t="n">
-        <v>1017</v>
-      </c>
-      <c r="T31" s="26" t="n">
         <v>156.5</v>
       </c>
+      <c r="T31" s="26" t="inlineStr">
+        <is>
+          <t>40"L X 40"W X 28"H</t>
+        </is>
+      </c>
       <c r="U31" s="26" t="inlineStr">
         <is>
-          <t>40"L X 40"W X 28"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V31" s="26" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
       <c r="W31" s="26" t="inlineStr">
         <is>
-          <t>Steel, Polyethylene Wicker, Polyspun</t>
+          <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,Ceramic tile table top,Rust-resistant, powder-coated steel frame,Includes umbrella hole and cap</t>
         </is>
       </c>
       <c r="X31" s="26" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,Ceramic tile table top,Rust-resistant, powder-coated steel frame,Includes umbrella hole and cap</t>
-        </is>
-      </c>
-      <c r="Y31" s="26" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y31" s="26" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="26" t="n"/>
-      <c r="AB31" s="26" t="n"/>
-      <c r="AC31" s="26" t="n">
+      <c r="AB31" s="26" t="n">
         <v>18</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, SINTRA</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Black/Gray</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>GM-2008-6PC</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GM-2008-6PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>SINTRA 6 Pc. Patio Dining Set w/ Bench</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
-        <is>
-          <t>SINTRA 6 Pc. Patio Dining Set w/ Bench</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 SINTRA 6 Pc. Patio Dining Set w/ Bench creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel, Polyspun construction and Black or Gray tones, it blends durability with visual warmth.
@@ -4418,111 +4713,120 @@
 Weight: 234.5 lbs</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SINTRA 6 Pc. Patio Dining Set w/ Bench in Black Gray | GOODDEG</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SINTRA 6 Pc. Patio Dining Set w/ Bench in Black or Gray | GOODDEG</t>
+          <t>SINTRA Patio Dining w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SINTRA Patio Dining w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SINTRA</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
           <t>6 Pc. Patio Dining Set w/ Bench</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2008, GM-2011-2PK, GM-2010-2PK, GM-2009</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>GM-2008, GM-2011-2PK, GM-2010-2PK, GM-2009</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
           <t>GM-2008-6PC-WB-1.jpg,GM-2008-6PC-1.jpg,GM-2008-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q32" t="n">
+      <c r="P32" t="n">
         <v>699</v>
       </c>
-      <c r="R32" s="2" t="n">
+      <c r="Q32" s="2" t="n">
         <v>699</v>
       </c>
+      <c r="R32" t="n">
+        <v>1797</v>
+      </c>
       <c r="S32" t="n">
-        <v>1797</v>
-      </c>
-      <c r="T32" t="n">
         <v>234.5</v>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>76"L X 40"W X 28"H</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>76"L X 40"W X 28"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel, Polyspun</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Steel, Polyspun</t>
+          <t>Contemporary,Black/Gray,Steel, Polyspun,Ceramic tile table top,360-degree swivel rocker chairs,Rust-resistant, powder-coated steel frame,Table includes umbrella hole and cap,Chair includes cushion and pillow</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Contemporary,Black/Gray,Steel, Polyspun,Ceramic tile table top,360-degree swivel rocker chairs,Rust-resistant, powder-coated steel frame,Table includes umbrella hole and cap,Chair includes cushion and pillow</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC32" t="n">
+      <c r="AB32" t="n">
         <v>27.4</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, SINTRA</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="n"/>
-      <c r="B33" s="28" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C33" s="28" t="n"/>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="inlineStr">
+        <is>
+          <t>FM80010BK-T-3PC</t>
+        </is>
+      </c>
       <c r="D33" s="28" t="inlineStr">
         <is>
-          <t>FM80010BK-T-3PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E33" s="28" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F33" s="28" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>ZALIKA 3 Pc. Conversation Set</t>
         </is>
       </c>
       <c r="G33" s="28" t="inlineStr">
-        <is>
-          <t>ZALIKA 3 Pc. Conversation Set</t>
-        </is>
-      </c>
-      <c r="H33" s="28" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZALIKA 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Fabric, Steel, PE Rattan, Foam build keeps the look polished and practical.
@@ -4537,113 +4841,122 @@
 Color: Black</t>
         </is>
       </c>
+      <c r="H33" s="28" t="inlineStr">
+        <is>
+          <t>ZALIKA 3 Pc. Conversation Set in Black | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I33" s="28" t="inlineStr">
         <is>
-          <t>ZALIKA 3 Pc. Conversation Set in Black | GOODDEGG</t>
+          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J33" s="28" t="inlineStr">
         <is>
-          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA</t>
         </is>
       </c>
       <c r="K33" s="28" t="inlineStr">
         <is>
-          <t>ZALIKA</t>
-        </is>
-      </c>
-      <c r="L33" s="28" t="inlineStr">
-        <is>
           <t>3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="M33" s="28" t="n"/>
+      <c r="L33" s="28" t="n"/>
+      <c r="M33" s="28" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N33" s="28" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80010BK-T, FM80010BK-CH-2PK</t>
         </is>
       </c>
       <c r="O33" s="28" t="inlineStr">
         <is>
-          <t>FM80010BK-T, FM80010BK-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P33" s="28" t="inlineStr">
-        <is>
           <t>FM80010BK-T-3PC-1.jpg</t>
         </is>
       </c>
-      <c r="Q33" s="28" t="n">
+      <c r="P33" s="28" t="n">
         <v>199</v>
       </c>
-      <c r="R33" s="29" t="n">
+      <c r="Q33" s="29" t="n">
         <v>199</v>
       </c>
-      <c r="S33" s="28" t="n">
+      <c r="R33" s="28" t="n">
         <v>507</v>
       </c>
-      <c r="T33" s="28" t="n"/>
+      <c r="S33" s="28" t="n"/>
+      <c r="T33" s="28" t="inlineStr">
+        <is>
+          <t>TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
+        </is>
+      </c>
       <c r="U33" s="28" t="inlineStr">
         <is>
-          <t>TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V33" s="28" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
       <c r="W33" s="28" t="inlineStr">
         <is>
-          <t>Fabric, Steel, PE Rattan, Foam</t>
+          <t>Contemporary,Black,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
       <c r="X33" s="28" t="inlineStr">
         <is>
-          <t>Contemporary,Black,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
-        </is>
-      </c>
-      <c r="Y33" s="28" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y33" s="28" t="n"/>
       <c r="Z33" s="28" t="n"/>
       <c r="AA33" s="28" t="n"/>
-      <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="28" t="n">
+      <c r="AB33" s="28" t="n">
         <v>10.9</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, ZALIKA</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="n"/>
-      <c r="B34" s="28" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="C34" s="28" t="n"/>
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>FM80010NT-T-3PC</t>
+        </is>
+      </c>
       <c r="D34" s="28" t="inlineStr">
         <is>
-          <t>FM80010NT-T-3PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E34" s="28" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F34" s="28" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>ZALIKA 3 Pc. Conversation Set</t>
         </is>
       </c>
       <c r="G34" s="28" t="inlineStr">
-        <is>
-          <t>ZALIKA 3 Pc. Conversation Set</t>
-        </is>
-      </c>
-      <c r="H34" s="28" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZALIKA 3 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Steel, PE Rattan, Foam and finished in Natural tones for a clean, cohesive look.
@@ -4658,113 +4971,122 @@
 Color: Natural</t>
         </is>
       </c>
+      <c r="H34" s="28" t="inlineStr">
+        <is>
+          <t>ZALIKA 3 Pc. Conversation Set in Natural | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I34" s="28" t="inlineStr">
         <is>
-          <t>ZALIKA 3 Pc. Conversation Set in Natural | GOODDEGG</t>
+          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J34" s="28" t="inlineStr">
         <is>
-          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA</t>
         </is>
       </c>
       <c r="K34" s="28" t="inlineStr">
         <is>
-          <t>ZALIKA</t>
-        </is>
-      </c>
-      <c r="L34" s="28" t="inlineStr">
-        <is>
           <t>3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="M34" s="28" t="n"/>
+      <c r="L34" s="28" t="n"/>
+      <c r="M34" s="28" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N34" s="28" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80010NT-T, FM80010NT-CH-2PK</t>
         </is>
       </c>
       <c r="O34" s="28" t="inlineStr">
         <is>
-          <t>FM80010NT-T, FM80010NT-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P34" s="28" t="inlineStr">
-        <is>
           <t>FM80010NT-T-3PC-1.jpg</t>
         </is>
       </c>
-      <c r="Q34" s="28" t="n">
+      <c r="P34" s="28" t="n">
         <v>199</v>
       </c>
-      <c r="R34" s="29" t="n">
+      <c r="Q34" s="29" t="n">
         <v>199</v>
       </c>
-      <c r="S34" s="28" t="n">
+      <c r="R34" s="28" t="n">
         <v>507</v>
       </c>
-      <c r="T34" s="28" t="n"/>
+      <c r="S34" s="28" t="n"/>
+      <c r="T34" s="28" t="inlineStr">
+        <is>
+          <t>TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
+        </is>
+      </c>
       <c r="U34" s="28" t="inlineStr">
         <is>
-          <t>TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V34" s="28" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
       <c r="W34" s="28" t="inlineStr">
         <is>
-          <t>Fabric, Steel, PE Rattan, Foam</t>
+          <t>Contemporary,Natural,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
       <c r="X34" s="28" t="inlineStr">
         <is>
-          <t>Contemporary,Natural,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
-        </is>
-      </c>
-      <c r="Y34" s="28" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y34" s="28" t="n"/>
       <c r="Z34" s="28" t="n"/>
       <c r="AA34" s="28" t="n"/>
-      <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="28" t="n">
+      <c r="AB34" s="28" t="n">
         <v>10.9</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, ZALIKA</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="n"/>
-      <c r="B35" s="30" t="inlineStr">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C35" s="30" t="n"/>
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>FM80010BK-T-4PC-BN</t>
+        </is>
+      </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
-          <t>FM80010BK-T-4PC-BN</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E35" s="30" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F35" s="30" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>ZALIKA 4 Pc. Conversation Set</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
-        <is>
-          <t>ZALIKA 4 Pc. Conversation Set</t>
-        </is>
-      </c>
-      <c r="H35" s="30" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZALIKA 4 Pc. Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Steel, PE Rattan, Foam, then finished in Black tones to suit a range of interiors.
@@ -4780,113 +5102,122 @@
 Color: Black</t>
         </is>
       </c>
+      <c r="H35" s="30" t="inlineStr">
+        <is>
+          <t>ZALIKA 4 Pc. Conversation Set in Black | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I35" s="30" t="inlineStr">
         <is>
-          <t>ZALIKA 4 Pc. Conversation Set in Black | GOODDEGG</t>
+          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J35" s="30" t="inlineStr">
         <is>
-          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA</t>
         </is>
       </c>
       <c r="K35" s="30" t="inlineStr">
         <is>
-          <t>ZALIKA</t>
-        </is>
-      </c>
-      <c r="L35" s="30" t="inlineStr">
-        <is>
           <t>4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="M35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
+      <c r="M35" s="30" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N35" s="30" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80010BK-T, FM80010BK-CH-2PK, FM80010BK-BN</t>
         </is>
       </c>
       <c r="O35" s="30" t="inlineStr">
         <is>
-          <t>FM80010BK-T, FM80010BK-CH-2PK, FM80010BK-BN</t>
-        </is>
-      </c>
-      <c r="P35" s="30" t="inlineStr">
-        <is>
           <t>FM80010BK-T-4PC-BN-1.jpg</t>
         </is>
       </c>
-      <c r="Q35" s="30" t="n">
+      <c r="P35" s="30" t="n">
         <v>418</v>
       </c>
-      <c r="R35" s="31" t="n">
+      <c r="Q35" s="31" t="n">
         <v>418</v>
       </c>
-      <c r="S35" s="30" t="n">
+      <c r="R35" s="30" t="n">
         <v>984</v>
       </c>
-      <c r="T35" s="30" t="n"/>
+      <c r="S35" s="30" t="n"/>
+      <c r="T35" s="30" t="inlineStr">
+        <is>
+          <t>TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H</t>
+        </is>
+      </c>
       <c r="U35" s="30" t="inlineStr">
         <is>
-          <t>TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V35" s="30" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
       <c r="W35" s="30" t="inlineStr">
         <is>
-          <t>Fabric, Steel, PE Rattan, Foam</t>
+          <t>Contemporary,Black,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
       <c r="X35" s="30" t="inlineStr">
         <is>
-          <t>Contemporary,Black,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
-        </is>
-      </c>
-      <c r="Y35" s="30" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y35" s="30" t="n"/>
       <c r="Z35" s="30" t="n"/>
       <c r="AA35" s="30" t="n"/>
-      <c r="AB35" s="30" t="n"/>
-      <c r="AC35" s="30" t="n">
+      <c r="AB35" s="30" t="n">
         <v>28.6</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, ZALIKA</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="n"/>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="C36" s="30" t="n"/>
+      <c r="B36" s="30" t="n"/>
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t>FM80010NT-T-4PC-BN</t>
+        </is>
+      </c>
       <c r="D36" s="30" t="inlineStr">
         <is>
-          <t>FM80010NT-T-4PC-BN</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>ZALIKA 4 Pc. Conversation Set</t>
         </is>
       </c>
       <c r="G36" s="30" t="inlineStr">
-        <is>
-          <t>ZALIKA 4 Pc. Conversation Set</t>
-        </is>
-      </c>
-      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZALIKA 4 Pc. Conversation Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Fabric, Steel, PE Rattan, Foam construction and Natural tones, it blends durability with visual warmth.
@@ -4902,113 +5233,122 @@
 Color: Natural</t>
         </is>
       </c>
+      <c r="H36" s="30" t="inlineStr">
+        <is>
+          <t>ZALIKA 4 Pc. Conversation Set in Natural | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I36" s="30" t="inlineStr">
         <is>
-          <t>ZALIKA 4 Pc. Conversation Set in Natural | GOODDEGG</t>
+          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J36" s="30" t="inlineStr">
         <is>
-          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA</t>
         </is>
       </c>
       <c r="K36" s="30" t="inlineStr">
         <is>
-          <t>ZALIKA</t>
-        </is>
-      </c>
-      <c r="L36" s="30" t="inlineStr">
-        <is>
           <t>4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="M36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
+      <c r="M36" s="30" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N36" s="30" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80010NT-T, FM80010NT-CH-2PK, FM80010NT-BN</t>
         </is>
       </c>
       <c r="O36" s="30" t="inlineStr">
         <is>
-          <t>FM80010NT-T, FM80010NT-CH-2PK, FM80010NT-BN</t>
-        </is>
-      </c>
-      <c r="P36" s="30" t="inlineStr">
-        <is>
           <t>FM80010NT-T-4PC-BN-1.jpg</t>
         </is>
       </c>
-      <c r="Q36" s="30" t="n">
+      <c r="P36" s="30" t="n">
         <v>418</v>
       </c>
-      <c r="R36" s="31" t="n">
+      <c r="Q36" s="31" t="n">
         <v>418</v>
       </c>
-      <c r="S36" s="30" t="n">
+      <c r="R36" s="30" t="n">
         <v>984</v>
       </c>
-      <c r="T36" s="30" t="n"/>
+      <c r="S36" s="30" t="n"/>
+      <c r="T36" s="30" t="inlineStr">
+        <is>
+          <t>TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H</t>
+        </is>
+      </c>
       <c r="U36" s="30" t="inlineStr">
         <is>
-          <t>TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V36" s="30" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
       <c r="W36" s="30" t="inlineStr">
         <is>
-          <t>Fabric, Steel, PE Rattan, Foam</t>
+          <t>Contemporary,Natural,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
       <c r="X36" s="30" t="inlineStr">
         <is>
-          <t>Contemporary,Natural,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
-        </is>
-      </c>
-      <c r="Y36" s="30" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y36" s="30" t="n"/>
       <c r="Z36" s="30" t="n"/>
       <c r="AA36" s="30" t="n"/>
-      <c r="AB36" s="30" t="n"/>
-      <c r="AC36" s="30" t="n">
+      <c r="AB36" s="30" t="n">
         <v>28.6</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, ZALIKA</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="n"/>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>Natural/Black</t>
         </is>
       </c>
-      <c r="C37" s="32" t="n"/>
+      <c r="B37" s="32" t="n"/>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>FM80003NT-3PC-02BB</t>
+        </is>
+      </c>
       <c r="D37" s="32" t="inlineStr">
         <is>
-          <t>FM80003NT-3PC-02BB</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E37" s="32" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F37" s="32" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
       <c r="G37" s="32" t="inlineStr">
-        <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set</t>
-        </is>
-      </c>
-      <c r="H37" s="32" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.
@@ -5025,119 +5365,128 @@
 Weight: 37.6 lbs</t>
         </is>
       </c>
+      <c r="H37" s="32" t="inlineStr">
+        <is>
+          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural Black | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I37" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural or Black | GOODDEGG</t>
+          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J37" s="32" t="inlineStr">
         <is>
-          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZUBERI</t>
         </is>
       </c>
       <c r="K37" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI</t>
+          <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
       <c r="L37" s="32" t="inlineStr">
         <is>
-          <t>3 Pc. Patio Conversation Set</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M37" s="32" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="N37" s="32" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80003NT-T, FM80002BB-CH-2PK</t>
         </is>
       </c>
       <c r="O37" s="32" t="inlineStr">
         <is>
-          <t>FM80003NT-T, FM80002BB-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P37" s="32" t="inlineStr">
-        <is>
           <t>FM80003NT-3PC-02BB-1-Z.jpg,FM80002BB-CH-1.jpg,FM80003NT-T-1.jpg</t>
         </is>
       </c>
-      <c r="Q37" s="32" t="n">
+      <c r="P37" s="32" t="n">
         <v>179</v>
       </c>
-      <c r="R37" s="33" t="n">
+      <c r="Q37" s="33" t="n">
         <v>179</v>
       </c>
+      <c r="R37" s="32" t="n">
+        <v>417</v>
+      </c>
       <c r="S37" s="32" t="n">
-        <v>417</v>
-      </c>
-      <c r="T37" s="32" t="n">
         <v>37.6</v>
       </c>
+      <c r="T37" s="32" t="inlineStr">
+        <is>
+          <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H</t>
+        </is>
+      </c>
       <c r="U37" s="32" t="inlineStr">
         <is>
-          <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V37" s="32" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
       <c r="W37" s="32" t="inlineStr">
         <is>
-          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
+          <t>Contemporary,Natural/Black,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
       <c r="X37" s="32" t="inlineStr">
         <is>
-          <t>Contemporary,Natural/Black,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
-        </is>
-      </c>
-      <c r="Y37" s="32" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y37" s="32" t="n"/>
       <c r="Z37" s="32" t="n"/>
       <c r="AA37" s="32" t="n"/>
-      <c r="AB37" s="32" t="n"/>
-      <c r="AC37" s="32" t="n">
+      <c r="AB37" s="32" t="n">
         <v>12</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, ZUBERI</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="n"/>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="C38" s="32" t="n"/>
+      <c r="B38" s="32" t="n"/>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>FM80003NT-3PC-02NT</t>
+        </is>
+      </c>
       <c r="D38" s="32" t="inlineStr">
         <is>
-          <t>FM80003NT-3PC-02NT</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E38" s="32" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F38" s="32" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
       <c r="G38" s="32" t="inlineStr">
-        <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set</t>
-        </is>
-      </c>
-      <c r="H38" s="32" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZUBERI 3 Pc. Patio Conversation Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric construction and Natural tones, it blends durability with visual warmth.
@@ -5153,115 +5502,124 @@
 Weight: 21.3 lbs</t>
         </is>
       </c>
+      <c r="H38" s="32" t="inlineStr">
+        <is>
+          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I38" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural | GOODDEGG</t>
+          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J38" s="32" t="inlineStr">
         <is>
-          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZUBERI</t>
         </is>
       </c>
       <c r="K38" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI</t>
-        </is>
-      </c>
-      <c r="L38" s="32" t="inlineStr">
-        <is>
           <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="M38" s="32" t="n"/>
+      <c r="L38" s="32" t="n"/>
+      <c r="M38" s="32" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N38" s="32" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80003NT-T, FM80002NT-CH-2PK</t>
         </is>
       </c>
       <c r="O38" s="32" t="inlineStr">
         <is>
-          <t>FM80003NT-T, FM80002NT-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P38" s="32" t="inlineStr">
-        <is>
           <t>FM80003NT-3PC-02NT-1-Z.jpg,FM80002NT-CH-1.jpg,FM80003NT-T-1.jpg</t>
         </is>
       </c>
-      <c r="Q38" s="32" t="n">
+      <c r="P38" s="32" t="n">
         <v>179</v>
       </c>
-      <c r="R38" s="33" t="n">
+      <c r="Q38" s="33" t="n">
         <v>179</v>
       </c>
+      <c r="R38" s="32" t="n">
+        <v>417</v>
+      </c>
       <c r="S38" s="32" t="n">
-        <v>417</v>
-      </c>
-      <c r="T38" s="32" t="n">
         <v>21.3</v>
       </c>
+      <c r="T38" s="32" t="inlineStr">
+        <is>
+          <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H</t>
+        </is>
+      </c>
       <c r="U38" s="32" t="inlineStr">
         <is>
-          <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V38" s="32" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
       <c r="W38" s="32" t="inlineStr">
         <is>
-          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
+          <t>Contemporary,Natural,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
       <c r="X38" s="32" t="inlineStr">
         <is>
-          <t>Contemporary,Natural,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
-        </is>
-      </c>
-      <c r="Y38" s="32" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y38" s="32" t="n"/>
       <c r="Z38" s="32" t="n"/>
       <c r="AA38" s="32" t="n"/>
-      <c r="AB38" s="32" t="n"/>
-      <c r="AC38" s="32" t="n">
+      <c r="AB38" s="32" t="n">
         <v>12</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, ZUBERI</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="n"/>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="C39" s="32" t="n"/>
+      <c r="B39" s="32" t="n"/>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>FM80003NT-3PC-05NT</t>
+        </is>
+      </c>
       <c r="D39" s="32" t="inlineStr">
         <is>
-          <t>FM80003NT-3PC-05NT</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E39" s="32" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F39" s="32" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
       <c r="G39" s="32" t="inlineStr">
-        <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set</t>
-        </is>
-      </c>
-      <c r="H39" s="32" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZUBERI 3 Pc. Patio Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric build keeps the look polished and practical.
@@ -5277,115 +5635,124 @@
 Weight: 28.1 lbs</t>
         </is>
       </c>
+      <c r="H39" s="32" t="inlineStr">
+        <is>
+          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I39" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural | GOODDEGG</t>
+          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J39" s="32" t="inlineStr">
         <is>
-          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZUBERI</t>
         </is>
       </c>
       <c r="K39" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI</t>
-        </is>
-      </c>
-      <c r="L39" s="32" t="inlineStr">
-        <is>
           <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="M39" s="32" t="n"/>
+      <c r="L39" s="32" t="n"/>
+      <c r="M39" s="32" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N39" s="32" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80003NT-T, FM80005NT-CH-2PK</t>
         </is>
       </c>
       <c r="O39" s="32" t="inlineStr">
         <is>
-          <t>FM80003NT-T, FM80005NT-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P39" s="32" t="inlineStr">
-        <is>
           <t>FM80003NT-3PC-05NT-1-Z.jpg,FM80003NT-T-1.jpg,FM80005NT-CH-1.jpg</t>
         </is>
       </c>
-      <c r="Q39" s="32" t="n">
+      <c r="P39" s="32" t="n">
         <v>169</v>
       </c>
-      <c r="R39" s="33" t="n">
+      <c r="Q39" s="33" t="n">
         <v>169</v>
       </c>
+      <c r="R39" s="32" t="n">
+        <v>327</v>
+      </c>
       <c r="S39" s="32" t="n">
-        <v>327</v>
-      </c>
-      <c r="T39" s="32" t="n">
         <v>28.1</v>
       </c>
+      <c r="T39" s="32" t="inlineStr">
+        <is>
+          <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H</t>
+        </is>
+      </c>
       <c r="U39" s="32" t="inlineStr">
         <is>
-          <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V39" s="32" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
       <c r="W39" s="32" t="inlineStr">
         <is>
-          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
+          <t>Contemporary,Natural,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
       <c r="X39" s="32" t="inlineStr">
         <is>
-          <t>Contemporary,Natural,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
-        </is>
-      </c>
-      <c r="Y39" s="32" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y39" s="32" t="n"/>
       <c r="Z39" s="32" t="n"/>
       <c r="AA39" s="32" t="n"/>
-      <c r="AB39" s="32" t="n"/>
-      <c r="AC39" s="32" t="n">
+      <c r="AB39" s="32" t="n">
         <v>24.1</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, ZUBERI</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="n"/>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="A40" s="32" t="inlineStr">
         <is>
           <t>Natural/Gray</t>
         </is>
       </c>
-      <c r="C40" s="32" t="n"/>
+      <c r="B40" s="32" t="n"/>
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>FM80003NT-3PC-06GY</t>
+        </is>
+      </c>
       <c r="D40" s="32" t="inlineStr">
         <is>
-          <t>FM80003NT-3PC-06GY</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E40" s="32" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Set</t>
         </is>
       </c>
       <c r="F40" s="32" t="inlineStr">
         <is>
-          <t>Patio Set</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
       <c r="G40" s="32" t="inlineStr">
-        <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set</t>
-        </is>
-      </c>
-      <c r="H40" s="32" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ZUBERI 3 Pc. Patio Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric and finished in Natural or Gray tones for a clean, cohesive look.
@@ -5402,119 +5769,128 @@
 Weight: 35.9 lbs</t>
         </is>
       </c>
+      <c r="H40" s="32" t="inlineStr">
+        <is>
+          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I40" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural or Gray | GOODDEGG</t>
+          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J40" s="32" t="inlineStr">
         <is>
-          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZUBERI</t>
         </is>
       </c>
       <c r="K40" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI</t>
+          <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
       <c r="L40" s="32" t="inlineStr">
         <is>
-          <t>3 Pc. Patio Conversation Set</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="M40" s="32" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="N40" s="32" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM80003NT-T, FM80006GY-CH-2PK</t>
         </is>
       </c>
       <c r="O40" s="32" t="inlineStr">
         <is>
-          <t>FM80003NT-T, FM80006GY-CH-2PK</t>
-        </is>
-      </c>
-      <c r="P40" s="32" t="inlineStr">
-        <is>
           <t>FM80003NT-3PC-06GY-1-Z.jpg,FM80003NT-T-1.jpg,FM80006GY-CH-1.jpg</t>
         </is>
       </c>
-      <c r="Q40" s="32" t="n">
+      <c r="P40" s="32" t="n">
         <v>249</v>
       </c>
-      <c r="R40" s="33" t="n">
+      <c r="Q40" s="33" t="n">
         <v>249</v>
       </c>
+      <c r="R40" s="32" t="n">
+        <v>477</v>
+      </c>
       <c r="S40" s="32" t="n">
-        <v>477</v>
-      </c>
-      <c r="T40" s="32" t="n">
         <v>35.9</v>
       </c>
+      <c r="T40" s="32" t="inlineStr">
+        <is>
+          <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H</t>
+        </is>
+      </c>
       <c r="U40" s="32" t="inlineStr">
         <is>
-          <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V40" s="32" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
       <c r="W40" s="32" t="inlineStr">
         <is>
-          <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
+          <t>Contemporary,Natural/Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
       <c r="X40" s="32" t="inlineStr">
         <is>
-          <t>Contemporary,Natural/Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
-        </is>
-      </c>
-      <c r="Y40" s="32" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
+      <c r="Y40" s="32" t="n"/>
       <c r="Z40" s="32" t="n"/>
       <c r="AA40" s="32" t="n"/>
-      <c r="AB40" s="32" t="n"/>
-      <c r="AC40" s="32" t="n">
+      <c r="AB40" s="32" t="n">
         <v>22.3</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Set, ZUBERI</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="34" t="n"/>
-      <c r="B41" s="34" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C41" s="34" t="n"/>
+      <c r="B41" s="34" t="n"/>
+      <c r="C41" s="34" t="inlineStr">
+        <is>
+          <t>GM-1010BK-SET</t>
+        </is>
+      </c>
       <c r="D41" s="34" t="inlineStr">
         <is>
-          <t>GM-1010BK-SET</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E41" s="34" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>BREEZE Swing Chair w/ Stand</t>
         </is>
       </c>
       <c r="G41" s="34" t="inlineStr">
-        <is>
-          <t>BREEZE Swing Chair w/ Stand</t>
-        </is>
-      </c>
-      <c r="H41" s="34" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 BREEZE Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Crafted with Steel, Mesh, Fabric, then finished in Black tones to suit a range of interiors.
@@ -5534,115 +5910,124 @@
 Weight: 71.42 lbs</t>
         </is>
       </c>
+      <c r="H41" s="34" t="inlineStr">
+        <is>
+          <t>BREEZE Swing Chair w/ Stand in Black | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I41" s="34" t="inlineStr">
         <is>
-          <t>BREEZE Swing Chair w/ Stand in Black | GOODDEGG</t>
+          <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J41" s="34" t="inlineStr">
         <is>
-          <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BREEZE</t>
         </is>
       </c>
       <c r="K41" s="34" t="inlineStr">
         <is>
-          <t>BREEZE</t>
-        </is>
-      </c>
-      <c r="L41" s="34" t="inlineStr">
-        <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="M41" s="34" t="n"/>
+      <c r="L41" s="34" t="n"/>
+      <c r="M41" s="34" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N41" s="34" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1010BK, GM-1012</t>
         </is>
       </c>
       <c r="O41" s="34" t="inlineStr">
         <is>
-          <t>GM-1010BK, GM-1012</t>
-        </is>
-      </c>
-      <c r="P41" s="34" t="inlineStr">
-        <is>
           <t>GM-1010BK-1-Z.jpg,GM-1010BK-1.jpg</t>
         </is>
       </c>
-      <c r="Q41" s="34" t="n">
+      <c r="P41" s="34" t="n">
         <v>219</v>
       </c>
-      <c r="R41" s="35" t="n">
+      <c r="Q41" s="35" t="n">
         <v>219</v>
       </c>
+      <c r="R41" s="34" t="n">
+        <v>567</v>
+      </c>
       <c r="S41" s="34" t="n">
-        <v>567</v>
-      </c>
-      <c r="T41" s="34" t="n">
         <v>71.42</v>
       </c>
+      <c r="T41" s="34" t="inlineStr">
+        <is>
+          <t>28""W X 34 1/4""D X 46""H"</t>
+        </is>
+      </c>
       <c r="U41" s="34" t="inlineStr">
         <is>
-          <t>28""W X 34 1/4""D X 46""H"</t>
+          <t>Modern</t>
         </is>
       </c>
       <c r="V41" s="34" t="inlineStr">
         <is>
-          <t>Modern</t>
+          <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
       <c r="W41" s="34" t="inlineStr">
         <is>
-          <t>Steel, Mesh, Fabric</t>
+          <t>Modern,Black,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
       <c r="X41" s="34" t="inlineStr">
         <is>
-          <t>Modern,Black,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
-        </is>
-      </c>
-      <c r="Y41" s="34" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y41" s="34" t="n"/>
       <c r="Z41" s="34" t="n"/>
       <c r="AA41" s="34" t="n"/>
-      <c r="AB41" s="34" t="n"/>
-      <c r="AC41" s="34" t="n">
+      <c r="AB41" s="34" t="n">
         <v>6.6</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Outdoor, Chair, BREEZE</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="34" t="n"/>
-      <c r="B42" s="34" t="inlineStr">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>Dark Gray</t>
         </is>
       </c>
-      <c r="C42" s="34" t="n"/>
+      <c r="B42" s="34" t="n"/>
+      <c r="C42" s="34" t="inlineStr">
+        <is>
+          <t>GM-1010DG-SET</t>
+        </is>
+      </c>
       <c r="D42" s="34" t="inlineStr">
         <is>
-          <t>GM-1010DG-SET</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E42" s="34" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>BREEZE Swing Chair w/ Stand</t>
         </is>
       </c>
       <c r="G42" s="34" t="inlineStr">
-        <is>
-          <t>BREEZE Swing Chair w/ Stand</t>
-        </is>
-      </c>
-      <c r="H42" s="34" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 BREEZE Swing Chair w/ Stand creates a cohesive setup that feels inviting the moment you walk in. As a outdoor chair, it is designed to coordinate with matching pieces. The Modern character adds definition without feeling heavy. With Steel, Mesh, Fabric construction and Dark Gray tones, it blends durability with visual warmth.
@@ -5662,115 +6047,124 @@
 Weight: 71.42 lbs</t>
         </is>
       </c>
+      <c r="H42" s="34" t="inlineStr">
+        <is>
+          <t>BREEZE Swing Chair w/ Stand in Dark Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I42" s="34" t="inlineStr">
         <is>
-          <t>BREEZE Swing Chair w/ Stand in Dark Gray | GOODDEGG</t>
+          <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J42" s="34" t="inlineStr">
         <is>
-          <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BREEZE</t>
         </is>
       </c>
       <c r="K42" s="34" t="inlineStr">
         <is>
-          <t>BREEZE</t>
-        </is>
-      </c>
-      <c r="L42" s="34" t="inlineStr">
-        <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="M42" s="34" t="n"/>
+      <c r="L42" s="34" t="n"/>
+      <c r="M42" s="34" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N42" s="34" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1010DG, GM-1012</t>
         </is>
       </c>
       <c r="O42" s="34" t="inlineStr">
         <is>
-          <t>GM-1010DG, GM-1012</t>
-        </is>
-      </c>
-      <c r="P42" s="34" t="inlineStr">
-        <is>
           <t>GM-1010DG-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q42" s="34" t="n">
+      <c r="P42" s="34" t="n">
         <v>219</v>
       </c>
-      <c r="R42" s="35" t="n">
+      <c r="Q42" s="35" t="n">
         <v>219</v>
       </c>
+      <c r="R42" s="34" t="n">
+        <v>567</v>
+      </c>
       <c r="S42" s="34" t="n">
-        <v>567</v>
-      </c>
-      <c r="T42" s="34" t="n">
         <v>71.42</v>
       </c>
+      <c r="T42" s="34" t="inlineStr">
+        <is>
+          <t>28""W X 34 1/4""D X 46""H"</t>
+        </is>
+      </c>
       <c r="U42" s="34" t="inlineStr">
         <is>
-          <t>28""W X 34 1/4""D X 46""H"</t>
+          <t>Modern</t>
         </is>
       </c>
       <c r="V42" s="34" t="inlineStr">
         <is>
-          <t>Modern</t>
+          <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
       <c r="W42" s="34" t="inlineStr">
         <is>
-          <t>Steel, Mesh, Fabric</t>
+          <t>Modern,Dark Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
       <c r="X42" s="34" t="inlineStr">
         <is>
-          <t>Modern,Dark Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
-        </is>
-      </c>
-      <c r="Y42" s="34" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y42" s="34" t="n"/>
       <c r="Z42" s="34" t="n"/>
       <c r="AA42" s="34" t="n"/>
-      <c r="AB42" s="34" t="n"/>
-      <c r="AC42" s="34" t="n">
+      <c r="AB42" s="34" t="n">
         <v>6.6</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Outdoor, Chair, BREEZE</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="34" t="n"/>
-      <c r="B43" s="34" t="inlineStr">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>Light Gray</t>
         </is>
       </c>
-      <c r="C43" s="34" t="n"/>
+      <c r="B43" s="34" t="n"/>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>GM-1010LG-SET</t>
+        </is>
+      </c>
       <c r="D43" s="34" t="inlineStr">
         <is>
-          <t>GM-1010LG-SET</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E43" s="34" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>BREEZE Swing Chair w/ Stand</t>
         </is>
       </c>
       <c r="G43" s="34" t="inlineStr">
-        <is>
-          <t>BREEZE Swing Chair w/ Stand</t>
-        </is>
-      </c>
-      <c r="H43" s="34" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 BREEZE Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. This outdoor chair is made to fit naturally into the room. A Modern profile gives the space a refined, approachable look. Finished in Light Gray tones, the Steel, Mesh, Fabric build keeps the look polished and practical.
@@ -5790,115 +6184,124 @@
 Weight: 71.42 lbs</t>
         </is>
       </c>
+      <c r="H43" s="34" t="inlineStr">
+        <is>
+          <t>BREEZE Swing Chair w/ Stand in Light Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I43" s="34" t="inlineStr">
         <is>
-          <t>BREEZE Swing Chair w/ Stand in Light Gray | GOODDEGG</t>
+          <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J43" s="34" t="inlineStr">
         <is>
-          <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BREEZE</t>
         </is>
       </c>
       <c r="K43" s="34" t="inlineStr">
         <is>
-          <t>BREEZE</t>
-        </is>
-      </c>
-      <c r="L43" s="34" t="inlineStr">
-        <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="M43" s="34" t="n"/>
+      <c r="L43" s="34" t="n"/>
+      <c r="M43" s="34" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N43" s="34" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1010LG, GM-1012</t>
         </is>
       </c>
       <c r="O43" s="34" t="inlineStr">
         <is>
-          <t>GM-1010LG, GM-1012</t>
-        </is>
-      </c>
-      <c r="P43" s="34" t="inlineStr">
-        <is>
           <t>GM-1010LG-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q43" s="34" t="n">
+      <c r="P43" s="34" t="n">
         <v>219</v>
       </c>
-      <c r="R43" s="35" t="n">
+      <c r="Q43" s="35" t="n">
         <v>219</v>
       </c>
+      <c r="R43" s="34" t="n">
+        <v>567</v>
+      </c>
       <c r="S43" s="34" t="n">
-        <v>567</v>
-      </c>
-      <c r="T43" s="34" t="n">
         <v>71.42</v>
       </c>
+      <c r="T43" s="34" t="inlineStr">
+        <is>
+          <t>28""W X 34 1/4""D X 46""H"</t>
+        </is>
+      </c>
       <c r="U43" s="34" t="inlineStr">
         <is>
-          <t>28""W X 34 1/4""D X 46""H"</t>
+          <t>Modern</t>
         </is>
       </c>
       <c r="V43" s="34" t="inlineStr">
         <is>
-          <t>Modern</t>
+          <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
       <c r="W43" s="34" t="inlineStr">
         <is>
-          <t>Steel, Mesh, Fabric</t>
+          <t>Modern,Light Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
       <c r="X43" s="34" t="inlineStr">
         <is>
-          <t>Modern,Light Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
-        </is>
-      </c>
-      <c r="Y43" s="34" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y43" s="34" t="n"/>
       <c r="Z43" s="34" t="n"/>
       <c r="AA43" s="34" t="n"/>
-      <c r="AB43" s="34" t="n"/>
-      <c r="AC43" s="34" t="n">
+      <c r="AB43" s="34" t="n">
         <v>6.6</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Outdoor, Chair, BREEZE</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36" t="n"/>
-      <c r="B44" s="36" t="inlineStr">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C44" s="36" t="n"/>
+      <c r="B44" s="36" t="n"/>
+      <c r="C44" s="36" t="inlineStr">
+        <is>
+          <t>GM-1011BK-SET</t>
+        </is>
+      </c>
       <c r="D44" s="36" t="inlineStr">
         <is>
-          <t>GM-1011BK-SET</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E44" s="36" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="F44" s="36" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>CRUSH Swing Chair w/ Stand</t>
         </is>
       </c>
       <c r="G44" s="36" t="inlineStr">
-        <is>
-          <t>CRUSH Swing Chair w/ Stand</t>
-        </is>
-      </c>
-      <c r="H44" s="36" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 CRUSH Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Steel, Mesh, Fabric build keeps the look polished and practical.
@@ -5918,115 +6321,124 @@
 Weight: 68.12 lbs</t>
         </is>
       </c>
+      <c r="H44" s="36" t="inlineStr">
+        <is>
+          <t>CRUSH Swing Chair w/ Stand in Black | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I44" s="36" t="inlineStr">
         <is>
-          <t>CRUSH Swing Chair w/ Stand in Black | GOODDEGG</t>
+          <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J44" s="36" t="inlineStr">
         <is>
-          <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRUSH</t>
         </is>
       </c>
       <c r="K44" s="36" t="inlineStr">
         <is>
-          <t>CRUSH</t>
-        </is>
-      </c>
-      <c r="L44" s="36" t="inlineStr">
-        <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="M44" s="36" t="n"/>
+      <c r="L44" s="36" t="n"/>
+      <c r="M44" s="36" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N44" s="36" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1011BK, GM-1012</t>
         </is>
       </c>
       <c r="O44" s="36" t="inlineStr">
         <is>
-          <t>GM-1011BK, GM-1012</t>
-        </is>
-      </c>
-      <c r="P44" s="36" t="inlineStr">
-        <is>
           <t>GM-1011BK-WB-1.jpg,GM-1011BK-1.jpg</t>
         </is>
       </c>
-      <c r="Q44" s="36" t="n">
+      <c r="P44" s="36" t="n">
         <v>219</v>
       </c>
-      <c r="R44" s="37" t="n">
+      <c r="Q44" s="37" t="n">
         <v>219</v>
       </c>
+      <c r="R44" s="36" t="n">
+        <v>567</v>
+      </c>
       <c r="S44" s="36" t="n">
-        <v>567</v>
-      </c>
-      <c r="T44" s="36" t="n">
         <v>68.12</v>
       </c>
+      <c r="T44" s="36" t="inlineStr">
+        <is>
+          <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
+        </is>
+      </c>
       <c r="U44" s="36" t="inlineStr">
         <is>
-          <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
+          <t>Modern</t>
         </is>
       </c>
       <c r="V44" s="36" t="inlineStr">
         <is>
-          <t>Modern</t>
+          <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
       <c r="W44" s="36" t="inlineStr">
         <is>
-          <t>Steel, Mesh, Fabric</t>
+          <t>Modern,Black,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
       <c r="X44" s="36" t="inlineStr">
         <is>
-          <t>Modern,Black,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
-        </is>
-      </c>
-      <c r="Y44" s="36" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y44" s="36" t="n"/>
       <c r="Z44" s="36" t="n"/>
       <c r="AA44" s="36" t="n"/>
-      <c r="AB44" s="36" t="n"/>
-      <c r="AC44" s="36" t="n">
+      <c r="AB44" s="36" t="n">
         <v>6.8</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Outdoor, Chair, CRUSH</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="n"/>
-      <c r="B45" s="36" t="inlineStr">
+      <c r="A45" s="36" t="inlineStr">
         <is>
           <t>Dark Gray</t>
         </is>
       </c>
-      <c r="C45" s="36" t="n"/>
+      <c r="B45" s="36" t="n"/>
+      <c r="C45" s="36" t="inlineStr">
+        <is>
+          <t>GM-1011DG-SET</t>
+        </is>
+      </c>
       <c r="D45" s="36" t="inlineStr">
         <is>
-          <t>GM-1011DG-SET</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E45" s="36" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="F45" s="36" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>CRUSH Swing Chair w/ Stand</t>
         </is>
       </c>
       <c r="G45" s="36" t="inlineStr">
-        <is>
-          <t>CRUSH Swing Chair w/ Stand</t>
-        </is>
-      </c>
-      <c r="H45" s="36" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 CRUSH Swing Chair w/ Stand is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Modern character adds definition without feeling heavy. Built from Steel, Mesh, Fabric and finished in Dark Gray tones for a clean, cohesive look.
@@ -6046,115 +6458,124 @@
 Weight: 68.12 lbs</t>
         </is>
       </c>
+      <c r="H45" s="36" t="inlineStr">
+        <is>
+          <t>CRUSH Swing Chair w/ Stand in Dark Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I45" s="36" t="inlineStr">
         <is>
-          <t>CRUSH Swing Chair w/ Stand in Dark Gray | GOODDEGG</t>
+          <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J45" s="36" t="inlineStr">
         <is>
-          <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRUSH</t>
         </is>
       </c>
       <c r="K45" s="36" t="inlineStr">
         <is>
-          <t>CRUSH</t>
-        </is>
-      </c>
-      <c r="L45" s="36" t="inlineStr">
-        <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="M45" s="36" t="n"/>
+      <c r="L45" s="36" t="n"/>
+      <c r="M45" s="36" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N45" s="36" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1011DG, GM-1012</t>
         </is>
       </c>
       <c r="O45" s="36" t="inlineStr">
         <is>
-          <t>GM-1011DG, GM-1012</t>
-        </is>
-      </c>
-      <c r="P45" s="36" t="inlineStr">
-        <is>
           <t>GM-1011DG-WB-1.jpg,GM-1011DG-1.jpg</t>
         </is>
       </c>
-      <c r="Q45" s="36" t="n">
+      <c r="P45" s="36" t="n">
         <v>219</v>
       </c>
-      <c r="R45" s="37" t="n">
+      <c r="Q45" s="37" t="n">
         <v>219</v>
       </c>
+      <c r="R45" s="36" t="n">
+        <v>567</v>
+      </c>
       <c r="S45" s="36" t="n">
-        <v>567</v>
-      </c>
-      <c r="T45" s="36" t="n">
         <v>68.12</v>
       </c>
+      <c r="T45" s="36" t="inlineStr">
+        <is>
+          <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
+        </is>
+      </c>
       <c r="U45" s="36" t="inlineStr">
         <is>
-          <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
+          <t>Modern</t>
         </is>
       </c>
       <c r="V45" s="36" t="inlineStr">
         <is>
-          <t>Modern</t>
+          <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
       <c r="W45" s="36" t="inlineStr">
         <is>
-          <t>Steel, Mesh, Fabric</t>
+          <t>Modern,Dark Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
       <c r="X45" s="36" t="inlineStr">
         <is>
-          <t>Modern,Dark Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
-        </is>
-      </c>
-      <c r="Y45" s="36" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y45" s="36" t="n"/>
       <c r="Z45" s="36" t="n"/>
       <c r="AA45" s="36" t="n"/>
-      <c r="AB45" s="36" t="n"/>
-      <c r="AC45" s="36" t="n">
+      <c r="AB45" s="36" t="n">
         <v>6.8</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Outdoor, Chair, CRUSH</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36" t="n"/>
-      <c r="B46" s="36" t="inlineStr">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>Light Gray</t>
         </is>
       </c>
-      <c r="C46" s="36" t="n"/>
+      <c r="B46" s="36" t="n"/>
+      <c r="C46" s="36" t="inlineStr">
+        <is>
+          <t>GM-1011LG-SET</t>
+        </is>
+      </c>
       <c r="D46" s="36" t="inlineStr">
         <is>
-          <t>GM-1011LG-SET</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E46" s="36" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="F46" s="36" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>CRUSH Swing Chair w/ Stand</t>
         </is>
       </c>
       <c r="G46" s="36" t="inlineStr">
-        <is>
-          <t>CRUSH Swing Chair w/ Stand</t>
-        </is>
-      </c>
-      <c r="H46" s="36" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 CRUSH Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor chair is made to fit naturally into the room. A Modern profile gives the space a refined, approachable look. Crafted with Steel, Mesh, Fabric, then finished in Light Gray tones to suit a range of interiors.
@@ -6174,113 +6595,123 @@
 Weight: 68.12 lbs</t>
         </is>
       </c>
+      <c r="H46" s="36" t="inlineStr">
+        <is>
+          <t>CRUSH Swing Chair w/ Stand in Light Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I46" s="36" t="inlineStr">
         <is>
-          <t>CRUSH Swing Chair w/ Stand in Light Gray | GOODDEGG</t>
+          <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J46" s="36" t="inlineStr">
         <is>
-          <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRUSH</t>
         </is>
       </c>
       <c r="K46" s="36" t="inlineStr">
         <is>
-          <t>CRUSH</t>
-        </is>
-      </c>
-      <c r="L46" s="36" t="inlineStr">
-        <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="M46" s="36" t="n"/>
+      <c r="L46" s="36" t="n"/>
+      <c r="M46" s="36" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N46" s="36" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1011LG, GM-1012</t>
         </is>
       </c>
       <c r="O46" s="36" t="inlineStr">
         <is>
-          <t>GM-1011LG, GM-1012</t>
-        </is>
-      </c>
-      <c r="P46" s="36" t="inlineStr">
-        <is>
           <t>GM-1011LG-WB-1.jpg</t>
         </is>
       </c>
-      <c r="Q46" s="36" t="n">
+      <c r="P46" s="36" t="n">
         <v>219</v>
       </c>
-      <c r="R46" s="37" t="n">
+      <c r="Q46" s="37" t="n">
         <v>219</v>
       </c>
+      <c r="R46" s="36" t="n">
+        <v>567</v>
+      </c>
       <c r="S46" s="36" t="n">
-        <v>567</v>
-      </c>
-      <c r="T46" s="36" t="n">
         <v>68.12</v>
       </c>
+      <c r="T46" s="36" t="inlineStr">
+        <is>
+          <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
+        </is>
+      </c>
       <c r="U46" s="36" t="inlineStr">
         <is>
-          <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
+          <t>Modern</t>
         </is>
       </c>
       <c r="V46" s="36" t="inlineStr">
         <is>
-          <t>Modern</t>
+          <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
       <c r="W46" s="36" t="inlineStr">
         <is>
-          <t>Steel, Mesh, Fabric</t>
+          <t>Modern,Light Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
       <c r="X46" s="36" t="inlineStr">
         <is>
-          <t>Modern,Light Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
-        </is>
-      </c>
-      <c r="Y46" s="36" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y46" s="36" t="n"/>
       <c r="Z46" s="36" t="n"/>
       <c r="AA46" s="36" t="n"/>
-      <c r="AB46" s="36" t="n"/>
-      <c r="AC46" s="36" t="n">
+      <c r="AB46" s="36" t="n">
         <v>6.8</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Outdoor, Chair, CRUSH</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Beige/Natural Teak</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GM-2002-4PC</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GM-2002-4PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>MACKAY 2 Reclining Chairs and 2 Ottomans</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
-        <is>
-          <t>MACKAY 2 Reclining Chairs and 2 Ottomans</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MACKAY 2 Reclining Chairs and 2 Ottomans is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Beige or Natural Teak tones for a clean, cohesive look.
@@ -6295,109 +6726,119 @@
 Weight: 90.37 lbs</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>MACKAY 2 Reclining Chairs and 2 Ottomans | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MACKAY 2 Reclining Chairs and 2 Ottomans | GOODDEGG</t>
+          <t>The MACKAY Reclining Chairs and Ottomans adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>The MACKAY Reclining Chairs and Ottomans adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>MACKAY</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
           <t>2 Reclining Chairs + 2 Ottomans</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2002-2PK, GM-2003-2PK</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>GM-2002-2PK, GM-2003-2PK</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
           <t>GM-2002-WB-1.jpg,GM-2002-WB-2.jpg,GM-2002-WB-3.jpg,GM-2001-7PC+OT-1.jpg</t>
         </is>
       </c>
-      <c r="Q47" t="n">
+      <c r="P47" t="n">
         <v>299</v>
       </c>
-      <c r="R47" s="1" t="n">
+      <c r="Q47" s="1" t="n">
         <v>299</v>
       </c>
+      <c r="R47" t="n">
+        <v>777</v>
+      </c>
       <c r="S47" t="n">
-        <v>777</v>
-      </c>
-      <c r="T47" t="n">
         <v>90.37</v>
       </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>24 1/2"W X 27 1/2"D X 42 1/2"H</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>24 1/2"W X 27 1/2"D X 42 1/2"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Aluminum, FSC Certified 100% Teak Wood</t>
+          <t>Contemporary,Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Button-tufted cushion</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Contemporary,Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Button-tufted cushion</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AC47" t="n">
+      <c r="AB47" t="n">
         <v>12.9</v>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Outdoor, Chair, MACKAY</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GM-2006-7PC</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GM-2006-7PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Bar Table Set</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bar Table Set</t>
+          <t>CYPRUS 7 Pc. Bar Table Set</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
-        <is>
-          <t>CYPRUS 7 Pc. Bar Table Set</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 CYPRUS 7 Pc. Bar Table Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor bar table set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, Polyethylene Wicker, Polyspun construction and Gray tones, it blends durability with visual warmth.
@@ -6414,111 +6855,120 @@
 Weight: 144.5 lbs</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>CYPRUS 7 Pc. Bar Table Set in Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CYPRUS 7 Pc. Bar Table Set in Gray | GOODDEGG</t>
+          <t>The CYPRUS Bar Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>The CYPRUS Bar Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CYPRUS</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>CYPRUS</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
           <t>7 Pc. Bar Table Set</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2006-2, GM-2007-6PK, GM-2006-1</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>GM-2006-2, GM-2007-6PK, GM-2006-1</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
           <t>GM-2006-1-Z.jpg,GM-2006-2.jpg,GM-2006-3.jpg</t>
         </is>
       </c>
-      <c r="Q48" t="n">
+      <c r="P48" t="n">
         <v>949</v>
       </c>
-      <c r="R48" s="1" t="n">
+      <c r="Q48" s="1" t="n">
         <v>949</v>
       </c>
+      <c r="R48" t="n">
+        <v>2547</v>
+      </c>
       <c r="S48" t="n">
-        <v>2547</v>
-      </c>
-      <c r="T48" t="n">
         <v>144.5</v>
       </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>46"DIA X 39 1/2"H</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>46"DIA X 39 1/2"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Aluminum, Polyethylene Wicker, Polyspun</t>
+          <t>Contemporary,Gray,Aluminum, Polyethylene Wicker, Polyspun,Includes stainless steel ice bucket,Removable bucket with center cover,Stackable wicker chairs,Stainless steel footrest around base,Includes umbrella hole and space for umbrella base</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Contemporary,Gray,Aluminum, Polyethylene Wicker, Polyspun,Includes stainless steel ice bucket,Removable bucket with center cover,Stackable wicker chairs,Stainless steel footrest around base,Includes umbrella hole and space for umbrella base</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC48" t="n">
+      <c r="AB48" t="n">
         <v>37.7</v>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Outdoor, Bar Table Set, CYPRUS</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="38" t="n"/>
-      <c r="B49" s="38" t="inlineStr">
+      <c r="A49" s="38" t="inlineStr">
         <is>
           <t>Brown/Beige</t>
         </is>
       </c>
-      <c r="C49" s="38" t="n"/>
+      <c r="B49" s="38" t="n"/>
+      <c r="C49" s="38" t="inlineStr">
+        <is>
+          <t>CM-OS2136-SET5</t>
+        </is>
+      </c>
       <c r="D49" s="38" t="inlineStr">
         <is>
-          <t>CM-OS2136-SET5</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E49" s="38" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Sofa Set</t>
         </is>
       </c>
       <c r="F49" s="38" t="inlineStr">
         <is>
-          <t>Sofa Set</t>
+          <t>ILONA L-Sectional and Coffee Table and End Table</t>
         </is>
       </c>
       <c r="G49" s="38" t="inlineStr">
-        <is>
-          <t>ILONA L-Sectional and Coffee Table and End Table</t>
-        </is>
-      </c>
-      <c r="H49" s="38" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ILONA L-Sectional and Coffee Table and End Table is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor sofa set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, Polyester Canvas, Faux Rattan and finished in Brown or Beige tones for a clean, cohesive look.
@@ -6541,115 +6991,124 @@
 Weight: 204 lbs</t>
         </is>
       </c>
+      <c r="H49" s="38" t="inlineStr">
+        <is>
+          <t>ILONA L-Sectional and Coffee Table and End Table | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I49" s="38" t="inlineStr">
         <is>
-          <t>ILONA L-Sectional and Coffee Table and End Table | GOODDEGG</t>
+          <t>ILONA L-Sectional and Coffee Table and End Table offers relaxed seating for everyday. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J49" s="38" t="inlineStr">
         <is>
-          <t>ILONA L-Sectional and Coffee Table and End Table offers relaxed seating for everyday. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ILONA</t>
         </is>
       </c>
       <c r="K49" s="38" t="inlineStr">
         <is>
-          <t>ILONA</t>
-        </is>
-      </c>
-      <c r="L49" s="38" t="inlineStr">
-        <is>
           <t>L-Sectional + Coffee Table + End Table</t>
         </is>
       </c>
-      <c r="M49" s="38" t="n"/>
+      <c r="L49" s="38" t="n"/>
+      <c r="M49" s="38" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N49" s="38" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>CM-OS2136-A, CM-OS2136-C, CM-OS2136-E, CM-OS2136-F, CM-OS2136-G, CM-OS2136-H</t>
         </is>
       </c>
       <c r="O49" s="38" t="inlineStr">
         <is>
-          <t>CM-OS2136-A, CM-OS2136-C, CM-OS2136-E, CM-OS2136-F, CM-OS2136-G, CM-OS2136-H</t>
-        </is>
-      </c>
-      <c r="P49" s="38" t="inlineStr">
-        <is>
           <t>CM-OS2136-5.jpg,CM-OS2136-1.jpg,CM-OS2136-2.jpg</t>
         </is>
       </c>
-      <c r="Q49" s="38" t="n">
+      <c r="P49" s="38" t="n">
         <v>1082</v>
       </c>
-      <c r="R49" s="39" t="n">
+      <c r="Q49" s="39" t="n">
         <v>1082</v>
       </c>
+      <c r="R49" s="38" t="n">
+        <v>2817</v>
+      </c>
       <c r="S49" s="38" t="n">
-        <v>2817</v>
-      </c>
-      <c r="T49" s="38" t="n">
         <v>204</v>
       </c>
+      <c r="T49" s="38" t="inlineStr">
+        <is>
+          <t>L-SECTIONAL: 103 1/4"W X 79 1/4"D X 25 1/2-31"H</t>
+        </is>
+      </c>
       <c r="U49" s="38" t="inlineStr">
         <is>
-          <t>L-SECTIONAL: 103 1/4"W X 79 1/4"D X 25 1/2-31"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V49" s="38" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Polyester Canvas, Faux Rattan</t>
         </is>
       </c>
       <c r="W49" s="38" t="inlineStr">
         <is>
-          <t>Aluminum, Polyester Canvas, Faux Rattan</t>
+          <t>Contemporary,Brown/Beige,Aluminum, Polyester Canvas, Faux Rattan,Aluminum Frame,Modular Design,5mm Tempered Glass Table Tops,UV &amp; Water Resistant,Beige Fabric Cushions</t>
         </is>
       </c>
       <c r="X49" s="38" t="inlineStr">
         <is>
-          <t>Contemporary,Brown/Beige,Aluminum, Polyester Canvas, Faux Rattan,Aluminum Frame,Modular Design,5mm Tempered Glass Table Tops,UV &amp; Water Resistant,Beige Fabric Cushions</t>
-        </is>
-      </c>
-      <c r="Y49" s="38" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y49" s="38" t="n"/>
       <c r="Z49" s="38" t="n"/>
       <c r="AA49" s="38" t="n"/>
-      <c r="AB49" s="38" t="n"/>
-      <c r="AC49" s="38" t="n">
+      <c r="AB49" s="38" t="n">
         <v>45.7</v>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Outdoor, Sofa Set, ILONA</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="38" t="n"/>
-      <c r="B50" s="38" t="inlineStr">
+      <c r="A50" s="38" t="inlineStr">
         <is>
           <t>Brown/Beige</t>
         </is>
       </c>
-      <c r="C50" s="38" t="n"/>
+      <c r="B50" s="38" t="n"/>
+      <c r="C50" s="38" t="inlineStr">
+        <is>
+          <t>CM-OS2136-SET7</t>
+        </is>
+      </c>
       <c r="D50" s="38" t="inlineStr">
         <is>
-          <t>CM-OS2136-SET7</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E50" s="38" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Sofa Set</t>
         </is>
       </c>
       <c r="F50" s="38" t="inlineStr">
         <is>
-          <t>Sofa Set</t>
+          <t>ILONA L-Sectional and Coffee Table and End Table</t>
         </is>
       </c>
       <c r="G50" s="38" t="inlineStr">
-        <is>
-          <t>ILONA L-Sectional and Coffee Table and End Table</t>
-        </is>
-      </c>
-      <c r="H50" s="38" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 ILONA L-Sectional and Coffee Table and End Table offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor sofa set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, Polyester Canvas, Faux Rattan, then finished in Brown or Beige tones to suit a range of interiors.
@@ -6672,115 +7131,124 @@
 Weight: 179 lbs</t>
         </is>
       </c>
+      <c r="H50" s="38" t="inlineStr">
+        <is>
+          <t>ILONA L-Sectional and Coffee Table and End Table | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I50" s="38" t="inlineStr">
         <is>
-          <t>ILONA L-Sectional and Coffee Table and End Table | GOODDEGG</t>
+          <t>ILONA L-Sectional and Coffee Table and End Table offers relaxed seating for everyday. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J50" s="38" t="inlineStr">
         <is>
-          <t>ILONA L-Sectional and Coffee Table and End Table offers relaxed seating for everyday. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ILONA</t>
         </is>
       </c>
       <c r="K50" s="38" t="inlineStr">
         <is>
-          <t>ILONA</t>
-        </is>
-      </c>
-      <c r="L50" s="38" t="inlineStr">
-        <is>
           <t>L-Sectional + Coffee Table + End Table</t>
         </is>
       </c>
-      <c r="M50" s="38" t="n"/>
+      <c r="L50" s="38" t="n"/>
+      <c r="M50" s="38" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N50" s="38" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>CM-OS2136-A, CM-OS2136-C, CM-OS2136-E, CM-OS2136-F, CM-OS2136-G, CM-OS2136-H</t>
         </is>
       </c>
       <c r="O50" s="38" t="inlineStr">
         <is>
-          <t>CM-OS2136-A, CM-OS2136-C, CM-OS2136-E, CM-OS2136-F, CM-OS2136-G, CM-OS2136-H</t>
-        </is>
-      </c>
-      <c r="P50" s="38" t="inlineStr">
-        <is>
           <t>CM-OS2136-7.jpg,CM-OS2136-1.jpg,CM-OS2136-2.jpg</t>
         </is>
       </c>
-      <c r="Q50" s="38" t="n">
+      <c r="P50" s="38" t="n">
         <v>933</v>
       </c>
-      <c r="R50" s="39" t="n">
+      <c r="Q50" s="39" t="n">
         <v>933</v>
       </c>
+      <c r="R50" s="38" t="n">
+        <v>2427</v>
+      </c>
       <c r="S50" s="38" t="n">
-        <v>2427</v>
-      </c>
-      <c r="T50" s="38" t="n">
         <v>179</v>
       </c>
+      <c r="T50" s="38" t="inlineStr">
+        <is>
+          <t>L-SECTIONAL: 79 1/2"W X 79"D X 25 1/2-31"H</t>
+        </is>
+      </c>
       <c r="U50" s="38" t="inlineStr">
         <is>
-          <t>L-SECTIONAL: 79 1/2"W X 79"D X 25 1/2-31"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V50" s="38" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Polyester Canvas, Faux Rattan</t>
         </is>
       </c>
       <c r="W50" s="38" t="inlineStr">
         <is>
-          <t>Aluminum, Polyester Canvas, Faux Rattan</t>
+          <t>Contemporary,Brown/Beige,Aluminum, Polyester Canvas, Faux Rattan,Aluminum Frame,Modular Design,5mm Tempered Glass Table Tops,UV &amp; Water Resistant,Beige Fabric Cushions</t>
         </is>
       </c>
       <c r="X50" s="38" t="inlineStr">
         <is>
-          <t>Contemporary,Brown/Beige,Aluminum, Polyester Canvas, Faux Rattan,Aluminum Frame,Modular Design,5mm Tempered Glass Table Tops,UV &amp; Water Resistant,Beige Fabric Cushions</t>
-        </is>
-      </c>
-      <c r="Y50" s="38" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y50" s="38" t="n"/>
       <c r="Z50" s="38" t="n"/>
       <c r="AA50" s="38" t="n"/>
-      <c r="AB50" s="38" t="n"/>
-      <c r="AC50" s="38" t="n">
+      <c r="AB50" s="38" t="n">
         <v>40.2</v>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Outdoor, Sofa Set, ILONA</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="40" t="n"/>
-      <c r="B51" s="40" t="inlineStr">
+      <c r="A51" s="40" t="inlineStr">
         <is>
           <t>Beige/Natural Teak</t>
         </is>
       </c>
-      <c r="C51" s="40" t="n"/>
+      <c r="B51" s="40" t="n"/>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>GM-2001-5PC</t>
+        </is>
+      </c>
       <c r="D51" s="40" t="inlineStr">
         <is>
-          <t>GM-2001-5PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E51" s="40" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Dining Set</t>
         </is>
       </c>
       <c r="F51" s="40" t="inlineStr">
         <is>
-          <t>Patio Dining Set</t>
+          <t>MACKAY 5 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G51" s="40" t="inlineStr">
-        <is>
-          <t>MACKAY 5 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H51" s="40" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MACKAY 5 Pc. Patio Dining Set sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, FSC Certified 100% Teak Wood, then finished in Beige or Natural Teak tones to suit a range of interiors.
@@ -6798,115 +7266,124 @@
 Weight: 174.14 lbs</t>
         </is>
       </c>
+      <c r="H51" s="40" t="inlineStr">
+        <is>
+          <t>MACKAY 5 Pc. Patio Dining Set in Beige Natural Teak | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I51" s="40" t="inlineStr">
         <is>
-          <t>MACKAY 5 Pc. Patio Dining Set in Beige or Natural Teak | GOODDEGG</t>
+          <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J51" s="40" t="inlineStr">
         <is>
-          <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY</t>
         </is>
       </c>
       <c r="K51" s="40" t="inlineStr">
         <is>
-          <t>MACKAY</t>
-        </is>
-      </c>
-      <c r="L51" s="40" t="inlineStr">
-        <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M51" s="40" t="n"/>
+      <c r="L51" s="40" t="n"/>
+      <c r="M51" s="40" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N51" s="40" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2001, GM-2002-2PK</t>
         </is>
       </c>
       <c r="O51" s="40" t="inlineStr">
         <is>
-          <t>GM-2001, GM-2002-2PK</t>
-        </is>
-      </c>
-      <c r="P51" s="40" t="inlineStr">
-        <is>
           <t>GM-2001-1-Z.jpg,GM-2001-2.jpg,GM-2001-3.jpg,GM-2001-4.jpg,GM-2001-5.jpg,GM-2001-6.jpg,GM-2001-7.jpg,GM-2001-8.jpg,GM-2001-9.jpg,GM-2001-9.jpg</t>
         </is>
       </c>
-      <c r="Q51" s="40" t="n">
+      <c r="P51" s="40" t="n">
         <v>789</v>
       </c>
-      <c r="R51" s="41" t="n">
+      <c r="Q51" s="41" t="n">
         <v>789</v>
       </c>
+      <c r="R51" s="40" t="n">
+        <v>2127</v>
+      </c>
       <c r="S51" s="40" t="n">
-        <v>2127</v>
-      </c>
-      <c r="T51" s="40" t="n">
         <v>174.14</v>
       </c>
+      <c r="T51" s="40" t="inlineStr">
+        <is>
+          <t>61 1/2 - 84"L X 35 1/2"W X 30"H</t>
+        </is>
+      </c>
       <c r="U51" s="40" t="inlineStr">
         <is>
-          <t>61 1/2 - 84"L X 35 1/2"W X 30"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V51" s="40" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
       <c r="W51" s="40" t="inlineStr">
         <is>
-          <t>Aluminum, FSC Certified 100% Teak Wood</t>
+          <t>Contemporary,Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Extends from 61" to 84" w/ butterfly leaf,Seats up to 8 people,Level control table legs</t>
         </is>
       </c>
       <c r="X51" s="40" t="inlineStr">
         <is>
-          <t>Contemporary,Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Extends from 61" to 84" w/ butterfly leaf,Seats up to 8 people,Level control table legs</t>
-        </is>
-      </c>
-      <c r="Y51" s="40" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y51" s="40" t="n"/>
       <c r="Z51" s="40" t="n"/>
       <c r="AA51" s="40" t="n"/>
-      <c r="AB51" s="40" t="n"/>
-      <c r="AC51" s="40" t="n">
+      <c r="AB51" s="40" t="n">
         <v>28.3</v>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Dining Set, MACKAY</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="40" t="n"/>
-      <c r="B52" s="40" t="inlineStr">
+      <c r="A52" s="40" t="inlineStr">
         <is>
           <t>Gun Metal/Natural Teak</t>
         </is>
       </c>
-      <c r="C52" s="40" t="n"/>
+      <c r="B52" s="40" t="n"/>
+      <c r="C52" s="40" t="inlineStr">
+        <is>
+          <t>GM-2004-5PC</t>
+        </is>
+      </c>
       <c r="D52" s="40" t="inlineStr">
         <is>
-          <t>GM-2004-5PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E52" s="40" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Dining Set</t>
         </is>
       </c>
       <c r="F52" s="40" t="inlineStr">
         <is>
-          <t>Patio Dining Set</t>
+          <t>MACKAY 5 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G52" s="40" t="inlineStr">
-        <is>
-          <t>MACKAY 5 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H52" s="40" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Gather around MACKAY 5 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, FSC Certified 100% Teak Wood construction and Gun Metal or Natural Teak tones, it blends durability with visual warmth.
@@ -6924,113 +7401,123 @@
 Weight: 55.1 lbs</t>
         </is>
       </c>
+      <c r="H52" s="40" t="inlineStr">
+        <is>
+          <t>MACKAY 5 Pc. Patio Dining Set in Gun Metal Natural Teak | GOODDEG</t>
+        </is>
+      </c>
       <c r="I52" s="40" t="inlineStr">
         <is>
-          <t>MACKAY 5 Pc. Patio Dining Set in Gun Metal or Natural Teak | GOODDEG</t>
+          <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J52" s="40" t="inlineStr">
         <is>
-          <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY</t>
         </is>
       </c>
       <c r="K52" s="40" t="inlineStr">
         <is>
-          <t>MACKAY</t>
-        </is>
-      </c>
-      <c r="L52" s="40" t="inlineStr">
-        <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M52" s="40" t="n"/>
+      <c r="L52" s="40" t="n"/>
+      <c r="M52" s="40" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N52" s="40" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2004, GM-2005</t>
         </is>
       </c>
       <c r="O52" s="40" t="inlineStr">
         <is>
-          <t>GM-2004, GM-2005</t>
-        </is>
-      </c>
-      <c r="P52" s="40" t="inlineStr">
-        <is>
           <t>GM-2004-5PC.jpg,GM-2004-WB-4.jpg,GM-2004-WB-5.jpg</t>
         </is>
       </c>
-      <c r="Q52" s="40" t="n">
+      <c r="P52" s="40" t="n">
         <v>499</v>
       </c>
-      <c r="R52" s="41" t="n">
+      <c r="Q52" s="41" t="n">
         <v>499</v>
       </c>
+      <c r="R52" s="40" t="n">
+        <v>1047</v>
+      </c>
       <c r="S52" s="40" t="n">
-        <v>1047</v>
-      </c>
-      <c r="T52" s="40" t="n">
         <v>55.1</v>
       </c>
+      <c r="T52" s="40" t="inlineStr">
+        <is>
+          <t>59"L X 35 1/2"W X 29"H</t>
+        </is>
+      </c>
       <c r="U52" s="40" t="inlineStr">
         <is>
-          <t>59"L X 35 1/2"W X 29"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V52" s="40" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
       <c r="W52" s="40" t="inlineStr">
         <is>
-          <t>Aluminum, FSC Certified 100% Teak Wood</t>
+          <t>Contemporary,Gun Metal/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Seats up to 6 people,Level control table legs,Includes umbrella hole and cap</t>
         </is>
       </c>
       <c r="X52" s="40" t="inlineStr">
         <is>
-          <t>Contemporary,Gun Metal/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Seats up to 6 people,Level control table legs,Includes umbrella hole and cap</t>
-        </is>
-      </c>
-      <c r="Y52" s="40" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
+      <c r="Y52" s="40" t="n"/>
       <c r="Z52" s="40" t="n"/>
       <c r="AA52" s="40" t="n"/>
-      <c r="AB52" s="40" t="n"/>
-      <c r="AC52" s="40" t="n">
+      <c r="AB52" s="40" t="n">
         <v>50</v>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Dining Set, MACKAY</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Gun Metal/Beige/Natural Teak</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GM-2001-7PC</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GM-2001-7PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Dining Set</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Patio Dining Set</t>
+          <t>MACKAY 7 Pc. Patio Dining Set</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
-        <is>
-          <t>MACKAY 7 Pc. Patio Dining Set</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MACKAY 7 Pc. Patio Dining Set anchors the dining area with a cohesive look that feels easy and welcoming. As a outdoor patio dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Gun Metal or Beige or Natural Teak tones, the Aluminum, FSC Certified 100% Teak Wood build keeps the look polished and practical.
@@ -7048,109 +7535,119 @@
 Weight: 234.76 lbs</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>MACKAY 7 Pc. Patio Dining Set | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MACKAY 7 Pc. Patio Dining Set | GOODDEGG</t>
+          <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>MACKAY</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
           <t>7 Pc. Patio Dining Set</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2001, GM-2002-2PK</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>GM-2001, GM-2002-2PK</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
           <t>GM-2001-1-Z.jpg,GM-2001-2.jpg,GM-2001-3.jpg,GM-2001-4.jpg,GM-2001-5.jpg,GM-2001-6.jpg,GM-2001-7.jpg,GM-2001-8.jpg,GM-2001-9.jpg,GM-2001-9.jpg</t>
         </is>
       </c>
-      <c r="Q53" t="n">
+      <c r="P53" t="n">
         <v>999</v>
       </c>
-      <c r="R53" s="1" t="n">
+      <c r="Q53" s="1" t="n">
         <v>999</v>
       </c>
+      <c r="R53" t="n">
+        <v>2697</v>
+      </c>
       <c r="S53" t="n">
-        <v>2697</v>
-      </c>
-      <c r="T53" t="n">
         <v>234.76</v>
       </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>61 1/2 - 84"L X 35 1/2"W X 30"H</t>
+        </is>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>61 1/2 - 84"L X 35 1/2"W X 30"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Aluminum, FSC Certified 100% Teak Wood</t>
+          <t>Contemporary,Gun Metal/Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Extends from 61" to 84" w/ butterfly leaf,Seats up to 8 people,Level control table legs</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Contemporary,Gun Metal/Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Extends from 61" to 84" w/ butterfly leaf,Seats up to 8 people,Level control table legs</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC53" t="n">
+      <c r="AB53" t="n">
         <v>37.7</v>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Dining Set, MACKAY</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Gun Metal/Beige/Natural Teak</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GM-2001-7PC-OT</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>GM-2001-7PC-OT</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Dining Set</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Patio Dining Set</t>
+          <t>MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
-        <is>
-          <t>MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Gun Metal or Beige or Natural Teak tones for a clean, cohesive look.
@@ -7169,109 +7666,119 @@
 Weight: 203.89 lbs</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans | GOODDEGG</t>
+          <t>MACKAY Patio Dining w/ Ottomans makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>MACKAY Patio Dining w/ Ottomans makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>MACKAY</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
           <t>7 Pc. Patio Dining Set w/ 2 Ottomans</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-2001, GM-2002-2PK, GM-2003-2PK</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>GM-2001, GM-2002-2PK, GM-2003-2PK</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
           <t>GM-2001-7PC+OT-1.jpg,GM-2001-2.jpg,GM-2001-3.jpg,GM-2001-4.jpg,GM-2001-5.jpg,GM-2001-6.jpg,GM-2001-7.jpg,GM-2001-8.jpg,GM-2001-9.jpg,GM-2001-9.jpg</t>
         </is>
       </c>
-      <c r="Q54" t="n">
+      <c r="P54" t="n">
         <v>879</v>
       </c>
-      <c r="R54" s="1" t="n">
+      <c r="Q54" s="1" t="n">
         <v>879</v>
       </c>
+      <c r="R54" t="n">
+        <v>2367</v>
+      </c>
       <c r="S54" t="n">
-        <v>2367</v>
-      </c>
-      <c r="T54" t="n">
         <v>203.89</v>
       </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>61 1/2 - 84"L X 35 1/2"W X 30"H</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>61 1/2 - 84"L X 35 1/2"W X 30"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Aluminum, FSC Certified 100% Teak Wood</t>
+          <t>Contemporary,Gun Metal/Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Extends from 61" to 84" w/ butterfly leaf,Seats up to 8 people,Level control table legs</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Contemporary,Gun Metal/Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Extends from 61" to 84" w/ butterfly leaf,Seats up to 8 people,Level control table legs</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC54" t="n">
+      <c r="AB54" t="n">
         <v>31.8</v>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Dining Set, MACKAY</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GM-1001-6PC</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>GM-1001-6PC</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Outdoor</t>
+          <t>Patio Dining Table</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Patio Dining Table</t>
+          <t>MALIA 6 Pc. Patio Dining Set w/ Bench</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
-        <is>
-          <t>MALIA 6 Pc. Patio Dining Set w/ Bench</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Gather around MALIA 6 Pc. Patio Dining Set w/ Bench, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining table, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build keeps the look polished and practical.
@@ -7293,80 +7800,90 @@
 Weight: 199.5 lbs</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>MALIA 6 Pc. Patio Dining Set w/ Bench in Gray | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MALIA 6 Pc. Patio Dining Set w/ Bench in Gray | GOODDEGG</t>
+          <t>The MALIA Patio Dining w/ Bench creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>The MALIA Patio Dining w/ Bench creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MALIA</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>MALIA</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
           <t>6 Pc. Patio Dining Set w/ Bench</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>GM-1001, GM-1002-5PK</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>GM-1001, GM-1002-5PK</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
           <t>GM-1001-1-Z.jpg,GM-1001-2.jpg,GM-1001-3.jpg,GM-1001-WB-1.jpg,GM-1001-WB-2.jpg,GM-1001-WB-3.jpg</t>
         </is>
       </c>
-      <c r="Q55" t="n">
+      <c r="P55" t="n">
         <v>1299</v>
       </c>
-      <c r="R55" s="1" t="n">
+      <c r="Q55" s="1" t="n">
         <v>1299</v>
       </c>
+      <c r="R55" t="n">
+        <v>3297</v>
+      </c>
       <c r="S55" t="n">
-        <v>3297</v>
-      </c>
-      <c r="T55" t="n">
         <v>199.5</v>
       </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>59"L X 31 1/4"W X 26 3/4"H</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>59"L X 31 1/4"W X 26 3/4"H</t>
+          <t>Contemporary</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Contemporary</t>
+          <t>Aluminum, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Aluminum, Polyethylene Wicker, Polyspun</t>
+          <t>Contemporary,Gray,Aluminum, Polyethylene Wicker, Polyspun,Modular Design,Sectional and two sofas settings,Can be a dining set,Convertible ottoman to bench,Bench plate stored under table top,Flap-open side storage,Includes cushions, pillows, and protective covers</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Contemporary,Gray,Aluminum, Polyethylene Wicker, Polyspun,Modular Design,Sectional and two sofas settings,Can be a dining set,Convertible ottoman to bench,Bench plate stored under table top,Flap-open side storage,Includes cushions, pillows, and protective covers</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AC55" t="n">
+      <c r="AB55" t="n">
         <v>74.3</v>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Outdoor, Patio Dining Table, MALIA</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/FOA SETS/Outdoor-Set.xlsx
+++ b/FOA SETS/Outdoor-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -765,16 +765,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Gather around ALYCIA 7 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White or Beige or Gray tones, the Aluminum, Polyester Canvas, Glass, build keeps the look polished and practical.
-Features
-- White or Beige or Gray
-- Aluminum Construction
-- 5mm Tempered Glass Table Included items and dimensions:
-- Arm Chair w/ Cushion (6 or CTN): color: White or Beige or Gray; dimensions: 22 3 or 8" W x 27"D x 33 1 or 2-35 1 or 2" H; feature: Transitional
-Materials: Aluminum, Polyester Canvas, Glass.
-Color: White or Beige or Gray
-Weight: 217.82 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Gather around ALYCIA 7 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White or Beige or Gray tones, the Aluminum, Polyester Canvas, Glass, build keeps the look polished and practical.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- White or Beige or Gray&lt;br&gt;
+- Aluminum Construction&lt;br&gt;
+- 5mm Tempered Glass Table Included items and dimensions:&lt;br&gt;
+- Arm Chair w/ Cushion (6 or CTN): color: White or Beige or Gray; dimensions: 22 3 or 8" W x 27"D x 33 1 or 2-35 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Glass.&lt;br&gt;
+Color: White or Beige or Gray&lt;br&gt;
+Weight: 217.82 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -886,23 +886,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ANTIGUA 4 Pc. Patio Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Aluminum, Polyethylene Wicker, Polyspun and finished in Gun Metal or Brown or Gray tones for a clean, cohesive look.
-Product Dimensions: 63"L X 35 1/2"W X 17 3/4 - 27"H
-Features
-- Gun Metal or Brown or Gray
-- Adjustable backrest with gas springs
-- Ottoman as footrest or extra seats
-- Adjustable table height
-- Padded headrest cushion
-- Washable cushion covers
-- Table includes umbrella hole and cap Included items and dimensions:
-- Adjustable Table Height: color: Gun Metal or Brown or Gray; dimensions: 63" L x 35 1 or 2" W x 17 3 or 4 - 27" H; feature: Contemporary
-- Sofa: color: Gun Metal or Brown or Gray; dimensions: 76 3 or 4" L x 34" W x 43" H; feature: Contemporary
-- Arm Chair: color: Gun Metal or Brown or Gray; dimensions: 25 1 or 2" W x 29 1 or 2"D x 40 1 or 4" H; feature: Contemporary
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gun Metal or Brown or Gray
-Weight: 174 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ANTIGUA 4 Pc. Patio Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Aluminum, Polyethylene Wicker, Polyspun and finished in Gun Metal or Brown or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 63"L X 35 1/2"W X 17 3/4 - 27"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gun Metal or Brown or Gray&lt;br&gt;
+- Adjustable backrest with gas springs&lt;br&gt;
+- Ottoman as footrest or extra seats&lt;br&gt;
+- Adjustable table height&lt;br&gt;
+- Padded headrest cushion&lt;br&gt;
+- Washable cushion covers&lt;br&gt;
+- Table includes umbrella hole and cap Included items and dimensions:&lt;br&gt;
+- Adjustable Table Height: color: Gun Metal or Brown or Gray; dimensions: 63" L x 35 1 or 2" W x 17 3 or 4 - 27" H; feature: Contemporary&lt;br&gt;
+- Sofa: color: Gun Metal or Brown or Gray; dimensions: 76 3 or 4" L x 34" W x 43" H; feature: Contemporary&lt;br&gt;
+- Arm Chair: color: Gun Metal or Brown or Gray; dimensions: 25 1 or 2" W x 29 1 or 2"D x 40 1 or 4" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gun Metal or Brown or Gray&lt;br&gt;
+Weight: 174 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1019,24 +1019,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Polyethylene Wicker, Polyspun, then finished in Gun Metal or Brown or Gray tones to suit a range of interiors.
-Product Dimensions: 63"L X 35 1/2"W X 17 3/4 - 27"H
-Features
-- Gun Metal or Brown or Gray
-- Adjustable backrest with gas springs
-- Ottoman as footrest or extra seats
-- Adjustable table height
-- Padded headrest cushion
-- Washable cushion covers
-- Table includes umbrella hole and cap Included items and dimensions:
-- Adjustable Table Height: color: Gun Metal or Brown or Gray; dimensions: 63" L x 35 1 or 2" W x 17 3 or 4 - 27" H; feature: Contemporary
-- Sofa: color: Gun Metal or Brown or Gray; dimensions: 76 3 or 4" L x 34" W x 43" H; feature: Contemporary
-- Arm Chair: color: Gun Metal or Brown or Gray; dimensions: 25 1 or 2" W x 29 1 or 2"D x 40 1 or 4" H; feature: Contemporary
-- Ottoman (2 / CTN): color: Gun Metal or Brown or Gray; dimensions: 17 3 or 4" L x 17 3 or 4" W x 16 1 or 4" H; feature: Contemporary
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gun Metal or Brown or Gray
-Weight: 191.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Polyethylene Wicker, Polyspun, then finished in Gun Metal or Brown or Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 63"L X 35 1/2"W X 17 3/4 - 27"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gun Metal or Brown or Gray&lt;br&gt;
+- Adjustable backrest with gas springs&lt;br&gt;
+- Ottoman as footrest or extra seats&lt;br&gt;
+- Adjustable table height&lt;br&gt;
+- Padded headrest cushion&lt;br&gt;
+- Washable cushion covers&lt;br&gt;
+- Table includes umbrella hole and cap Included items and dimensions:&lt;br&gt;
+- Adjustable Table Height: color: Gun Metal or Brown or Gray; dimensions: 63" L x 35 1 or 2" W x 17 3 or 4 - 27" H; feature: Contemporary&lt;br&gt;
+- Sofa: color: Gun Metal or Brown or Gray; dimensions: 76 3 or 4" L x 34" W x 43" H; feature: Contemporary&lt;br&gt;
+- Arm Chair: color: Gun Metal or Brown or Gray; dimensions: 25 1 or 2" W x 29 1 or 2"D x 40 1 or 4" H; feature: Contemporary&lt;br&gt;
+- Ottoman (2 / CTN): color: Gun Metal or Brown or Gray; dimensions: 17 3 or 4" L x 17 3 or 4" W x 16 1 or 4" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gun Metal or Brown or Gray&lt;br&gt;
+Weight: 191.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1153,21 +1153,21 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AROSA 3 Pc. Fire Pit Counter Height Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Ceramic Tile, Polyrattan, Polyspun Fabric construction and Black or Gray tones, it blends durability with visual warmth.
-Product Dimensions: Table: 36.4"L X 36.4"W X 36.6"H, Chair: 25.1"W X 26.3"D X 44.8"H
-Features
-- Black or Gray
-- 360-Degree Swivel Seats
-- Tile Top Firepit Tabletop
-- Mixed Material Construction
-- Powder Coated Steel Frame
-- Easy To Assemble Included items and dimensions:
-- Fire Pit Counter Height Table: color: Black or Gray; dimensions: 36.5" W x 36.5"D x 36.5" H; feature: Contemporary
-- Swivel Counter Height Arm Chair (2 / CTN): color: Black or Gray; dimensions: 25" W x 26"D x 45" H; feature: Contemporary
-Materials: Steel, Ceramic Tile, Polyrattan, Polyspun Fabric.
-Color: Black or Gray
-Weight: 154 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AROSA 3 Pc. Fire Pit Counter Height Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Ceramic Tile, Polyrattan, Polyspun Fabric construction and Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Table: 36.4"L X 36.4"W X 36.6"H, Chair: 25.1"W X 26.3"D X 44.8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Gray&lt;br&gt;
+- 360-Degree Swivel Seats&lt;br&gt;
+- Tile Top Firepit Tabletop&lt;br&gt;
+- Mixed Material Construction&lt;br&gt;
+- Powder Coated Steel Frame&lt;br&gt;
+- Easy To Assemble Included items and dimensions:&lt;br&gt;
+- Fire Pit Counter Height Table: color: Black or Gray; dimensions: 36.5" W x 36.5"D x 36.5" H; feature: Contemporary&lt;br&gt;
+- Swivel Counter Height Arm Chair (2 / CTN): color: Black or Gray; dimensions: 25" W x 26"D x 45" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Ceramic Tile, Polyrattan, Polyspun Fabric.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 154 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1284,21 +1284,21 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BARBUDA 6 Pc. Conversation Set w/ Fire Pit is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyrattan, Polyspun Fabric and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: Fire Pit Table: 39"DIA X 27"H, Semi-circle Sectional: 64"W X 29"D X 33.5"H, End Table: 21"W X 28.5"D X 24"H
-Features
-- Modular Design
-- Tile Top Firepit Tabletop
-- FSC Certified Teak Wood
-- Mixed Material Construction
-- Powder Coated Steel Frame
-- Washable Cushion Covers Included items and dimensions:
-- Fire Pit Table: color: Gray; dimensions: 39" DIA x 27.2" H; feature: Contemporary
-- 5 Pc. Sectional Sofa w/ 2 End Tables: color: Gray or Natural; dimensions: Sofa: 64.25" W x 29"D x 33.5" H, End Table: 21.25" L x 28.7" W x 24" H; feature: Contemporary
-Materials: Steel, Polyrattan, Polyspun Fabric.
-Color: Gray
-Weight: 322.87 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BARBUDA 6 Pc. Conversation Set w/ Fire Pit is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyrattan, Polyspun Fabric and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Fire Pit Table: 39"DIA X 27"H, Semi-circle Sectional: 64"W X 29"D X 33.5"H, End Table: 21"W X 28.5"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Modular Design&lt;br&gt;
+- Tile Top Firepit Tabletop&lt;br&gt;
+- FSC Certified Teak Wood&lt;br&gt;
+- Mixed Material Construction&lt;br&gt;
+- Powder Coated Steel Frame&lt;br&gt;
+- Washable Cushion Covers Included items and dimensions:&lt;br&gt;
+- Fire Pit Table: color: Gray; dimensions: 39" DIA x 27.2" H; feature: Contemporary&lt;br&gt;
+- 5 Pc. Sectional Sofa w/ 2 End Tables: color: Gray or Natural; dimensions: Sofa: 64.25" W x 29"D x 33.5" H, End Table: 21.25" L x 28.7" W x 24" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyrattan, Polyspun Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 322.87 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1415,24 +1415,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BORDEAUX 6 Pc. Dining Set w/ Bench brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural or Light Gray or Beige tones, the Aluminum, Stainless Steel, Polyspun Fabric build keeps the look polished and practical.
-Product Dimensions: Table: 70.5"W X 38.5"D X 29"H, Chair: 20"W X 26.5"D X 32"H, Armless Chair: 20"W X 26.5"D X 32"H, Bench: 57"W X 16"D X 18.5"H
-Features
-- Natural or Light Gray or Beige
-- Tabletop Fire Pit with Storage Cabinet
-- Heat Output: 55000BTU
-- Propane Tank Capacity: 20 Pound
-- Stainless Steel Ice Chest with Cover
-- Hand-brushed Wood Texture
-- Washable Cushion Cover
-- UV &amp; Water-Resistant Included items and dimensions:
-- Side Chair (2 / CTN): color: Natural or Beige; dimensions: 20" W x 26.5"D x 33" H; feature: Contemporary
-- Bench: color: Natural or Beige; dimensions: 57" W x 16.5"D x 18.5" H; feature: Contemporary
-- Arm Chair (2 / CTN): color: Natural or Beige; dimensions: 24" W x 26.5"D x 33" H; feature: Contemporary
-Materials: Aluminum, Stainless Steel, Polyspun Fabric.
-Color: Natural or Light Gray or Beige
-Weight: 307.89 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BORDEAUX 6 Pc. Dining Set w/ Bench brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural or Light Gray or Beige tones, the Aluminum, Stainless Steel, Polyspun Fabric build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: Table: 70.5"W X 38.5"D X 29"H, Chair: 20"W X 26.5"D X 32"H, Armless Chair: 20"W X 26.5"D X 32"H, Bench: 57"W X 16"D X 18.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Natural or Light Gray or Beige&lt;br&gt;
+- Tabletop Fire Pit with Storage Cabinet&lt;br&gt;
+- Heat Output: 55000BTU&lt;br&gt;
+- Propane Tank Capacity: 20 Pound&lt;br&gt;
+- Stainless Steel Ice Chest with Cover&lt;br&gt;
+- Hand-brushed Wood Texture&lt;br&gt;
+- Washable Cushion Cover&lt;br&gt;
+- UV &amp;amp; Water-Resistant Included items and dimensions:&lt;br&gt;
+- Side Chair (2 / CTN): color: Natural or Beige; dimensions: 20" W x 26.5"D x 33" H; feature: Contemporary&lt;br&gt;
+- Bench: color: Natural or Beige; dimensions: 57" W x 16.5"D x 18.5" H; feature: Contemporary&lt;br&gt;
+- Arm Chair (2 / CTN): color: Natural or Beige; dimensions: 24" W x 26.5"D x 33" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Stainless Steel, Polyspun Fabric.&lt;br&gt;
+Color: Natural or Light Gray or Beige&lt;br&gt;
+Weight: 307.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1549,21 +1549,21 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JOHARI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural or Beige tones, the Steel, Fabric, Foam, PE Rattan build keeps the look polished and practical.
-Product Dimensions: COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5")
-Features
-- Natural or Beige
-- Powder Coated Steel Frame
-- 10mm Round Wicker
-- Seat Cushion
-- Pillow Back w/ 100% Fiber Fill
-- Weather Resistant Included items and dimensions:
-- Patio Chair (2 / CTN): dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
-- Patio Coffee Table: dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
-Materials: Steel, Fabric, Foam, PE Rattan.
-Color: Natural or Beige
-Weight: 91.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JOHARI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural or Beige tones, the Steel, Fabric, Foam, PE Rattan build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Natural or Beige&lt;br&gt;
+- Powder Coated Steel Frame&lt;br&gt;
+- 10mm Round Wicker&lt;br&gt;
+- Seat Cushion&lt;br&gt;
+- Pillow Back w/ 100% Fiber Fill&lt;br&gt;
+- Weather Resistant Included items and dimensions:&lt;br&gt;
+- Patio Chair (2 / CTN): dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")&lt;br&gt;
+- Patio Coffee Table: dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Fabric, Foam, PE Rattan.&lt;br&gt;
+Color: Natural or Beige&lt;br&gt;
+Weight: 91.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JOHARI 4 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel, Fabric, Foam, PE Rattan and finished in Natural or Beige tones for a clean, cohesive look.
-Product Dimensions: COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5"), BENCH: 58"W X 29"D X 25.5"H (SEAT HT: 16.5")
-Features
-- Natural or Beige
-- Powder Coated Steel Frame
-- 10mm Round Wicker
-- Seat Cushion
-- Pillow Back w/ 100% Fiber Fill
-- Weather Resistant Included items and dimensions:
-- Patio Chair (2 / CTN): dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
-- Patio Bench: dimensions: 58" W x 29"D x 25.5" H (SEAT HT: 16.5")
-- Patio Coffee Table: dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")
-Materials: Steel, Fabric, Foam, PE Rattan.
-Color: Natural or Beige
-Weight: 144.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JOHARI 4 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel, Fabric, Foam, PE Rattan and finished in Natural or Beige tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5"), BENCH: 58"W X 29"D X 25.5"H (SEAT HT: 16.5")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Natural or Beige&lt;br&gt;
+- Powder Coated Steel Frame&lt;br&gt;
+- 10mm Round Wicker&lt;br&gt;
+- Seat Cushion&lt;br&gt;
+- Pillow Back w/ 100% Fiber Fill&lt;br&gt;
+- Weather Resistant Included items and dimensions:&lt;br&gt;
+- Patio Chair (2 / CTN): dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")&lt;br&gt;
+- Patio Bench: dimensions: 58" W x 29"D x 25.5" H (SEAT HT: 16.5")&lt;br&gt;
+- Patio Coffee Table: dimensions: 30" W x 29"D x 25.5" H (SEAT HT: 16.5")&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Fabric, Foam, PE Rattan.&lt;br&gt;
+Color: Natural or Beige&lt;br&gt;
+Weight: 144.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1813,16 +1813,16 @@
       </c>
       <c r="G10" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KIMARA 3 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and finished in Black tones for a clean, cohesive look.
-Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H
-Features
-- Sturdy &amp; Durable Design
-- Weather Resistance Included items and dimensions:
-- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
-Color: Black
-Weight: 149.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KIMARA 3 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and finished in Black tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Weather Resistance Included items and dimensions:&lt;br&gt;
+- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 149.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" s="18" t="inlineStr">
@@ -1944,16 +1944,16 @@
       </c>
       <c r="G11" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KIMARA 3 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, then finished in Gray tones to suit a range of interiors.
-Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H
-Features
-- Sturdy &amp; Durable Design
-- Weather Resistance Included items and dimensions:
-- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
-Color: Gray
-Weight: 150.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KIMARA 3 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Weather Resistance Included items and dimensions:&lt;br&gt;
+- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 150.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" s="18" t="inlineStr">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KIMARA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam construction and Black tones, it blends durability with visual warmth.
-Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 25"W X 23"D X 30.5"H
-Features
-- Sturdy &amp; Durable Design
-- Weather Resistance Included items and dimensions:
-- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
-- Patio Chair (2 / CTN): color: Black; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
-Color: Black
-Weight: 175 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KIMARA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 25"W X 23"D X 30.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Weather Resistance Included items and dimensions:&lt;br&gt;
+- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary&lt;br&gt;
+- Patio Chair (2 / CTN): color: Black; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 175 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -2207,17 +2207,17 @@
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KIMARA 5 Pc. Patio Dining Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Gray tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam build keeps the look polished and practical.
-Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 22.5"W X 23.5"D X 35"H
-Features
-- Sturdy &amp; Durable Design
-- Weather Resistance Included items and dimensions:
-- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary
-- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
-Color: Gray
-Weight: 174.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KIMARA 5 Pc. Patio Dining Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Gray tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 22.5"W X 23.5"D X 35"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Weather Resistance Included items and dimensions:&lt;br&gt;
+- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary&lt;br&gt;
+- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 174.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -2339,21 +2339,21 @@
       </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KYUSHU 4 Pc. Patio Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Acacia Wood, Polyester construction and Beige or Natural tones, it blends durability with visual warmth.
-Product Dimensions: LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H
-Features
-- Rustic
-- Beige or Natural
-- Weather-resistant
-- Natural acacia wood
-- Includes tie-back cushions
-- Easy to assemble with included hardware kit Included items and dimensions:
-- Table and Loveseat: color: Beige or Natural; dimensions: TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H; feature: Rustic
-- Chair (2 / CTN): color: Beige or Natural; dimensions: CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H; feature: Rustic
-Materials: Acacia Wood, Polyester.
-Color: Beige or Natural
-Weight: 125.04 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KYUSHU 4 Pc. Patio Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Acacia Wood, Polyester construction and Beige or Natural tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Rustic&lt;br&gt;
+- Beige or Natural&lt;br&gt;
+- Weather-resistant&lt;br&gt;
+- Natural acacia wood&lt;br&gt;
+- Includes tie-back cushions&lt;br&gt;
+- Easy to assemble with included hardware kit Included items and dimensions:&lt;br&gt;
+- Table and Loveseat: color: Beige or Natural; dimensions: TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H; feature: Rustic&lt;br&gt;
+- Chair (2 / CTN): color: Beige or Natural; dimensions: CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H; feature: Rustic&lt;/p&gt;
+&lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
+Color: Beige or Natural&lt;br&gt;
+Weight: 125.04 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -2475,21 +2475,21 @@
       </c>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KYUSHU 4 Pc. Patio Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Black or Natural tones, the Acacia Wood, Polyester build keeps the look polished and practical.
-Product Dimensions: LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H
-Features
-- Rustic
-- Black or Natural
-- Weather-resistant
-- Natural acacia wood
-- Includes tie-back cushions
-- Easy to assemble with included hardware kit Included items and dimensions:
-- Table and Loveseat: color: Black or Natural; dimensions: TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H; feature: Rustic
-- Chair (2 / CTN): color: Black or Natural; dimensions: CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H; feature: Rustic
-Materials: Acacia Wood, Polyester.
-Color: Black or Natural
-Weight: 125.04 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KYUSHU 4 Pc. Patio Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Black or Natural tones, the Acacia Wood, Polyester build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Rustic&lt;br&gt;
+- Black or Natural&lt;br&gt;
+- Weather-resistant&lt;br&gt;
+- Natural acacia wood&lt;br&gt;
+- Includes tie-back cushions&lt;br&gt;
+- Easy to assemble with included hardware kit Included items and dimensions:&lt;br&gt;
+- Table and Loveseat: color: Black or Natural; dimensions: TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H; feature: Rustic&lt;br&gt;
+- Chair (2 / CTN): color: Black or Natural; dimensions: CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H; feature: Rustic&lt;/p&gt;
+&lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
+Color: Black or Natural&lt;br&gt;
+Weight: 125.04 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -2610,21 +2610,21 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LOTUS 5 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black or Light Brown tones, the Aluminum, Fabric, Ceramic build keeps the look polished and practical.
-Product Dimensions: Sofa: 74 1/4"W X 29 1/2"D X 34"H, Coffee Table: 47 1/4"L X 25 1/2"W X 15 1/2"H, Chair: 28 1/4"W X 26 1/2"D X 37"H
-Features
-- Black or Light Brown
-- Washable Cushion Covers
-- Open Storage Shelf
-- Slatted Tabletop Design
-- Durable Aluminum Frame
-- Ceramic Tabletop on End Table Included items and dimensions:
-- Sofa &amp; Coffee Table Set: color: Black or Light Brown; dimensions: Sofa: 74" W x 29.5"D x 34" H, Table: 47" W x 25.5"D x 15.5" H; feature: Contemporary
-- 3 Pc. Patio Set: color: Black or Light Brown; dimensions: Chair: 74" W x 29.5"D x 34" H, Table: 28" W x 26.5"D x 37" H; feature: Contemporary
-Materials: Aluminum, Fabric, Ceramic.
-Color: Black or Light Brown
-Weight: 96.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LOTUS 5 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black or Light Brown tones, the Aluminum, Fabric, Ceramic build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: Sofa: 74 1/4"W X 29 1/2"D X 34"H, Coffee Table: 47 1/4"L X 25 1/2"W X 15 1/2"H, Chair: 28 1/4"W X 26 1/2"D X 37"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Light Brown&lt;br&gt;
+- Washable Cushion Covers&lt;br&gt;
+- Open Storage Shelf&lt;br&gt;
+- Slatted Tabletop Design&lt;br&gt;
+- Durable Aluminum Frame&lt;br&gt;
+- Ceramic Tabletop on End Table Included items and dimensions:&lt;br&gt;
+- Sofa &amp;amp; Coffee Table Set: color: Black or Light Brown; dimensions: Sofa: 74" W x 29.5"D x 34" H, Table: 47" W x 25.5"D x 15.5" H; feature: Contemporary&lt;br&gt;
+- 3 Pc. Patio Set: color: Black or Light Brown; dimensions: Chair: 74" W x 29.5"D x 34" H, Table: 28" W x 26.5"D x 37" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Fabric, Ceramic.&lt;br&gt;
+Color: Black or Light Brown&lt;br&gt;
+Weight: 96.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYON 5 Pc. Game Table Set w/ 4 Arm Chairs brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black or Natural or Brown tones, the Aluminum, Outdoor Fabric build keeps the look polished and practical.
-Product Dimensions: Table: 50.5" DIA X 29.5"H, Arm Chair: 20"W X 26.5"D X 32.25"H
-Features
-- Black or Natural or Brown
-- Inlaid Chess Board
-- Teak Poker Race Track Table
-- UV &amp; Rain-Resistant
-- FSC Certified Teak Wood Included items and dimensions:
-- Game Table: color: Black or Natural or Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary
-- Arm Chair (2 / CTN): color: Natural or Beige; dimensions: 24" W x 26.5"D x 33" H; feature: Contemporary
-Materials: Aluminum, Outdoor Fabric.
-Color: Black or Natural or Brown
-Weight: 184.85 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYON 5 Pc. Game Table Set w/ 4 Arm Chairs brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black or Natural or Brown tones, the Aluminum, Outdoor Fabric build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: Table: 50.5" DIA X 29.5"H, Arm Chair: 20"W X 26.5"D X 32.25"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Natural or Brown&lt;br&gt;
+- Inlaid Chess Board&lt;br&gt;
+- Teak Poker Race Track Table&lt;br&gt;
+- UV &amp;amp; Rain-Resistant&lt;br&gt;
+- FSC Certified Teak Wood Included items and dimensions:&lt;br&gt;
+- Game Table: color: Black or Natural or Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary&lt;br&gt;
+- Arm Chair (2 / CTN): color: Natural or Beige; dimensions: 24" W x 26.5"D x 33" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Outdoor Fabric.&lt;br&gt;
+Color: Black or Natural or Brown&lt;br&gt;
+Weight: 184.85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2871,20 +2871,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYON 5 Pc. Game Table Set w/ 4 Armless Chairs is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, Outdoor Fabric and finished in Black or Natural or Brown tones for a clean, cohesive look.
-Product Dimensions: Table: 50.5" DIA X 29.5"H
-Features
-- Black or Natural or Brown
-- Inlaid Chess Board
-- Teak Poker Race Track Table
-- UV &amp; Rain-Resistant
-- FSC Certified Teak Wood Included items and dimensions:
-- Game Table: color: Black or Natural or Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary
-- Side Chair (2 / CTN): color: Natural or Beige; dimensions: 20" W x 26.5"D x 33" H; feature: Contemporary
-Materials: Aluminum, Outdoor Fabric.
-Color: Black or Natural or Brown
-Weight: 175.17 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYON 5 Pc. Game Table Set w/ 4 Armless Chairs is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, Outdoor Fabric and finished in Black or Natural or Brown tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Table: 50.5" DIA X 29.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Natural or Brown&lt;br&gt;
+- Inlaid Chess Board&lt;br&gt;
+- Teak Poker Race Track Table&lt;br&gt;
+- UV &amp;amp; Rain-Resistant&lt;br&gt;
+- FSC Certified Teak Wood Included items and dimensions:&lt;br&gt;
+- Game Table: color: Black or Natural or Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary&lt;br&gt;
+- Side Chair (2 / CTN): color: Natural or Beige; dimensions: 20" W x 26.5"D x 33" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Outdoor Fabric.&lt;br&gt;
+Color: Black or Natural or Brown&lt;br&gt;
+Weight: 175.17 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3001,20 +3001,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Aluminum, Outdoor Fabric, then finished in Black or Natural or Brown tones to suit a range of interiors.
-Product Dimensions: Table: 50.5" DIA X 29.5"H
-Features
-- Black or Natural or Brown
-- Inlaid Chess Board
-- Teak Poker Race Track Table
-- UV &amp; Rain-Resistant
-- FSC Certified Teak Wood Included items and dimensions:
-- Game Table: color: Black or Natural or Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary
-- Stacking Chair: color: Gun Metal or Natural Teak; dimensions: 22.5" W x 25"D x 34" H; feature: Contemporary
-Materials: Aluminum, Outdoor Fabric.
-Color: Black or Natural or Brown
-Weight: 105.33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Aluminum, Outdoor Fabric, then finished in Black or Natural or Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Table: 50.5" DIA X 29.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Natural or Brown&lt;br&gt;
+- Inlaid Chess Board&lt;br&gt;
+- Teak Poker Race Track Table&lt;br&gt;
+- UV &amp;amp; Rain-Resistant&lt;br&gt;
+- FSC Certified Teak Wood Included items and dimensions:&lt;br&gt;
+- Game Table: color: Black or Natural or Brown; dimensions: 50.5"DIA x 29.5" H; feature: Contemporary&lt;br&gt;
+- Stacking Chair: color: Gun Metal or Natural Teak; dimensions: 22.5" W x 25"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Outdoor Fabric.&lt;br&gt;
+Color: Black or Natural or Brown&lt;br&gt;
+Weight: 105.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MONZA 7 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Tempered Glass, Textilene, then finished in Gun Metal or Gray tones to suit a range of interiors.
-Product Dimensions: Table: 63" (EXTENDED: 94 1/2") L X 35 1/2"W X 29 1/2"H
-Features
-- Gun Metal or Gray
-- Extendable Top
-- 5-way Adjustable Seat Back Included items and dimensions:
-- Extendable Dining Table: color: Gun Metal or Gray; dimensions: 63" (EXTENDED 94.5")W x 35.5"D x 29.5" H; feature: Contemporary
-- Adjustable Chairs (2 / CTN): color: Gun Metal or Gray; dimensions: 27.5"D x 23"D x 43" H; feature: Contemporary
-Materials: Aluminum, Tempered Glass, Textilene.
-Color: Gun Metal or Gray</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MONZA 7 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Tempered Glass, Textilene, then finished in Gun Metal or Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Table: 63" (EXTENDED: 94 1/2") L X 35 1/2"W X 29 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gun Metal or Gray&lt;br&gt;
+- Extendable Top&lt;br&gt;
+- 5-way Adjustable Seat Back Included items and dimensions:&lt;br&gt;
+- Extendable Dining Table: color: Gun Metal or Gray; dimensions: 63" (EXTENDED 94.5")W x 35.5"D x 29.5" H; feature: Contemporary&lt;br&gt;
+- Adjustable Chairs (2 / CTN): color: Gun Metal or Gray; dimensions: 27.5"D x 23"D x 43" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Tempered Glass, Textilene.&lt;br&gt;
+Color: Gun Metal or Gray&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3255,17 +3255,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NIAMBI 3 Pc. Patio Bistro Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber construction and Natural tones, it blends durability with visual warmth.
-Product Dimensions: Table: 26.6" x 23.6" x 29.1"H, Chair: 21.3" x 25.2" x 34.3"H
-Features
-- Marble Base
-- Sturdy &amp; Durable Design
-- Easy to store Included items and dimensions:
-- Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary
-Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.
-Color: Natural
-Weight: 50.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NIAMBI 3 Pc. Patio Bistro Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber construction and Natural tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Table: 26.6" x 23.6" x 29.1"H, Chair: 21.3" x 25.2" x 34.3"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Marble Base&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Easy to store Included items and dimensions:&lt;br&gt;
+- Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 50.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3382,17 +3382,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NIAMBI 3 Pc. Patio Dining Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber build keeps the look polished and practical.
-Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 22.5"W X 23.5"D X 35"H
-Features
-- Marble Base
-- Sturdy &amp; Durable Design
-- Easy to store Included items and dimensions:
-- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary
-Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.
-Color: Gray
-Weight: 58 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NIAMBI 3 Pc. Patio Dining Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 22.5"W X 23.5"D X 35"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Marble Base&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Easy to store Included items and dimensions:&lt;br&gt;
+- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3510,17 +3510,17 @@
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NIAMBI 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 22.5"W X 23.5"D X 35"H
-Features
-- Marble Base
-- Sturdy &amp; Durable Design
-- Easy to store Included items and dimensions:
-- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary
-Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.
-Color: Gray
-Weight: 82.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NIAMBI 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 22.5"W X 23.5"D X 35"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Marble Base&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Easy to store Included items and dimensions:&lt;br&gt;
+- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 82.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -3642,17 +3642,17 @@
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NIAMBI 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber, then finished in Natural tones to suit a range of interiors.
-Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 21"W X 25"D X 34"H
-Features
-- Marble Base
-- Sturdy &amp; Durable Design
-- Easy to store Included items and dimensions:
-- Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary
-Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.
-Color: Natural
-Weight: 66.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NIAMBI 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber, then finished in Natural tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 21"W X 25"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Marble Base&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Easy to store Included items and dimensions:&lt;br&gt;
+- Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 66.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -3773,18 +3773,18 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NUSA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Teak Wood construction and Natural tones, it blends durability with visual warmth.
-Product Dimensions: Table: 78 3/4"L X 47 1/4"W X 29 1/2"H
-Features
-- Slat Design
-- Pedestal Base
-- 5-way Adjustable Chair
-- Sand Finish Included items and dimensions:
-- Folding Arm Chair: color: Natural; dimensions: 22" W x 24.5"D x 37.5" H; feature: Transitional
-Materials: Teak Wood.
-Color: Natural
-Weight: 307.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NUSA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Teak Wood construction and Natural tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Table: 78 3/4"L X 47 1/4"W X 29 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Slat Design&lt;br&gt;
+- Pedestal Base&lt;br&gt;
+- 5-way Adjustable Chair&lt;br&gt;
+- Sand Finish Included items and dimensions:&lt;br&gt;
+- Folding Arm Chair: color: Natural; dimensions: 22" W x 24.5"D x 37.5" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Teak Wood.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 307.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3901,23 +3901,23 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PALMA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Glass, Polyspun Fabric construction and Black or Gray tones, it blends durability with visual warmth.
-Product Dimensions: Table: 70.8"L X 35.4"W X 27.9"H, Chair: 24"W X 33"D X 38.3"H
-Features
-- Black or Gray
-- 5mm Tempered Water Wave Glass Tabletop
-- Powder Coated Steel Frame
-- Reclining Backrest
-- Washable Cushion Cover
-- Built-In Umbrella Hole
-- Tie-Back Cushions
-- Lumbar Pillows Included Included items and dimensions:
-- Dining Table: color: Black or Gray; dimensions: 71" W x 35.5"D x 28" H; feature: Contemporary
-- Adjustable Chairs (6 or CTN): color: Black or Gray; dimensions: 24" W x 33"D x 38" H; feature: Contemporary
-Materials: Steel, Glass, Polyspun Fabric.
-Color: Black or Gray
-Weight: 190.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PALMA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Glass, Polyspun Fabric construction and Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Table: 70.8"L X 35.4"W X 27.9"H, Chair: 24"W X 33"D X 38.3"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Gray&lt;br&gt;
+- 5mm Tempered Water Wave Glass Tabletop&lt;br&gt;
+- Powder Coated Steel Frame&lt;br&gt;
+- Reclining Backrest&lt;br&gt;
+- Washable Cushion Cover&lt;br&gt;
+- Built-In Umbrella Hole&lt;br&gt;
+- Tie-Back Cushions&lt;br&gt;
+- Lumbar Pillows Included Included items and dimensions:&lt;br&gt;
+- Dining Table: color: Black or Gray; dimensions: 71" W x 35.5"D x 28" H; feature: Contemporary&lt;br&gt;
+- Adjustable Chairs (6 or CTN): color: Black or Gray; dimensions: 24" W x 33"D x 38" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Glass, Polyspun Fabric.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 190.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4034,19 +4034,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SARABI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Black or Natural tones, the Steel, Wicker, Fabric build keeps the look polished and practical.
-Product Dimensions: TABLE: 21.5"W X 21.5"D X 15.5"H, CHAIR: 25.5"W X 28.5"D X 26.5"H (SEAT HT: 14", SEAT DP: 20")
-Features
-- Black or Natural
-- Powder-coated Steel Frame
-- 3.5mm Round Wicker
-- Sloped Back &amp; Curbed Seat Lounge Chair Included items and dimensions:
-- Patio Side Table: dimensions: 21.5" W x 21.5"D x 15.5" H
-- Patio Chair (2 / CTN): dimensions: CHAIR: 25.5" W x 28.5"D x 26.5" H (SEAT HT: 14", SEAT DP: 20")
-Materials: Steel, Wicker, Fabric.
-Color: Black or Natural
-Weight: 11.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SARABI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Black or Natural tones, the Steel, Wicker, Fabric build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: TABLE: 21.5"W X 21.5"D X 15.5"H, CHAIR: 25.5"W X 28.5"D X 26.5"H (SEAT HT: 14", SEAT DP: 20")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Natural&lt;br&gt;
+- Powder-coated Steel Frame&lt;br&gt;
+- 3.5mm Round Wicker&lt;br&gt;
+- Sloped Back &amp;amp; Curbed Seat Lounge Chair Included items and dimensions:&lt;br&gt;
+- Patio Side Table: dimensions: 21.5" W x 21.5"D x 15.5" H&lt;br&gt;
+- Patio Chair (2 / CTN): dimensions: CHAIR: 25.5" W x 28.5"D x 26.5" H (SEAT HT: 14", SEAT DP: 20")&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Wicker, Fabric.&lt;br&gt;
+Color: Black or Natural&lt;br&gt;
+Weight: 11.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4163,20 +4163,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SEGOVIA 5 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Steel, Polyethylene Wicker, Ceremic, Polyspun, then finished in Navy or Black or Gray tones to suit a range of interiors.
-Product Dimensions: Firepit Table: 40"L X 40"W X 26 1/2"H Chair: 30 3/4"W X 25 1/2"D X 30 3/4"H"
-Features
-- Navy or Black or Gray
-- 360-degree Swivel Glider
-- Gray Ceramic Tile Table Top
-- Fire Pit Table with Tile Table Top
-- Includes Cushions and Pillows Included items and dimensions:
-- Fire Pit Table: color: Black or Gray; dimensions: 40" W x 40"D x 26.5" H; feature: Contemporary
-- Swivel Glider Arm Chair (2 / CTN): color: Navy or Black or Gray; dimensions: 30.5" W x 25.5"D x 30.5" H; feature: Transitional
-Materials: Steel, Polyethylene Wicker, Ceremic, Polyspun.
-Color: Navy or Black or Gray
-Weight: 263.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SEGOVIA 5 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Steel, Polyethylene Wicker, Ceremic, Polyspun, then finished in Navy or Black or Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Firepit Table: 40"L X 40"W X 26 1/2"H Chair: 30 3/4"W X 25 1/2"D X 30 3/4"H"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Navy or Black or Gray&lt;br&gt;
+- 360-degree Swivel Glider&lt;br&gt;
+- Gray Ceramic Tile Table Top&lt;br&gt;
+- Fire Pit Table with Tile Table Top&lt;br&gt;
+- Includes Cushions and Pillows Included items and dimensions:&lt;br&gt;
+- Fire Pit Table: color: Black or Gray; dimensions: 40" W x 40"D x 26.5" H; feature: Contemporary&lt;br&gt;
+- Swivel Glider Arm Chair (2 / CTN): color: Navy or Black or Gray; dimensions: 30.5" W x 25.5"D x 30.5" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyethylene Wicker, Ceremic, Polyspun.&lt;br&gt;
+Color: Navy or Black or Gray&lt;br&gt;
+Weight: 263.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4293,20 +4293,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SEGOVIA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Steel, Polyethylene Wicker, Polyspun construction and Black or Gray tones, it blends durability with visual warmth.
-Product Dimensions: 40"L X 40"W X 26 1/2"H
-Features
-- Black or Gray
-- 360-degree swivel rockers
-- Gray ceramic tile table top
-- Fire pit table with tile-top and wicker base
-- Includes cushions and pillows Included items and dimensions:
-- Fire Pit Table: color: Black or Gray; dimensions: 40" W x 40"D x 26.5" H; feature: Contemporary
-- Swivel Chair: color: Black or Gray; dimensions: 29 3 or 4" W x 27 1 or 4"D x 33 1 or 4" H; feature: Contemporary
-Materials: Steel, Polyethylene Wicker, Polyspun.
-Color: Black or Gray
-Weight: 248.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SEGOVIA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Steel, Polyethylene Wicker, Polyspun construction and Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 40"L X 40"W X 26 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Gray&lt;br&gt;
+- 360-degree swivel rockers&lt;br&gt;
+- Gray ceramic tile table top&lt;br&gt;
+- Fire pit table with tile-top and wicker base&lt;br&gt;
+- Includes cushions and pillows Included items and dimensions:&lt;br&gt;
+- Fire Pit Table: color: Black or Gray; dimensions: 40" W x 40"D x 26.5" H; feature: Contemporary&lt;br&gt;
+- Swivel Chair: color: Black or Gray; dimensions: 29 3 or 4" W x 27 1 or 4"D x 33 1 or 4" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 248.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4424,20 +4424,20 @@
       </c>
       <c r="G30" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SINTRA 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyethylene Wicker, Polyspun and finished in Black or Gray tones for a clean, cohesive look.
-Product Dimensions: 40"L X 40"W X 28"H
-Features
-- Black or Gray
-- Ceramic tile table top
-- Rust-resistant
-- powder-coated steel frame
-- Includes umbrella hole and cap Included items and dimensions:
-- Patio Dining Table: color: Black or Gray; dimensions: 40" L x 40" W x 28" H; feature: Contemporary
-- Swivel Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
-Materials: Steel, Polyethylene Wicker, Polyspun.
-Color: Black or Gray
-Weight: 180.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SINTRA 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyethylene Wicker, Polyspun and finished in Black or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 40"L X 40"W X 28"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Gray&lt;br&gt;
+- Ceramic tile table top&lt;br&gt;
+- Rust-resistant&lt;br&gt;
+- powder-coated steel frame&lt;br&gt;
+- Includes umbrella hole and cap Included items and dimensions:&lt;br&gt;
+- Patio Dining Table: color: Black or Gray; dimensions: 40" L x 40" W x 28" H; feature: Contemporary&lt;br&gt;
+- Swivel Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 180.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" s="26" t="inlineStr">
@@ -4559,20 +4559,20 @@
       </c>
       <c r="G31" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SINTRA 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel, Polyethylene Wicker, Polyspun, then finished in Black or Gray tones to suit a range of interiors.
-Product Dimensions: 40"L X 40"W X 28"H
-Features
-- Black or Gray
-- Ceramic tile table top
-- Rust-resistant
-- powder-coated steel frame
-- Includes umbrella hole and cap Included items and dimensions:
-- Patio Dining Table: color: Black or Gray; dimensions: 40" L x 40" W x 28" H; feature: Contemporary
-- Arm Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
-Materials: Steel, Polyethylene Wicker, Polyspun.
-Color: Black or Gray
-Weight: 156.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SINTRA 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel, Polyethylene Wicker, Polyspun, then finished in Black or Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 40"L X 40"W X 28"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Gray&lt;br&gt;
+- Ceramic tile table top&lt;br&gt;
+- Rust-resistant&lt;br&gt;
+- powder-coated steel frame&lt;br&gt;
+- Includes umbrella hole and cap Included items and dimensions:&lt;br&gt;
+- Patio Dining Table: color: Black or Gray; dimensions: 40" L x 40" W x 28" H; feature: Contemporary&lt;br&gt;
+- Arm Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 156.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" s="26" t="inlineStr">
@@ -4693,24 +4693,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SINTRA 6 Pc. Patio Dining Set w/ Bench creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel, Polyspun construction and Black or Gray tones, it blends durability with visual warmth.
-Product Dimensions: 76"L X 40"W X 28"H
-Features
-- Black or Gray
-- Ceramic tile table top
-- 360-degree swivel rocker chairs
-- Rust-resistant
-- powder-coated steel frame
-- Table includes umbrella hole and cap
-- Chair includes cushion and pillow Included items and dimensions:
-- Patio Dining Table: color: Black or Gray; dimensions: 76" L x 40" W x 28" H; feature: Contemporary
-- Arm Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
-- Swivel Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary
-- Bench: color: Black or Gray; dimensions: 59" W x 15 3 or 4"D x 17 1 or 4" H; feature: Contemporary
-Materials: Steel, Polyspun.
-Color: Black or Gray
-Weight: 234.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SINTRA 6 Pc. Patio Dining Set w/ Bench creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel, Polyspun construction and Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 76"L X 40"W X 28"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Black or Gray&lt;br&gt;
+- Ceramic tile table top&lt;br&gt;
+- 360-degree swivel rocker chairs&lt;br&gt;
+- Rust-resistant&lt;br&gt;
+- powder-coated steel frame&lt;br&gt;
+- Table includes umbrella hole and cap&lt;br&gt;
+- Chair includes cushion and pillow Included items and dimensions:&lt;br&gt;
+- Patio Dining Table: color: Black or Gray; dimensions: 76" L x 40" W x 28" H; feature: Contemporary&lt;br&gt;
+- Arm Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary&lt;br&gt;
+- Swivel Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary&lt;br&gt;
+- Bench: color: Black or Gray; dimensions: 59" W x 15 3 or 4"D x 17 1 or 4" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyspun.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 234.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4828,17 +4828,17 @@
       </c>
       <c r="G33" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZALIKA 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Fabric, Steel, PE Rattan, Foam build keeps the look polished and practical.
-Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")
-Features
-- Powder-Coated Steel Frame
-- 3.5mm Round Wicker
-- Tempered Glass Table Top Included items and dimensions:
-- Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H
-- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
-Materials: Fabric, Steel, PE Rattan, Foam.
-Color: Black</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZALIKA 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Fabric, Steel, PE Rattan, Foam build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Powder-Coated Steel Frame&lt;br&gt;
+- 3.5mm Round Wicker&lt;br&gt;
+- Tempered Glass Table Top Included items and dimensions:&lt;br&gt;
+- Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H&lt;br&gt;
+- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel, PE Rattan, Foam.&lt;br&gt;
+Color: Black&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H33" s="28" t="inlineStr">
@@ -4958,17 +4958,17 @@
       </c>
       <c r="G34" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZALIKA 3 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Steel, PE Rattan, Foam and finished in Natural tones for a clean, cohesive look.
-Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")
-Features
-- Powder-Coated Steel Frame
-- 3.5mm Round Wicker
-- Tempered Glass Table Top Included items and dimensions:
-- Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H
-- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
-Materials: Fabric, Steel, PE Rattan, Foam.
-Color: Natural</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZALIKA 3 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Steel, PE Rattan, Foam and finished in Natural tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Powder-Coated Steel Frame&lt;br&gt;
+- 3.5mm Round Wicker&lt;br&gt;
+- Tempered Glass Table Top Included items and dimensions:&lt;br&gt;
+- Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H&lt;br&gt;
+- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel, PE Rattan, Foam.&lt;br&gt;
+Color: Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H34" s="28" t="inlineStr">
@@ -5088,18 +5088,18 @@
       </c>
       <c r="G35" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZALIKA 4 Pc. Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Steel, PE Rattan, Foam, then finished in Black tones to suit a range of interiors.
-Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H
-Features
-- Powder-Coated Steel Frame
-- 3.5mm Round Wicker
-- Tempered Glass Table Top Included items and dimensions:
-- Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H
-- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
-- Patio Bench: dimensions: 51.5" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
-Materials: Fabric, Steel, PE Rattan, Foam.
-Color: Black</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZALIKA 4 Pc. Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Steel, PE Rattan, Foam, then finished in Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Powder-Coated Steel Frame&lt;br&gt;
+- 3.5mm Round Wicker&lt;br&gt;
+- Tempered Glass Table Top Included items and dimensions:&lt;br&gt;
+- Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H&lt;br&gt;
+- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;br&gt;
+- Patio Bench: dimensions: 51.5" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel, PE Rattan, Foam.&lt;br&gt;
+Color: Black&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" s="30" t="inlineStr">
@@ -5219,18 +5219,18 @@
       </c>
       <c r="G36" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZALIKA 4 Pc. Conversation Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Fabric, Steel, PE Rattan, Foam construction and Natural tones, it blends durability with visual warmth.
-Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H
-Features
-- Powder-Coated Steel Frame
-- 3.5mm Round Wicker
-- Tempered Glass Table Top Included items and dimensions:
-- Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H
-- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
-- Patio Bench: dimensions: 51.5" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")
-Materials: Fabric, Steel, PE Rattan, Foam.
-Color: Natural</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZALIKA 4 Pc. Conversation Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Fabric, Steel, PE Rattan, Foam construction and Natural tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Powder-Coated Steel Frame&lt;br&gt;
+- 3.5mm Round Wicker&lt;br&gt;
+- Tempered Glass Table Top Included items and dimensions:&lt;br&gt;
+- Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H&lt;br&gt;
+- Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;br&gt;
+- Patio Bench: dimensions: 51.5" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel, PE Rattan, Foam.&lt;br&gt;
+Color: Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H36" s="30" t="inlineStr">
@@ -5350,19 +5350,19 @@
       </c>
       <c r="G37" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.
-Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H
-Features
-- Natural or Black
-- Sturdy &amp; Durable Design
-- Easy to store
-- Handcrafted BOHO Chic Included items and dimensions:
-- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary
-- Patio Chair (2 / CTN): color: Black; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.
-Color: Natural or Black
-Weight: 37.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Natural or Black&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Easy to store&lt;br&gt;
+- Handcrafted BOHO Chic Included items and dimensions:&lt;br&gt;
+- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary&lt;br&gt;
+- Patio Chair (2 / CTN): color: Black; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.&lt;br&gt;
+Color: Natural or Black&lt;br&gt;
+Weight: 37.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H37" s="32" t="inlineStr">
@@ -5488,18 +5488,18 @@
       </c>
       <c r="G38" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZUBERI 3 Pc. Patio Conversation Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric construction and Natural tones, it blends durability with visual warmth.
-Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H
-Features
-- Sturdy &amp; Durable Design
-- Easy to store
-- Handcrafted BOHO Chic Included items and dimensions:
-- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary
-- Patio Chair (2 / CTN): color: Natural; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.
-Color: Natural
-Weight: 21.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZUBERI 3 Pc. Patio Conversation Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric construction and Natural tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Easy to store&lt;br&gt;
+- Handcrafted BOHO Chic Included items and dimensions:&lt;br&gt;
+- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary&lt;br&gt;
+- Patio Chair (2 / CTN): color: Natural; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 21.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H38" s="32" t="inlineStr">
@@ -5621,18 +5621,18 @@
       </c>
       <c r="G39" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZUBERI 3 Pc. Patio Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric build keeps the look polished and practical.
-Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H
-Features
-- Sturdy &amp; Durable Design
-- Easy to store
-- Handcrafted BOHO Chic Included items and dimensions:
-- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary
-- Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.
-Color: Natural
-Weight: 28.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZUBERI 3 Pc. Patio Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Easy to store&lt;br&gt;
+- Handcrafted BOHO Chic Included items and dimensions:&lt;br&gt;
+- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary&lt;br&gt;
+- Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 28.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H39" s="32" t="inlineStr">
@@ -5754,19 +5754,19 @@
       </c>
       <c r="G40" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZUBERI 3 Pc. Patio Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric and finished in Natural or Gray tones for a clean, cohesive look.
-Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H
-Features
-- Natural or Gray
-- Sturdy &amp; Durable Design
-- Easy to store
-- Handcrafted BOHO Chic Included items and dimensions:
-- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary
-- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.
-Color: Natural or Gray
-Weight: 35.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZUBERI 3 Pc. Patio Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric and finished in Natural or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Natural or Gray&lt;br&gt;
+- Sturdy &amp;amp; Durable Design&lt;br&gt;
+- Easy to store&lt;br&gt;
+- Handcrafted BOHO Chic Included items and dimensions:&lt;br&gt;
+- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary&lt;br&gt;
+- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.&lt;br&gt;
+Color: Natural or Gray&lt;br&gt;
+Weight: 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H40" s="32" t="inlineStr">
@@ -5892,22 +5892,22 @@
       </c>
       <c r="G41" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BREEZE Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Crafted with Steel, Mesh, Fabric, then finished in Black tones to suit a range of interiors.
-Product Dimensions: 28""W X 34 1/4""D X 46""H"
-Features
-- Modern
-- For indoor or outdoor use
-- Easy-store foldable design
-- Breathable and UV-resistant mesh
-- Includes back and seat cushions
-- Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs Included items and dimensions:
-- Swing Chair: color: Black; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric.
-Color: Black
-Weight: 71.42 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BREEZE Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Crafted with Steel, Mesh, Fabric, then finished in Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 28""W X 34 1/4""D X 46""H"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Modern&lt;br&gt;
+- For indoor or outdoor use&lt;br&gt;
+- Easy-store foldable design&lt;br&gt;
+- Breathable and UV-resistant mesh&lt;br&gt;
+- Includes back and seat cushions&lt;br&gt;
+- Easy to assemble with included hardware kit&lt;br&gt;
+- Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
+- Swing Chair: color: Black; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern&lt;br&gt;
+- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 71.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H41" s="34" t="inlineStr">
@@ -6029,22 +6029,22 @@
       </c>
       <c r="G42" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BREEZE Swing Chair w/ Stand creates a cohesive setup that feels inviting the moment you walk in. As a outdoor chair, it is designed to coordinate with matching pieces. The Modern character adds definition without feeling heavy. With Steel, Mesh, Fabric construction and Dark Gray tones, it blends durability with visual warmth.
-Product Dimensions: 28""W X 34 1/4""D X 46""H"
-Features
-- Modern
-- For indoor or outdoor use
-- Easy-store foldable design
-- Breathable and UV-resistant mesh
-- Includes back and seat cushions
-- Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs Included items and dimensions:
-- Swing Chair: color: Dark Gray; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric.
-Color: Dark Gray
-Weight: 71.42 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BREEZE Swing Chair w/ Stand creates a cohesive setup that feels inviting the moment you walk in. As a outdoor chair, it is designed to coordinate with matching pieces. The Modern character adds definition without feeling heavy. With Steel, Mesh, Fabric construction and Dark Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 28""W X 34 1/4""D X 46""H"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Modern&lt;br&gt;
+- For indoor or outdoor use&lt;br&gt;
+- Easy-store foldable design&lt;br&gt;
+- Breathable and UV-resistant mesh&lt;br&gt;
+- Includes back and seat cushions&lt;br&gt;
+- Easy to assemble with included hardware kit&lt;br&gt;
+- Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
+- Swing Chair: color: Dark Gray; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern&lt;br&gt;
+- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 71.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H42" s="34" t="inlineStr">
@@ -6166,22 +6166,22 @@
       </c>
       <c r="G43" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BREEZE Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. This outdoor chair is made to fit naturally into the room. A Modern profile gives the space a refined, approachable look. Finished in Light Gray tones, the Steel, Mesh, Fabric build keeps the look polished and practical.
-Product Dimensions: 28""W X 34 1/4""D X 46""H"
-Features
-- Modern
-- For indoor or outdoor use
-- Easy-store foldable design
-- Breathable and UV-resistant mesh
-- Includes back and seat cushions
-- Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs Included items and dimensions:
-- Swing Chair: color: Light Gray; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric.
-Color: Light Gray
-Weight: 71.42 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BREEZE Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. This outdoor chair is made to fit naturally into the room. A Modern profile gives the space a refined, approachable look. Finished in Light Gray tones, the Steel, Mesh, Fabric build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 28""W X 34 1/4""D X 46""H"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Modern&lt;br&gt;
+- For indoor or outdoor use&lt;br&gt;
+- Easy-store foldable design&lt;br&gt;
+- Breathable and UV-resistant mesh&lt;br&gt;
+- Includes back and seat cushions&lt;br&gt;
+- Easy to assemble with included hardware kit&lt;br&gt;
+- Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
+- Swing Chair: color: Light Gray; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern&lt;br&gt;
+- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 71.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H43" s="34" t="inlineStr">
@@ -6303,22 +6303,22 @@
       </c>
       <c r="G44" s="36" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CRUSH Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Steel, Mesh, Fabric build keeps the look polished and practical.
-Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"
-Features
-- Modern
-- For indoor or outdoor use
-- Easy-store foldable design
-- Breathable and UV-resistant mesh
-- Includes back and seat cushions
-- Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs Included items and dimensions:
-- Swing Chair: color: Black; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric.
-Color: Black
-Weight: 68.12 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CRUSH Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Steel, Mesh, Fabric build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Modern&lt;br&gt;
+- For indoor or outdoor use&lt;br&gt;
+- Easy-store foldable design&lt;br&gt;
+- Breathable and UV-resistant mesh&lt;br&gt;
+- Includes back and seat cushions&lt;br&gt;
+- Easy to assemble with included hardware kit&lt;br&gt;
+- Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
+- Swing Chair: color: Black; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern&lt;br&gt;
+- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 68.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" s="36" t="inlineStr">
@@ -6440,22 +6440,22 @@
       </c>
       <c r="G45" s="36" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CRUSH Swing Chair w/ Stand is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Modern character adds definition without feeling heavy. Built from Steel, Mesh, Fabric and finished in Dark Gray tones for a clean, cohesive look.
-Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"
-Features
-- Modern
-- For indoor or outdoor use
-- Easy-store foldable design
-- Breathable and UV-resistant mesh
-- Includes back and seat cushions
-- Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs Included items and dimensions:
-- Swing Chair: color: Dark Gray; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric.
-Color: Dark Gray
-Weight: 68.12 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CRUSH Swing Chair w/ Stand is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Modern character adds definition without feeling heavy. Built from Steel, Mesh, Fabric and finished in Dark Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Modern&lt;br&gt;
+- For indoor or outdoor use&lt;br&gt;
+- Easy-store foldable design&lt;br&gt;
+- Breathable and UV-resistant mesh&lt;br&gt;
+- Includes back and seat cushions&lt;br&gt;
+- Easy to assemble with included hardware kit&lt;br&gt;
+- Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
+- Swing Chair: color: Dark Gray; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern&lt;br&gt;
+- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 68.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" s="36" t="inlineStr">
@@ -6577,22 +6577,22 @@
       </c>
       <c r="G46" s="36" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CRUSH Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor chair is made to fit naturally into the room. A Modern profile gives the space a refined, approachable look. Crafted with Steel, Mesh, Fabric, then finished in Light Gray tones to suit a range of interiors.
-Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"
-Features
-- Modern
-- For indoor or outdoor use
-- Easy-store foldable design
-- Breathable and UV-resistant mesh
-- Includes back and seat cushions
-- Easy to assemble with included hardware kit
-- Max weight capacity: 220 lbs Included items and dimensions:
-- Swing Chair: color: Light Gray; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern
-Materials: Steel, Mesh, Fabric.
-Color: Light Gray
-Weight: 68.12 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CRUSH Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor chair is made to fit naturally into the room. A Modern profile gives the space a refined, approachable look. Crafted with Steel, Mesh, Fabric, then finished in Light Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Modern&lt;br&gt;
+- For indoor or outdoor use&lt;br&gt;
+- Easy-store foldable design&lt;br&gt;
+- Breathable and UV-resistant mesh&lt;br&gt;
+- Includes back and seat cushions&lt;br&gt;
+- Easy to assemble with included hardware kit&lt;br&gt;
+- Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
+- Swing Chair: color: Light Gray; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern&lt;br&gt;
+- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 68.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H46" s="36" t="inlineStr">
@@ -6713,17 +6713,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MACKAY 2 Reclining Chairs and 2 Ottomans is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Beige or Natural Teak tones for a clean, cohesive look.
-Product Dimensions: 24 1/2"W X 27 1/2"D X 42 1/2"H
-Features
-- Beige or Natural Teak
-- Button-tufted cushion Included items and dimensions:
-- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
-- Ottoman (2 / CTN): color: Beige or Natural Teak; dimensions: 21 1 or 4" L x 21 1 or 4" W x 16 1 or 2" H; feature: Contemporary
-Materials: Aluminum, FSC Certified 100% Teak Wood.
-Color: Beige or Natural Teak
-Weight: 90.37 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MACKAY 2 Reclining Chairs and 2 Ottomans is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Beige or Natural Teak tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 24 1/2"W X 27 1/2"D X 42 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Natural Teak&lt;br&gt;
+- Button-tufted cushion Included items and dimensions:&lt;br&gt;
+- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary&lt;br&gt;
+- Ottoman (2 / CTN): color: Beige or Natural Teak; dimensions: 21 1 or 4" L x 21 1 or 4" W x 16 1 or 2" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
+Color: Beige or Natural Teak&lt;br&gt;
+Weight: 90.37 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6840,19 +6840,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CYPRUS 7 Pc. Bar Table Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor bar table set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, Polyethylene Wicker, Polyspun construction and Gray tones, it blends durability with visual warmth.
-Product Dimensions: 46"DIA X 39 1/2"H
-Features
-- Includes stainless steel ice bucket
-- Removable bucket with center cover
-- Stackable wicker chairs
-- Stainless steel footrest around base
-- Includes umbrella hole and space for umbrella base Included items and dimensions:
-- Bar Chair: color: Gray; dimensions: 20 1 or 4" W x 18"D x 41 3 or 4" H; feature: Contemporary
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gray
-Weight: 144.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CYPRUS 7 Pc. Bar Table Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor bar table set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, Polyethylene Wicker, Polyspun construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 46"DIA X 39 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Includes stainless steel ice bucket&lt;br&gt;
+- Removable bucket with center cover&lt;br&gt;
+- Stackable wicker chairs&lt;br&gt;
+- Stainless steel footrest around base&lt;br&gt;
+- Includes umbrella hole and space for umbrella base Included items and dimensions:&lt;br&gt;
+- Bar Chair: color: Gray; dimensions: 20 1 or 4" W x 18"D x 41 3 or 4" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 144.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6970,25 +6970,25 @@
       </c>
       <c r="G49" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ILONA L-Sectional and Coffee Table and End Table is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor sofa set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, Polyester Canvas, Faux Rattan and finished in Brown or Beige tones for a clean, cohesive look.
-Product Dimensions: L-SECTIONAL: 103 1/4"W X 79 1/4"D X 25 1/2-31"H
-Features
-- Brown or Beige
-- Aluminum Frame
-- Modular Design
-- 5mm Tempered Glass Table Tops
-- UV &amp; Water Resistant
-- Beige Fabric Cushions Included items and dimensions:
-- Left Arm Chair: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
-- Corner: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
-- Ottoman: color: Brown or Beige; dimensions: 27 3 or 4" W x 27 1 or 4"D x 18" H; feature: Contemporary
-- Coffee Table: color: Brown or Beige; dimensions: 34 5 or 8" L x 19 1 or 4" W x 13 3 or 4" H; feature: Contemporary
-- End Table: color: Brown or Beige; dimensions: 17 3 or 4" L x 17 3 or 4" W x 19 5 or 8" H; feature: Contemporary
-- Armless Chair: color: Brown or Beige; dimensions: 24 1 or 4" W x 27 1 or 2"D x 25 1 or 2 - 31" H; feature: Contemporary
-Materials: Aluminum, Polyester Canvas, Faux Rattan.
-Color: Brown or Beige
-Weight: 204 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ILONA L-Sectional and Coffee Table and End Table is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor sofa set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, Polyester Canvas, Faux Rattan and finished in Brown or Beige tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: L-SECTIONAL: 103 1/4"W X 79 1/4"D X 25 1/2-31"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Brown or Beige&lt;br&gt;
+- Aluminum Frame&lt;br&gt;
+- Modular Design&lt;br&gt;
+- 5mm Tempered Glass Table Tops&lt;br&gt;
+- UV &amp;amp; Water Resistant&lt;br&gt;
+- Beige Fabric Cushions Included items and dimensions:&lt;br&gt;
+- Left Arm Chair: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary&lt;br&gt;
+- Corner: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary&lt;br&gt;
+- Ottoman: color: Brown or Beige; dimensions: 27 3 or 4" W x 27 1 or 4"D x 18" H; feature: Contemporary&lt;br&gt;
+- Coffee Table: color: Brown or Beige; dimensions: 34 5 or 8" L x 19 1 or 4" W x 13 3 or 4" H; feature: Contemporary&lt;br&gt;
+- End Table: color: Brown or Beige; dimensions: 17 3 or 4" L x 17 3 or 4" W x 19 5 or 8" H; feature: Contemporary&lt;br&gt;
+- Armless Chair: color: Brown or Beige; dimensions: 24 1 or 4" W x 27 1 or 2"D x 25 1 or 2 - 31" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
+Color: Brown or Beige&lt;br&gt;
+Weight: 204 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" s="38" t="inlineStr">
@@ -7110,25 +7110,25 @@
       </c>
       <c r="G50" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ILONA L-Sectional and Coffee Table and End Table offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor sofa set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, Polyester Canvas, Faux Rattan, then finished in Brown or Beige tones to suit a range of interiors.
-Product Dimensions: L-SECTIONAL: 79 1/2"W X 79"D X 25 1/2-31"H
-Features
-- Brown or Beige
-- Aluminum Frame
-- Modular Design
-- 5mm Tempered Glass Table Tops
-- UV &amp; Water Resistant
-- Beige Fabric Cushions Included items and dimensions:
-- Left Arm Chair: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
-- Corner: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary
-- Ottoman: color: Brown or Beige; dimensions: 27 3 or 4" W x 27 1 or 4"D x 18" H; feature: Contemporary
-- Coffee Table: color: Brown or Beige; dimensions: 34 5 or 8" L x 19 1 or 4" W x 13 3 or 4" H; feature: Contemporary
-- End Table: color: Brown or Beige; dimensions: 17 3 or 4" L x 17 3 or 4" W x 19 5 or 8" H; feature: Contemporary
-- Armless Chair: color: Brown or Beige; dimensions: 24 1 or 4" W x 27 1 or 2"D x 25 1 or 2 - 31" H; feature: Contemporary
-Materials: Aluminum, Polyester Canvas, Faux Rattan.
-Color: Brown or Beige
-Weight: 179 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ILONA L-Sectional and Coffee Table and End Table offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor sofa set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, Polyester Canvas, Faux Rattan, then finished in Brown or Beige tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: L-SECTIONAL: 79 1/2"W X 79"D X 25 1/2-31"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Brown or Beige&lt;br&gt;
+- Aluminum Frame&lt;br&gt;
+- Modular Design&lt;br&gt;
+- 5mm Tempered Glass Table Tops&lt;br&gt;
+- UV &amp;amp; Water Resistant&lt;br&gt;
+- Beige Fabric Cushions Included items and dimensions:&lt;br&gt;
+- Left Arm Chair: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary&lt;br&gt;
+- Corner: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary&lt;br&gt;
+- Ottoman: color: Brown or Beige; dimensions: 27 3 or 4" W x 27 1 or 4"D x 18" H; feature: Contemporary&lt;br&gt;
+- Coffee Table: color: Brown or Beige; dimensions: 34 5 or 8" L x 19 1 or 4" W x 13 3 or 4" H; feature: Contemporary&lt;br&gt;
+- End Table: color: Brown or Beige; dimensions: 17 3 or 4" L x 17 3 or 4" W x 19 5 or 8" H; feature: Contemporary&lt;br&gt;
+- Armless Chair: color: Brown or Beige; dimensions: 24 1 or 4" W x 27 1 or 2"D x 25 1 or 2 - 31" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
+Color: Brown or Beige&lt;br&gt;
+Weight: 179 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" s="38" t="inlineStr">
@@ -7250,20 +7250,20 @@
       </c>
       <c r="G51" s="40" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MACKAY 5 Pc. Patio Dining Set sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, FSC Certified 100% Teak Wood, then finished in Beige or Natural Teak tones to suit a range of interiors.
-Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H
-Features
-- Beige or Natural Teak
-- Mixed material of teak wood and metal frame
-- Extends from 61" to 84" w/ butterfly leaf
-- Seats up to 8 people
-- Level control table legs Included items and dimensions:
-- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary
-- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
-Materials: Aluminum, FSC Certified 100% Teak Wood.
-Color: Beige or Natural Teak
-Weight: 174.14 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MACKAY 5 Pc. Patio Dining Set sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, FSC Certified 100% Teak Wood, then finished in Beige or Natural Teak tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Natural Teak&lt;br&gt;
+- Mixed material of teak wood and metal frame&lt;br&gt;
+- Extends from 61" to 84" w/ butterfly leaf&lt;br&gt;
+- Seats up to 8 people&lt;br&gt;
+- Level control table legs Included items and dimensions:&lt;br&gt;
+- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary&lt;br&gt;
+- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
+Color: Beige or Natural Teak&lt;br&gt;
+Weight: 174.14 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" s="40" t="inlineStr">
@@ -7385,20 +7385,20 @@
       </c>
       <c r="G52" s="40" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Gather around MACKAY 5 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, FSC Certified 100% Teak Wood construction and Gun Metal or Natural Teak tones, it blends durability with visual warmth.
-Product Dimensions: 59"L X 35 1/2"W X 29"H
-Features
-- Gun Metal or Natural Teak
-- Mixed material of teak wood and metal frame
-- Seats up to 6 people
-- Level control table legs
-- Includes umbrella hole and cap Included items and dimensions:
-- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 59" L x 35 1 or 2" W x 29" H; feature: Contemporary
-- Stacking Chair: color: Gun Metal or Natural Teak; dimensions: 22.5" W x 25"D x 34" H; feature: Contemporary
-Materials: Aluminum, FSC Certified 100% Teak Wood.
-Color: Gun Metal or Natural Teak
-Weight: 55.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Gather around MACKAY 5 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, FSC Certified 100% Teak Wood construction and Gun Metal or Natural Teak tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 59"L X 35 1/2"W X 29"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gun Metal or Natural Teak&lt;br&gt;
+- Mixed material of teak wood and metal frame&lt;br&gt;
+- Seats up to 6 people&lt;br&gt;
+- Level control table legs&lt;br&gt;
+- Includes umbrella hole and cap Included items and dimensions:&lt;br&gt;
+- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 59" L x 35 1 or 2" W x 29" H; feature: Contemporary&lt;br&gt;
+- Stacking Chair: color: Gun Metal or Natural Teak; dimensions: 22.5" W x 25"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
+Color: Gun Metal or Natural Teak&lt;br&gt;
+Weight: 55.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" s="40" t="inlineStr">
@@ -7519,20 +7519,20 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MACKAY 7 Pc. Patio Dining Set anchors the dining area with a cohesive look that feels easy and welcoming. As a outdoor patio dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Gun Metal or Beige or Natural Teak tones, the Aluminum, FSC Certified 100% Teak Wood build keeps the look polished and practical.
-Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H
-Features
-- Gun Metal or Beige or Natural Teak
-- Mixed material of teak wood and metal frame
-- Extends from 61" to 84" w/ butterfly leaf
-- Seats up to 8 people
-- Level control table legs Included items and dimensions:
-- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary
-- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
-Materials: Aluminum, FSC Certified 100% Teak Wood.
-Color: Gun Metal or Beige or Natural Teak
-Weight: 234.76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MACKAY 7 Pc. Patio Dining Set anchors the dining area with a cohesive look that feels easy and welcoming. As a outdoor patio dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Gun Metal or Beige or Natural Teak tones, the Aluminum, FSC Certified 100% Teak Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gun Metal or Beige or Natural Teak&lt;br&gt;
+- Mixed material of teak wood and metal frame&lt;br&gt;
+- Extends from 61" to 84" w/ butterfly leaf&lt;br&gt;
+- Seats up to 8 people&lt;br&gt;
+- Level control table legs Included items and dimensions:&lt;br&gt;
+- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary&lt;br&gt;
+- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
+Color: Gun Metal or Beige or Natural Teak&lt;br&gt;
+Weight: 234.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7649,21 +7649,21 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Gun Metal or Beige or Natural Teak tones for a clean, cohesive look.
-Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H
-Features
-- Gun Metal or Beige or Natural Teak
-- Mixed material of teak wood and metal frame
-- Extends from 61" to 84" w/ butterfly leaf
-- Seats up to 8 people
-- Level control table legs Included items and dimensions:
-- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary
-- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary
-- Ottoman (2 / CTN): color: Beige or Natural Teak; dimensions: 21 1 or 4" L x 21 1 or 4" W x 16 1 or 2" H; feature: Contemporary
-Materials: Aluminum, FSC Certified 100% Teak Wood.
-Color: Gun Metal or Beige or Natural Teak
-Weight: 203.89 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Gun Metal or Beige or Natural Teak tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gun Metal or Beige or Natural Teak&lt;br&gt;
+- Mixed material of teak wood and metal frame&lt;br&gt;
+- Extends from 61" to 84" w/ butterfly leaf&lt;br&gt;
+- Seats up to 8 people&lt;br&gt;
+- Level control table legs Included items and dimensions:&lt;br&gt;
+- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary&lt;br&gt;
+- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary&lt;br&gt;
+- Ottoman (2 / CTN): color: Beige or Natural Teak; dimensions: 21 1 or 4" L x 21 1 or 4" W x 16 1 or 2" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
+Color: Gun Metal or Beige or Natural Teak&lt;br&gt;
+Weight: 203.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7780,24 +7780,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Gather around MALIA 6 Pc. Patio Dining Set w/ Bench, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining table, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build keeps the look polished and practical.
-Product Dimensions: 59"L X 31 1/4"W X 26 3/4"H
-Features
-- Modular Design
-- Sectional and two sofas settings
-- Can be a dining set
-- Convertible ottoman to bench
-- Bench plate stored under table top
-- Flap-open side storage
-- Includes cushions
-- pillows
-- and protective covers Included items and dimensions:
-- Patio Dining Table: color: Gray; dimensions: 59" L x 31 1 or 4" W x 26 3 or 4" H; feature: Contemporary
-- 5 Pc. Sectional Set w/ Bench: color: Gray; dimensions: LEFT SOFA: 86 1 or 4" L x 31" W x 33" H, RIGHT SOFA: 78" L x 31" W x 33" H, OTTOMAN: 15" L x 15" W x 16" H, BENCH: 55" W x 15"D x 19 3 or 4" H; feature: Contemporary
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gray
-Weight: 199.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Gather around MALIA 6 Pc. Patio Dining Set w/ Bench, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining table, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 59"L X 31 1/4"W X 26 3/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Modular Design&lt;br&gt;
+- Sectional and two sofas settings&lt;br&gt;
+- Can be a dining set&lt;br&gt;
+- Convertible ottoman to bench&lt;br&gt;
+- Bench plate stored under table top&lt;br&gt;
+- Flap-open side storage&lt;br&gt;
+- Includes cushions&lt;br&gt;
+- pillows&lt;br&gt;
+- and protective covers Included items and dimensions:&lt;br&gt;
+- Patio Dining Table: color: Gray; dimensions: 59" L x 31 1 or 4" W x 26 3 or 4" H; feature: Contemporary&lt;br&gt;
+- 5 Pc. Sectional Set w/ Bench: color: Gray; dimensions: LEFT SOFA: 86 1 or 4" L x 31" W x 33" H, RIGHT SOFA: 78" L x 31" W x 33" H, OTTOMAN: 15" L x 15" W x 16" H, BENCH: 55" W x 15"D x 19 3 or 4" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 199.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">

--- a/FOA SETS/Outdoor-Set.xlsx
+++ b/FOA SETS/Outdoor-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD55"/>
+  <dimension ref="A1:AG55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,6 +734,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -854,7 +869,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Set, ALYCIA</t>
+          <t>Outdoor, Dining Set, ALYCIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -988,6 +1018,21 @@
       <c r="AD3" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ANTIGUA</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1124,6 +1169,21 @@
           <t>Outdoor, Patio Set, ANTIGUA</t>
         </is>
       </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1255,6 +1315,21 @@
           <t>Outdoor, Patio Set, AROSA</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1384,6 +1459,21 @@
       <c r="AD6" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, BARBUDA</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1520,6 +1610,21 @@
           <t>Outdoor, Patio Set, BORDEAUX</t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1649,6 +1754,21 @@
       <c r="AD8" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, JOHARI</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1783,6 +1903,21 @@
           <t>Outdoor, Patio Set, JOHARI</t>
         </is>
       </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
@@ -1914,6 +2049,21 @@
           <t>Outdoor, Patio Set, KIMARA</t>
         </is>
       </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
@@ -2043,6 +2193,21 @@
       <c r="AD11" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, KIMARA</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2177,6 +2342,21 @@
           <t>Outdoor, Patio Set, KIMARA</t>
         </is>
       </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
@@ -2307,6 +2487,21 @@
       <c r="AD13" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, KIMARA</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2445,6 +2640,21 @@
           <t>Outdoor, Patio Set, KYUSHU</t>
         </is>
       </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
@@ -2581,6 +2791,21 @@
           <t>Outdoor, Patio Set, KYUSHU</t>
         </is>
       </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2712,6 +2937,21 @@
           <t>Outdoor, Patio Set, LOTUS</t>
         </is>
       </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2842,6 +3082,21 @@
           <t>Outdoor, Patio Set, LYON</t>
         </is>
       </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2972,6 +3227,21 @@
           <t>Outdoor, Patio Set, LYON</t>
         </is>
       </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3102,6 +3372,21 @@
           <t>Outdoor, Patio Set, LYON</t>
         </is>
       </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3226,6 +3511,21 @@
           <t>Outdoor, Patio Set, MONZA</t>
         </is>
       </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3353,6 +3653,21 @@
           <t>Outdoor, Patio Set, NIAMBI</t>
         </is>
       </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3480,6 +3795,21 @@
           <t>Outdoor, Patio Set, NIAMBI</t>
         </is>
       </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
@@ -3612,6 +3942,21 @@
           <t>Outdoor, Patio Set, NIAMBI</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="24" t="inlineStr">
@@ -3742,6 +4087,21 @@
       <c r="AD24" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, NIAMBI</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3870,6 +4230,21 @@
       <c r="AD25" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, NUSA</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4005,6 +4380,21 @@
           <t>Outdoor, Patio Set, PALMA</t>
         </is>
       </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4132,6 +4522,21 @@
       <c r="AD27" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, SARABI</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4264,6 +4669,21 @@
           <t>Outdoor, Patio Set, SEGOVIA</t>
         </is>
       </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4394,6 +4814,21 @@
           <t>Outdoor, Patio Set, SEGOVIA</t>
         </is>
       </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="26" t="inlineStr">
@@ -4529,6 +4964,21 @@
           <t>Outdoor, Patio Set, SINTRA</t>
         </is>
       </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="26" t="inlineStr">
@@ -4662,6 +5112,21 @@
       <c r="AD31" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, SINTRA</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4798,6 +5263,21 @@
           <t>Outdoor, Patio Set, SINTRA</t>
         </is>
       </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="28" t="inlineStr">
@@ -4928,6 +5408,21 @@
           <t>Outdoor, Patio Set, ZALIKA</t>
         </is>
       </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="28" t="inlineStr">
@@ -5056,6 +5551,21 @@
       <c r="AD34" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZALIKA</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5189,6 +5699,21 @@
           <t>Outdoor, Patio Set, ZALIKA</t>
         </is>
       </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="30" t="inlineStr">
@@ -5318,6 +5843,21 @@
       <c r="AD36" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZALIKA</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5458,6 +5998,21 @@
           <t>Outdoor, Patio Set, ZUBERI</t>
         </is>
       </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="32" t="inlineStr">
@@ -5591,6 +6146,21 @@
           <t>Outdoor, Patio Set, ZUBERI</t>
         </is>
       </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="32" t="inlineStr">
@@ -5722,6 +6292,21 @@
       <c r="AD39" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZUBERI</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5860,6 +6445,21 @@
       <c r="AD40" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZUBERI</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5996,7 +6596,22 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, BREEZE</t>
+          <t>Outdoor, Chair, BREEZE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6748,22 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, BREEZE</t>
+          <t>Outdoor, Chair, BREEZE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6900,22 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, BREEZE</t>
+          <t>Outdoor, Chair, BREEZE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6407,7 +7052,22 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, CRUSH</t>
+          <t>Outdoor, Chair, CRUSH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6544,7 +7204,22 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, CRUSH</t>
+          <t>Outdoor, Chair, CRUSH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6681,7 +7356,22 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, CRUSH</t>
+          <t>Outdoor, Chair, CRUSH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6808,7 +7498,22 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, MACKAY</t>
+          <t>Outdoor, Chair, MACKAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6937,7 +7642,22 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Outdoor, Bar Table Set, CYPRUS</t>
+          <t>Outdoor, Bar Table Set, CYPRUS, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7797,22 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Outdoor, Sofa Set, ILONA</t>
+          <t>Outdoor, Sofa Set, ILONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7952,22 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Outdoor, Sofa Set, ILONA</t>
+          <t>Outdoor, Sofa Set, ILONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7355,6 +8105,21 @@
           <t>Outdoor, Patio Dining Set, MACKAY</t>
         </is>
       </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="40" t="inlineStr">
@@ -7490,6 +8255,21 @@
           <t>Outdoor, Patio Dining Set, MACKAY</t>
         </is>
       </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7618,6 +8398,21 @@
       <c r="AD53" t="inlineStr">
         <is>
           <t>Outdoor, Patio Dining Set, MACKAY</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7749,6 +8544,21 @@
       <c r="AD54" t="inlineStr">
         <is>
           <t>Outdoor, Patio Dining Set, MACKAY</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7885,6 +8695,21 @@
           <t>Outdoor, Patio Dining Table, MALIA</t>
         </is>
       </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables &gt; Dining Tables</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/FOA SETS/Outdoor-Set.xlsx
+++ b/FOA SETS/Outdoor-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1954,10 +1954,10 @@
 &lt;p&gt;Features&lt;br&gt;
 - Sturdy &amp;amp; Durable Design&lt;br&gt;
 - Weather Resistance Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary&lt;/p&gt;
+- Dining Table: color: Black or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 149.1 lbs&lt;/p&gt;</t>
+Color: Black or Gray&lt;br&gt;
+Weight: 149.1 or 150.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" s="18" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2095,15 +2095,15 @@
       <c r="G11" s="18" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KIMARA 3 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+KIMARA 3 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and finished in Black tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Sturdy &amp;amp; Durable Design&lt;br&gt;
 - Weather Resistance Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary&lt;/p&gt;
+- Dining Table: color: Black or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 150.7 lbs&lt;/p&gt;</t>
+Color: Black or Gray&lt;br&gt;
+Weight: 149.1 or 150.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" s="18" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2242,15 +2242,15 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 KIMARA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 25"W X 23"D X 30.5"H&lt;/p&gt;
+Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 25"W X 23"D X 30.5"H / Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 22.5"W X 23.5"D X 35"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Sturdy &amp;amp; Durable Design&lt;br&gt;
 - Weather Resistance Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary&lt;br&gt;
-- Patio Chair (2 / CTN): color: Black; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary&lt;/p&gt;
+- Dining Table: color: Black or Gray&lt;br&gt;
+- Patio Chair (2 / CTN): color: Black or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 175 lbs&lt;/p&gt;</t>
+Color: Black or Gray&lt;br&gt;
+Weight: 175 or 174.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2388,16 +2388,16 @@
       <c r="G13" s="20" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KIMARA 5 Pc. Patio Dining Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Gray tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 22.5"W X 23.5"D X 35"H&lt;/p&gt;
+KIMARA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 25"W X 23"D X 30.5"H / Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 22.5"W X 23.5"D X 35"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Sturdy &amp;amp; Durable Design&lt;br&gt;
 - Weather Resistance Included items and dimensions:&lt;br&gt;
-- Dining Table: color: Black or Gray; dimensions: 56.7" L x 29.13" W x 26.77" H; feature: Contemporary&lt;br&gt;
-- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary&lt;/p&gt;
+- Dining Table: color: Black or Gray&lt;br&gt;
+- Patio Chair (2 / CTN): color: Black or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 174.9 lbs&lt;/p&gt;</t>
+Color: Black or Gray&lt;br&gt;
+Weight: 175 or 174.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2544,10 +2544,10 @@
 - Natural acacia wood&lt;br&gt;
 - Includes tie-back cushions&lt;br&gt;
 - Easy to assemble with included hardware kit Included items and dimensions:&lt;br&gt;
-- Table and Loveseat: color: Beige or Natural; dimensions: TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H; feature: Rustic&lt;br&gt;
-- Chair (2 / CTN): color: Beige or Natural; dimensions: CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H; feature: Rustic&lt;/p&gt;
+- Table and Loveseat: color: Beige or Natural or Black or Natural&lt;br&gt;
+- Chair (2 / CTN): color: Beige or Natural or Black or Natural&lt;/p&gt;
 &lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
-Color: Beige or Natural&lt;br&gt;
+Color: Beige or Natural or Black or Natural&lt;br&gt;
 Weight: 125.04 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2686,19 +2686,19 @@
       <c r="G15" s="22" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KYUSHU 4 Pc. Patio Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Black or Natural tones, the Acacia Wood, Polyester build keeps the look polished and practical.&lt;br&gt;
+KYUSHU 4 Pc. Patio Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Acacia Wood, Polyester construction and Beige or Natural tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic&lt;br&gt;
-- Black or Natural&lt;br&gt;
+- Beige or Natural&lt;br&gt;
 - Weather-resistant&lt;br&gt;
 - Natural acacia wood&lt;br&gt;
 - Includes tie-back cushions&lt;br&gt;
 - Easy to assemble with included hardware kit Included items and dimensions:&lt;br&gt;
-- Table and Loveseat: color: Black or Natural; dimensions: TABLE: 39 1 or 2" L x 23 1 or 2" W x 18" H, LOVESEAT: 52 3 or 4" L x 27 1 or 4" W x 34 1 or 4" H; feature: Rustic&lt;br&gt;
-- Chair (2 / CTN): color: Black or Natural; dimensions: CHAIR: 24" W x 27 1 or 4"D x 34 1 or 4" H; feature: Rustic&lt;/p&gt;
+- Table and Loveseat: color: Beige or Natural or Black or Natural&lt;br&gt;
+- Chair (2 / CTN): color: Beige or Natural or Black or Natural&lt;/p&gt;
 &lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
-Color: Black or Natural&lt;br&gt;
+Color: Beige or Natural or Black or Natural&lt;br&gt;
 Weight: 125.04 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3842,15 +3842,15 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 NIAMBI 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 22.5"W X 23.5"D X 35"H&lt;/p&gt;
+Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair : 22.5"W X 23.5"D X 35"H / Table: 26.5"W X 23.5"D X 29"H, Chair : 21"W X 25"D X 34"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Marble Base&lt;br&gt;
 - Sturdy &amp;amp; Durable Design&lt;br&gt;
 - Easy to store Included items and dimensions:&lt;br&gt;
-- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary&lt;/p&gt;
+- Stacking Chair (2 or STACK): color: Gray or Natural&lt;/p&gt;
 &lt;p&gt;Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 82.2 lbs&lt;/p&gt;</t>
+Color: Gray or Natural&lt;br&gt;
+Weight: 82.2 or 66.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3988,16 +3988,16 @@
       <c r="G24" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NIAMBI 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber, then finished in Natural tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair: 21"W X 25"D X 34"H&lt;/p&gt;
+NIAMBI 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Table: 26.5"W X 23.5"D X 29"H, Chair : 22.5"W X 23.5"D X 35"H / Table: 26.5"W X 23.5"D X 29"H, Chair : 21"W X 25"D X 34"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Marble Base&lt;br&gt;
 - Sturdy &amp;amp; Durable Design&lt;br&gt;
 - Easy to store Included items and dimensions:&lt;br&gt;
-- Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary&lt;/p&gt;
+- Stacking Chair (2 or STACK): color: Gray or Natural&lt;/p&gt;
 &lt;p&gt;Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.&lt;br&gt;
-Color: Natural&lt;br&gt;
-Weight: 66.6 lbs&lt;/p&gt;</t>
+Color: Gray or Natural&lt;br&gt;
+Weight: 82.2 or 66.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -4868,11 +4868,11 @@
 - Rust-resistant&lt;br&gt;
 - powder-coated steel frame&lt;br&gt;
 - Includes umbrella hole and cap Included items and dimensions:&lt;br&gt;
-- Patio Dining Table: color: Black or Gray; dimensions: 40" L x 40" W x 28" H; feature: Contemporary&lt;br&gt;
-- Swivel Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary&lt;/p&gt;
+- Patio Dining Table: color: Black or Gray&lt;br&gt;
+- Swivel Chair: color: Black or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyethylene Wicker, Polyspun.&lt;br&gt;
 Color: Black or Gray&lt;br&gt;
-Weight: 180.7 lbs&lt;/p&gt;</t>
+Weight: 180.7 or 156.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" s="26" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -5010,7 +5010,7 @@
       <c r="G31" s="26" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SINTRA 5 Pc. Patio Dining Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel, Polyethylene Wicker, Polyspun, then finished in Black or Gray tones to suit a range of interiors.&lt;br&gt;
+SINTRA 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyethylene Wicker, Polyspun and finished in Black or Gray tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 40"L X 40"W X 28"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Black or Gray&lt;br&gt;
@@ -5018,11 +5018,11 @@
 - Rust-resistant&lt;br&gt;
 - powder-coated steel frame&lt;br&gt;
 - Includes umbrella hole and cap Included items and dimensions:&lt;br&gt;
-- Patio Dining Table: color: Black or Gray; dimensions: 40" L x 40" W x 28" H; feature: Contemporary&lt;br&gt;
-- Arm Chair: color: Black or Gray; dimensions: 26 1 or 2" W x 23 1 or 2"D x 36 1 or 2" H; feature: Contemporary&lt;/p&gt;
+- Patio Dining Table: color: Black or Gray&lt;br&gt;
+- Swivel Chair: color: Black or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyethylene Wicker, Polyspun.&lt;br&gt;
 Color: Black or Gray&lt;br&gt;
-Weight: 156.5 lbs&lt;/p&gt;</t>
+Weight: 180.7 or 156.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" s="26" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5318,7 +5318,7 @@
 - Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H&lt;br&gt;
 - Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Steel, PE Rattan, Foam.&lt;br&gt;
-Color: Black&lt;/p&gt;</t>
+Color: Black or Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H33" s="28" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5454,7 +5454,7 @@
       <c r="G34" s="28" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZALIKA 3 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Steel, PE Rattan, Foam and finished in Natural tones for a clean, cohesive look.&lt;br&gt;
+ZALIKA 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Fabric, Steel, PE Rattan, Foam build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Powder-Coated Steel Frame&lt;br&gt;
@@ -5463,7 +5463,7 @@
 - Patio Side Table: dimensions: 19.5" W x 19.5"D x 21" H&lt;br&gt;
 - Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Steel, PE Rattan, Foam.&lt;br&gt;
-Color: Natural&lt;/p&gt;</t>
+Color: Black or Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H34" s="28" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -5609,7 +5609,7 @@
 - Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;br&gt;
 - Patio Bench: dimensions: 51.5" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Steel, PE Rattan, Foam.&lt;br&gt;
-Color: Black&lt;/p&gt;</t>
+Color: Black or Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" s="30" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -5745,7 +5745,7 @@
       <c r="G36" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZALIKA 4 Pc. Conversation Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Fabric, Steel, PE Rattan, Foam construction and Natural tones, it blends durability with visual warmth.&lt;br&gt;
+ZALIKA 4 Pc. Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Steel, PE Rattan, Foam, then finished in Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Powder-Coated Steel Frame&lt;br&gt;
@@ -5755,7 +5755,7 @@
 - Patio Chair (2 / CTN): dimensions: 22" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;br&gt;
 - Patio Bench: dimensions: 51.5" W x 26.5"D x 35" H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Steel, PE Rattan, Foam.&lt;br&gt;
-Color: Natural&lt;/p&gt;</t>
+Color: Black or Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H36" s="30" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -5892,17 +5892,17 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H&lt;/p&gt;
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H / Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Natural or Black&lt;br&gt;
 - Sturdy &amp;amp; Durable Design&lt;br&gt;
 - Easy to store&lt;br&gt;
 - Handcrafted BOHO Chic Included items and dimensions:&lt;br&gt;
-- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary&lt;br&gt;
-- Patio Chair (2 / CTN): color: Black; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary&lt;/p&gt;
+- Round Table: color: Natural or Black or Natural or Natural or Gray&lt;br&gt;
+- Patio Chair (2 / CTN): color: Natural or Black or Natural or Natural or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.&lt;br&gt;
-Color: Natural or Black&lt;br&gt;
-Weight: 37.6 lbs&lt;/p&gt;</t>
+Color: Natural or Black or Natural or Natural or Gray&lt;br&gt;
+Weight: 37.6 or 21.3 or 28.1 or 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H37" s="32" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6044,17 +6044,18 @@
       <c r="G38" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZUBERI 3 Pc. Patio Conversation Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric construction and Natural tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H&lt;/p&gt;
+ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H / Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
+- Natural or Black&lt;br&gt;
 - Sturdy &amp;amp; Durable Design&lt;br&gt;
 - Easy to store&lt;br&gt;
 - Handcrafted BOHO Chic Included items and dimensions:&lt;br&gt;
-- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary&lt;br&gt;
-- Patio Chair (2 / CTN): color: Natural; dimensions: 25" W x 23.5"D x 31" H; feature: Contemporary&lt;/p&gt;
+- Round Table: color: Natural or Black or Natural or Natural or Gray&lt;br&gt;
+- Patio Chair (2 / CTN): color: Natural or Black or Natural or Natural or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.&lt;br&gt;
-Color: Natural&lt;br&gt;
-Weight: 21.3 lbs&lt;/p&gt;</t>
+Color: Natural or Black or Natural or Natural or Gray&lt;br&gt;
+Weight: 37.6 or 21.3 or 28.1 or 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H38" s="32" t="inlineStr">
@@ -6138,7 +6139,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -6192,17 +6193,18 @@
       <c r="G39" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZUBERI 3 Pc. Patio Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H&lt;/p&gt;
+ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H / Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
+- Natural or Black&lt;br&gt;
 - Sturdy &amp;amp; Durable Design&lt;br&gt;
 - Easy to store&lt;br&gt;
 - Handcrafted BOHO Chic Included items and dimensions:&lt;br&gt;
-- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary&lt;br&gt;
-- Stacking Chair (2 or STACK): color: Natural; dimensions: 21" W x 25"D x 34" H; feature: Contemporary&lt;/p&gt;
+- Round Table: color: Natural or Black or Natural or Natural or Gray&lt;br&gt;
+- Patio Chair (2 / CTN): color: Natural or Black or Natural or Natural or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.&lt;br&gt;
-Color: Natural&lt;br&gt;
-Weight: 28.1 lbs&lt;/p&gt;</t>
+Color: Natural or Black or Natural or Natural or Gray&lt;br&gt;
+Weight: 37.6 or 21.3 or 28.1 or 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H39" s="32" t="inlineStr">
@@ -6286,7 +6288,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -6340,18 +6342,18 @@
       <c r="G40" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZUBERI 3 Pc. Patio Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric and finished in Natural or Gray tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H&lt;/p&gt;
+ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H / Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Natural or Gray&lt;br&gt;
+- Natural or Black&lt;br&gt;
 - Sturdy &amp;amp; Durable Design&lt;br&gt;
 - Easy to store&lt;br&gt;
 - Handcrafted BOHO Chic Included items and dimensions:&lt;br&gt;
-- Round Table: color: Natural; dimensions: 21.7" L x 21.7" W x 15.7" H; feature: Contemporary&lt;br&gt;
-- Stacking Chair (2 or STACK): color: Gray; dimensions: 23" W x 23.5"D x 35" H; feature: Contemporary&lt;/p&gt;
+- Round Table: color: Natural or Black or Natural or Natural or Gray&lt;br&gt;
+- Patio Chair (2 / CTN): color: Natural or Black or Natural or Natural or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric.&lt;br&gt;
-Color: Natural or Gray&lt;br&gt;
-Weight: 35.9 lbs&lt;/p&gt;</t>
+Color: Natural or Black or Natural or Natural or Gray&lt;br&gt;
+Weight: 37.6 or 21.3 or 28.1 or 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H40" s="32" t="inlineStr">
@@ -6439,7 +6441,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -6503,10 +6505,10 @@
 - Includes back and seat cushions&lt;br&gt;
 - Easy to assemble with included hardware kit&lt;br&gt;
 - Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
-- Swing Chair: color: Black; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern&lt;br&gt;
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+- Swing Chair: color: Black or Dark Gray or Light Gray&lt;br&gt;
+- Stand: color: Black or Dark Gray or Light Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 71.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6591,7 +6593,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -6645,7 +6647,7 @@
       <c r="G42" s="34" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BREEZE Swing Chair w/ Stand creates a cohesive setup that feels inviting the moment you walk in. As a outdoor chair, it is designed to coordinate with matching pieces. The Modern character adds definition without feeling heavy. With Steel, Mesh, Fabric construction and Dark Gray tones, it blends durability with visual warmth.&lt;br&gt;
+BREEZE Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Crafted with Steel, Mesh, Fabric, then finished in Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 28""W X 34 1/4""D X 46""H"&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Modern&lt;br&gt;
@@ -6655,10 +6657,10 @@
 - Includes back and seat cushions&lt;br&gt;
 - Easy to assemble with included hardware kit&lt;br&gt;
 - Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
-- Swing Chair: color: Dark Gray; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern&lt;br&gt;
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+- Swing Chair: color: Black or Dark Gray or Light Gray&lt;br&gt;
+- Stand: color: Black or Dark Gray or Light Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 71.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6743,7 +6745,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -6797,7 +6799,7 @@
       <c r="G43" s="34" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BREEZE Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. This outdoor chair is made to fit naturally into the room. A Modern profile gives the space a refined, approachable look. Finished in Light Gray tones, the Steel, Mesh, Fabric build keeps the look polished and practical.&lt;br&gt;
+BREEZE Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Crafted with Steel, Mesh, Fabric, then finished in Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 28""W X 34 1/4""D X 46""H"&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Modern&lt;br&gt;
@@ -6807,10 +6809,10 @@
 - Includes back and seat cushions&lt;br&gt;
 - Easy to assemble with included hardware kit&lt;br&gt;
 - Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
-- Swing Chair: color: Light Gray; dimensions: 28" W x 34 1 or 4"D x 46" H; feature: Modern&lt;br&gt;
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+- Swing Chair: color: Black or Dark Gray or Light Gray&lt;br&gt;
+- Stand: color: Black or Dark Gray or Light Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 71.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6895,7 +6897,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -6959,10 +6961,10 @@
 - Includes back and seat cushions&lt;br&gt;
 - Easy to assemble with included hardware kit&lt;br&gt;
 - Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
-- Swing Chair: color: Black; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern&lt;br&gt;
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+- Swing Chair: color: Black or Dark Gray or Light Gray&lt;br&gt;
+- Stand: color: Black or Dark Gray or Light Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 68.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7047,7 +7049,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -7101,7 +7103,7 @@
       <c r="G45" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CRUSH Swing Chair w/ Stand is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Modern character adds definition without feeling heavy. Built from Steel, Mesh, Fabric and finished in Dark Gray tones for a clean, cohesive look.&lt;br&gt;
+CRUSH Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Steel, Mesh, Fabric build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Modern&lt;br&gt;
@@ -7111,10 +7113,10 @@
 - Includes back and seat cushions&lt;br&gt;
 - Easy to assemble with included hardware kit&lt;br&gt;
 - Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
-- Swing Chair: color: Dark Gray; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern&lt;br&gt;
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+- Swing Chair: color: Black or Dark Gray or Light Gray&lt;br&gt;
+- Stand: color: Black or Dark Gray or Light Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 68.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7199,7 +7201,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -7253,7 +7255,7 @@
       <c r="G46" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CRUSH Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor chair is made to fit naturally into the room. A Modern profile gives the space a refined, approachable look. Crafted with Steel, Mesh, Fabric, then finished in Light Gray tones to suit a range of interiors.&lt;br&gt;
+CRUSH Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Steel, Mesh, Fabric build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 28 1/4""W X 29 1/2""D X 43 1/4""H"&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Modern&lt;br&gt;
@@ -7263,10 +7265,10 @@
 - Includes back and seat cushions&lt;br&gt;
 - Easy to assemble with included hardware kit&lt;br&gt;
 - Max weight capacity: 220 lbs Included items and dimensions:&lt;br&gt;
-- Swing Chair: color: Light Gray; dimensions: 28 1 or 4" W x 29 1 or 2"D x 43 1 or 4" H; feature: Modern&lt;br&gt;
-- Stand: color: Black; dimensions: 45 1 or 4" L x 42 1 or 2" W x 75 1 or 2" H; feature: Modern&lt;/p&gt;
+- Swing Chair: color: Black or Dark Gray or Light Gray&lt;br&gt;
+- Stand: color: Black or Dark Gray or Light Gray&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 68.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7351,7 +7353,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -7493,7 +7495,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -7637,7 +7639,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -7692,7 +7694,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ILONA L-Sectional and Coffee Table and End Table is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor sofa set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, Polyester Canvas, Faux Rattan and finished in Brown or Beige tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: L-SECTIONAL: 103 1/4"W X 79 1/4"D X 25 1/2-31"H&lt;/p&gt;
+Product Dimensions: L-SECTIONAL: 103 1/4"W X 79 1/4"D X 25 1/2-31"H / L-SECTIONAL: 79 1/2"W X 79"D X 25 1/2-31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Brown or Beige&lt;br&gt;
 - Aluminum Frame&lt;br&gt;
@@ -7700,15 +7702,15 @@
 - 5mm Tempered Glass Table Tops&lt;br&gt;
 - UV &amp;amp; Water Resistant&lt;br&gt;
 - Beige Fabric Cushions Included items and dimensions:&lt;br&gt;
-- Left Arm Chair: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary&lt;br&gt;
-- Corner: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary&lt;br&gt;
-- Ottoman: color: Brown or Beige; dimensions: 27 3 or 4" W x 27 1 or 4"D x 18" H; feature: Contemporary&lt;br&gt;
-- Coffee Table: color: Brown or Beige; dimensions: 34 5 or 8" L x 19 1 or 4" W x 13 3 or 4" H; feature: Contemporary&lt;br&gt;
-- End Table: color: Brown or Beige; dimensions: 17 3 or 4" L x 17 3 or 4" W x 19 5 or 8" H; feature: Contemporary&lt;br&gt;
-- Armless Chair: color: Brown or Beige; dimensions: 24 1 or 4" W x 27 1 or 2"D x 25 1 or 2 - 31" H; feature: Contemporary&lt;/p&gt;
+- Left Arm Chair: color: Brown or Beige&lt;br&gt;
+- Corner: color: Brown or Beige&lt;br&gt;
+- Ottoman: color: Brown or Beige&lt;br&gt;
+- Coffee Table: color: Brown or Beige&lt;br&gt;
+- End Table: color: Brown or Beige&lt;br&gt;
+- Armless Chair: color: Brown or Beige&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
 Color: Brown or Beige&lt;br&gt;
-Weight: 204 lbs&lt;/p&gt;</t>
+Weight: 204 or 179 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" s="38" t="inlineStr">
@@ -7792,7 +7794,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -7846,8 +7848,8 @@
       <c r="G50" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ILONA L-Sectional and Coffee Table and End Table offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor sofa set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, Polyester Canvas, Faux Rattan, then finished in Brown or Beige tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: L-SECTIONAL: 79 1/2"W X 79"D X 25 1/2-31"H&lt;/p&gt;
+ILONA L-Sectional and Coffee Table and End Table is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor sofa set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, Polyester Canvas, Faux Rattan and finished in Brown or Beige tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: L-SECTIONAL: 103 1/4"W X 79 1/4"D X 25 1/2-31"H / L-SECTIONAL: 79 1/2"W X 79"D X 25 1/2-31"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Brown or Beige&lt;br&gt;
 - Aluminum Frame&lt;br&gt;
@@ -7855,15 +7857,15 @@
 - 5mm Tempered Glass Table Tops&lt;br&gt;
 - UV &amp;amp; Water Resistant&lt;br&gt;
 - Beige Fabric Cushions Included items and dimensions:&lt;br&gt;
-- Left Arm Chair: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary&lt;br&gt;
-- Corner: color: Brown or Beige; dimensions: 27 1 or 2" W x 27 1 or 2"D x 31" H; feature: Contemporary&lt;br&gt;
-- Ottoman: color: Brown or Beige; dimensions: 27 3 or 4" W x 27 1 or 4"D x 18" H; feature: Contemporary&lt;br&gt;
-- Coffee Table: color: Brown or Beige; dimensions: 34 5 or 8" L x 19 1 or 4" W x 13 3 or 4" H; feature: Contemporary&lt;br&gt;
-- End Table: color: Brown or Beige; dimensions: 17 3 or 4" L x 17 3 or 4" W x 19 5 or 8" H; feature: Contemporary&lt;br&gt;
-- Armless Chair: color: Brown or Beige; dimensions: 24 1 or 4" W x 27 1 or 2"D x 25 1 or 2 - 31" H; feature: Contemporary&lt;/p&gt;
+- Left Arm Chair: color: Brown or Beige&lt;br&gt;
+- Corner: color: Brown or Beige&lt;br&gt;
+- Ottoman: color: Brown or Beige&lt;br&gt;
+- Coffee Table: color: Brown or Beige&lt;br&gt;
+- End Table: color: Brown or Beige&lt;br&gt;
+- Armless Chair: color: Brown or Beige&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
 Color: Brown or Beige&lt;br&gt;
-Weight: 179 lbs&lt;/p&gt;</t>
+Weight: 204 or 179 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" s="38" t="inlineStr">
@@ -7947,7 +7949,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -8002,18 +8004,18 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MACKAY 5 Pc. Patio Dining Set sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, FSC Certified 100% Teak Wood, then finished in Beige or Natural Teak tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H&lt;/p&gt;
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H / 59"L X 35 1/2"W X 29"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Beige or Natural Teak&lt;br&gt;
 - Mixed material of teak wood and metal frame&lt;br&gt;
 - Extends from 61" to 84" w/ butterfly leaf&lt;br&gt;
 - Seats up to 8 people&lt;br&gt;
 - Level control table legs Included items and dimensions:&lt;br&gt;
-- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 61 1 or 2 - 84" L x 35 1 or 2" W x 30" H; feature: Contemporary&lt;br&gt;
-- Reclining Chair (2 / CTN): color: Beige or Natural Teak; dimensions: 24 1 or 2" W x 27 1 or 2"D x 42 1 or 2" H; feature: Contemporary&lt;/p&gt;
+- Patio Dining Table: color: Beige or Natural Teak or Gun Metal or Natural Teak&lt;br&gt;
+- Reclining Chair (2 / CTN): color: Beige or Natural Teak or Gun Metal or Natural Teak&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
-Color: Beige or Natural Teak&lt;br&gt;
-Weight: 174.14 lbs&lt;/p&gt;</t>
+Color: Beige or Natural Teak or Gun Metal or Natural Teak&lt;br&gt;
+Weight: 174.14 or 55.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" s="40" t="inlineStr">
@@ -8097,7 +8099,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -8151,19 +8153,19 @@
       <c r="G52" s="40" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Gather around MACKAY 5 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, FSC Certified 100% Teak Wood construction and Gun Metal or Natural Teak tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 59"L X 35 1/2"W X 29"H&lt;/p&gt;
+MACKAY 5 Pc. Patio Dining Set sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, FSC Certified 100% Teak Wood, then finished in Beige or Natural Teak tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H / 59"L X 35 1/2"W X 29"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Gun Metal or Natural Teak&lt;br&gt;
+- Beige or Natural Teak&lt;br&gt;
 - Mixed material of teak wood and metal frame&lt;br&gt;
-- Seats up to 6 people&lt;br&gt;
-- Level control table legs&lt;br&gt;
-- Includes umbrella hole and cap Included items and dimensions:&lt;br&gt;
-- Patio Dining Table: color: Gun Metal or Natural Teak; dimensions: 59" L x 35 1 or 2" W x 29" H; feature: Contemporary&lt;br&gt;
-- Stacking Chair: color: Gun Metal or Natural Teak; dimensions: 22.5" W x 25"D x 34" H; feature: Contemporary&lt;/p&gt;
+- Extends from 61" to 84" w/ butterfly leaf&lt;br&gt;
+- Seats up to 8 people&lt;br&gt;
+- Level control table legs Included items and dimensions:&lt;br&gt;
+- Patio Dining Table: color: Beige or Natural Teak or Gun Metal or Natural Teak&lt;br&gt;
+- Reclining Chair (2 / CTN): color: Beige or Natural Teak or Gun Metal or Natural Teak&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
-Color: Gun Metal or Natural Teak&lt;br&gt;
-Weight: 55.1 lbs&lt;/p&gt;</t>
+Color: Beige or Natural Teak or Gun Metal or Natural Teak&lt;br&gt;
+Weight: 174.14 or 55.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" s="40" t="inlineStr">
@@ -8247,7 +8249,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -8392,7 +8394,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -8538,7 +8540,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8687,7 +8689,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">

--- a/FOA SETS/Outdoor-Set.xlsx
+++ b/FOA SETS/Outdoor-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -794,12 +794,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ALYCIA 7 Pc. Patio Dining Set in White Beige Gray | GOODDEGG</t>
+          <t>ALYCIA 7 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The ALYCIA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALYCIA 7 Pc. Patio Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -937,12 +937,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ANTIGUA 4 Pc. Patio Set in Gun Metal Brown Gray | GOODDEGG</t>
+          <t>ANTIGUA 4 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The ANTIGUA Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTIGUA 4 Pc. Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The ANTIGUA Patio w/ Ottomans makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AROSA 3 Pc. Fire Pit Counter Height Set in Black Gray | GOODDEGG</t>
+          <t>AROSA 3 Pc. Fire Pit Counter Height Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AROSA Fire Pit Counter Height makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Patio Set AROSA 3 Pc. Fire Pit Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BARBUDA 6 Pc. Conversation Set w/ Fire Pit in Gray | GOODDEGG</t>
+          <t>BARBUDA 6 Pc. Conversation Set w/ Fire Pit | GOODDEGG</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BARBUDA Conversation w/ Fire Pit makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Patio Set BARBUDA 6 Pc. Conversation Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The BORDEAUX Dining w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORDEAUX 6 Pc. Dining Set w/ Bench Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>JOHARI 3 Pc. Conversation Set in Natural Beige | GOODDEGG</t>
+          <t>JOHARI 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The JOHARI Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOHARI 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>JOHARI 4 Pc. Conversation Set in Natural Beige | GOODDEGG</t>
+          <t>JOHARI 4 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The JOHARI Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOHARI 4 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>KIMARA 3 Pc. Patio Dining Set in Black | GOODDEGG</t>
+          <t>KIMARA 3 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMARA 3 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J10" s="18" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>KIMARA 3 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+          <t>KIMARA 3 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMARA 3 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J11" s="18" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>KIMARA 5 Pc. Patio Dining Set in Black | GOODDEGG</t>
+          <t>KIMARA 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMARA 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -2402,12 +2402,12 @@
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>KIMARA 5 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+          <t>KIMARA 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>The KIMARA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMARA 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
-          <t>KYUSHU 4 Pc. Patio Set in Beige Natural | GOODDEGG</t>
+          <t>KYUSHU 4 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>The KYUSHU Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KYUSHU 4 Pc. Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
-          <t>KYUSHU 4 Pc. Patio Set in Black Natural | GOODDEGG</t>
+          <t>KYUSHU 4 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t>The KYUSHU Patio makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KYUSHU 4 Pc. Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>LOTUS 5 Pc. Conversation Set in Black Light Brown | GOODDEGG</t>
+          <t>LOTUS 5 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>The LOTUS Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOTUS 5 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LYON Game Table w/ Arm Chairs makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Patio Set LYON 5 Pc. Game Table Set w/ 4 Arm supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LYON Game Table w/ Armless Chairs makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Patio Set LYON 5 Pc. Game Table Set w/ 4 supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LYON Game Table w/ Stacking Chairs makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Patio Set LYON 5 Pc. Game Table Set w/ 4 supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MONZA 7 Pc. Dining Table Set in Gun Metal Gray | GOODDEGG</t>
+          <t>MONZA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>The MONZA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONZA 7 Pc. Dining Table Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NIAMBI 3 Pc. Patio Bistro Set in Natural | GOODDEGG</t>
+          <t>NIAMBI 3 Pc. Patio Bistro Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>The NIAMBI Patio Bistro makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIAMBI 3 Pc. Patio Bistro Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NIAMBI 3 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+          <t>NIAMBI 3 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIAMBI 3 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>NIAMBI 5 Pc. Patio Dining Set in Gray | GOODDEGG</t>
+          <t>NIAMBI 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIAMBI 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J23" s="24" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="H24" s="24" t="inlineStr">
         <is>
-          <t>NIAMBI 5 Pc. Patio Dining Set in Natural | GOODDEGG</t>
+          <t>NIAMBI 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I24" s="24" t="inlineStr">
         <is>
-          <t>The NIAMBI Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIAMBI 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J24" s="24" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NUSA 7 Pc. Dining Table Set in Natural | GOODDEGG</t>
+          <t>NUSA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>The NUSA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUSA 7 Pc. Dining Table Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PALMA 7 Pc. Dining Table Set in Black Gray | GOODDEGG</t>
+          <t>PALMA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>The PALMA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALMA 7 Pc. Dining Table Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SARABI 3 Pc. Conversation Set in Black Natural | GOODDEGG</t>
+          <t>SARABI 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>The SARABI Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SARABI 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SEGOVIA 5 Pc. Dining Table Set in Navy Black Gray | GOODDEGG</t>
+          <t>SEGOVIA 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>The SEGOVIA Dining Table makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SEGOVIA 5 Pc. Dining Table Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SEGOVIA 5 Pc. Patio Dining Set in Black Gray | GOODDEGG</t>
+          <t>SEGOVIA 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>The SEGOVIA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SEGOVIA 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="H30" s="26" t="inlineStr">
         <is>
-          <t>SINTRA 5 Pc. Patio Dining Set in Black Gray | GOODDEGG</t>
+          <t>SINTRA 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I30" s="26" t="inlineStr">
         <is>
-          <t>The SINTRA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J30" s="26" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="H31" s="26" t="inlineStr">
         <is>
-          <t>SINTRA 5 Pc. Patio Dining Set in Black Gray | GOODDEGG</t>
+          <t>SINTRA 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I31" s="26" t="inlineStr">
         <is>
-          <t>The SINTRA Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J31" s="26" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SINTRA 6 Pc. Patio Dining Set w/ Bench in Black Gray | GOODDEG</t>
+          <t>SINTRA 6 Pc. Patio Dining Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SINTRA Patio Dining w/ Bench makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA 6 Pc. Patio Dining Set w/ Bench Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="H33" s="28" t="inlineStr">
         <is>
-          <t>ZALIKA 3 Pc. Conversation Set in Black | GOODDEGG</t>
+          <t>ZALIKA 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I33" s="28" t="inlineStr">
         <is>
-          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J33" s="28" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="H34" s="28" t="inlineStr">
         <is>
-          <t>ZALIKA 3 Pc. Conversation Set in Natural | GOODDEGG</t>
+          <t>ZALIKA 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I34" s="28" t="inlineStr">
         <is>
-          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J34" s="28" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="H35" s="30" t="inlineStr">
         <is>
-          <t>ZALIKA 4 Pc. Conversation Set in Black | GOODDEGG</t>
+          <t>ZALIKA 4 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I35" s="30" t="inlineStr">
         <is>
-          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA 4 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J35" s="30" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H36" s="30" t="inlineStr">
         <is>
-          <t>ZALIKA 4 Pc. Conversation Set in Natural | GOODDEGG</t>
+          <t>ZALIKA 4 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I36" s="30" t="inlineStr">
         <is>
-          <t>The ZALIKA Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA 4 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J36" s="30" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="H37" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural Black | GOODDEGG</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I37" s="32" t="inlineStr">
         <is>
-          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J37" s="32" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="H38" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural | GOODDEGG</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I38" s="32" t="inlineStr">
         <is>
-          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J38" s="32" t="inlineStr">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="H39" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural | GOODDEGG</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I39" s="32" t="inlineStr">
         <is>
-          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J39" s="32" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="H40" s="32" t="inlineStr">
         <is>
-          <t>ZUBERI 3 Pc. Patio Conversation Set in Natural Gray | GOODDEGG</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I40" s="32" t="inlineStr">
         <is>
-          <t>The ZUBERI Patio Conversation makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZUBERI 3 Pc. Patio Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J40" s="32" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="H41" s="34" t="inlineStr">
         <is>
-          <t>BREEZE Swing Chair w/ Stand in Black | GOODDEGG</t>
+          <t>BREEZE Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I41" s="34" t="inlineStr">
         <is>
-          <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BREEZE Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J41" s="34" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
-          <t>BREEZE Swing Chair w/ Stand in Dark Gray | GOODDEGG</t>
+          <t>BREEZE Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I42" s="34" t="inlineStr">
         <is>
-          <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BREEZE Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J42" s="34" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
-          <t>BREEZE Swing Chair w/ Stand in Light Gray | GOODDEGG</t>
+          <t>BREEZE Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I43" s="34" t="inlineStr">
         <is>
-          <t>The BREEZE Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BREEZE Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J43" s="34" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="H44" s="36" t="inlineStr">
         <is>
-          <t>CRUSH Swing Chair w/ Stand in Black | GOODDEGG</t>
+          <t>CRUSH Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I44" s="36" t="inlineStr">
         <is>
-          <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRUSH Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J44" s="36" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="H45" s="36" t="inlineStr">
         <is>
-          <t>CRUSH Swing Chair w/ Stand in Dark Gray | GOODDEGG</t>
+          <t>CRUSH Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I45" s="36" t="inlineStr">
         <is>
-          <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRUSH Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J45" s="36" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="H46" s="36" t="inlineStr">
         <is>
-          <t>CRUSH Swing Chair w/ Stand in Light Gray | GOODDEGG</t>
+          <t>CRUSH Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I46" s="36" t="inlineStr">
         <is>
-          <t>The CRUSH Swing Chair w/ Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRUSH Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J46" s="36" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The MACKAY Reclining Chairs and Ottomans adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY 2 Reclining Chairs and 2 Ottomans supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CYPRUS 7 Pc. Bar Table Set in Gray | GOODDEGG</t>
+          <t>CYPRUS 7 Pc. Bar Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>The CYPRUS Bar Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CYPRUS 7 Pc. Bar Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="I49" s="38" t="inlineStr">
         <is>
-          <t>ILONA L-Sectional and Coffee Table and End Table offers relaxed seating for everyday. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Sofa Set ILONA L-Sectional and Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J49" s="38" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="I50" s="38" t="inlineStr">
         <is>
-          <t>ILONA L-Sectional and Coffee Table and End Table offers relaxed seating for everyday. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Sofa Set ILONA L-Sectional and Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J50" s="38" t="inlineStr">
@@ -8020,12 +8020,12 @@
       </c>
       <c r="H51" s="40" t="inlineStr">
         <is>
-          <t>MACKAY 5 Pc. Patio Dining Set in Beige Natural Teak | GOODDEGG</t>
+          <t>MACKAY 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I51" s="40" t="inlineStr">
         <is>
-          <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY 5 Pc. Patio Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J51" s="40" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="H52" s="40" t="inlineStr">
         <is>
-          <t>MACKAY 5 Pc. Patio Dining Set in Gun Metal Natural Teak | GOODDEG</t>
+          <t>MACKAY 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I52" s="40" t="inlineStr">
         <is>
-          <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY 5 Pc. Patio Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J52" s="40" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>The MACKAY Patio Dining makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY 7 Pc. Patio Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>MACKAY Patio Dining w/ Ottomans makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>MALIA 6 Pc. Patio Dining Set w/ Bench in Gray | GOODDEGG</t>
+          <t>MALIA 6 Pc. Patio Dining Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>The MALIA Patio Dining w/ Bench creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Patio Dining Table MALIA 6 Pc. Patio Dining supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">

--- a/FOA SETS/Outdoor-Set.xlsx
+++ b/FOA SETS/Outdoor-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,171 +582,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG55"/>
+  <dimension ref="A1:AJ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>seo title(70char)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>seo description(160char)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Short Description</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Short Description - Red Text</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Item Type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Parts for Group Items</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Images</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Image src</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>combine image src</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>East(cost)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>EAST COST (Updated)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MSRP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Weight (LB)</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Product Dimension (Inch)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Shipping Length (IN)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Shipping Width (IN)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Shipping Height (IN)</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Volume (CUFT)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Fixed tags</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Variable tags</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
@@ -755,30 +770,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>alycia-7-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>White/Beige/Gray</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>CM-OT2141T-7PC</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Dining Set</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ALYCIA 7 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Gather around ALYCIA 7 Pc. Patio Dining Set, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor dining set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White or Beige or Gray tones, the Aluminum, Polyester Canvas, Glass, build keeps the look polished and practical.&lt;/p&gt;
@@ -792,97 +812,103 @@
 Weight: 217.82 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>ALYCIA 7 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>ALYCIA 7 Pc. Patio Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>ALYCIA</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>7 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>CM-OT2141T-1, CM-OT2141T-2, CM-OT2141AC-6PK</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>CM-OT2141-1.jpg,CM-OT2141T-WB-1.jpg,CM-OT2141SC-WB-1.jpg,CM-OT2141-3.jpg,CM-OT2141-4.jpg,CM-OT2141-5.jpg</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>CM-OT2141-1.jpg,CM-OT2141T-WB-1.jpg,CM-OT2141SC-WB-1.jpg,CM-OT2141-3.jpg,CM-OT2141-4.jpg,CM-OT2141-5.jpg</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>849</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="T2" s="2" t="n">
         <v>849</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>2247</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>217.82</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Aluminum, Polyester Canvas, Glass, Others</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Transitional,White/Beige/Gray,Aluminum, Polyester Canvas, Glass, Others,Aluminum Construction,5mm Tempered Glass Table</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>34.9</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Outdoor, Dining Set, ALYCIA, DINING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
@@ -891,30 +917,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>antigua-4-pc-patio-set</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Gun Metal/Brown/Gray</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>GM-1003-4PC</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>ANTIGUA 4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ANTIGUA 4 Pc. Patio Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Aluminum, Polyethylene Wicker, Polyspun and finished in Gun Metal or Brown or Gray tones for a clean, cohesive look.&lt;br&gt;
@@ -935,102 +966,108 @@
 Weight: 174 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>ANTIGUA 4 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>ANTIGUA 4 Pc. Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>ANTIGUA</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>GM-1003, GM-1004, GM-1005</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>GM-1003-1-Z.jpg,GM-1003-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>GM-1003-1-Z.jpg,GM-1003-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>1129</v>
       </c>
-      <c r="Q3" s="1" t="n">
+      <c r="T3" s="1" t="n">
         <v>1129</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>2877</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>174</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>63"L X 35 1/2"W X 17 3/4 - 27"H</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Aluminum, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Contemporary,Gun Metal/Brown/Gray,Aluminum, Polyethylene Wicker, Polyspun,Adjustable backrest with gas springs,Ottoman as footrest or extra seats,Adjustable table height,Padded headrest cushion,Washable cushion covers,Table includes umbrella hole and cap</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
         <v>60.7</v>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ANTIGUA</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -1039,30 +1076,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>antigua-6-pc-patio-set-w-2-ottomans</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Gun Metal/Brown/Gray</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>GM-1003-6PC</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Polyethylene Wicker, Polyspun, then finished in Gun Metal or Brown or Gray tones to suit a range of interiors.&lt;br&gt;
@@ -1084,102 +1126,108 @@
 Weight: 191.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans | GOODDEGG</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>ANTIGUA 6 Pc. Patio Set w/ 2 Ottomans supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>ANTIGUA</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>6 Pc. Patio Set w/ 2 Ottomans</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>GM-1003, GM-1004, GM-1005, GM-1006-2PK</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>GM-1003-6PC.jpg,GM-1003-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>GM-1003-6PC.jpg,GM-1003-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
         <v>1299</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="T4" s="1" t="n">
         <v>1299</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>3297</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>191.9</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>63"L X 35 1/2"W X 17 3/4 - 27"H</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Aluminum, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Contemporary,Gun Metal/Brown/Gray,Aluminum, Polyethylene Wicker, Polyspun,Adjustable backrest with gas springs,Ottoman as footrest or extra seats,Adjustable table height,Padded headrest cushion,Washable cushion covers,Table includes umbrella hole and cap</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
         <v>71</v>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ANTIGUA</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -1188,30 +1236,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>arosa-3-pc-fire-pit-counter-height-set</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Black/Gray</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>GM-2024-3PC</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>AROSA 3 Pc. Fire Pit Counter Height Set</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 AROSA 3 Pc. Fire Pit Counter Height Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Ceramic Tile, Polyrattan, Polyspun Fabric construction and Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
@@ -1230,102 +1283,108 @@
 Weight: 154 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>AROSA 3 Pc. Fire Pit Counter Height Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Patio Set AROSA 3 Pc. Fire Pit Counter Height supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>AROSA</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>3 Pc. Fire Pit Counter Height Set</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>GM-2024, GM-2025-2PK</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>GM-2024-3PC.jpg,GM-2024-3PC-WB-1.jpg,GM-2024-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>GM-2024-3PC.jpg,GM-2024-3PC-WB-1.jpg,GM-2024-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
         <v>649</v>
       </c>
-      <c r="Q5" s="1" t="n">
+      <c r="T5" s="1" t="n">
         <v>649</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>1707</v>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
         <v>154</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Table: 36.4"L X 36.4"W X 36.6"H, Chair: 25.1"W X 26.3"D X 44.8"H</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Steel, Ceramic Tile, Polyrattan, Polyspun Fabric</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Contemporary,Black/Gray,Steel, Ceramic Tile, Polyrattan, Polyspun Fabric,360-Degree Swivel Seats,Tile Top Firepit Tabletop,Mixed Material Construction,Powder Coated Steel Frame,Easy To Assemble</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
         <v>20.3</v>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, AROSA</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -1334,30 +1393,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>barbuda-6-pc-conversation-set-w-fire-pit</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>GM-1045-6PC</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>BARBUDA 6 Pc. Conversation Set w/ Fire Pit</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 BARBUDA 6 Pc. Conversation Set w/ Fire Pit is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyrattan, Polyspun Fabric and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
@@ -1376,102 +1440,108 @@
 Weight: 322.87 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>BARBUDA 6 Pc. Conversation Set w/ Fire Pit | GOODDEGG</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Patio Set BARBUDA 6 Pc. Conversation Set w/ supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>BARBUDA</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>6 Pc. Conversation Set w/ Fire Pit</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>GM-1045, GM-1046-5PK</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>GM-1045-6PC-1.jpg,GM-1045-6PC-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>GM-1045-6PC-1.jpg,GM-1045-6PC-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
         <v>1749</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="T6" s="2" t="n">
         <v>1749</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>4497</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>322.87</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Fire Pit Table: 39"DIA X 27"H, Semi-circle Sectional: 64"W X 29"D X 33.5"H, End Table: 21"W X 28.5"D X 24"H</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Steel, Polyrattan, Polyspun Fabric</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Contemporary,Gray,Steel, Polyrattan, Polyspun Fabric,Modular Design,Tile Top Firepit Tabletop,FSC Certified Teak Wood,Mixed Material Construction,Powder Coated Steel Frame,Washable Cushion Covers</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB6" t="n">
+      <c r="AE6" t="n">
         <v>64.5</v>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, BARBUDA</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -1480,30 +1550,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>bordeaux-6-pc-dining-set-w-bench</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Natural/Light Gray/Beige</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>GM-2017-6PC</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>BORDEAUX 6 Pc. Dining Set w/ Bench</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 BORDEAUX 6 Pc. Dining Set w/ Bench brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural or Light Gray or Beige tones, the Aluminum, Stainless Steel, Polyspun Fabric build keeps the look polished and practical.&lt;br&gt;
@@ -1525,102 +1600,108 @@
 Weight: 307.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>BORDEAUX 6 Pc. Dining Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>BORDEAUX 6 Pc. Dining Set w/ Bench Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>BORDEAUX</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>6 Pc. Dining Set w/ Bench</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>GM-2017-1, GM-2017-2, GM-2020-2PK, GM-2021, GM-2019-2PK</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>GM-2017-6PC.jpg,GM-2017-WB-1.jpg,GM-2017-2.jpg,GM-2017-3.jpg,GM-2017-2.jpg,GM-2017-3.jpg,GM-2017-4.jpg,GM-2017-5.jpg,GM-2017-6.jpg,GM-2017-7.jpg</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>GM-2017-6PC.jpg,GM-2017-WB-1.jpg,GM-2017-2.jpg,GM-2017-3.jpg,GM-2017-4.jpg,GM-2017-5.jpg,GM-2017-6.jpg,GM-2017-7.jpg</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
         <v>2099</v>
       </c>
-      <c r="Q7" s="1" t="n">
+      <c r="T7" s="1" t="n">
         <v>2099</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>5697</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>307.89</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Table: 70.5"W X 38.5"D X 29"H, Chair: 20"W X 26.5"D X 32"H, Armless Chair: 20"W X 26.5"D X 32"H, Bench: 57"W X 16"D X 18.5"H</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Aluminum, Stainless Steel, Polyspun Fabric</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Contemporary,Natural/Light Gray/Beige,Aluminum, Stainless Steel, Polyspun Fabric,Tabletop Fire Pit with Storage Cabinet,Heat Output: 55000BTU,Propane Tank Capacity: 20 Pound,Stainless Steel Ice Chest with Cover,Hand-brushed Wood Texture,Washable Cushion Cover,UV &amp; Water-Resistant</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
         <v>49.1</v>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, BORDEAUX</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -1629,30 +1710,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>johari-3-pc-conversation-set</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Natural/Beige</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>FM80016NT-3PC</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>JOHARI 3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 JOHARI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Natural or Beige tones, the Steel, Fabric, Foam, PE Rattan build keeps the look polished and practical.&lt;br&gt;
@@ -1671,102 +1757,108 @@
 Weight: 91.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>JOHARI 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>JOHARI 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>JOHARI</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>FM80016NT-CH, FM80016NT-T</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>FM80016NT-3PC-1.jpg</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>FM80016NT-3PC-1.jpg</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
         <v>389</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="T8" s="1" t="n">
         <v>389</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>897</v>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>91.3</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5")</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Steel, Fabric, Foam, PE Rattan</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Contemporary,Natural/Beige,Steel, Fabric, Foam, PE Rattan,Powder Coated Steel Frame,10mm Round Wicker,Seat Cushion,Pillow Back w/ 100% Fiber Fill,Weather Resistant</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AB8" t="n">
+      <c r="AE8" t="n">
         <v>19.4</v>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, JOHARI</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -1775,30 +1867,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>johari-4-pc-conversation-set</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Natural/Beige</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>FM80016NT-4PC-BN</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>JOHARI 4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 JOHARI 4 Pc. Conversation Set is designed for everyday living, balancing comfort with a clean, finished look. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Steel, Fabric, Foam, PE Rattan and finished in Natural or Beige tones for a clean, cohesive look.&lt;br&gt;
@@ -1818,135 +1915,146 @@
 Weight: 144.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>JOHARI 4 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>JOHARI 4 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>JOHARI</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>FM80016NT-CH, FM80016NT-BN, FM80016NT-T</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>FM80016NT-4PC-BN-1.jpg</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>FM80016NT-4PC-BN-1.jpg</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
         <v>669</v>
       </c>
-      <c r="Q9" s="1" t="n">
+      <c r="T9" s="1" t="n">
         <v>669</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>1587</v>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>144.1</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>COFFEE TABLE: 30"W X 30"D X 16.5"H, CHAIR: 30"W X 29"D X 25.5"H (SEAT HT: 16.5"), BENCH: 58"W X 29"D X 25.5"H (SEAT HT: 16.5")</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Steel, Fabric, Foam, PE Rattan</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Contemporary,Natural/Beige,Steel, Fabric, Foam, PE Rattan,Powder Coated Steel Frame,10mm Round Wicker,Seat Cushion,Pillow Back w/ 100% Fiber Fill,Weather Resistant</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AB9" t="n">
+      <c r="AE9" t="n">
         <v>38.1</v>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, JOHARI</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>kimara-3-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>FM80001BB-SET</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>KIMARA 3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 KIMARA 3 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and finished in Black tones for a clean, cohesive look.&lt;br&gt;
@@ -1960,139 +2068,150 @@
 Weight: 149.1 or 150.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>KIMARA 3 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>KIMARA 3 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>KIMARA</t>
         </is>
       </c>
-      <c r="K10" s="18" t="inlineStr">
+      <c r="L10" s="18" t="inlineStr">
         <is>
           <t>3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="L10" s="18" t="n"/>
-      <c r="M10" s="18" t="inlineStr">
+      <c r="M10" s="18" t="n"/>
+      <c r="N10" s="18" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="O10" s="18" t="inlineStr">
         <is>
           <t>FM80001BB-1, FM80001BB-2, FM80001BB-T</t>
         </is>
       </c>
-      <c r="O10" s="18" t="inlineStr">
+      <c r="P10" s="18" t="inlineStr">
         <is>
           <t>FM80001BB-SET-1-Z.jpg</t>
         </is>
       </c>
-      <c r="P10" s="18" t="n">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>FM80001BB-SET-1-Z.jpg,FM80001GG-SET-1-Z.jpg</t>
+        </is>
+      </c>
+      <c r="S10" s="18" t="n">
         <v>419</v>
       </c>
-      <c r="Q10" s="19" t="n">
+      <c r="T10" s="19" t="n">
         <v>419</v>
       </c>
-      <c r="R10" s="18" t="n">
+      <c r="U10" s="18" t="n">
         <v>957</v>
       </c>
-      <c r="S10" s="18" t="n">
+      <c r="V10" s="18" t="n">
         <v>149.1</v>
       </c>
-      <c r="T10" s="18" t="inlineStr">
+      <c r="W10" s="18" t="inlineStr">
         <is>
           <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H</t>
         </is>
       </c>
-      <c r="U10" s="18" t="inlineStr">
+      <c r="X10" s="18" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V10" s="18" t="inlineStr">
+      <c r="Y10" s="18" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
-      <c r="W10" s="18" t="inlineStr">
+      <c r="Z10" s="18" t="inlineStr">
         <is>
           <t>Contemporary,Black,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
-      <c r="X10" s="18" t="inlineStr">
+      <c r="AA10" s="18" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y10" s="18" t="n"/>
-      <c r="Z10" s="18" t="n"/>
-      <c r="AA10" s="18" t="n"/>
-      <c r="AB10" s="18" t="n">
+      <c r="AB10" s="18" t="n"/>
+      <c r="AC10" s="18" t="n"/>
+      <c r="AD10" s="18" t="n"/>
+      <c r="AE10" s="18" t="n">
         <v>26.9</v>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, KIMARA</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>kimara-3-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>FM80001GG-SET</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>KIMARA 3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 KIMARA 3 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and finished in Black tones for a clean, cohesive look.&lt;br&gt;
@@ -2106,139 +2225,146 @@
 Weight: 149.1 or 150.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>KIMARA 3 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>KIMARA 3 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="K11" s="18" t="inlineStr">
         <is>
           <t>KIMARA</t>
         </is>
       </c>
-      <c r="K11" s="18" t="inlineStr">
+      <c r="L11" s="18" t="inlineStr">
         <is>
           <t>3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="L11" s="18" t="n"/>
-      <c r="M11" s="18" t="inlineStr">
+      <c r="M11" s="18" t="n"/>
+      <c r="N11" s="18" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="O11" s="18" t="inlineStr">
         <is>
           <t>FM80001GG-T, FM80001GG-1, FM80001GG-2</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="P11" s="18" t="inlineStr">
         <is>
           <t>FM80001GG-SET-1-Z.jpg</t>
         </is>
       </c>
-      <c r="P11" s="18" t="n">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" s="18" t="n">
         <v>399</v>
       </c>
-      <c r="Q11" s="19" t="n">
+      <c r="T11" s="19" t="n">
         <v>399</v>
       </c>
-      <c r="R11" s="18" t="n">
+      <c r="U11" s="18" t="n">
         <v>957</v>
       </c>
-      <c r="S11" s="18" t="n">
+      <c r="V11" s="18" t="n">
         <v>150.7</v>
       </c>
-      <c r="T11" s="18" t="inlineStr">
+      <c r="W11" s="18" t="inlineStr">
         <is>
           <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H</t>
         </is>
       </c>
-      <c r="U11" s="18" t="inlineStr">
+      <c r="X11" s="18" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V11" s="18" t="inlineStr">
+      <c r="Y11" s="18" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
-      <c r="W11" s="18" t="inlineStr">
+      <c r="Z11" s="18" t="inlineStr">
         <is>
           <t>Contemporary,Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
-      <c r="X11" s="18" t="inlineStr">
+      <c r="AA11" s="18" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y11" s="18" t="n"/>
-      <c r="Z11" s="18" t="n"/>
-      <c r="AA11" s="18" t="n"/>
-      <c r="AB11" s="18" t="n">
+      <c r="AB11" s="18" t="n"/>
+      <c r="AC11" s="18" t="n"/>
+      <c r="AD11" s="18" t="n"/>
+      <c r="AE11" s="18" t="n">
         <v>28.1</v>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, KIMARA</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>kimara-5-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>FM80001BB-SET+2CH</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>KIMARA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 KIMARA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
@@ -2253,139 +2379,150 @@
 Weight: 175 or 174.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>KIMARA 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>KIMARA 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J12" s="20" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>KIMARA</t>
         </is>
       </c>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="inlineStr">
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>FM80001BB-T, FM80001BB-1, FM80001BB-2, FM80002BB-CH-2PK</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr">
+      <c r="P12" s="20" t="inlineStr">
         <is>
           <t>FM80001BB-SET+2CH-1-Z.jpg</t>
         </is>
       </c>
-      <c r="P12" s="20" t="n">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FM80001BB-SET+2CH-1-Z.jpg,FM80001GG-SET+2CH-1-Z.jpg</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="n">
         <v>559</v>
       </c>
-      <c r="Q12" s="21" t="n">
+      <c r="T12" s="21" t="n">
         <v>559</v>
       </c>
-      <c r="R12" s="20" t="n">
+      <c r="U12" s="20" t="n">
         <v>1287</v>
       </c>
-      <c r="S12" s="20" t="n">
+      <c r="V12" s="20" t="n">
         <v>175</v>
       </c>
-      <c r="T12" s="20" t="inlineStr">
+      <c r="W12" s="20" t="inlineStr">
         <is>
           <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 25"W X 23"D X 30.5"H</t>
         </is>
       </c>
-      <c r="U12" s="20" t="inlineStr">
+      <c r="X12" s="20" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V12" s="20" t="inlineStr">
+      <c r="Y12" s="20" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
-      <c r="W12" s="20" t="inlineStr">
+      <c r="Z12" s="20" t="inlineStr">
         <is>
           <t>Contemporary,Black,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
-      <c r="X12" s="20" t="inlineStr">
+      <c r="AA12" s="20" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y12" s="20" t="n"/>
-      <c r="Z12" s="20" t="n"/>
-      <c r="AA12" s="20" t="n"/>
-      <c r="AB12" s="20" t="n">
+      <c r="AB12" s="20" t="n"/>
+      <c r="AC12" s="20" t="n"/>
+      <c r="AD12" s="20" t="n"/>
+      <c r="AE12" s="20" t="n">
         <v>34.1</v>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, KIMARA</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>kimara-5-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>FM80001GG-SET+2CH</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>KIMARA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 KIMARA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
@@ -2400,139 +2537,146 @@
 Weight: 175 or 174.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>KIMARA 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>KIMARA 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J13" s="20" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>KIMARA</t>
         </is>
       </c>
-      <c r="K13" s="20" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="L13" s="20" t="n"/>
-      <c r="M13" s="20" t="inlineStr">
+      <c r="M13" s="20" t="n"/>
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N13" s="20" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>FM80001GG-T, FM80001GG-1, FM80001GG-2, FM80006GY-CH-2PK</t>
         </is>
       </c>
-      <c r="O13" s="20" t="inlineStr">
+      <c r="P13" s="20" t="inlineStr">
         <is>
           <t>FM80001GG-SET+2CH-1-Z.jpg</t>
         </is>
       </c>
-      <c r="P13" s="20" t="n">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" s="20" t="n">
         <v>529</v>
       </c>
-      <c r="Q13" s="21" t="n">
+      <c r="T13" s="21" t="n">
         <v>529</v>
       </c>
-      <c r="R13" s="20" t="n">
+      <c r="U13" s="20" t="n">
         <v>1257</v>
       </c>
-      <c r="S13" s="20" t="n">
+      <c r="V13" s="20" t="n">
         <v>174.9</v>
       </c>
-      <c r="T13" s="20" t="inlineStr">
+      <c r="W13" s="20" t="inlineStr">
         <is>
           <t>Table: 56.5"W X 29"D X 26.5"H, Sectional: 97"W X 70.5"D X 28.5"H, Chair: 22.5"W X 23.5"D X 35"H</t>
         </is>
       </c>
-      <c r="U13" s="20" t="inlineStr">
+      <c r="X13" s="20" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V13" s="20" t="inlineStr">
+      <c r="Y13" s="20" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam</t>
         </is>
       </c>
-      <c r="W13" s="20" t="inlineStr">
+      <c r="Z13" s="20" t="inlineStr">
         <is>
           <t>Contemporary,Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam,Sturdy &amp; Durable Design,Weather Resistance</t>
         </is>
       </c>
-      <c r="X13" s="20" t="inlineStr">
+      <c r="AA13" s="20" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y13" s="20" t="n"/>
-      <c r="Z13" s="20" t="n"/>
-      <c r="AA13" s="20" t="n"/>
-      <c r="AB13" s="20" t="n">
+      <c r="AB13" s="20" t="n"/>
+      <c r="AC13" s="20" t="n"/>
+      <c r="AD13" s="20" t="n"/>
+      <c r="AE13" s="20" t="n">
         <v>45.6</v>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, KIMARA</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>kyushu-4-pc-patio-set</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Beige/Natural</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>GM-1022BG-4PC</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>KYUSHU 4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 KYUSHU 4 Pc. Patio Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Acacia Wood, Polyester construction and Beige or Natural tones, it blends durability with visual warmth.&lt;br&gt;
@@ -2551,139 +2695,150 @@
 Weight: 125.04 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>KYUSHU 4 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>KYUSHU 4 Pc. Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>KYUSHU</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
+      <c r="L14" s="22" t="inlineStr">
         <is>
           <t>4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="L14" s="22" t="n"/>
-      <c r="M14" s="22" t="inlineStr">
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N14" s="22" t="inlineStr">
+      <c r="O14" s="22" t="inlineStr">
         <is>
           <t>GM-1022BG-2PK, GM-1023BG-2PK</t>
         </is>
       </c>
-      <c r="O14" s="22" t="inlineStr">
+      <c r="P14" s="22" t="inlineStr">
         <is>
           <t>GM-1022BG-1.jpg,GM-1022BG-2.jpg</t>
         </is>
       </c>
-      <c r="P14" s="22" t="n">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>GM-1022BG-1.jpg,GM-1022BG-2.jpg,GM-1022BK-1.jpg,GM-1022BK-2.jpg</t>
+        </is>
+      </c>
+      <c r="S14" s="22" t="n">
         <v>319</v>
       </c>
-      <c r="Q14" s="23" t="n">
+      <c r="T14" s="23" t="n">
         <v>319</v>
       </c>
-      <c r="R14" s="22" t="n">
+      <c r="U14" s="22" t="n">
         <v>807</v>
       </c>
-      <c r="S14" s="22" t="n">
+      <c r="V14" s="22" t="n">
         <v>125.04</v>
       </c>
-      <c r="T14" s="22" t="inlineStr">
+      <c r="W14" s="22" t="inlineStr">
         <is>
           <t>LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H</t>
         </is>
       </c>
-      <c r="U14" s="22" t="inlineStr">
+      <c r="X14" s="22" t="inlineStr">
         <is>
           <t>Rustic</t>
         </is>
       </c>
-      <c r="V14" s="22" t="inlineStr">
+      <c r="Y14" s="22" t="inlineStr">
         <is>
           <t>Acacia Wood, Polyester</t>
         </is>
       </c>
-      <c r="W14" s="22" t="inlineStr">
+      <c r="Z14" s="22" t="inlineStr">
         <is>
           <t>Rustic,Beige/Natural,Acacia Wood, Polyester,Weather-resistant,Natural acacia wood,Includes tie-back cushions,Easy to assemble with included hardware kit</t>
         </is>
       </c>
-      <c r="X14" s="22" t="inlineStr">
+      <c r="AA14" s="22" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y14" s="22" t="n"/>
-      <c r="Z14" s="22" t="n"/>
-      <c r="AA14" s="22" t="n"/>
-      <c r="AB14" s="22" t="n">
+      <c r="AB14" s="22" t="n"/>
+      <c r="AC14" s="22" t="n"/>
+      <c r="AD14" s="22" t="n"/>
+      <c r="AE14" s="22" t="n">
         <v>15.1</v>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, KYUSHU</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AH14" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>kyushu-4-pc-patio-set</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Black/Natural</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>GM-1022BK-4PC</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>KYUSHU 4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 KYUSHU 4 Pc. Patio Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Acacia Wood, Polyester construction and Beige or Natural tones, it blends durability with visual warmth.&lt;br&gt;
@@ -2702,106 +2857,108 @@
 Weight: 125.04 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>KYUSHU 4 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>KYUSHU 4 Pc. Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>KYUSHU</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>4 Pc. Patio Set</t>
         </is>
       </c>
-      <c r="L15" s="22" t="n"/>
-      <c r="M15" s="22" t="inlineStr">
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N15" s="22" t="inlineStr">
+      <c r="O15" s="22" t="inlineStr">
         <is>
           <t>GM-1022BK-2PK, GM-1023BK-2PK</t>
         </is>
       </c>
-      <c r="O15" s="22" t="inlineStr">
+      <c r="P15" s="22" t="inlineStr">
         <is>
           <t>GM-1022BK-1.jpg,GM-1022BK-2.jpg</t>
         </is>
       </c>
-      <c r="P15" s="22" t="n">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" s="22" t="n">
         <v>319</v>
       </c>
-      <c r="Q15" s="23" t="n">
+      <c r="T15" s="23" t="n">
         <v>319</v>
       </c>
-      <c r="R15" s="22" t="n">
+      <c r="U15" s="22" t="n">
         <v>807</v>
       </c>
-      <c r="S15" s="22" t="n">
+      <c r="V15" s="22" t="n">
         <v>125.04</v>
       </c>
-      <c r="T15" s="22" t="inlineStr">
+      <c r="W15" s="22" t="inlineStr">
         <is>
           <t>LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H, TABLE: 39 1/2"L X 23 1/2"W X 18"H, CHAIR: 24"W X 27 1/4"D X 34 1/4"H</t>
         </is>
       </c>
-      <c r="U15" s="22" t="inlineStr">
+      <c r="X15" s="22" t="inlineStr">
         <is>
           <t>Rustic</t>
         </is>
       </c>
-      <c r="V15" s="22" t="inlineStr">
+      <c r="Y15" s="22" t="inlineStr">
         <is>
           <t>Acacia Wood, Polyester</t>
         </is>
       </c>
-      <c r="W15" s="22" t="inlineStr">
+      <c r="Z15" s="22" t="inlineStr">
         <is>
           <t>Rustic,Black/Natural,Acacia Wood, Polyester,Weather-resistant,Natural acacia wood,Includes tie-back cushions,Easy to assemble with included hardware kit</t>
         </is>
       </c>
-      <c r="X15" s="22" t="inlineStr">
+      <c r="AA15" s="22" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y15" s="22" t="n"/>
-      <c r="Z15" s="22" t="n"/>
-      <c r="AA15" s="22" t="n"/>
-      <c r="AB15" s="22" t="n">
+      <c r="AB15" s="22" t="n"/>
+      <c r="AC15" s="22" t="n"/>
+      <c r="AD15" s="22" t="n"/>
+      <c r="AE15" s="22" t="n">
         <v>15.1</v>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, KYUSHU</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AH15" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -2810,30 +2967,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>lotus-5-pc-conversation-set</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Black/Light Brown</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>GM-1049BK-5PC</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>LOTUS 5 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LOTUS 5 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black or Light Brown tones, the Aluminum, Fabric, Ceramic build keeps the look polished and practical.&lt;br&gt;
@@ -2852,102 +3014,108 @@
 Weight: 96.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>LOTUS 5 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>LOTUS 5 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>LOTUS</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>5 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>GM-1049BK-2PK, GM-1024BK-3PK</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>GM-1049-5PC-1.jpg,GM-1049-5PC-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>GM-1049-5PC-1.jpg,GM-1049-5PC-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
         <v>1099</v>
       </c>
-      <c r="Q16" s="1" t="n">
+      <c r="T16" s="1" t="n">
         <v>1099</v>
       </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
         <v>2817</v>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>96.8</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Sofa: 74 1/4"W X 29 1/2"D X 34"H, Coffee Table: 47 1/4"L X 25 1/2"W X 15 1/2"H, Chair: 28 1/4"W X 26 1/2"D X 37"H</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Aluminum, Fabric, Ceramic</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Contemporary,Black/Light Brown,Aluminum, Fabric, Ceramic,Washable Cushion Covers,Open Storage Shelf,Slatted Tabletop Design,Durable Aluminum Frame,Ceramic Tabletop on End Table</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB16" t="n">
+      <c r="AE16" t="n">
         <v>54.3</v>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, LOTUS</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AH16" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -2956,30 +3124,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>lyon-5-pc-game-table-set-w-4-arm-chairs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Black/Natural/Brown</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>GM-2018-5PC-19</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>LYON 5 Pc. Game Table Set w/ 4 Arm Chairs</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LYON 5 Pc. Game Table Set w/ 4 Arm Chairs brings a composed, welcoming feel to the room without overwhelming the space. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Black or Natural or Brown tones, the Aluminum, Outdoor Fabric build keeps the look polished and practical.&lt;br&gt;
@@ -2997,102 +3170,108 @@
 Weight: 184.85 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>LYON 5 Pc. Game Table Set w/ 4 Arm Chairs | GOODDEGG</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Patio Set LYON 5 Pc. Game Table Set w/ 4 Arm supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>LYON</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>5 Pc. Game Table Set w/ 4 Arm Chairs</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>GM-2018, GM-2019-2PK</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>GM-2018-5PC-19-1.jpg,GM-2018-WB-3.jpg,GM-2018-WB-2.jpg,GM-2018-WB-1.jpg,GM-2018-WB-4.jpg</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>GM-2018-5PC-19-1.jpg,GM-2018-WB-3.jpg,GM-2018-WB-2.jpg,GM-2018-WB-1.jpg,GM-2018-WB-4.jpg</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
         <v>1209</v>
       </c>
-      <c r="Q17" s="1" t="n">
+      <c r="T17" s="1" t="n">
         <v>1209</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
         <v>3357</v>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>184.85</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Table: 50.5" DIA X 29.5"H, Arm Chair: 20"W X 26.5"D X 32.25"H</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Aluminum, Outdoor Fabric</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Contemporary,Black/Natural/Brown,Aluminum, Outdoor Fabric,Inlaid Chess Board,Teak Poker Race Track Table,UV &amp; Rain-Resistant,FSC Certified Teak Wood</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB17" t="n">
+      <c r="AE17" t="n">
         <v>24.9</v>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, LYON</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -3101,30 +3280,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>lyon-5-pc-game-table-set-w-4-armless-chairs</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Black/Natural/Brown</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>GM-2018-5PC-20</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>LYON 5 Pc. Game Table Set w/ 4 Armless Chairs</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LYON 5 Pc. Game Table Set w/ 4 Armless Chairs is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, Outdoor Fabric and finished in Black or Natural or Brown tones for a clean, cohesive look.&lt;br&gt;
@@ -3142,102 +3326,108 @@
 Weight: 175.17 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>LYON 5 Pc. Game Table Set w/ 4 Armless Chairs | GOODDEGG</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Patio Set LYON 5 Pc. Game Table Set w/ 4 supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>LYON</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>5 Pc. Game Table Set w/ 4 Armless Chairs</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>GM-2018, GM-2020-2PK</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>GM-2018-5PC-20-WB-1.jpg,GM-2018-WB-3.jpg,GM-2018-WB-2.jpg,GM-2018-WB-1.jpg,GM-2018-WB-4.jpg</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>GM-2018-5PC-20-WB-1.jpg,GM-2018-WB-3.jpg,GM-2018-WB-2.jpg,GM-2018-WB-1.jpg,GM-2018-WB-4.jpg</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
         <v>1149</v>
       </c>
-      <c r="Q18" s="1" t="n">
+      <c r="T18" s="1" t="n">
         <v>1149</v>
       </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
         <v>3177</v>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
         <v>175.17</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Table: 50.5" DIA X 29.5"H</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Aluminum, Outdoor Fabric</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Contemporary,Black/Natural/Brown,Aluminum, Outdoor Fabric,Inlaid Chess Board,Teak Poker Race Track Table,UV &amp; Rain-Resistant,FSC Certified Teak Wood</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB18" t="n">
+      <c r="AE18" t="n">
         <v>23.1</v>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, LYON</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -3246,30 +3436,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>lyon-5-pc-game-table-set-w-4-stacking-chairs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Black/Natural/Brown</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>GM-2018-5PC-05</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Aluminum, Outdoor Fabric, then finished in Black or Natural or Brown tones to suit a range of interiors.&lt;br&gt;
@@ -3287,102 +3482,108 @@
 Weight: 105.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>LYON 5 Pc. Game Table Set w/ 4 Stacking Chairs | GOODDEGG</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Patio Set LYON 5 Pc. Game Table Set w/ 4 supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>LYON</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>5 Pc. Game Table Set w/ 4 Stacking Chairs</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>GM-2018, GM-2005</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>GM-2018-5PC-05-1.jpg,GM-2018-WB-3.jpg,GM-2018-WB-2.jpg,GM-2018-WB-1.jpg,GM-2018-WB-4.jpg</t>
         </is>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>GM-2018-5PC-05-1.jpg,GM-2018-WB-3.jpg,GM-2018-WB-2.jpg,GM-2018-WB-1.jpg,GM-2018-WB-4.jpg</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
         <v>949</v>
       </c>
-      <c r="Q19" s="1" t="n">
+      <c r="T19" s="1" t="n">
         <v>949</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>2397</v>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>105.33</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Table: 50.5" DIA X 29.5"H</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Aluminum, Outdoor Fabric</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>Contemporary,Black/Natural/Brown,Aluminum, Outdoor Fabric,Inlaid Chess Board,Teak Poker Race Track Table,UV &amp; Rain-Resistant,FSC Certified Teak Wood</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB19" t="n">
+      <c r="AE19" t="n">
         <v>54.9</v>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, LYON</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AH19" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -3391,30 +3592,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>monza-7-pc-dining-table-set</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Gun Metal/Gray</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>GM-2027-7PC</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>MONZA 7 Pc. Dining Table Set</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MONZA 7 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Aluminum, Tempered Glass, Textilene, then finished in Gun Metal or Gray tones to suit a range of interiors.&lt;br&gt;
@@ -3429,99 +3635,105 @@
 Color: Gun Metal or Gray&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>MONZA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>MONZA 7 Pc. Dining Table Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>MONZA</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>7 Pc. Dining Table Set</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>GM-2027, GM-2028-2PK</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>GM-2027-7PC-1.jpg,GM-2027-2.jpg,GM-2028-2PK-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>GM-2027-7PC-1.jpg,GM-2027-2.jpg,GM-2028-2PK-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
         <v>759</v>
       </c>
-      <c r="Q20" s="1" t="n">
+      <c r="T20" s="1" t="n">
         <v>759</v>
       </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
         <v>1977</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Table: 63" (EXTENDED: 94 1/2") L X 35 1/2"W X 29 1/2"H</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Aluminum, Tempered Glass, Textilene</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>Contemporary,Gun Metal/Gray,Aluminum, Tempered Glass, Textilene,Extendable Top,5-way Adjustable Seat Back</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB20" t="n">
+      <c r="AE20" t="n">
         <v>20.7</v>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, MONZA</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AH20" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -3530,30 +3742,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>niambi-3-pc-patio-bistro-set</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>FM80004NT-3PC-05NT</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>NIAMBI 3 Pc. Patio Bistro Set</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 NIAMBI 3 Pc. Patio Bistro Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber construction and Natural tones, it blends durability with visual warmth.&lt;br&gt;
@@ -3568,102 +3785,108 @@
 Weight: 50.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>NIAMBI 3 Pc. Patio Bistro Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>NIAMBI 3 Pc. Patio Bistro Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>NIAMBI</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>3 Pc. Patio Bistro Set</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>FM80004NT-T-1, FM80004NT-T-2, FM80005NT-CH-2PK</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>FM80004NT-3PC-05NT-1-Z.jpg</t>
         </is>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>FM80004NT-3PC-05NT-1-Z.jpg</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
         <v>169</v>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="T21" s="2" t="n">
         <v>169</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>357</v>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>50.2</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Table: 26.6" x 23.6" x 29.1"H, Chair: 21.3" x 25.2" x 34.3"H</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AB21" t="n">
+      <c r="AE21" t="n">
         <v>21.5</v>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, NIAMBI</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AH21" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -3672,30 +3895,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>niambi-3-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>FM80004GY-3PC-06GY</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>NIAMBI 3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 NIAMBI 3 Pc. Patio Dining Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber build keeps the look polished and practical.&lt;br&gt;
@@ -3710,135 +3938,146 @@
 Weight: 58 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>NIAMBI 3 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>NIAMBI 3 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>NIAMBI</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>3 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>FM80004GY-T-1, FM80004GY-T-2, FM80006GY-CH-2PK</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>FM80004GY-3PC-06GY-1-Z.jpg,FM80006GY-CH-1.jpg</t>
         </is>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>FM80004GY-3PC-06GY-1-Z.jpg,FM80006GY-CH-1.jpg</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
         <v>249</v>
       </c>
-      <c r="Q22" s="1" t="n">
+      <c r="T22" s="1" t="n">
         <v>249</v>
       </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
         <v>507</v>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>58</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 22.5"W X 23.5"D X 35"H</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Contemporary,Gray,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AB22" t="n">
+      <c r="AE22" t="n">
         <v>19.6</v>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AF22" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, NIAMBI</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AH22" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>niambi-5-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>FM80004GY-5PC-06GY</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F23" s="24" t="inlineStr">
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>NIAMBI 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G23" s="24" t="inlineStr">
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 NIAMBI 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
@@ -3853,139 +4092,150 @@
 Weight: 82.2 or 66.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="I23" s="24" t="inlineStr">
         <is>
           <t>NIAMBI 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
+      <c r="J23" s="24" t="inlineStr">
         <is>
           <t>NIAMBI 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J23" s="24" t="inlineStr">
+      <c r="K23" s="24" t="inlineStr">
         <is>
           <t>NIAMBI</t>
         </is>
       </c>
-      <c r="K23" s="24" t="inlineStr">
+      <c r="L23" s="24" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="L23" s="24" t="n"/>
-      <c r="M23" s="24" t="inlineStr">
+      <c r="M23" s="24" t="n"/>
+      <c r="N23" s="24" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N23" s="24" t="inlineStr">
+      <c r="O23" s="24" t="inlineStr">
         <is>
           <t>FM80004GY-T-1, FM80004GY-T-2, FM80006GY-CH-2PK</t>
         </is>
       </c>
-      <c r="O23" s="24" t="inlineStr">
+      <c r="P23" s="24" t="inlineStr">
         <is>
           <t>FM80004GY-5PC-06GY-1-Z.jpg,FM80006GY-CH-1.jpg</t>
         </is>
       </c>
-      <c r="P23" s="24" t="n">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>FM80004GY-5PC-06GY-1-Z.jpg,FM80006GY-CH-1.jpg,FM80004NT-5PC-05NT-1-Z.jpg,FM80005NT-CH-1.jpg</t>
+        </is>
+      </c>
+      <c r="S23" s="24" t="n">
         <v>379</v>
       </c>
-      <c r="Q23" s="25" t="n">
+      <c r="T23" s="25" t="n">
         <v>379</v>
       </c>
-      <c r="R23" s="24" t="n">
+      <c r="U23" s="24" t="n">
         <v>837</v>
       </c>
-      <c r="S23" s="24" t="n">
+      <c r="V23" s="24" t="n">
         <v>82.2</v>
       </c>
-      <c r="T23" s="24" t="inlineStr">
+      <c r="W23" s="24" t="inlineStr">
         <is>
           <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 22.5"W X 23.5"D X 35"H</t>
         </is>
       </c>
-      <c r="U23" s="24" t="inlineStr">
+      <c r="X23" s="24" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V23" s="24" t="inlineStr">
+      <c r="Y23" s="24" t="inlineStr">
         <is>
           <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
         </is>
       </c>
-      <c r="W23" s="24" t="inlineStr">
+      <c r="Z23" s="24" t="inlineStr">
         <is>
           <t>Contemporary,Gray,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
         </is>
       </c>
-      <c r="X23" s="24" t="inlineStr">
+      <c r="AA23" s="24" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y23" s="24" t="n"/>
-      <c r="Z23" s="24" t="n"/>
-      <c r="AA23" s="24" t="n"/>
-      <c r="AB23" s="24" t="n">
+      <c r="AB23" s="24" t="n"/>
+      <c r="AC23" s="24" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="24" t="n">
         <v>37.1</v>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AF23" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, NIAMBI</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AH23" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>niambi-5-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>FM80004NT-5PC-05NT</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F24" s="24" t="inlineStr">
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>NIAMBI 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G24" s="24" t="inlineStr">
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 NIAMBI 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
@@ -4000,106 +4250,108 @@
 Weight: 82.2 or 66.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H24" s="24" t="inlineStr">
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>NIAMBI 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I24" s="24" t="inlineStr">
+      <c r="J24" s="24" t="inlineStr">
         <is>
           <t>NIAMBI 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J24" s="24" t="inlineStr">
+      <c r="K24" s="24" t="inlineStr">
         <is>
           <t>NIAMBI</t>
         </is>
       </c>
-      <c r="K24" s="24" t="inlineStr">
+      <c r="L24" s="24" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="L24" s="24" t="n"/>
-      <c r="M24" s="24" t="inlineStr">
+      <c r="M24" s="24" t="n"/>
+      <c r="N24" s="24" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N24" s="24" t="inlineStr">
+      <c r="O24" s="24" t="inlineStr">
         <is>
           <t>FM80004NT-T-1, FM80004NT-T-2, FM80005NT-CH-2PK</t>
         </is>
       </c>
-      <c r="O24" s="24" t="inlineStr">
+      <c r="P24" s="24" t="inlineStr">
         <is>
           <t>FM80004NT-5PC-05NT-1-Z.jpg,FM80005NT-CH-1.jpg</t>
         </is>
       </c>
-      <c r="P24" s="24" t="n">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" s="24" t="n">
         <v>249</v>
       </c>
-      <c r="Q24" s="25" t="n">
+      <c r="T24" s="25" t="n">
         <v>249</v>
       </c>
-      <c r="R24" s="24" t="n">
+      <c r="U24" s="24" t="n">
         <v>477</v>
       </c>
-      <c r="S24" s="24" t="n">
+      <c r="V24" s="24" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="T24" s="24" t="inlineStr">
+      <c r="W24" s="24" t="inlineStr">
         <is>
           <t>Table: 26.5"W X 23.5"D X 29"H, Chair : 21"W X 25"D X 34"H</t>
         </is>
       </c>
-      <c r="U24" s="24" t="inlineStr">
+      <c r="X24" s="24" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V24" s="24" t="inlineStr">
+      <c r="Y24" s="24" t="inlineStr">
         <is>
           <t>Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber</t>
         </is>
       </c>
-      <c r="W24" s="24" t="inlineStr">
+      <c r="Z24" s="24" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber,Marble Base,Sturdy &amp; Durable Design,Easy to store</t>
         </is>
       </c>
-      <c r="X24" s="24" t="inlineStr">
+      <c r="AA24" s="24" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y24" s="24" t="n"/>
-      <c r="Z24" s="24" t="n"/>
-      <c r="AA24" s="24" t="n"/>
-      <c r="AB24" s="24" t="n">
+      <c r="AB24" s="24" t="n"/>
+      <c r="AC24" s="24" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="24" t="n">
         <v>40.8</v>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AF24" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, NIAMBI</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AH24" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -4108,30 +4360,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>nusa-7-pc-dining-table-set</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>GM-2031-7PC-2037</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>NUSA 7 Pc. Dining Table Set</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 NUSA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Teak Wood construction and Natural tones, it blends durability with visual warmth.&lt;br&gt;
@@ -4147,102 +4404,108 @@
 Weight: 307.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>NUSA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>NUSA 7 Pc. Dining Table Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>NUSA</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>7 Pc. Dining Table Set</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>GM-2031-1, GM-2031-2, GM-2037</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>GM-2031-7PC-2037.jpg</t>
         </is>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>GM-2031-7PC-2037.jpg</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
         <v>1399</v>
       </c>
-      <c r="Q25" s="1" t="n">
+      <c r="T25" s="1" t="n">
         <v>1399</v>
       </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
         <v>3597</v>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>307.2</v>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Table: 78 3/4"L X 47 1/4"W X 29 1/2"H</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Teak Wood</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Transitional,Natural,Teak Wood,Slat Design,Pedestal Base,5-way Adjustable Chair,Sand Finish</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="AB25" t="n">
+      <c r="AE25" t="n">
         <v>52.8</v>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AF25" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, NUSA</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AH25" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -4251,30 +4514,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>palma-7-pc-dining-table-set</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Black/Gray</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>GM-2022-7PC</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>PALMA 7 Pc. Dining Table Set</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 PALMA 7 Pc. Dining Table Set creates a cohesive setup that feels inviting the moment you walk in. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Steel, Glass, Polyspun Fabric construction and Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
@@ -4295,102 +4563,108 @@
 Weight: 190.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>PALMA 7 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>PALMA 7 Pc. Dining Table Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>PALMA</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>7 Pc. Dining Table Set</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>GM-2022, GM-2023-6PK</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>GM-2022-7PC-1-Z.jpg,GM-2022-WB-1.jpg,GM-2023-6PK-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>GM-2022-7PC-1-Z.jpg,GM-2022-WB-1.jpg,GM-2023-6PK-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
         <v>649</v>
       </c>
-      <c r="Q26" s="2" t="n">
+      <c r="T26" s="2" t="n">
         <v>649</v>
       </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
         <v>1647</v>
       </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
         <v>190.6</v>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Table: 70.8"L X 35.4"W X 27.9"H, Chair: 24"W X 33"D X 38.3"H</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Steel, Glass, Polyspun Fabric</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>Contemporary,Black/Gray,Steel, Glass, Polyspun Fabric,5mm Tempered Water Wave Glass Tabletop,Powder Coated Steel Frame,Reclining Backrest,Washable Cushion Cover,Built-In Umbrella Hole,Tie-Back Cushions,Lumbar Pillows Included</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB26" t="n">
+      <c r="AE26" t="n">
         <v>27.2</v>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AF26" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, PALMA</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AH26" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -4399,30 +4673,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>sarabi-3-pc-conversation-set</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>Black/Natural</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>FM80003BK-T-3PC</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>SARABI 3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SARABI 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Black or Natural tones, the Steel, Wicker, Fabric build keeps the look polished and practical.&lt;br&gt;
@@ -4439,102 +4718,108 @@
 Weight: 11.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>SARABI 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>SARABI 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>SARABI</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>FM80003BK-T, FM80020NT-CH-2PK</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>FM80003BK-T-3PC-1.jpg</t>
         </is>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>FM80003BK-T-3PC-1.jpg</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
         <v>219</v>
       </c>
-      <c r="Q27" s="1" t="n">
+      <c r="T27" s="1" t="n">
         <v>219</v>
       </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
         <v>507</v>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
         <v>11.7</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>TABLE: 21.5"W X 21.5"D X 15.5"H, CHAIR: 25.5"W X 28.5"D X 26.5"H (SEAT HT: 14", SEAT DP: 20")</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Steel, Wicker, Fabric</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>Contemporary,Black/Natural,Steel, Wicker, Fabric,Powder-coated Steel Frame,3.5mm Round Wicker,Sloped Back &amp; Curbed Seat Lounge Chair</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AB27" t="n">
+      <c r="AE27" t="n">
         <v>14.3</v>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AF27" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, SARABI</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AH27" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -4543,30 +4828,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>segovia-5-pc-dining-table-set</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Navy/Black/Gray</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>GM-2013-5PC-2039</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>SEGOVIA 5 Pc. Dining Table Set</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SEGOVIA 5 Pc. Dining Table Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Steel, Polyethylene Wicker, Ceremic, Polyspun, then finished in Navy or Black or Gray tones to suit a range of interiors.&lt;br&gt;
@@ -4584,102 +4874,108 @@
 Weight: 263.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>SEGOVIA 5 Pc. Dining Table Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>SEGOVIA 5 Pc. Dining Table Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>SEGOVIA</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>5 Pc. Dining Table Set</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>GM-2013, GM-2039-2PK</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>GM-2013-5PC-2039-1.jpg,GM-2013-2.jpg,GM-2013-WB-2.jpg,GM-2013-WB-3.jpg</t>
         </is>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>GM-2013-5PC-2039-1.jpg,GM-2013-2.jpg,GM-2013-WB-2.jpg,GM-2013-WB-3.jpg</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
         <v>859</v>
       </c>
-      <c r="Q28" s="2" t="n">
+      <c r="T28" s="2" t="n">
         <v>859</v>
       </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
         <v>2307</v>
       </c>
-      <c r="S28" t="n">
+      <c r="V28" t="n">
         <v>263.1</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Firepit Table: 40"L X 40"W X 26 1/2"H Chair: 30 3/4"W X 25 1/2"D X 30 3/4"H"</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Steel, Polyethylene Wicker, Ceremic, Polyspun</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>Transitional,Navy/Black/Gray,Steel, Polyethylene Wicker, Ceremic, Polyspun,360-degree Swivel Glider,Gray Ceramic Tile Table Top,Fire Pit Table with Tile Table Top,Includes Cushions and Pillows</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB28" t="n">
+      <c r="AE28" t="n">
         <v>23.4</v>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AF28" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, SEGOVIA</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AH28" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF28" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -4688,30 +4984,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>segovia-5-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Black/Gray</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>GM-2013-5PC</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>SEGOVIA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SEGOVIA 5 Pc. Patio Dining Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Steel, Polyethylene Wicker, Polyspun construction and Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
@@ -4729,135 +5030,146 @@
 Weight: 248.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>SEGOVIA 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>SEGOVIA 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>SEGOVIA</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>GM-2013, GM-2014-4PK</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>GM-2013-1.jpg,GM-2013-2.jpg,GM-2013-WB-2.jpg,GM-2013-WB-3.jpg</t>
         </is>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>GM-2013-1.jpg,GM-2013-2.jpg,GM-2013-WB-2.jpg,GM-2013-WB-3.jpg</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
         <v>799</v>
       </c>
-      <c r="Q29" s="2" t="n">
+      <c r="T29" s="2" t="n">
         <v>799</v>
       </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
         <v>2097</v>
       </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
         <v>248.1</v>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>40"L X 40"W X 26 1/2"H</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Steel, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,360-degree swivel rockers,Gray ceramic tile table top,Fire pit table with tile-top and wicker base,Includes cushions and pillows</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB29" t="n">
+      <c r="AE29" t="n">
         <v>33.7</v>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, SEGOVIA</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sintra-5-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Black/Gray</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n"/>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>GM-2012-5PC-10</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="F30" s="26" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="G30" s="26" t="inlineStr">
         <is>
           <t>SINTRA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G30" s="26" t="inlineStr">
+      <c r="H30" s="26" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SINTRA 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyethylene Wicker, Polyspun and finished in Black or Gray tones for a clean, cohesive look.&lt;br&gt;
@@ -4875,139 +5187,150 @@
 Weight: 180.7 or 156.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H30" s="26" t="inlineStr">
+      <c r="I30" s="26" t="inlineStr">
         <is>
           <t>SINTRA 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I30" s="26" t="inlineStr">
+      <c r="J30" s="26" t="inlineStr">
         <is>
           <t>SINTRA 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J30" s="26" t="inlineStr">
+      <c r="K30" s="26" t="inlineStr">
         <is>
           <t>SINTRA</t>
         </is>
       </c>
-      <c r="K30" s="26" t="inlineStr">
+      <c r="L30" s="26" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="L30" s="26" t="n"/>
-      <c r="M30" s="26" t="inlineStr">
+      <c r="M30" s="26" t="n"/>
+      <c r="N30" s="26" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N30" s="26" t="inlineStr">
+      <c r="O30" s="26" t="inlineStr">
         <is>
           <t>GM-2012, GM-2010-2PK</t>
         </is>
       </c>
-      <c r="O30" s="26" t="inlineStr">
+      <c r="P30" s="26" t="inlineStr">
         <is>
           <t>GM-2012-5PC-10.jpg,GM-2012-1.jpg,GM-2012-WB-1.jpg,GM-2012-2.jpg,GM-2012-3.jpg,GM-2012-4.jpg,GM-2010-2PK-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P30" s="26" t="n">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>GM-2012-5PC-10.jpg,GM-2012-1.jpg,GM-2012-WB-1.jpg,GM-2012-2.jpg,GM-2012-3.jpg,GM-2012-4.jpg,GM-2010-2PK-WB-1.jpg,GM-2012-5PC-11.jpg,GM-2011-2PK-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S30" s="26" t="n">
         <v>539</v>
       </c>
-      <c r="Q30" s="27" t="n">
+      <c r="T30" s="27" t="n">
         <v>539</v>
       </c>
-      <c r="R30" s="26" t="n">
+      <c r="U30" s="26" t="n">
         <v>1377</v>
       </c>
-      <c r="S30" s="26" t="n">
+      <c r="V30" s="26" t="n">
         <v>180.7</v>
       </c>
-      <c r="T30" s="26" t="inlineStr">
+      <c r="W30" s="26" t="inlineStr">
         <is>
           <t>40"L X 40"W X 28"H</t>
         </is>
       </c>
-      <c r="U30" s="26" t="inlineStr">
+      <c r="X30" s="26" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V30" s="26" t="inlineStr">
+      <c r="Y30" s="26" t="inlineStr">
         <is>
           <t>Steel, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
-      <c r="W30" s="26" t="inlineStr">
+      <c r="Z30" s="26" t="inlineStr">
         <is>
           <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,Ceramic tile table top,Rust-resistant, powder-coated steel frame,Includes umbrella hole and cap</t>
         </is>
       </c>
-      <c r="X30" s="26" t="inlineStr">
+      <c r="AA30" s="26" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y30" s="26" t="n"/>
-      <c r="Z30" s="26" t="n"/>
-      <c r="AA30" s="26" t="n"/>
-      <c r="AB30" s="26" t="n">
+      <c r="AB30" s="26" t="n"/>
+      <c r="AC30" s="26" t="n"/>
+      <c r="AD30" s="26" t="n"/>
+      <c r="AE30" s="26" t="n">
         <v>22.4</v>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, SINTRA</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AH30" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AJ30" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sintra-5-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Black/Gray</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n"/>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>GM-2012-5PC-11</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E31" s="26" t="inlineStr">
+      <c r="F31" s="26" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
+      <c r="G31" s="26" t="inlineStr">
         <is>
           <t>SINTRA 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G31" s="26" t="inlineStr">
+      <c r="H31" s="26" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SINTRA 5 Pc. Patio Dining Set is designed for everyday living, balancing comfort with a clean, finished look. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Steel, Polyethylene Wicker, Polyspun and finished in Black or Gray tones for a clean, cohesive look.&lt;br&gt;
@@ -5025,106 +5348,108 @@
 Weight: 180.7 or 156.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H31" s="26" t="inlineStr">
+      <c r="I31" s="26" t="inlineStr">
         <is>
           <t>SINTRA 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I31" s="26" t="inlineStr">
+      <c r="J31" s="26" t="inlineStr">
         <is>
           <t>SINTRA 5 Pc. Patio Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J31" s="26" t="inlineStr">
+      <c r="K31" s="26" t="inlineStr">
         <is>
           <t>SINTRA</t>
         </is>
       </c>
-      <c r="K31" s="26" t="inlineStr">
+      <c r="L31" s="26" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="L31" s="26" t="n"/>
-      <c r="M31" s="26" t="inlineStr">
+      <c r="M31" s="26" t="n"/>
+      <c r="N31" s="26" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N31" s="26" t="inlineStr">
+      <c r="O31" s="26" t="inlineStr">
         <is>
           <t>GM-2012, GM-2011-2PK</t>
         </is>
       </c>
-      <c r="O31" s="26" t="inlineStr">
+      <c r="P31" s="26" t="inlineStr">
         <is>
           <t>GM-2012-5PC-11.jpg,GM-2012-1.jpg,GM-2012-WB-1.jpg,GM-2012-2.jpg,GM-2012-3.jpg,GM-2012-4.jpg,GM-2011-2PK-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P31" s="26" t="n">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" s="26" t="n">
         <v>419</v>
       </c>
-      <c r="Q31" s="27" t="n">
+      <c r="T31" s="27" t="n">
         <v>419</v>
       </c>
-      <c r="R31" s="26" t="n">
+      <c r="U31" s="26" t="n">
         <v>1017</v>
       </c>
-      <c r="S31" s="26" t="n">
+      <c r="V31" s="26" t="n">
         <v>156.5</v>
       </c>
-      <c r="T31" s="26" t="inlineStr">
+      <c r="W31" s="26" t="inlineStr">
         <is>
           <t>40"L X 40"W X 28"H</t>
         </is>
       </c>
-      <c r="U31" s="26" t="inlineStr">
+      <c r="X31" s="26" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V31" s="26" t="inlineStr">
+      <c r="Y31" s="26" t="inlineStr">
         <is>
           <t>Steel, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
-      <c r="W31" s="26" t="inlineStr">
+      <c r="Z31" s="26" t="inlineStr">
         <is>
           <t>Contemporary,Black/Gray,Steel, Polyethylene Wicker, Polyspun,Ceramic tile table top,Rust-resistant, powder-coated steel frame,Includes umbrella hole and cap</t>
         </is>
       </c>
-      <c r="X31" s="26" t="inlineStr">
+      <c r="AA31" s="26" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y31" s="26" t="n"/>
-      <c r="Z31" s="26" t="n"/>
-      <c r="AA31" s="26" t="n"/>
-      <c r="AB31" s="26" t="n">
+      <c r="AB31" s="26" t="n"/>
+      <c r="AC31" s="26" t="n"/>
+      <c r="AD31" s="26" t="n"/>
+      <c r="AE31" s="26" t="n">
         <v>18</v>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, SINTRA</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -5133,30 +5458,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>sintra-6-pc-patio-dining-set-w-bench</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Black/Gray</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>GM-2008-6PC</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>SINTRA 6 Pc. Patio Dining Set w/ Bench</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SINTRA 6 Pc. Patio Dining Set w/ Bench creates a cohesive setup that feels inviting the moment you walk in. As a outdoor patio set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Steel, Polyspun construction and Black or Gray tones, it blends durability with visual warmth.&lt;br&gt;
@@ -5178,135 +5508,146 @@
 Weight: 234.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>SINTRA 6 Pc. Patio Dining Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>SINTRA 6 Pc. Patio Dining Set w/ Bench Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>SINTRA</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>6 Pc. Patio Dining Set w/ Bench</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>GM-2008, GM-2011-2PK, GM-2010-2PK, GM-2009</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>GM-2008-6PC-WB-1.jpg,GM-2008-6PC-1.jpg,GM-2008-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>GM-2008-6PC-WB-1.jpg,GM-2008-6PC-1.jpg,GM-2008-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
         <v>699</v>
       </c>
-      <c r="Q32" s="2" t="n">
+      <c r="T32" s="2" t="n">
         <v>699</v>
       </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
         <v>1797</v>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
         <v>234.5</v>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>76"L X 40"W X 28"H</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Steel, Polyspun</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>Contemporary,Black/Gray,Steel, Polyspun,Ceramic tile table top,360-degree swivel rocker chairs,Rust-resistant, powder-coated steel frame,Table includes umbrella hole and cap,Chair includes cushion and pillow</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB32" t="n">
+      <c r="AE32" t="n">
         <v>27.4</v>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, SINTRA</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr">
+      <c r="AH32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF32" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="inlineStr">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>zalika-3-pc-conversation-set</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="B33" s="28" t="n"/>
-      <c r="C33" s="28" t="inlineStr">
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>FM80010BK-T-3PC</t>
         </is>
       </c>
-      <c r="D33" s="28" t="inlineStr">
+      <c r="E33" s="28" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="F33" s="28" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F33" s="28" t="inlineStr">
+      <c r="G33" s="28" t="inlineStr">
         <is>
           <t>ZALIKA 3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="H33" s="28" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ZALIKA 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Fabric, Steel, PE Rattan, Foam build keeps the look polished and practical.&lt;br&gt;
@@ -5321,137 +5662,148 @@
 Color: Black or Natural&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H33" s="28" t="inlineStr">
+      <c r="I33" s="28" t="inlineStr">
         <is>
           <t>ZALIKA 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I33" s="28" t="inlineStr">
+      <c r="J33" s="28" t="inlineStr">
         <is>
           <t>ZALIKA 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J33" s="28" t="inlineStr">
+      <c r="K33" s="28" t="inlineStr">
         <is>
           <t>ZALIKA</t>
         </is>
       </c>
-      <c r="K33" s="28" t="inlineStr">
+      <c r="L33" s="28" t="inlineStr">
         <is>
           <t>3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="28" t="inlineStr">
+      <c r="M33" s="28" t="n"/>
+      <c r="N33" s="28" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N33" s="28" t="inlineStr">
+      <c r="O33" s="28" t="inlineStr">
         <is>
           <t>FM80010BK-T, FM80010BK-CH-2PK</t>
         </is>
       </c>
-      <c r="O33" s="28" t="inlineStr">
+      <c r="P33" s="28" t="inlineStr">
         <is>
           <t>FM80010BK-T-3PC-1.jpg</t>
         </is>
       </c>
-      <c r="P33" s="28" t="n">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>FM80010BK-T-3PC-1.jpg,FM80010NT-T-3PC-1.jpg</t>
+        </is>
+      </c>
+      <c r="S33" s="28" t="n">
         <v>199</v>
       </c>
-      <c r="Q33" s="29" t="n">
+      <c r="T33" s="29" t="n">
         <v>199</v>
       </c>
-      <c r="R33" s="28" t="n">
+      <c r="U33" s="28" t="n">
         <v>507</v>
       </c>
-      <c r="S33" s="28" t="n"/>
-      <c r="T33" s="28" t="inlineStr">
+      <c r="V33" s="28" t="n"/>
+      <c r="W33" s="28" t="inlineStr">
         <is>
           <t>TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
         </is>
       </c>
-      <c r="U33" s="28" t="inlineStr">
+      <c r="X33" s="28" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V33" s="28" t="inlineStr">
+      <c r="Y33" s="28" t="inlineStr">
         <is>
           <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
-      <c r="W33" s="28" t="inlineStr">
+      <c r="Z33" s="28" t="inlineStr">
         <is>
           <t>Contemporary,Black,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
-      <c r="X33" s="28" t="inlineStr">
+      <c r="AA33" s="28" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y33" s="28" t="n"/>
-      <c r="Z33" s="28" t="n"/>
-      <c r="AA33" s="28" t="n"/>
-      <c r="AB33" s="28" t="n">
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="28" t="n"/>
+      <c r="AD33" s="28" t="n"/>
+      <c r="AE33" s="28" t="n">
         <v>10.9</v>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AF33" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZALIKA</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr">
+      <c r="AH33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF33" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG33" t="inlineStr">
+      <c r="AJ33" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>zalika-3-pc-conversation-set</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="B34" s="28" t="n"/>
-      <c r="C34" s="28" t="inlineStr">
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>FM80010NT-T-3PC</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="F34" s="28" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="G34" s="28" t="inlineStr">
         <is>
           <t>ZALIKA 3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="H34" s="28" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ZALIKA 3 Pc. Conversation Set brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Fabric, Steel, PE Rattan, Foam build keeps the look polished and practical.&lt;br&gt;
@@ -5466,137 +5818,144 @@
 Color: Black or Natural&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H34" s="28" t="inlineStr">
+      <c r="I34" s="28" t="inlineStr">
         <is>
           <t>ZALIKA 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I34" s="28" t="inlineStr">
+      <c r="J34" s="28" t="inlineStr">
         <is>
           <t>ZALIKA 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J34" s="28" t="inlineStr">
+      <c r="K34" s="28" t="inlineStr">
         <is>
           <t>ZALIKA</t>
         </is>
       </c>
-      <c r="K34" s="28" t="inlineStr">
+      <c r="L34" s="28" t="inlineStr">
         <is>
           <t>3 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="28" t="inlineStr">
+      <c r="M34" s="28" t="n"/>
+      <c r="N34" s="28" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N34" s="28" t="inlineStr">
+      <c r="O34" s="28" t="inlineStr">
         <is>
           <t>FM80010NT-T, FM80010NT-CH-2PK</t>
         </is>
       </c>
-      <c r="O34" s="28" t="inlineStr">
+      <c r="P34" s="28" t="inlineStr">
         <is>
           <t>FM80010NT-T-3PC-1.jpg</t>
         </is>
       </c>
-      <c r="P34" s="28" t="n">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" s="28" t="n">
         <v>199</v>
       </c>
-      <c r="Q34" s="29" t="n">
+      <c r="T34" s="29" t="n">
         <v>199</v>
       </c>
-      <c r="R34" s="28" t="n">
+      <c r="U34" s="28" t="n">
         <v>507</v>
       </c>
-      <c r="S34" s="28" t="n"/>
-      <c r="T34" s="28" t="inlineStr">
+      <c r="V34" s="28" t="n"/>
+      <c r="W34" s="28" t="inlineStr">
         <is>
           <t>TABLE: 19.5"W X 19.5"D X 21"HCHAIR: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
         </is>
       </c>
-      <c r="U34" s="28" t="inlineStr">
+      <c r="X34" s="28" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V34" s="28" t="inlineStr">
+      <c r="Y34" s="28" t="inlineStr">
         <is>
           <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
-      <c r="W34" s="28" t="inlineStr">
+      <c r="Z34" s="28" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
-      <c r="X34" s="28" t="inlineStr">
+      <c r="AA34" s="28" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y34" s="28" t="n"/>
-      <c r="Z34" s="28" t="n"/>
-      <c r="AA34" s="28" t="n"/>
-      <c r="AB34" s="28" t="n">
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="28" t="n"/>
+      <c r="AD34" s="28" t="n"/>
+      <c r="AE34" s="28" t="n">
         <v>10.9</v>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZALIKA</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr">
+      <c r="AH34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF34" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG34" t="inlineStr">
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>zalika-4-pc-conversation-set</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n"/>
-      <c r="C35" s="30" t="inlineStr">
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>FM80010BK-T-4PC-BN</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E35" s="30" t="inlineStr">
+      <c r="F35" s="30" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="G35" s="30" t="inlineStr">
         <is>
           <t>ZALIKA 4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="G35" s="30" t="inlineStr">
+      <c r="H35" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ZALIKA 4 Pc. Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Steel, PE Rattan, Foam, then finished in Black tones to suit a range of interiors.&lt;br&gt;
@@ -5612,137 +5971,148 @@
 Color: Black or Natural&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H35" s="30" t="inlineStr">
+      <c r="I35" s="30" t="inlineStr">
         <is>
           <t>ZALIKA 4 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I35" s="30" t="inlineStr">
+      <c r="J35" s="30" t="inlineStr">
         <is>
           <t>ZALIKA 4 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J35" s="30" t="inlineStr">
+      <c r="K35" s="30" t="inlineStr">
         <is>
           <t>ZALIKA</t>
         </is>
       </c>
-      <c r="K35" s="30" t="inlineStr">
+      <c r="L35" s="30" t="inlineStr">
         <is>
           <t>4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="L35" s="30" t="n"/>
-      <c r="M35" s="30" t="inlineStr">
+      <c r="M35" s="30" t="n"/>
+      <c r="N35" s="30" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N35" s="30" t="inlineStr">
+      <c r="O35" s="30" t="inlineStr">
         <is>
           <t>FM80010BK-T, FM80010BK-CH-2PK, FM80010BK-BN</t>
         </is>
       </c>
-      <c r="O35" s="30" t="inlineStr">
+      <c r="P35" s="30" t="inlineStr">
         <is>
           <t>FM80010BK-T-4PC-BN-1.jpg</t>
         </is>
       </c>
-      <c r="P35" s="30" t="n">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>FM80010BK-T-4PC-BN-1.jpg,FM80010NT-T-4PC-BN-1.jpg</t>
+        </is>
+      </c>
+      <c r="S35" s="30" t="n">
         <v>418</v>
       </c>
-      <c r="Q35" s="31" t="n">
+      <c r="T35" s="31" t="n">
         <v>418</v>
       </c>
-      <c r="R35" s="30" t="n">
+      <c r="U35" s="30" t="n">
         <v>984</v>
       </c>
-      <c r="S35" s="30" t="n"/>
-      <c r="T35" s="30" t="inlineStr">
+      <c r="V35" s="30" t="n"/>
+      <c r="W35" s="30" t="inlineStr">
         <is>
           <t>TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H</t>
         </is>
       </c>
-      <c r="U35" s="30" t="inlineStr">
+      <c r="X35" s="30" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V35" s="30" t="inlineStr">
+      <c r="Y35" s="30" t="inlineStr">
         <is>
           <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
-      <c r="W35" s="30" t="inlineStr">
+      <c r="Z35" s="30" t="inlineStr">
         <is>
           <t>Contemporary,Black,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
-      <c r="X35" s="30" t="inlineStr">
+      <c r="AA35" s="30" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y35" s="30" t="n"/>
-      <c r="Z35" s="30" t="n"/>
-      <c r="AA35" s="30" t="n"/>
-      <c r="AB35" s="30" t="n">
+      <c r="AB35" s="30" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="30" t="n"/>
+      <c r="AE35" s="30" t="n">
         <v>28.6</v>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AF35" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZALIKA</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr">
+      <c r="AH35" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF35" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG35" t="inlineStr">
+      <c r="AJ35" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="inlineStr">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>zalika-4-pc-conversation-set</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n"/>
-      <c r="C36" s="30" t="inlineStr">
+      <c r="C36" s="30" t="n"/>
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>FM80010NT-T-4PC-BN</t>
         </is>
       </c>
-      <c r="D36" s="30" t="inlineStr">
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E36" s="30" t="inlineStr">
+      <c r="F36" s="30" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F36" s="30" t="inlineStr">
+      <c r="G36" s="30" t="inlineStr">
         <is>
           <t>ZALIKA 4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="G36" s="30" t="inlineStr">
+      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ZALIKA 4 Pc. Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. This outdoor patio set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Steel, PE Rattan, Foam, then finished in Black tones to suit a range of interiors.&lt;br&gt;
@@ -5758,137 +6128,144 @@
 Color: Black or Natural&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H36" s="30" t="inlineStr">
+      <c r="I36" s="30" t="inlineStr">
         <is>
           <t>ZALIKA 4 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I36" s="30" t="inlineStr">
+      <c r="J36" s="30" t="inlineStr">
         <is>
           <t>ZALIKA 4 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J36" s="30" t="inlineStr">
+      <c r="K36" s="30" t="inlineStr">
         <is>
           <t>ZALIKA</t>
         </is>
       </c>
-      <c r="K36" s="30" t="inlineStr">
+      <c r="L36" s="30" t="inlineStr">
         <is>
           <t>4 Pc. Conversation Set</t>
         </is>
       </c>
-      <c r="L36" s="30" t="n"/>
-      <c r="M36" s="30" t="inlineStr">
+      <c r="M36" s="30" t="n"/>
+      <c r="N36" s="30" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N36" s="30" t="inlineStr">
+      <c r="O36" s="30" t="inlineStr">
         <is>
           <t>FM80010NT-T, FM80010NT-CH-2PK, FM80010NT-BN</t>
         </is>
       </c>
-      <c r="O36" s="30" t="inlineStr">
+      <c r="P36" s="30" t="inlineStr">
         <is>
           <t>FM80010NT-T-4PC-BN-1.jpg</t>
         </is>
       </c>
-      <c r="P36" s="30" t="n">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" s="30" t="n">
         <v>418</v>
       </c>
-      <c r="Q36" s="31" t="n">
+      <c r="T36" s="31" t="n">
         <v>418</v>
       </c>
-      <c r="R36" s="30" t="n">
+      <c r="U36" s="30" t="n">
         <v>984</v>
       </c>
-      <c r="S36" s="30" t="n"/>
-      <c r="T36" s="30" t="inlineStr">
+      <c r="V36" s="30" t="n"/>
+      <c r="W36" s="30" t="inlineStr">
         <is>
           <t>TABLE: 19.5"W X 19.5"D X 21"H, CHAIR: 22"W X 26.5"D X 35"H, BENCH: 51.5"W X 26.5"D X 35"H</t>
         </is>
       </c>
-      <c r="U36" s="30" t="inlineStr">
+      <c r="X36" s="30" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V36" s="30" t="inlineStr">
+      <c r="Y36" s="30" t="inlineStr">
         <is>
           <t>Fabric, Steel, PE Rattan, Foam</t>
         </is>
       </c>
-      <c r="W36" s="30" t="inlineStr">
+      <c r="Z36" s="30" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Fabric, Steel, PE Rattan, Foam,Powder-Coated Steel Frame,3.5mm Round Wicker,Tempered Glass Table Top</t>
         </is>
       </c>
-      <c r="X36" s="30" t="inlineStr">
+      <c r="AA36" s="30" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y36" s="30" t="n"/>
-      <c r="Z36" s="30" t="n"/>
-      <c r="AA36" s="30" t="n"/>
-      <c r="AB36" s="30" t="n">
+      <c r="AB36" s="30" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="30" t="n"/>
+      <c r="AE36" s="30" t="n">
         <v>28.6</v>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AF36" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZALIKA</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr">
+      <c r="AH36" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF36" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG36" t="inlineStr">
+      <c r="AJ36" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="inlineStr">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>zuberi-3-pc-patio-conversation-set</t>
+        </is>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>Natural/Black</t>
         </is>
       </c>
-      <c r="B37" s="32" t="n"/>
-      <c r="C37" s="32" t="inlineStr">
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-02BB</t>
         </is>
       </c>
-      <c r="D37" s="32" t="inlineStr">
+      <c r="E37" s="32" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E37" s="32" t="inlineStr">
+      <c r="F37" s="32" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="G37" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="G37" s="32" t="inlineStr">
+      <c r="H37" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.&lt;br&gt;
@@ -5905,143 +6282,154 @@
 Weight: 37.6 or 21.3 or 28.1 or 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H37" s="32" t="inlineStr">
+      <c r="I37" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I37" s="32" t="inlineStr">
+      <c r="J37" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J37" s="32" t="inlineStr">
+      <c r="K37" s="32" t="inlineStr">
         <is>
           <t>ZUBERI</t>
         </is>
       </c>
-      <c r="K37" s="32" t="inlineStr">
+      <c r="L37" s="32" t="inlineStr">
         <is>
           <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="L37" s="32" t="inlineStr">
+      <c r="M37" s="32" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="M37" s="32" t="inlineStr">
+      <c r="N37" s="32" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N37" s="32" t="inlineStr">
+      <c r="O37" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-T, FM80002BB-CH-2PK</t>
         </is>
       </c>
-      <c r="O37" s="32" t="inlineStr">
+      <c r="P37" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-02BB-1-Z.jpg,FM80002BB-CH-1.jpg,FM80003NT-T-1.jpg</t>
         </is>
       </c>
-      <c r="P37" s="32" t="n">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>FM80003NT-3PC-02BB-1-Z.jpg,FM80002BB-CH-1.jpg,FM80003NT-T-1.jpg,FM80003NT-3PC-02NT-1-Z.jpg,FM80002NT-CH-1.jpg,FM80003NT-3PC-05NT-1-Z.jpg,FM80005NT-CH-1.jpg,FM80003NT-3PC-06GY-1-Z.jpg,FM80006GY-CH-1.jpg</t>
+        </is>
+      </c>
+      <c r="S37" s="32" t="n">
         <v>179</v>
       </c>
-      <c r="Q37" s="33" t="n">
+      <c r="T37" s="33" t="n">
         <v>179</v>
       </c>
-      <c r="R37" s="32" t="n">
+      <c r="U37" s="32" t="n">
         <v>417</v>
       </c>
-      <c r="S37" s="32" t="n">
+      <c r="V37" s="32" t="n">
         <v>37.6</v>
       </c>
-      <c r="T37" s="32" t="inlineStr">
+      <c r="W37" s="32" t="inlineStr">
         <is>
           <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H</t>
         </is>
       </c>
-      <c r="U37" s="32" t="inlineStr">
+      <c r="X37" s="32" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V37" s="32" t="inlineStr">
+      <c r="Y37" s="32" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
-      <c r="W37" s="32" t="inlineStr">
+      <c r="Z37" s="32" t="inlineStr">
         <is>
           <t>Contemporary,Natural/Black,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
-      <c r="X37" s="32" t="inlineStr">
+      <c r="AA37" s="32" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y37" s="32" t="n"/>
-      <c r="Z37" s="32" t="n"/>
-      <c r="AA37" s="32" t="n"/>
-      <c r="AB37" s="32" t="n">
+      <c r="AB37" s="32" t="n"/>
+      <c r="AC37" s="32" t="n"/>
+      <c r="AD37" s="32" t="n"/>
+      <c r="AE37" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AF37" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZUBERI</t>
         </is>
       </c>
-      <c r="AE37" t="inlineStr">
+      <c r="AH37" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF37" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG37" t="inlineStr">
+      <c r="AJ37" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="inlineStr">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>zuberi-3-pc-patio-conversation-set</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="B38" s="32" t="n"/>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="C38" s="32" t="n"/>
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-02NT</t>
         </is>
       </c>
-      <c r="D38" s="32" t="inlineStr">
+      <c r="E38" s="32" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E38" s="32" t="inlineStr">
+      <c r="F38" s="32" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F38" s="32" t="inlineStr">
+      <c r="G38" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="G38" s="32" t="inlineStr">
+      <c r="H38" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.&lt;br&gt;
@@ -6058,139 +6446,146 @@
 Weight: 37.6 or 21.3 or 28.1 or 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H38" s="32" t="inlineStr">
+      <c r="I38" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I38" s="32" t="inlineStr">
+      <c r="J38" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J38" s="32" t="inlineStr">
+      <c r="K38" s="32" t="inlineStr">
         <is>
           <t>ZUBERI</t>
         </is>
       </c>
-      <c r="K38" s="32" t="inlineStr">
+      <c r="L38" s="32" t="inlineStr">
         <is>
           <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="L38" s="32" t="n"/>
-      <c r="M38" s="32" t="inlineStr">
+      <c r="M38" s="32" t="n"/>
+      <c r="N38" s="32" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N38" s="32" t="inlineStr">
+      <c r="O38" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-T, FM80002NT-CH-2PK</t>
         </is>
       </c>
-      <c r="O38" s="32" t="inlineStr">
+      <c r="P38" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-02NT-1-Z.jpg,FM80002NT-CH-1.jpg,FM80003NT-T-1.jpg</t>
         </is>
       </c>
-      <c r="P38" s="32" t="n">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" s="32" t="n">
         <v>179</v>
       </c>
-      <c r="Q38" s="33" t="n">
+      <c r="T38" s="33" t="n">
         <v>179</v>
       </c>
-      <c r="R38" s="32" t="n">
+      <c r="U38" s="32" t="n">
         <v>417</v>
       </c>
-      <c r="S38" s="32" t="n">
+      <c r="V38" s="32" t="n">
         <v>21.3</v>
       </c>
-      <c r="T38" s="32" t="inlineStr">
+      <c r="W38" s="32" t="inlineStr">
         <is>
           <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 25"W X 23.5"D X 31"H</t>
         </is>
       </c>
-      <c r="U38" s="32" t="inlineStr">
+      <c r="X38" s="32" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V38" s="32" t="inlineStr">
+      <c r="Y38" s="32" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
-      <c r="W38" s="32" t="inlineStr">
+      <c r="Z38" s="32" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
-      <c r="X38" s="32" t="inlineStr">
+      <c r="AA38" s="32" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y38" s="32" t="n"/>
-      <c r="Z38" s="32" t="n"/>
-      <c r="AA38" s="32" t="n"/>
-      <c r="AB38" s="32" t="n">
+      <c r="AB38" s="32" t="n"/>
+      <c r="AC38" s="32" t="n"/>
+      <c r="AD38" s="32" t="n"/>
+      <c r="AE38" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AF38" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZUBERI</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr">
+      <c r="AH38" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF38" t="inlineStr">
+      <c r="AI38" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG38" t="inlineStr">
+      <c r="AJ38" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>zuberi-3-pc-patio-conversation-set</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>Natural</t>
         </is>
       </c>
-      <c r="B39" s="32" t="n"/>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="C39" s="32" t="n"/>
+      <c r="D39" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-05NT</t>
         </is>
       </c>
-      <c r="D39" s="32" t="inlineStr">
+      <c r="E39" s="32" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E39" s="32" t="inlineStr">
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F39" s="32" t="inlineStr">
+      <c r="G39" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="G39" s="32" t="inlineStr">
+      <c r="H39" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.&lt;br&gt;
@@ -6207,139 +6602,146 @@
 Weight: 37.6 or 21.3 or 28.1 or 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H39" s="32" t="inlineStr">
+      <c r="I39" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I39" s="32" t="inlineStr">
+      <c r="J39" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J39" s="32" t="inlineStr">
+      <c r="K39" s="32" t="inlineStr">
         <is>
           <t>ZUBERI</t>
         </is>
       </c>
-      <c r="K39" s="32" t="inlineStr">
+      <c r="L39" s="32" t="inlineStr">
         <is>
           <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="L39" s="32" t="n"/>
-      <c r="M39" s="32" t="inlineStr">
+      <c r="M39" s="32" t="n"/>
+      <c r="N39" s="32" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N39" s="32" t="inlineStr">
+      <c r="O39" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-T, FM80005NT-CH-2PK</t>
         </is>
       </c>
-      <c r="O39" s="32" t="inlineStr">
+      <c r="P39" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-05NT-1-Z.jpg,FM80003NT-T-1.jpg,FM80005NT-CH-1.jpg</t>
         </is>
       </c>
-      <c r="P39" s="32" t="n">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" s="32" t="n">
         <v>169</v>
       </c>
-      <c r="Q39" s="33" t="n">
+      <c r="T39" s="33" t="n">
         <v>169</v>
       </c>
-      <c r="R39" s="32" t="n">
+      <c r="U39" s="32" t="n">
         <v>327</v>
       </c>
-      <c r="S39" s="32" t="n">
+      <c r="V39" s="32" t="n">
         <v>28.1</v>
       </c>
-      <c r="T39" s="32" t="inlineStr">
+      <c r="W39" s="32" t="inlineStr">
         <is>
           <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H</t>
         </is>
       </c>
-      <c r="U39" s="32" t="inlineStr">
+      <c r="X39" s="32" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V39" s="32" t="inlineStr">
+      <c r="Y39" s="32" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
-      <c r="W39" s="32" t="inlineStr">
+      <c r="Z39" s="32" t="inlineStr">
         <is>
           <t>Contemporary,Natural,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
-      <c r="X39" s="32" t="inlineStr">
+      <c r="AA39" s="32" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y39" s="32" t="n"/>
-      <c r="Z39" s="32" t="n"/>
-      <c r="AA39" s="32" t="n"/>
-      <c r="AB39" s="32" t="n">
+      <c r="AB39" s="32" t="n"/>
+      <c r="AC39" s="32" t="n"/>
+      <c r="AD39" s="32" t="n"/>
+      <c r="AE39" s="32" t="n">
         <v>24.1</v>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AF39" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD39" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZUBERI</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr">
+      <c r="AH39" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF39" t="inlineStr">
+      <c r="AI39" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG39" t="inlineStr">
+      <c r="AJ39" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="inlineStr">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>zuberi-3-pc-patio-conversation-set</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="inlineStr">
         <is>
           <t>Natural/Gray</t>
         </is>
       </c>
-      <c r="B40" s="32" t="n"/>
-      <c r="C40" s="32" t="inlineStr">
+      <c r="C40" s="32" t="n"/>
+      <c r="D40" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-06GY</t>
         </is>
       </c>
-      <c r="D40" s="32" t="inlineStr">
+      <c r="E40" s="32" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E40" s="32" t="inlineStr">
+      <c r="F40" s="32" t="inlineStr">
         <is>
           <t>Patio Set</t>
         </is>
       </c>
-      <c r="F40" s="32" t="inlineStr">
+      <c r="G40" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="G40" s="32" t="inlineStr">
+      <c r="H40" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ZUBERI 3 Pc. Patio Conversation Set offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor patio set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Steel Frame, PE Rattan Wicker, Polyester Fabric, then finished in Natural or Black tones to suit a range of interiors.&lt;br&gt;
@@ -6356,143 +6758,150 @@
 Weight: 37.6 or 21.3 or 28.1 or 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H40" s="32" t="inlineStr">
+      <c r="I40" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I40" s="32" t="inlineStr">
+      <c r="J40" s="32" t="inlineStr">
         <is>
           <t>ZUBERI 3 Pc. Patio Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J40" s="32" t="inlineStr">
+      <c r="K40" s="32" t="inlineStr">
         <is>
           <t>ZUBERI</t>
         </is>
       </c>
-      <c r="K40" s="32" t="inlineStr">
+      <c r="L40" s="32" t="inlineStr">
         <is>
           <t>3 Pc. Patio Conversation Set</t>
         </is>
       </c>
-      <c r="L40" s="32" t="inlineStr">
+      <c r="M40" s="32" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="M40" s="32" t="inlineStr">
+      <c r="N40" s="32" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N40" s="32" t="inlineStr">
+      <c r="O40" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-T, FM80006GY-CH-2PK</t>
         </is>
       </c>
-      <c r="O40" s="32" t="inlineStr">
+      <c r="P40" s="32" t="inlineStr">
         <is>
           <t>FM80003NT-3PC-06GY-1-Z.jpg,FM80003NT-T-1.jpg,FM80006GY-CH-1.jpg</t>
         </is>
       </c>
-      <c r="P40" s="32" t="n">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" s="32" t="n">
         <v>249</v>
       </c>
-      <c r="Q40" s="33" t="n">
+      <c r="T40" s="33" t="n">
         <v>249</v>
       </c>
-      <c r="R40" s="32" t="n">
+      <c r="U40" s="32" t="n">
         <v>477</v>
       </c>
-      <c r="S40" s="32" t="n">
+      <c r="V40" s="32" t="n">
         <v>35.9</v>
       </c>
-      <c r="T40" s="32" t="inlineStr">
+      <c r="W40" s="32" t="inlineStr">
         <is>
           <t>Table: 21.5"W X 21.5"D X 15.5"H, Chair: 23"W X 23.5"D X 35"H</t>
         </is>
       </c>
-      <c r="U40" s="32" t="inlineStr">
+      <c r="X40" s="32" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V40" s="32" t="inlineStr">
+      <c r="Y40" s="32" t="inlineStr">
         <is>
           <t>Steel Frame, PE Rattan Wicker, Polyester Fabric</t>
         </is>
       </c>
-      <c r="W40" s="32" t="inlineStr">
+      <c r="Z40" s="32" t="inlineStr">
         <is>
           <t>Contemporary,Natural/Gray,Steel Frame, PE Rattan Wicker, Polyester Fabric,Sturdy &amp; Durable Design,Easy to store,Handcrafted BOHO Chic</t>
         </is>
       </c>
-      <c r="X40" s="32" t="inlineStr">
+      <c r="AA40" s="32" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Y40" s="32" t="n"/>
-      <c r="Z40" s="32" t="n"/>
-      <c r="AA40" s="32" t="n"/>
-      <c r="AB40" s="32" t="n">
+      <c r="AB40" s="32" t="n"/>
+      <c r="AC40" s="32" t="n"/>
+      <c r="AD40" s="32" t="n"/>
+      <c r="AE40" s="32" t="n">
         <v>22.3</v>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AF40" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD40" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>Outdoor, Patio Set, ZUBERI</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr">
+      <c r="AH40" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF40" t="inlineStr">
+      <c r="AI40" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG40" t="inlineStr">
+      <c r="AJ40" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>breeze-swing-chair-w-stand</t>
+        </is>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="B41" s="34" t="n"/>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C41" s="34" t="n"/>
+      <c r="D41" s="34" t="inlineStr">
         <is>
           <t>GM-1010BK-SET</t>
         </is>
       </c>
-      <c r="D41" s="34" t="inlineStr">
+      <c r="E41" s="34" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E41" s="34" t="inlineStr">
+      <c r="F41" s="34" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="F41" s="34" t="inlineStr">
+      <c r="G41" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="G41" s="34" t="inlineStr">
+      <c r="H41" s="34" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 BREEZE Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Crafted with Steel, Mesh, Fabric, then finished in Black tones to suit a range of interiors.&lt;br&gt;
@@ -6512,139 +6921,150 @@
 Weight: 71.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H41" s="34" t="inlineStr">
+      <c r="I41" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
-      <c r="I41" s="34" t="inlineStr">
+      <c r="J41" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J41" s="34" t="inlineStr">
+      <c r="K41" s="34" t="inlineStr">
         <is>
           <t>BREEZE</t>
         </is>
       </c>
-      <c r="K41" s="34" t="inlineStr">
+      <c r="L41" s="34" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="L41" s="34" t="n"/>
-      <c r="M41" s="34" t="inlineStr">
+      <c r="M41" s="34" t="n"/>
+      <c r="N41" s="34" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N41" s="34" t="inlineStr">
+      <c r="O41" s="34" t="inlineStr">
         <is>
           <t>GM-1010BK, GM-1012</t>
         </is>
       </c>
-      <c r="O41" s="34" t="inlineStr">
+      <c r="P41" s="34" t="inlineStr">
         <is>
           <t>GM-1010BK-1-Z.jpg,GM-1010BK-1.jpg</t>
         </is>
       </c>
-      <c r="P41" s="34" t="n">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>GM-1010BK-1-Z.jpg,GM-1010BK-1.jpg,GM-1010DG-WB-1.jpg,GM-1010LG-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S41" s="34" t="n">
         <v>219</v>
       </c>
-      <c r="Q41" s="35" t="n">
+      <c r="T41" s="35" t="n">
         <v>219</v>
       </c>
-      <c r="R41" s="34" t="n">
+      <c r="U41" s="34" t="n">
         <v>567</v>
       </c>
-      <c r="S41" s="34" t="n">
+      <c r="V41" s="34" t="n">
         <v>71.42</v>
       </c>
-      <c r="T41" s="34" t="inlineStr">
+      <c r="W41" s="34" t="inlineStr">
         <is>
           <t>28""W X 34 1/4""D X 46""H"</t>
         </is>
       </c>
-      <c r="U41" s="34" t="inlineStr">
+      <c r="X41" s="34" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="V41" s="34" t="inlineStr">
+      <c r="Y41" s="34" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="W41" s="34" t="inlineStr">
+      <c r="Z41" s="34" t="inlineStr">
         <is>
           <t>Modern,Black,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="X41" s="34" t="inlineStr">
+      <c r="AA41" s="34" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y41" s="34" t="n"/>
-      <c r="Z41" s="34" t="n"/>
-      <c r="AA41" s="34" t="n"/>
-      <c r="AB41" s="34" t="n">
+      <c r="AB41" s="34" t="n"/>
+      <c r="AC41" s="34" t="n"/>
+      <c r="AD41" s="34" t="n"/>
+      <c r="AE41" s="34" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AF41" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>Outdoor, Chair, BREEZE, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE41" t="inlineStr">
+      <c r="AH41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr">
+      <c r="AI41" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG41" t="inlineStr">
+      <c r="AJ41" t="inlineStr">
         <is>
           <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>breeze-swing-chair-w-stand</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
         <is>
           <t>Dark Gray</t>
         </is>
       </c>
-      <c r="B42" s="34" t="n"/>
-      <c r="C42" s="34" t="inlineStr">
+      <c r="C42" s="34" t="n"/>
+      <c r="D42" s="34" t="inlineStr">
         <is>
           <t>GM-1010DG-SET</t>
         </is>
       </c>
-      <c r="D42" s="34" t="inlineStr">
+      <c r="E42" s="34" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E42" s="34" t="inlineStr">
+      <c r="F42" s="34" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="F42" s="34" t="inlineStr">
+      <c r="G42" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="G42" s="34" t="inlineStr">
+      <c r="H42" s="34" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 BREEZE Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Crafted with Steel, Mesh, Fabric, then finished in Black tones to suit a range of interiors.&lt;br&gt;
@@ -6664,139 +7084,146 @@
 Weight: 71.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H42" s="34" t="inlineStr">
+      <c r="I42" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
-      <c r="I42" s="34" t="inlineStr">
+      <c r="J42" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J42" s="34" t="inlineStr">
+      <c r="K42" s="34" t="inlineStr">
         <is>
           <t>BREEZE</t>
         </is>
       </c>
-      <c r="K42" s="34" t="inlineStr">
+      <c r="L42" s="34" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="L42" s="34" t="n"/>
-      <c r="M42" s="34" t="inlineStr">
+      <c r="M42" s="34" t="n"/>
+      <c r="N42" s="34" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N42" s="34" t="inlineStr">
+      <c r="O42" s="34" t="inlineStr">
         <is>
           <t>GM-1010DG, GM-1012</t>
         </is>
       </c>
-      <c r="O42" s="34" t="inlineStr">
+      <c r="P42" s="34" t="inlineStr">
         <is>
           <t>GM-1010DG-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P42" s="34" t="n">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" s="34" t="n">
         <v>219</v>
       </c>
-      <c r="Q42" s="35" t="n">
+      <c r="T42" s="35" t="n">
         <v>219</v>
       </c>
-      <c r="R42" s="34" t="n">
+      <c r="U42" s="34" t="n">
         <v>567</v>
       </c>
-      <c r="S42" s="34" t="n">
+      <c r="V42" s="34" t="n">
         <v>71.42</v>
       </c>
-      <c r="T42" s="34" t="inlineStr">
+      <c r="W42" s="34" t="inlineStr">
         <is>
           <t>28""W X 34 1/4""D X 46""H"</t>
         </is>
       </c>
-      <c r="U42" s="34" t="inlineStr">
+      <c r="X42" s="34" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="V42" s="34" t="inlineStr">
+      <c r="Y42" s="34" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="W42" s="34" t="inlineStr">
+      <c r="Z42" s="34" t="inlineStr">
         <is>
           <t>Modern,Dark Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="X42" s="34" t="inlineStr">
+      <c r="AA42" s="34" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y42" s="34" t="n"/>
-      <c r="Z42" s="34" t="n"/>
-      <c r="AA42" s="34" t="n"/>
-      <c r="AB42" s="34" t="n">
+      <c r="AB42" s="34" t="n"/>
+      <c r="AC42" s="34" t="n"/>
+      <c r="AD42" s="34" t="n"/>
+      <c r="AE42" s="34" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AF42" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD42" t="inlineStr">
+      <c r="AG42" t="inlineStr">
         <is>
           <t>Outdoor, Chair, BREEZE, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE42" t="inlineStr">
+      <c r="AH42" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF42" t="inlineStr">
+      <c r="AI42" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG42" t="inlineStr">
+      <c r="AJ42" t="inlineStr">
         <is>
           <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>breeze-swing-chair-w-stand</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
         <is>
           <t>Light Gray</t>
         </is>
       </c>
-      <c r="B43" s="34" t="n"/>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="C43" s="34" t="n"/>
+      <c r="D43" s="34" t="inlineStr">
         <is>
           <t>GM-1010LG-SET</t>
         </is>
       </c>
-      <c r="D43" s="34" t="inlineStr">
+      <c r="E43" s="34" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E43" s="34" t="inlineStr">
+      <c r="F43" s="34" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="F43" s="34" t="inlineStr">
+      <c r="G43" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="G43" s="34" t="inlineStr">
+      <c r="H43" s="34" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 BREEZE Swing Chair w/ Stand offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Crafted with Steel, Mesh, Fabric, then finished in Black tones to suit a range of interiors.&lt;br&gt;
@@ -6816,139 +7243,146 @@
 Weight: 71.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H43" s="34" t="inlineStr">
+      <c r="I43" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
-      <c r="I43" s="34" t="inlineStr">
+      <c r="J43" s="34" t="inlineStr">
         <is>
           <t>BREEZE Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J43" s="34" t="inlineStr">
+      <c r="K43" s="34" t="inlineStr">
         <is>
           <t>BREEZE</t>
         </is>
       </c>
-      <c r="K43" s="34" t="inlineStr">
+      <c r="L43" s="34" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="L43" s="34" t="n"/>
-      <c r="M43" s="34" t="inlineStr">
+      <c r="M43" s="34" t="n"/>
+      <c r="N43" s="34" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N43" s="34" t="inlineStr">
+      <c r="O43" s="34" t="inlineStr">
         <is>
           <t>GM-1010LG, GM-1012</t>
         </is>
       </c>
-      <c r="O43" s="34" t="inlineStr">
+      <c r="P43" s="34" t="inlineStr">
         <is>
           <t>GM-1010LG-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P43" s="34" t="n">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" s="34" t="n">
         <v>219</v>
       </c>
-      <c r="Q43" s="35" t="n">
+      <c r="T43" s="35" t="n">
         <v>219</v>
       </c>
-      <c r="R43" s="34" t="n">
+      <c r="U43" s="34" t="n">
         <v>567</v>
       </c>
-      <c r="S43" s="34" t="n">
+      <c r="V43" s="34" t="n">
         <v>71.42</v>
       </c>
-      <c r="T43" s="34" t="inlineStr">
+      <c r="W43" s="34" t="inlineStr">
         <is>
           <t>28""W X 34 1/4""D X 46""H"</t>
         </is>
       </c>
-      <c r="U43" s="34" t="inlineStr">
+      <c r="X43" s="34" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="V43" s="34" t="inlineStr">
+      <c r="Y43" s="34" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="W43" s="34" t="inlineStr">
+      <c r="Z43" s="34" t="inlineStr">
         <is>
           <t>Modern,Light Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="X43" s="34" t="inlineStr">
+      <c r="AA43" s="34" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y43" s="34" t="n"/>
-      <c r="Z43" s="34" t="n"/>
-      <c r="AA43" s="34" t="n"/>
-      <c r="AB43" s="34" t="n">
+      <c r="AB43" s="34" t="n"/>
+      <c r="AC43" s="34" t="n"/>
+      <c r="AD43" s="34" t="n"/>
+      <c r="AE43" s="34" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AF43" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr">
+      <c r="AG43" t="inlineStr">
         <is>
           <t>Outdoor, Chair, BREEZE, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE43" t="inlineStr">
+      <c r="AH43" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF43" t="inlineStr">
+      <c r="AI43" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG43" t="inlineStr">
+      <c r="AJ43" t="inlineStr">
         <is>
           <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>crush-swing-chair-w-stand</t>
+        </is>
+      </c>
+      <c r="B44" s="36" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="B44" s="36" t="n"/>
-      <c r="C44" s="36" t="inlineStr">
+      <c r="C44" s="36" t="n"/>
+      <c r="D44" s="36" t="inlineStr">
         <is>
           <t>GM-1011BK-SET</t>
         </is>
       </c>
-      <c r="D44" s="36" t="inlineStr">
+      <c r="E44" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E44" s="36" t="inlineStr">
+      <c r="F44" s="36" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="F44" s="36" t="inlineStr">
+      <c r="G44" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="G44" s="36" t="inlineStr">
+      <c r="H44" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 CRUSH Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Steel, Mesh, Fabric build keeps the look polished and practical.&lt;br&gt;
@@ -6968,139 +7402,150 @@
 Weight: 68.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H44" s="36" t="inlineStr">
+      <c r="I44" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
-      <c r="I44" s="36" t="inlineStr">
+      <c r="J44" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J44" s="36" t="inlineStr">
+      <c r="K44" s="36" t="inlineStr">
         <is>
           <t>CRUSH</t>
         </is>
       </c>
-      <c r="K44" s="36" t="inlineStr">
+      <c r="L44" s="36" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="L44" s="36" t="n"/>
-      <c r="M44" s="36" t="inlineStr">
+      <c r="M44" s="36" t="n"/>
+      <c r="N44" s="36" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N44" s="36" t="inlineStr">
+      <c r="O44" s="36" t="inlineStr">
         <is>
           <t>GM-1011BK, GM-1012</t>
         </is>
       </c>
-      <c r="O44" s="36" t="inlineStr">
+      <c r="P44" s="36" t="inlineStr">
         <is>
           <t>GM-1011BK-WB-1.jpg,GM-1011BK-1.jpg</t>
         </is>
       </c>
-      <c r="P44" s="36" t="n">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>GM-1011BK-WB-1.jpg,GM-1011BK-1.jpg,GM-1011DG-WB-1.jpg,GM-1011DG-1.jpg,GM-1011LG-WB-1.jpg</t>
+        </is>
+      </c>
+      <c r="S44" s="36" t="n">
         <v>219</v>
       </c>
-      <c r="Q44" s="37" t="n">
+      <c r="T44" s="37" t="n">
         <v>219</v>
       </c>
-      <c r="R44" s="36" t="n">
+      <c r="U44" s="36" t="n">
         <v>567</v>
       </c>
-      <c r="S44" s="36" t="n">
+      <c r="V44" s="36" t="n">
         <v>68.12</v>
       </c>
-      <c r="T44" s="36" t="inlineStr">
+      <c r="W44" s="36" t="inlineStr">
         <is>
           <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
         </is>
       </c>
-      <c r="U44" s="36" t="inlineStr">
+      <c r="X44" s="36" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="V44" s="36" t="inlineStr">
+      <c r="Y44" s="36" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="W44" s="36" t="inlineStr">
+      <c r="Z44" s="36" t="inlineStr">
         <is>
           <t>Modern,Black,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="X44" s="36" t="inlineStr">
+      <c r="AA44" s="36" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y44" s="36" t="n"/>
-      <c r="Z44" s="36" t="n"/>
-      <c r="AA44" s="36" t="n"/>
-      <c r="AB44" s="36" t="n">
+      <c r="AB44" s="36" t="n"/>
+      <c r="AC44" s="36" t="n"/>
+      <c r="AD44" s="36" t="n"/>
+      <c r="AE44" s="36" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AF44" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
+      <c r="AG44" t="inlineStr">
         <is>
           <t>Outdoor, Chair, CRUSH, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE44" t="inlineStr">
+      <c r="AH44" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF44" t="inlineStr">
+      <c r="AI44" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG44" t="inlineStr">
+      <c r="AJ44" t="inlineStr">
         <is>
           <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>crush-swing-chair-w-stand</t>
+        </is>
+      </c>
+      <c r="B45" s="36" t="inlineStr">
         <is>
           <t>Dark Gray</t>
         </is>
       </c>
-      <c r="B45" s="36" t="n"/>
-      <c r="C45" s="36" t="inlineStr">
+      <c r="C45" s="36" t="n"/>
+      <c r="D45" s="36" t="inlineStr">
         <is>
           <t>GM-1011DG-SET</t>
         </is>
       </c>
-      <c r="D45" s="36" t="inlineStr">
+      <c r="E45" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E45" s="36" t="inlineStr">
+      <c r="F45" s="36" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="F45" s="36" t="inlineStr">
+      <c r="G45" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="G45" s="36" t="inlineStr">
+      <c r="H45" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 CRUSH Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Steel, Mesh, Fabric build keeps the look polished and practical.&lt;br&gt;
@@ -7120,139 +7565,146 @@
 Weight: 68.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H45" s="36" t="inlineStr">
+      <c r="I45" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
-      <c r="I45" s="36" t="inlineStr">
+      <c r="J45" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J45" s="36" t="inlineStr">
+      <c r="K45" s="36" t="inlineStr">
         <is>
           <t>CRUSH</t>
         </is>
       </c>
-      <c r="K45" s="36" t="inlineStr">
+      <c r="L45" s="36" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="L45" s="36" t="n"/>
-      <c r="M45" s="36" t="inlineStr">
+      <c r="M45" s="36" t="n"/>
+      <c r="N45" s="36" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N45" s="36" t="inlineStr">
+      <c r="O45" s="36" t="inlineStr">
         <is>
           <t>GM-1011DG, GM-1012</t>
         </is>
       </c>
-      <c r="O45" s="36" t="inlineStr">
+      <c r="P45" s="36" t="inlineStr">
         <is>
           <t>GM-1011DG-WB-1.jpg,GM-1011DG-1.jpg</t>
         </is>
       </c>
-      <c r="P45" s="36" t="n">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" s="36" t="n">
         <v>219</v>
       </c>
-      <c r="Q45" s="37" t="n">
+      <c r="T45" s="37" t="n">
         <v>219</v>
       </c>
-      <c r="R45" s="36" t="n">
+      <c r="U45" s="36" t="n">
         <v>567</v>
       </c>
-      <c r="S45" s="36" t="n">
+      <c r="V45" s="36" t="n">
         <v>68.12</v>
       </c>
-      <c r="T45" s="36" t="inlineStr">
+      <c r="W45" s="36" t="inlineStr">
         <is>
           <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
         </is>
       </c>
-      <c r="U45" s="36" t="inlineStr">
+      <c r="X45" s="36" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="V45" s="36" t="inlineStr">
+      <c r="Y45" s="36" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="W45" s="36" t="inlineStr">
+      <c r="Z45" s="36" t="inlineStr">
         <is>
           <t>Modern,Dark Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="X45" s="36" t="inlineStr">
+      <c r="AA45" s="36" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y45" s="36" t="n"/>
-      <c r="Z45" s="36" t="n"/>
-      <c r="AA45" s="36" t="n"/>
-      <c r="AB45" s="36" t="n">
+      <c r="AB45" s="36" t="n"/>
+      <c r="AC45" s="36" t="n"/>
+      <c r="AD45" s="36" t="n"/>
+      <c r="AE45" s="36" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AF45" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AG45" t="inlineStr">
         <is>
           <t>Outdoor, Chair, CRUSH, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE45" t="inlineStr">
+      <c r="AH45" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF45" t="inlineStr">
+      <c r="AI45" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG45" t="inlineStr">
+      <c r="AJ45" t="inlineStr">
         <is>
           <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>crush-swing-chair-w-stand</t>
+        </is>
+      </c>
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t>Light Gray</t>
         </is>
       </c>
-      <c r="B46" s="36" t="n"/>
-      <c r="C46" s="36" t="inlineStr">
+      <c r="C46" s="36" t="n"/>
+      <c r="D46" s="36" t="inlineStr">
         <is>
           <t>GM-1011LG-SET</t>
         </is>
       </c>
-      <c r="D46" s="36" t="inlineStr">
+      <c r="E46" s="36" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E46" s="36" t="inlineStr">
+      <c r="F46" s="36" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="F46" s="36" t="inlineStr">
+      <c r="G46" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="G46" s="36" t="inlineStr">
+      <c r="H46" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 CRUSH Swing Chair w/ Stand brings a composed, welcoming feel to the room without overwhelming the space. Designed as a outdoor chair, it pairs easily with surrounding decor. Its Modern styling keeps the room feeling polished yet comfortable. Finished in Black tones, the Steel, Mesh, Fabric build keeps the look polished and practical.&lt;br&gt;
@@ -7272,106 +7724,108 @@
 Weight: 68.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H46" s="36" t="inlineStr">
+      <c r="I46" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand | GOODDEGG</t>
         </is>
       </c>
-      <c r="I46" s="36" t="inlineStr">
+      <c r="J46" s="36" t="inlineStr">
         <is>
           <t>CRUSH Swing Chair w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J46" s="36" t="inlineStr">
+      <c r="K46" s="36" t="inlineStr">
         <is>
           <t>CRUSH</t>
         </is>
       </c>
-      <c r="K46" s="36" t="inlineStr">
+      <c r="L46" s="36" t="inlineStr">
         <is>
           <t>Swing Chair w/ Stand</t>
         </is>
       </c>
-      <c r="L46" s="36" t="n"/>
-      <c r="M46" s="36" t="inlineStr">
+      <c r="M46" s="36" t="n"/>
+      <c r="N46" s="36" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N46" s="36" t="inlineStr">
+      <c r="O46" s="36" t="inlineStr">
         <is>
           <t>GM-1011LG, GM-1012</t>
         </is>
       </c>
-      <c r="O46" s="36" t="inlineStr">
+      <c r="P46" s="36" t="inlineStr">
         <is>
           <t>GM-1011LG-WB-1.jpg</t>
         </is>
       </c>
-      <c r="P46" s="36" t="n">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" s="36" t="n">
         <v>219</v>
       </c>
-      <c r="Q46" s="37" t="n">
+      <c r="T46" s="37" t="n">
         <v>219</v>
       </c>
-      <c r="R46" s="36" t="n">
+      <c r="U46" s="36" t="n">
         <v>567</v>
       </c>
-      <c r="S46" s="36" t="n">
+      <c r="V46" s="36" t="n">
         <v>68.12</v>
       </c>
-      <c r="T46" s="36" t="inlineStr">
+      <c r="W46" s="36" t="inlineStr">
         <is>
           <t>28 1/4""W X 29 1/2""D X 43 1/4""H"</t>
         </is>
       </c>
-      <c r="U46" s="36" t="inlineStr">
+      <c r="X46" s="36" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="V46" s="36" t="inlineStr">
+      <c r="Y46" s="36" t="inlineStr">
         <is>
           <t>Steel, Mesh, Fabric</t>
         </is>
       </c>
-      <c r="W46" s="36" t="inlineStr">
+      <c r="Z46" s="36" t="inlineStr">
         <is>
           <t>Modern,Light Gray,Steel, Mesh, Fabric,For indoor or outdoor use,Easy-store foldable design,Breathable and UV-resistant mesh,Includes back and seat cushions,Easy to assemble with included hardware kit,Max weight capacity: 220 lbs</t>
         </is>
       </c>
-      <c r="X46" s="36" t="inlineStr">
+      <c r="AA46" s="36" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y46" s="36" t="n"/>
-      <c r="Z46" s="36" t="n"/>
-      <c r="AA46" s="36" t="n"/>
-      <c r="AB46" s="36" t="n">
+      <c r="AB46" s="36" t="n"/>
+      <c r="AC46" s="36" t="n"/>
+      <c r="AD46" s="36" t="n"/>
+      <c r="AE46" s="36" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AF46" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>Outdoor, Chair, CRUSH, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE46" t="inlineStr">
+      <c r="AH46" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF46" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG46" t="inlineStr">
+      <c r="AJ46" t="inlineStr">
         <is>
           <t>Furniture &gt; Chairs</t>
         </is>
@@ -7380,30 +7834,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>mackay-2-reclining-chairs-and-2-ottomans</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Beige/Natural Teak</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>GM-2002-4PC</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>MACKAY 2 Reclining Chairs and 2 Ottomans</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MACKAY 2 Reclining Chairs and 2 Ottomans is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor chair, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Beige or Natural Teak tones for a clean, cohesive look.&lt;br&gt;
@@ -7418,102 +7877,108 @@
 Weight: 90.37 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>MACKAY 2 Reclining Chairs and 2 Ottomans | GOODDEGG</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>MACKAY 2 Reclining Chairs and 2 Ottomans supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>MACKAY</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>2 Reclining Chairs + 2 Ottomans</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>GM-2002-2PK, GM-2003-2PK</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>GM-2002-WB-1.jpg,GM-2002-WB-2.jpg,GM-2002-WB-3.jpg,GM-2001-7PC+OT-1.jpg</t>
         </is>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>GM-2002-WB-1.jpg,GM-2002-WB-2.jpg,GM-2002-WB-3.jpg,GM-2001-7PC+OT-1.jpg</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
         <v>299</v>
       </c>
-      <c r="Q47" s="1" t="n">
+      <c r="T47" s="1" t="n">
         <v>299</v>
       </c>
-      <c r="R47" t="n">
+      <c r="U47" t="n">
         <v>777</v>
       </c>
-      <c r="S47" t="n">
+      <c r="V47" t="n">
         <v>90.37</v>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>24 1/2"W X 27 1/2"D X 42 1/2"H</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>Contemporary,Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Button-tufted cushion</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="AB47" t="n">
+      <c r="AE47" t="n">
         <v>12.9</v>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AF47" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
+      <c r="AG47" t="inlineStr">
         <is>
           <t>Outdoor, Chair, MACKAY, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE47" t="inlineStr">
+      <c r="AH47" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF47" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG47" t="inlineStr">
+      <c r="AJ47" t="inlineStr">
         <is>
           <t>Furniture &gt; Chairs</t>
         </is>
@@ -7522,30 +7987,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>cyprus-7-pc-bar-table-set</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>GM-2006-7PC</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Bar Table Set</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>CYPRUS 7 Pc. Bar Table Set</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 CYPRUS 7 Pc. Bar Table Set creates a cohesive setup that feels inviting the moment you walk in. Designed as a outdoor bar table set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Aluminum, Polyethylene Wicker, Polyspun construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
@@ -7562,135 +8032,146 @@
 Weight: 144.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>CYPRUS 7 Pc. Bar Table Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>CYPRUS 7 Pc. Bar Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>CYPRUS</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>7 Pc. Bar Table Set</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>GM-2006-2, GM-2007-6PK, GM-2006-1</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>GM-2006-1-Z.jpg,GM-2006-2.jpg,GM-2006-3.jpg</t>
         </is>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>GM-2006-1-Z.jpg,GM-2006-2.jpg,GM-2006-3.jpg</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
         <v>949</v>
       </c>
-      <c r="Q48" s="1" t="n">
+      <c r="T48" s="1" t="n">
         <v>949</v>
       </c>
-      <c r="R48" t="n">
+      <c r="U48" t="n">
         <v>2547</v>
       </c>
-      <c r="S48" t="n">
+      <c r="V48" t="n">
         <v>144.5</v>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>46"DIA X 39 1/2"H</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Aluminum, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>Contemporary,Gray,Aluminum, Polyethylene Wicker, Polyspun,Includes stainless steel ice bucket,Removable bucket with center cover,Stackable wicker chairs,Stainless steel footrest around base,Includes umbrella hole and space for umbrella base</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB48" t="n">
+      <c r="AE48" t="n">
         <v>37.7</v>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AF48" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
+      <c r="AG48" t="inlineStr">
         <is>
           <t>Outdoor, Bar Table Set, CYPRUS, DINING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE48" t="inlineStr">
+      <c r="AH48" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF48" t="inlineStr">
+      <c r="AI48" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG48" t="inlineStr">
+      <c r="AJ48" t="inlineStr">
         <is>
           <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="38" t="inlineStr">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ilona-l-sectional-and-coffee-table-and-end-table</t>
+        </is>
+      </c>
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>Brown/Beige</t>
         </is>
       </c>
-      <c r="B49" s="38" t="n"/>
-      <c r="C49" s="38" t="inlineStr">
+      <c r="C49" s="38" t="n"/>
+      <c r="D49" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-SET5</t>
         </is>
       </c>
-      <c r="D49" s="38" t="inlineStr">
+      <c r="E49" s="38" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E49" s="38" t="inlineStr">
+      <c r="F49" s="38" t="inlineStr">
         <is>
           <t>Sofa Set</t>
         </is>
       </c>
-      <c r="F49" s="38" t="inlineStr">
+      <c r="G49" s="38" t="inlineStr">
         <is>
           <t>ILONA L-Sectional and Coffee Table and End Table</t>
         </is>
       </c>
-      <c r="G49" s="38" t="inlineStr">
+      <c r="H49" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ILONA L-Sectional and Coffee Table and End Table is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor sofa set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, Polyester Canvas, Faux Rattan and finished in Brown or Beige tones for a clean, cohesive look.&lt;br&gt;
@@ -7713,139 +8194,150 @@
 Weight: 204 or 179 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H49" s="38" t="inlineStr">
+      <c r="I49" s="38" t="inlineStr">
         <is>
           <t>ILONA L-Sectional and Coffee Table and End Table | GOODDEGG</t>
         </is>
       </c>
-      <c r="I49" s="38" t="inlineStr">
+      <c r="J49" s="38" t="inlineStr">
         <is>
           <t>Sofa Set ILONA L-Sectional and Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J49" s="38" t="inlineStr">
+      <c r="K49" s="38" t="inlineStr">
         <is>
           <t>ILONA</t>
         </is>
       </c>
-      <c r="K49" s="38" t="inlineStr">
+      <c r="L49" s="38" t="inlineStr">
         <is>
           <t>L-Sectional + Coffee Table + End Table</t>
         </is>
       </c>
-      <c r="L49" s="38" t="n"/>
-      <c r="M49" s="38" t="inlineStr">
+      <c r="M49" s="38" t="n"/>
+      <c r="N49" s="38" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N49" s="38" t="inlineStr">
+      <c r="O49" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-A, CM-OS2136-C, CM-OS2136-E, CM-OS2136-F, CM-OS2136-G, CM-OS2136-H</t>
         </is>
       </c>
-      <c r="O49" s="38" t="inlineStr">
+      <c r="P49" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-5.jpg,CM-OS2136-1.jpg,CM-OS2136-2.jpg</t>
         </is>
       </c>
-      <c r="P49" s="38" t="n">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>CM-OS2136-5.jpg,CM-OS2136-1.jpg,CM-OS2136-2.jpg,CM-OS2136-7.jpg</t>
+        </is>
+      </c>
+      <c r="S49" s="38" t="n">
         <v>1082</v>
       </c>
-      <c r="Q49" s="39" t="n">
+      <c r="T49" s="39" t="n">
         <v>1082</v>
       </c>
-      <c r="R49" s="38" t="n">
+      <c r="U49" s="38" t="n">
         <v>2817</v>
       </c>
-      <c r="S49" s="38" t="n">
+      <c r="V49" s="38" t="n">
         <v>204</v>
       </c>
-      <c r="T49" s="38" t="inlineStr">
+      <c r="W49" s="38" t="inlineStr">
         <is>
           <t>L-SECTIONAL: 103 1/4"W X 79 1/4"D X 25 1/2-31"H</t>
         </is>
       </c>
-      <c r="U49" s="38" t="inlineStr">
+      <c r="X49" s="38" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V49" s="38" t="inlineStr">
+      <c r="Y49" s="38" t="inlineStr">
         <is>
           <t>Aluminum, Polyester Canvas, Faux Rattan</t>
         </is>
       </c>
-      <c r="W49" s="38" t="inlineStr">
+      <c r="Z49" s="38" t="inlineStr">
         <is>
           <t>Contemporary,Brown/Beige,Aluminum, Polyester Canvas, Faux Rattan,Aluminum Frame,Modular Design,5mm Tempered Glass Table Tops,UV &amp; Water Resistant,Beige Fabric Cushions</t>
         </is>
       </c>
-      <c r="X49" s="38" t="inlineStr">
+      <c r="AA49" s="38" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y49" s="38" t="n"/>
-      <c r="Z49" s="38" t="n"/>
-      <c r="AA49" s="38" t="n"/>
-      <c r="AB49" s="38" t="n">
+      <c r="AB49" s="38" t="n"/>
+      <c r="AC49" s="38" t="n"/>
+      <c r="AD49" s="38" t="n"/>
+      <c r="AE49" s="38" t="n">
         <v>45.7</v>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AF49" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AG49" t="inlineStr">
         <is>
           <t>Outdoor, Sofa Set, ILONA, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE49" t="inlineStr">
+      <c r="AH49" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF49" t="inlineStr">
+      <c r="AI49" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG49" t="inlineStr">
+      <c r="AJ49" t="inlineStr">
         <is>
           <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="38" t="inlineStr">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ilona-l-sectional-and-coffee-table-and-end-table</t>
+        </is>
+      </c>
+      <c r="B50" s="38" t="inlineStr">
         <is>
           <t>Brown/Beige</t>
         </is>
       </c>
-      <c r="B50" s="38" t="n"/>
-      <c r="C50" s="38" t="inlineStr">
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-SET7</t>
         </is>
       </c>
-      <c r="D50" s="38" t="inlineStr">
+      <c r="E50" s="38" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E50" s="38" t="inlineStr">
+      <c r="F50" s="38" t="inlineStr">
         <is>
           <t>Sofa Set</t>
         </is>
       </c>
-      <c r="F50" s="38" t="inlineStr">
+      <c r="G50" s="38" t="inlineStr">
         <is>
           <t>ILONA L-Sectional and Coffee Table and End Table</t>
         </is>
       </c>
-      <c r="G50" s="38" t="inlineStr">
+      <c r="H50" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ILONA L-Sectional and Coffee Table and End Table is designed for everyday living, balancing comfort with a clean, finished look. As a outdoor sofa set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Aluminum, Polyester Canvas, Faux Rattan and finished in Brown or Beige tones for a clean, cohesive look.&lt;br&gt;
@@ -7868,139 +8360,146 @@
 Weight: 204 or 179 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H50" s="38" t="inlineStr">
+      <c r="I50" s="38" t="inlineStr">
         <is>
           <t>ILONA L-Sectional and Coffee Table and End Table | GOODDEGG</t>
         </is>
       </c>
-      <c r="I50" s="38" t="inlineStr">
+      <c r="J50" s="38" t="inlineStr">
         <is>
           <t>Sofa Set ILONA L-Sectional and Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J50" s="38" t="inlineStr">
+      <c r="K50" s="38" t="inlineStr">
         <is>
           <t>ILONA</t>
         </is>
       </c>
-      <c r="K50" s="38" t="inlineStr">
+      <c r="L50" s="38" t="inlineStr">
         <is>
           <t>L-Sectional + Coffee Table + End Table</t>
         </is>
       </c>
-      <c r="L50" s="38" t="n"/>
-      <c r="M50" s="38" t="inlineStr">
+      <c r="M50" s="38" t="n"/>
+      <c r="N50" s="38" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N50" s="38" t="inlineStr">
+      <c r="O50" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-A, CM-OS2136-C, CM-OS2136-E, CM-OS2136-F, CM-OS2136-G, CM-OS2136-H</t>
         </is>
       </c>
-      <c r="O50" s="38" t="inlineStr">
+      <c r="P50" s="38" t="inlineStr">
         <is>
           <t>CM-OS2136-7.jpg,CM-OS2136-1.jpg,CM-OS2136-2.jpg</t>
         </is>
       </c>
-      <c r="P50" s="38" t="n">
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" s="38" t="n">
         <v>933</v>
       </c>
-      <c r="Q50" s="39" t="n">
+      <c r="T50" s="39" t="n">
         <v>933</v>
       </c>
-      <c r="R50" s="38" t="n">
+      <c r="U50" s="38" t="n">
         <v>2427</v>
       </c>
-      <c r="S50" s="38" t="n">
+      <c r="V50" s="38" t="n">
         <v>179</v>
       </c>
-      <c r="T50" s="38" t="inlineStr">
+      <c r="W50" s="38" t="inlineStr">
         <is>
           <t>L-SECTIONAL: 79 1/2"W X 79"D X 25 1/2-31"H</t>
         </is>
       </c>
-      <c r="U50" s="38" t="inlineStr">
+      <c r="X50" s="38" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V50" s="38" t="inlineStr">
+      <c r="Y50" s="38" t="inlineStr">
         <is>
           <t>Aluminum, Polyester Canvas, Faux Rattan</t>
         </is>
       </c>
-      <c r="W50" s="38" t="inlineStr">
+      <c r="Z50" s="38" t="inlineStr">
         <is>
           <t>Contemporary,Brown/Beige,Aluminum, Polyester Canvas, Faux Rattan,Aluminum Frame,Modular Design,5mm Tempered Glass Table Tops,UV &amp; Water Resistant,Beige Fabric Cushions</t>
         </is>
       </c>
-      <c r="X50" s="38" t="inlineStr">
+      <c r="AA50" s="38" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y50" s="38" t="n"/>
-      <c r="Z50" s="38" t="n"/>
-      <c r="AA50" s="38" t="n"/>
-      <c r="AB50" s="38" t="n">
+      <c r="AB50" s="38" t="n"/>
+      <c r="AC50" s="38" t="n"/>
+      <c r="AD50" s="38" t="n"/>
+      <c r="AE50" s="38" t="n">
         <v>40.2</v>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AF50" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr">
+      <c r="AG50" t="inlineStr">
         <is>
           <t>Outdoor, Sofa Set, ILONA, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE50" t="inlineStr">
+      <c r="AH50" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF50" t="inlineStr">
+      <c r="AI50" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG50" t="inlineStr">
+      <c r="AJ50" t="inlineStr">
         <is>
           <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="40" t="inlineStr">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>mackay-5-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>Beige/Natural Teak</t>
         </is>
       </c>
-      <c r="B51" s="40" t="n"/>
-      <c r="C51" s="40" t="inlineStr">
+      <c r="C51" s="40" t="n"/>
+      <c r="D51" s="40" t="inlineStr">
         <is>
           <t>GM-2001-5PC</t>
         </is>
       </c>
-      <c r="D51" s="40" t="inlineStr">
+      <c r="E51" s="40" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E51" s="40" t="inlineStr">
+      <c r="F51" s="40" t="inlineStr">
         <is>
           <t>Patio Dining Set</t>
         </is>
       </c>
-      <c r="F51" s="40" t="inlineStr">
+      <c r="G51" s="40" t="inlineStr">
         <is>
           <t>MACKAY 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G51" s="40" t="inlineStr">
+      <c r="H51" s="40" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MACKAY 5 Pc. Patio Dining Set sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, FSC Certified 100% Teak Wood, then finished in Beige or Natural Teak tones to suit a range of interiors.&lt;br&gt;
@@ -8018,139 +8517,150 @@
 Weight: 174.14 or 55.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H51" s="40" t="inlineStr">
+      <c r="I51" s="40" t="inlineStr">
         <is>
           <t>MACKAY 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I51" s="40" t="inlineStr">
+      <c r="J51" s="40" t="inlineStr">
         <is>
           <t>MACKAY 5 Pc. Patio Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J51" s="40" t="inlineStr">
+      <c r="K51" s="40" t="inlineStr">
         <is>
           <t>MACKAY</t>
         </is>
       </c>
-      <c r="K51" s="40" t="inlineStr">
+      <c r="L51" s="40" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="L51" s="40" t="n"/>
-      <c r="M51" s="40" t="inlineStr">
+      <c r="M51" s="40" t="n"/>
+      <c r="N51" s="40" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N51" s="40" t="inlineStr">
+      <c r="O51" s="40" t="inlineStr">
         <is>
           <t>GM-2001, GM-2002-2PK</t>
         </is>
       </c>
-      <c r="O51" s="40" t="inlineStr">
+      <c r="P51" s="40" t="inlineStr">
         <is>
           <t>GM-2001-1-Z.jpg,GM-2001-2.jpg,GM-2001-3.jpg,GM-2001-4.jpg,GM-2001-5.jpg,GM-2001-6.jpg,GM-2001-7.jpg,GM-2001-8.jpg,GM-2001-9.jpg,GM-2001-9.jpg</t>
         </is>
       </c>
-      <c r="P51" s="40" t="n">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>GM-2001-1-Z.jpg,GM-2001-2.jpg,GM-2001-3.jpg,GM-2001-4.jpg,GM-2001-5.jpg,GM-2001-6.jpg,GM-2001-7.jpg,GM-2001-8.jpg,GM-2001-9.jpg,GM-2004-5PC.jpg,GM-2004-WB-4.jpg,GM-2004-WB-5.jpg</t>
+        </is>
+      </c>
+      <c r="S51" s="40" t="n">
         <v>789</v>
       </c>
-      <c r="Q51" s="41" t="n">
+      <c r="T51" s="41" t="n">
         <v>789</v>
       </c>
-      <c r="R51" s="40" t="n">
+      <c r="U51" s="40" t="n">
         <v>2127</v>
       </c>
-      <c r="S51" s="40" t="n">
+      <c r="V51" s="40" t="n">
         <v>174.14</v>
       </c>
-      <c r="T51" s="40" t="inlineStr">
+      <c r="W51" s="40" t="inlineStr">
         <is>
           <t>61 1/2 - 84"L X 35 1/2"W X 30"H</t>
         </is>
       </c>
-      <c r="U51" s="40" t="inlineStr">
+      <c r="X51" s="40" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V51" s="40" t="inlineStr">
+      <c r="Y51" s="40" t="inlineStr">
         <is>
           <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
-      <c r="W51" s="40" t="inlineStr">
+      <c r="Z51" s="40" t="inlineStr">
         <is>
           <t>Contemporary,Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Extends from 61" to 84" w/ butterfly leaf,Seats up to 8 people,Level control table legs</t>
         </is>
       </c>
-      <c r="X51" s="40" t="inlineStr">
+      <c r="AA51" s="40" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y51" s="40" t="n"/>
-      <c r="Z51" s="40" t="n"/>
-      <c r="AA51" s="40" t="n"/>
-      <c r="AB51" s="40" t="n">
+      <c r="AB51" s="40" t="n"/>
+      <c r="AC51" s="40" t="n"/>
+      <c r="AD51" s="40" t="n"/>
+      <c r="AE51" s="40" t="n">
         <v>28.3</v>
       </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AF51" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD51" t="inlineStr">
+      <c r="AG51" t="inlineStr">
         <is>
           <t>Outdoor, Patio Dining Set, MACKAY</t>
         </is>
       </c>
-      <c r="AE51" t="inlineStr">
+      <c r="AH51" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF51" t="inlineStr">
+      <c r="AI51" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG51" t="inlineStr">
+      <c r="AJ51" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="40" t="inlineStr">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>mackay-5-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B52" s="40" t="inlineStr">
         <is>
           <t>Gun Metal/Natural Teak</t>
         </is>
       </c>
-      <c r="B52" s="40" t="n"/>
-      <c r="C52" s="40" t="inlineStr">
+      <c r="C52" s="40" t="n"/>
+      <c r="D52" s="40" t="inlineStr">
         <is>
           <t>GM-2004-5PC</t>
         </is>
       </c>
-      <c r="D52" s="40" t="inlineStr">
+      <c r="E52" s="40" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E52" s="40" t="inlineStr">
+      <c r="F52" s="40" t="inlineStr">
         <is>
           <t>Patio Dining Set</t>
         </is>
       </c>
-      <c r="F52" s="40" t="inlineStr">
+      <c r="G52" s="40" t="inlineStr">
         <is>
           <t>MACKAY 5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G52" s="40" t="inlineStr">
+      <c r="H52" s="40" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MACKAY 5 Pc. Patio Dining Set sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Aluminum, FSC Certified 100% Teak Wood, then finished in Beige or Natural Teak tones to suit a range of interiors.&lt;br&gt;
@@ -8168,106 +8678,108 @@
 Weight: 174.14 or 55.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H52" s="40" t="inlineStr">
+      <c r="I52" s="40" t="inlineStr">
         <is>
           <t>MACKAY 5 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I52" s="40" t="inlineStr">
+      <c r="J52" s="40" t="inlineStr">
         <is>
           <t>MACKAY 5 Pc. Patio Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J52" s="40" t="inlineStr">
+      <c r="K52" s="40" t="inlineStr">
         <is>
           <t>MACKAY</t>
         </is>
       </c>
-      <c r="K52" s="40" t="inlineStr">
+      <c r="L52" s="40" t="inlineStr">
         <is>
           <t>5 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="L52" s="40" t="n"/>
-      <c r="M52" s="40" t="inlineStr">
+      <c r="M52" s="40" t="n"/>
+      <c r="N52" s="40" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N52" s="40" t="inlineStr">
+      <c r="O52" s="40" t="inlineStr">
         <is>
           <t>GM-2004, GM-2005</t>
         </is>
       </c>
-      <c r="O52" s="40" t="inlineStr">
+      <c r="P52" s="40" t="inlineStr">
         <is>
           <t>GM-2004-5PC.jpg,GM-2004-WB-4.jpg,GM-2004-WB-5.jpg</t>
         </is>
       </c>
-      <c r="P52" s="40" t="n">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" s="40" t="n">
         <v>499</v>
       </c>
-      <c r="Q52" s="41" t="n">
+      <c r="T52" s="41" t="n">
         <v>499</v>
       </c>
-      <c r="R52" s="40" t="n">
+      <c r="U52" s="40" t="n">
         <v>1047</v>
       </c>
-      <c r="S52" s="40" t="n">
+      <c r="V52" s="40" t="n">
         <v>55.1</v>
       </c>
-      <c r="T52" s="40" t="inlineStr">
+      <c r="W52" s="40" t="inlineStr">
         <is>
           <t>59"L X 35 1/2"W X 29"H</t>
         </is>
       </c>
-      <c r="U52" s="40" t="inlineStr">
+      <c r="X52" s="40" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V52" s="40" t="inlineStr">
+      <c r="Y52" s="40" t="inlineStr">
         <is>
           <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
-      <c r="W52" s="40" t="inlineStr">
+      <c r="Z52" s="40" t="inlineStr">
         <is>
           <t>Contemporary,Gun Metal/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Seats up to 6 people,Level control table legs,Includes umbrella hole and cap</t>
         </is>
       </c>
-      <c r="X52" s="40" t="inlineStr">
+      <c r="AA52" s="40" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="Y52" s="40" t="n"/>
-      <c r="Z52" s="40" t="n"/>
-      <c r="AA52" s="40" t="n"/>
-      <c r="AB52" s="40" t="n">
+      <c r="AB52" s="40" t="n"/>
+      <c r="AC52" s="40" t="n"/>
+      <c r="AD52" s="40" t="n"/>
+      <c r="AE52" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AF52" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD52" t="inlineStr">
+      <c r="AG52" t="inlineStr">
         <is>
           <t>Outdoor, Patio Dining Set, MACKAY</t>
         </is>
       </c>
-      <c r="AE52" t="inlineStr">
+      <c r="AH52" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF52" t="inlineStr">
+      <c r="AI52" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG52" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -8276,30 +8788,35 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>mackay-7-pc-patio-dining-set</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Gun Metal/Beige/Natural Teak</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>GM-2001-7PC</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Patio Dining Set</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>MACKAY 7 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MACKAY 7 Pc. Patio Dining Set anchors the dining area with a cohesive look that feels easy and welcoming. As a outdoor patio dining set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Gun Metal or Beige or Natural Teak tones, the Aluminum, FSC Certified 100% Teak Wood build keeps the look polished and practical.&lt;br&gt;
@@ -8317,102 +8834,108 @@
 Weight: 234.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>MACKAY 7 Pc. Patio Dining Set | GOODDEGG</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>MACKAY 7 Pc. Patio Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>MACKAY</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>7 Pc. Patio Dining Set</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>GM-2001, GM-2002-2PK</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>GM-2001-1-Z.jpg,GM-2001-2.jpg,GM-2001-3.jpg,GM-2001-4.jpg,GM-2001-5.jpg,GM-2001-6.jpg,GM-2001-7.jpg,GM-2001-8.jpg,GM-2001-9.jpg,GM-2001-9.jpg</t>
         </is>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>GM-2001-1-Z.jpg,GM-2001-2.jpg,GM-2001-3.jpg,GM-2001-4.jpg,GM-2001-5.jpg,GM-2001-6.jpg,GM-2001-7.jpg,GM-2001-8.jpg,GM-2001-9.jpg</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
         <v>999</v>
       </c>
-      <c r="Q53" s="1" t="n">
+      <c r="T53" s="1" t="n">
         <v>999</v>
       </c>
-      <c r="R53" t="n">
+      <c r="U53" t="n">
         <v>2697</v>
       </c>
-      <c r="S53" t="n">
+      <c r="V53" t="n">
         <v>234.76</v>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>61 1/2 - 84"L X 35 1/2"W X 30"H</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>Contemporary,Gun Metal/Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Extends from 61" to 84" w/ butterfly leaf,Seats up to 8 people,Level control table legs</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB53" t="n">
+      <c r="AE53" t="n">
         <v>37.7</v>
       </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AF53" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD53" t="inlineStr">
+      <c r="AG53" t="inlineStr">
         <is>
           <t>Outdoor, Patio Dining Set, MACKAY</t>
         </is>
       </c>
-      <c r="AE53" t="inlineStr">
+      <c r="AH53" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF53" t="inlineStr">
+      <c r="AI53" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG53" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -8421,30 +8944,35 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>mackay-7-pc-patio-dining-set-w-2-ottomans</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>Gun Metal/Beige/Natural Teak</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>GM-2001-7PC-OT</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Patio Dining Set</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans sets the tone for shared meals with a comfortable, coordinated look. This outdoor patio dining set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Aluminum, FSC Certified 100% Teak Wood and finished in Gun Metal or Beige or Natural Teak tones for a clean, cohesive look.&lt;br&gt;
@@ -8463,102 +8991,108 @@
 Weight: 203.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans | GOODDEGG</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>MACKAY 7 Pc. Patio Dining Set w/ 2 Ottomans supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>MACKAY</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>7 Pc. Patio Dining Set w/ 2 Ottomans</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>GM-2001, GM-2002-2PK, GM-2003-2PK</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>GM-2001-7PC+OT-1.jpg,GM-2001-2.jpg,GM-2001-3.jpg,GM-2001-4.jpg,GM-2001-5.jpg,GM-2001-6.jpg,GM-2001-7.jpg,GM-2001-8.jpg,GM-2001-9.jpg,GM-2001-9.jpg</t>
         </is>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>GM-2001-7PC+OT-1.jpg,GM-2001-2.jpg,GM-2001-3.jpg,GM-2001-4.jpg,GM-2001-5.jpg,GM-2001-6.jpg,GM-2001-7.jpg,GM-2001-8.jpg,GM-2001-9.jpg</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
         <v>879</v>
       </c>
-      <c r="Q54" s="1" t="n">
+      <c r="T54" s="1" t="n">
         <v>879</v>
       </c>
-      <c r="R54" t="n">
+      <c r="U54" t="n">
         <v>2367</v>
       </c>
-      <c r="S54" t="n">
+      <c r="V54" t="n">
         <v>203.89</v>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>61 1/2 - 84"L X 35 1/2"W X 30"H</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Aluminum, FSC Certified 100% Teak Wood</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>Contemporary,Gun Metal/Beige/Natural Teak,Aluminum, FSC Certified 100% Teak Wood,Mixed material of teak wood and metal frame,Extends from 61" to 84" w/ butterfly leaf,Seats up to 8 people,Level control table legs</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB54" t="n">
+      <c r="AE54" t="n">
         <v>31.8</v>
       </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AF54" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD54" t="inlineStr">
+      <c r="AG54" t="inlineStr">
         <is>
           <t>Outdoor, Patio Dining Set, MACKAY</t>
         </is>
       </c>
-      <c r="AE54" t="inlineStr">
+      <c r="AH54" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF54" t="inlineStr">
+      <c r="AI54" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG54" t="inlineStr">
+      <c r="AJ54" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
@@ -8567,30 +9101,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>malia-6-pc-patio-dining-set-w-bench</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>GM-1001-6PC</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Patio Dining Table</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>MALIA 6 Pc. Patio Dining Set w/ Bench</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Gather around MALIA 6 Pc. Patio Dining Set w/ Bench, designed to keep the dining space warm, balanced, and inviting. Designed as a outdoor patio dining table, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build keeps the look polished and practical.&lt;br&gt;
@@ -8612,102 +9151,108 @@
 Weight: 199.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>MALIA 6 Pc. Patio Dining Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Patio Dining Table MALIA 6 Pc. Patio Dining supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>MALIA</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>6 Pc. Patio Dining Set w/ Bench</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>GM-1001, GM-1002-5PK</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>GM-1001-1-Z.jpg,GM-1001-2.jpg,GM-1001-3.jpg,GM-1001-WB-1.jpg,GM-1001-WB-2.jpg,GM-1001-WB-3.jpg</t>
         </is>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>GM-1001-1-Z.jpg,GM-1001-2.jpg,GM-1001-3.jpg,GM-1001-WB-1.jpg,GM-1001-WB-2.jpg,GM-1001-WB-3.jpg</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
         <v>1299</v>
       </c>
-      <c r="Q55" s="1" t="n">
+      <c r="T55" s="1" t="n">
         <v>1299</v>
       </c>
-      <c r="R55" t="n">
+      <c r="U55" t="n">
         <v>3297</v>
       </c>
-      <c r="S55" t="n">
+      <c r="V55" t="n">
         <v>199.5</v>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>59"L X 31 1/4"W X 26 3/4"H</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Aluminum, Polyethylene Wicker, Polyspun</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>Contemporary,Gray,Aluminum, Polyethylene Wicker, Polyspun,Modular Design,Sectional and two sofas settings,Can be a dining set,Convertible ottoman to bench,Bench plate stored under table top,Flap-open side storage,Includes cushions, pillows, and protective covers</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AB55" t="n">
+      <c r="AE55" t="n">
         <v>74.3</v>
       </c>
-      <c r="AC55" t="inlineStr">
+      <c r="AF55" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD55" t="inlineStr">
+      <c r="AG55" t="inlineStr">
         <is>
           <t>Outdoor, Patio Dining Table, MALIA</t>
         </is>
       </c>
-      <c r="AE55" t="inlineStr">
+      <c r="AH55" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF55" t="inlineStr">
+      <c r="AI55" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG55" t="inlineStr">
+      <c r="AJ55" t="inlineStr">
         <is>
           <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables &gt; Dining Tables</t>
         </is>
